--- a/20_設計書/お知らせ登録画面.xlsx
+++ b/20_設計書/お知らせ登録画面.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C70D4FF-A684-471B-A110-72546B768813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A340AC3B-B7F7-4CDE-92A1-4232FAD805BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30285" yWindow="1515" windowWidth="20595" windowHeight="12375" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -221,7 +221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="85">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -788,26 +788,6 @@
     <phoneticPr fontId="55"/>
   </si>
   <si>
-    <t>「お知らせ登録画面へ」ボタンを押下した時に遷移する</t>
-    <rPh sb="15" eb="17">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
-    <t>・本画面は化学物質データ画面で管理者権限のあるログインユーザのみに表示される</t>
-    <rPh sb="33" eb="35">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
     <t>処理詳細</t>
     <rPh sb="0" eb="2">
       <t>ショリ</t>
@@ -909,10 +889,6 @@
     <phoneticPr fontId="55"/>
   </si>
   <si>
-    <t>・本設計はリッチテキストを使用</t>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
     <t>①</t>
     <phoneticPr fontId="55"/>
   </si>
@@ -940,6 +916,85 @@
     <t>③</t>
     <phoneticPr fontId="55"/>
   </si>
+  <si>
+    <t>※本画面は他画面からの画面遷移ではなく、別で管理されているURLで表示</t>
+    <rPh sb="5" eb="6">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ガメンセンイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="55"/>
+  </si>
+  <si>
+    <t>ｒ1.1</t>
+    <phoneticPr fontId="51"/>
+  </si>
+  <si>
+    <t>「お知らせ登録画面」「画面項目」</t>
+    <rPh sb="11" eb="15">
+      <t>ガメンコウモク</t>
+    </rPh>
+    <phoneticPr fontId="51"/>
+  </si>
+  <si>
+    <t>・本設計はリッチテキストを使用
+　必要機能は文字色変更、太字を想定。
+　リンク挿入方法は検討中</t>
+    <rPh sb="17" eb="21">
+      <t>ヒツヨウキノウ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>モジイロ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フトジ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ソウニュウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="55"/>
+  </si>
+  <si>
+    <t>リッチテキストに必要な機能を修正</t>
+    <rPh sb="8" eb="10">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="51"/>
+  </si>
 </sst>
 </file>
 
@@ -952,7 +1007,7 @@
     <numFmt numFmtId="179" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="180" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="79">
+  <fonts count="80">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1496,6 +1551,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -2636,7 +2698,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="274">
+  <cellXfs count="275">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3153,162 +3215,165 @@
     <xf numFmtId="0" fontId="66" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="59" fillId="14" borderId="0" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="14" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="59" fillId="14" borderId="0" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="14" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="3" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="17" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="53" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="10" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="2" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="17" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="15" borderId="22" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="3" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="21" fillId="0" borderId="3" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="23" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="21" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="17" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="3" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="10" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="2" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="17" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="15" borderId="22" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="23" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="21" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="53" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="3" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="10" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="2" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="17" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="53" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3335,6 +3400,104 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="17" xfId="46" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="10" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="17" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="0" borderId="25" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="34" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="35" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="36" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="10" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="17" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="10" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="26" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="27" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="28" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="22" borderId="21" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3372,104 +3535,6 @@
     <xf numFmtId="0" fontId="68" fillId="23" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="10" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="17" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="61" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="61" fillId="0" borderId="25" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="26" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="27" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="28" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="34" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="35" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="36" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="10" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="25" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="10" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="17" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="22" borderId="21" xfId="188" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4135,184 +4200,6 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>57</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>71</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="吹き出し: 四角形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B1E3229-D37B-9E8C-8C43-83697941102B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10315575" y="2705099"/>
-          <a:ext cx="2628900" cy="914401"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -113066"/>
-            <a:gd name="adj2" fmla="val -35520"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="72000" tIns="72000" rIns="36000" bIns="36000" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>AA </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>古竹</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>各入力欄ですがリッチテキストで使える機能としては色変更のみを現状想定しております。</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>他の必要</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="700">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>機能</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>がありましたらご回答お願いいたします。</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="800">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -6347,16 +6234,16 @@
     <row r="20" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="21" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B22" s="174" t="str">
+      <c r="B22" s="173" t="str">
         <f ca="1">TEXT(IF(変更来歴!AT2="",変更来歴!AT1,変更来歴!AT2),"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 05月 21日 ｒ1.0</v>
+        <v>2026年 06月 04日 ｒ1.1</v>
       </c>
-      <c r="C22" s="175"/>
-      <c r="D22" s="175"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="175"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="175"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="174"/>
+      <c r="E22" s="174"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="174"/>
     </row>
     <row r="23" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="24" spans="2:8" ht="14.25" customHeight="1"/>
@@ -6458,7 +6345,7 @@
       <c r="Q38" s="15"/>
       <c r="R38" s="14"/>
       <c r="S38" s="16"/>
-      <c r="T38" s="172"/>
+      <c r="T38" s="175"/>
     </row>
     <row r="39" spans="3:20" ht="14.25" customHeight="1">
       <c r="K39" s="17"/>
@@ -6470,7 +6357,7 @@
       <c r="Q39" s="8"/>
       <c r="R39" s="14"/>
       <c r="S39" s="19"/>
-      <c r="T39" s="173"/>
+      <c r="T39" s="178"/>
     </row>
     <row r="40" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="41" spans="3:20" ht="14.25" customHeight="1">
@@ -6494,7 +6381,7 @@
       <c r="Q42" s="15"/>
       <c r="R42" s="14"/>
       <c r="S42" s="16"/>
-      <c r="T42" s="172"/>
+      <c r="T42" s="175"/>
     </row>
     <row r="43" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K43" s="17"/>
@@ -6502,7 +6389,7 @@
       <c r="N43" s="12"/>
       <c r="R43" s="14"/>
       <c r="S43" s="19"/>
-      <c r="T43" s="172"/>
+      <c r="T43" s="175"/>
     </row>
     <row r="44" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K44" s="1"/>
@@ -6538,7 +6425,7 @@
       <c r="Q46" s="15"/>
       <c r="R46" s="14"/>
       <c r="S46" s="16"/>
-      <c r="T46" s="172"/>
+      <c r="T46" s="175"/>
     </row>
     <row r="47" spans="3:20" ht="14.25" customHeight="1">
       <c r="K47" s="17"/>
@@ -6550,7 +6437,7 @@
       <c r="Q47" s="8"/>
       <c r="R47" s="14"/>
       <c r="S47" s="19"/>
-      <c r="T47" s="172"/>
+      <c r="T47" s="175"/>
     </row>
     <row r="48" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="49" spans="11:20" ht="14.25" customHeight="1">
@@ -6575,7 +6462,7 @@
       <c r="Q50" s="15"/>
       <c r="R50" s="14"/>
       <c r="S50" s="16"/>
-      <c r="T50" s="172"/>
+      <c r="T50" s="175"/>
     </row>
     <row r="51" spans="11:20" ht="14.25" customHeight="1">
       <c r="K51" s="17"/>
@@ -6587,7 +6474,7 @@
       <c r="Q51" s="8"/>
       <c r="R51" s="14"/>
       <c r="S51" s="19"/>
-      <c r="T51" s="172"/>
+      <c r="T51" s="175"/>
     </row>
     <row r="52" spans="11:20" ht="14.25" customHeight="1"/>
     <row r="53" spans="11:20" ht="14.25" customHeight="1">
@@ -6612,7 +6499,7 @@
       <c r="Q54" s="15"/>
       <c r="R54" s="14"/>
       <c r="S54" s="16"/>
-      <c r="T54" s="172"/>
+      <c r="T54" s="175"/>
     </row>
     <row r="55" spans="11:20">
       <c r="K55" s="17"/>
@@ -6624,7 +6511,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="14"/>
       <c r="S55" s="19"/>
-      <c r="T55" s="173"/>
+      <c r="T55" s="178"/>
     </row>
     <row r="57" spans="11:20">
       <c r="K57" s="11"/>
@@ -6648,7 +6535,7 @@
       <c r="Q58" s="15"/>
       <c r="R58" s="14"/>
       <c r="S58" s="16"/>
-      <c r="T58" s="172"/>
+      <c r="T58" s="175"/>
     </row>
     <row r="59" spans="11:20">
       <c r="K59" s="17"/>
@@ -6660,7 +6547,7 @@
       <c r="Q59" s="8"/>
       <c r="R59" s="14"/>
       <c r="S59" s="19"/>
-      <c r="T59" s="173"/>
+      <c r="T59" s="178"/>
     </row>
     <row r="61" spans="11:20">
       <c r="K61" s="11"/>
@@ -6684,7 +6571,7 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
       <c r="S62" s="16"/>
-      <c r="T62" s="172"/>
+      <c r="T62" s="175"/>
     </row>
     <row r="63" spans="11:20">
       <c r="K63" s="17"/>
@@ -6696,7 +6583,7 @@
       <c r="Q63" s="8"/>
       <c r="R63" s="14"/>
       <c r="S63" s="19"/>
-      <c r="T63" s="173"/>
+      <c r="T63" s="178"/>
     </row>
     <row r="65" spans="11:20">
       <c r="K65" s="11"/>
@@ -6720,7 +6607,7 @@
       <c r="Q66" s="15"/>
       <c r="R66" s="14"/>
       <c r="S66" s="16"/>
-      <c r="T66" s="172"/>
+      <c r="T66" s="175"/>
     </row>
     <row r="67" spans="11:20">
       <c r="K67" s="17"/>
@@ -6732,7 +6619,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="14"/>
       <c r="S67" s="19"/>
-      <c r="T67" s="173"/>
+      <c r="T67" s="178"/>
     </row>
     <row r="69" spans="11:20">
       <c r="K69" s="11"/>
@@ -6756,7 +6643,7 @@
       <c r="Q70" s="15"/>
       <c r="R70" s="14"/>
       <c r="S70" s="16"/>
-      <c r="T70" s="172"/>
+      <c r="T70" s="175"/>
     </row>
     <row r="71" spans="11:20">
       <c r="K71" s="17"/>
@@ -6768,7 +6655,7 @@
       <c r="Q71" s="8"/>
       <c r="R71" s="14"/>
       <c r="S71" s="19"/>
-      <c r="T71" s="173"/>
+      <c r="T71" s="178"/>
     </row>
     <row r="73" spans="11:20">
       <c r="K73" s="11"/>
@@ -6792,7 +6679,7 @@
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
       <c r="S74" s="16"/>
-      <c r="T74" s="172"/>
+      <c r="T74" s="175"/>
     </row>
     <row r="75" spans="11:20">
       <c r="K75" s="17"/>
@@ -6804,7 +6691,7 @@
       <c r="Q75" s="8"/>
       <c r="R75" s="14"/>
       <c r="S75" s="19"/>
-      <c r="T75" s="173"/>
+      <c r="T75" s="178"/>
     </row>
     <row r="77" spans="11:20">
       <c r="K77" s="11"/>
@@ -6828,7 +6715,7 @@
       <c r="Q78" s="15"/>
       <c r="R78" s="14"/>
       <c r="S78" s="16"/>
-      <c r="T78" s="172"/>
+      <c r="T78" s="175"/>
     </row>
     <row r="79" spans="11:20">
       <c r="K79" s="17"/>
@@ -6840,7 +6727,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="14"/>
       <c r="S79" s="19"/>
-      <c r="T79" s="173"/>
+      <c r="T79" s="178"/>
     </row>
     <row r="81" spans="11:20">
       <c r="K81" s="11"/>
@@ -6864,7 +6751,7 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
       <c r="S82" s="16"/>
-      <c r="T82" s="172"/>
+      <c r="T82" s="175"/>
     </row>
     <row r="83" spans="11:20">
       <c r="K83" s="17"/>
@@ -6876,7 +6763,7 @@
       <c r="Q83" s="8"/>
       <c r="R83" s="14"/>
       <c r="S83" s="19"/>
-      <c r="T83" s="173"/>
+      <c r="T83" s="178"/>
     </row>
     <row r="85" spans="11:20">
       <c r="K85" s="11"/>
@@ -6900,7 +6787,7 @@
       <c r="Q86" s="15"/>
       <c r="R86" s="14"/>
       <c r="S86" s="16"/>
-      <c r="T86" s="172"/>
+      <c r="T86" s="175"/>
     </row>
     <row r="87" spans="11:20">
       <c r="K87" s="17"/>
@@ -6912,7 +6799,7 @@
       <c r="Q87" s="8"/>
       <c r="R87" s="14"/>
       <c r="S87" s="19"/>
-      <c r="T87" s="173"/>
+      <c r="T87" s="178"/>
     </row>
     <row r="89" spans="11:20">
       <c r="K89" s="11"/>
@@ -6936,7 +6823,7 @@
       <c r="Q90" s="15"/>
       <c r="R90" s="14"/>
       <c r="S90" s="16"/>
-      <c r="T90" s="172"/>
+      <c r="T90" s="175"/>
     </row>
     <row r="91" spans="11:20">
       <c r="K91" s="17"/>
@@ -6948,7 +6835,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="14"/>
       <c r="S91" s="19"/>
-      <c r="T91" s="173"/>
+      <c r="T91" s="178"/>
     </row>
     <row r="93" spans="11:20">
       <c r="K93" s="11"/>
@@ -6972,7 +6859,7 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
       <c r="S94" s="16"/>
-      <c r="T94" s="172"/>
+      <c r="T94" s="175"/>
     </row>
     <row r="95" spans="11:20">
       <c r="K95" s="17"/>
@@ -6984,7 +6871,7 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="14"/>
       <c r="S95" s="19"/>
-      <c r="T95" s="173"/>
+      <c r="T95" s="178"/>
     </row>
     <row r="97" spans="11:20">
       <c r="K97" s="11"/>
@@ -7008,7 +6895,7 @@
       <c r="Q98" s="15"/>
       <c r="R98" s="14"/>
       <c r="S98" s="16"/>
-      <c r="T98" s="172"/>
+      <c r="T98" s="175"/>
     </row>
     <row r="99" spans="11:20">
       <c r="K99" s="17"/>
@@ -7020,7 +6907,7 @@
       <c r="Q99" s="8"/>
       <c r="R99" s="14"/>
       <c r="S99" s="19"/>
-      <c r="T99" s="173"/>
+      <c r="T99" s="178"/>
     </row>
     <row r="101" spans="11:20">
       <c r="K101" s="11"/>
@@ -7044,7 +6931,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
       <c r="S102" s="16"/>
-      <c r="T102" s="172"/>
+      <c r="T102" s="175"/>
     </row>
     <row r="103" spans="11:20">
       <c r="K103" s="17"/>
@@ -7056,7 +6943,7 @@
       <c r="Q103" s="8"/>
       <c r="R103" s="14"/>
       <c r="S103" s="19"/>
-      <c r="T103" s="173"/>
+      <c r="T103" s="178"/>
     </row>
     <row r="105" spans="11:20">
       <c r="K105" s="11"/>
@@ -7080,7 +6967,7 @@
       <c r="Q106" s="15"/>
       <c r="R106" s="14"/>
       <c r="S106" s="16"/>
-      <c r="T106" s="172"/>
+      <c r="T106" s="175"/>
     </row>
     <row r="107" spans="11:20">
       <c r="K107" s="17"/>
@@ -7092,7 +6979,7 @@
       <c r="Q107" s="8"/>
       <c r="R107" s="14"/>
       <c r="S107" s="19"/>
-      <c r="T107" s="173"/>
+      <c r="T107" s="178"/>
     </row>
     <row r="109" spans="11:20">
       <c r="K109" s="11"/>
@@ -7116,7 +7003,7 @@
       <c r="Q110" s="15"/>
       <c r="R110" s="14"/>
       <c r="S110" s="16"/>
-      <c r="T110" s="172"/>
+      <c r="T110" s="175"/>
     </row>
     <row r="111" spans="11:20">
       <c r="K111" s="17"/>
@@ -7128,7 +7015,7 @@
       <c r="Q111" s="8"/>
       <c r="R111" s="14"/>
       <c r="S111" s="19"/>
-      <c r="T111" s="173"/>
+      <c r="T111" s="178"/>
     </row>
     <row r="113" spans="11:20">
       <c r="K113" s="11"/>
@@ -7152,7 +7039,7 @@
       <c r="Q114" s="15"/>
       <c r="R114" s="14"/>
       <c r="S114" s="16"/>
-      <c r="T114" s="172"/>
+      <c r="T114" s="175"/>
     </row>
     <row r="115" spans="11:20">
       <c r="K115" s="17"/>
@@ -7164,7 +7051,7 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="14"/>
       <c r="S115" s="19"/>
-      <c r="T115" s="173"/>
+      <c r="T115" s="178"/>
     </row>
     <row r="117" spans="11:20">
       <c r="K117" s="11"/>
@@ -7188,7 +7075,7 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
       <c r="S118" s="16"/>
-      <c r="T118" s="172"/>
+      <c r="T118" s="175"/>
     </row>
     <row r="119" spans="11:20">
       <c r="K119" s="17"/>
@@ -7200,7 +7087,7 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="14"/>
       <c r="S119" s="19"/>
-      <c r="T119" s="173"/>
+      <c r="T119" s="178"/>
     </row>
     <row r="121" spans="11:20">
       <c r="K121" s="11"/>
@@ -7224,7 +7111,7 @@
       <c r="Q122" s="15"/>
       <c r="R122" s="14"/>
       <c r="S122" s="16"/>
-      <c r="T122" s="172"/>
+      <c r="T122" s="175"/>
     </row>
     <row r="123" spans="11:20">
       <c r="K123" s="17"/>
@@ -7236,17 +7123,18 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="14"/>
       <c r="S123" s="19"/>
-      <c r="T123" s="173"/>
+      <c r="T123" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="T42:T43"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="T118:T119"/>
+    <mergeCell ref="T122:T123"/>
+    <mergeCell ref="T94:T95"/>
+    <mergeCell ref="T98:T99"/>
+    <mergeCell ref="T102:T103"/>
+    <mergeCell ref="T106:T107"/>
+    <mergeCell ref="T110:T111"/>
+    <mergeCell ref="T114:T115"/>
     <mergeCell ref="T90:T91"/>
     <mergeCell ref="T46:T47"/>
     <mergeCell ref="T50:T51"/>
@@ -7259,14 +7147,13 @@
     <mergeCell ref="T78:T79"/>
     <mergeCell ref="T82:T83"/>
     <mergeCell ref="T86:T87"/>
-    <mergeCell ref="T118:T119"/>
-    <mergeCell ref="T122:T123"/>
-    <mergeCell ref="T94:T95"/>
-    <mergeCell ref="T98:T99"/>
-    <mergeCell ref="T102:T103"/>
-    <mergeCell ref="T106:T107"/>
-    <mergeCell ref="T110:T111"/>
-    <mergeCell ref="T114:T115"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="T42:T43"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="T38:T39"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <printOptions horizontalCentered="1"/>
@@ -7289,1923 +7176,2084 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="12" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="219" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="189" t="s">
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="189"/>
-      <c r="K1" s="189"/>
-      <c r="L1" s="189"/>
-      <c r="M1" s="200" t="s">
+      <c r="J1" s="202"/>
+      <c r="K1" s="202"/>
+      <c r="L1" s="202"/>
+      <c r="M1" s="217" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="200"/>
-      <c r="O1" s="200"/>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="189" t="s">
+      <c r="N1" s="217"/>
+      <c r="O1" s="217"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="189"/>
-      <c r="AA1" s="204" t="s">
+      <c r="Y1" s="202"/>
+      <c r="Z1" s="202"/>
+      <c r="AA1" s="221" t="s">
         <v>44</v>
       </c>
-      <c r="AB1" s="204"/>
-      <c r="AC1" s="204"/>
-      <c r="AD1" s="204"/>
-      <c r="AE1" s="204"/>
-      <c r="AF1" s="204"/>
-      <c r="AG1" s="204"/>
-      <c r="AH1" s="204"/>
-      <c r="AI1" s="204"/>
-      <c r="AJ1" s="204"/>
-      <c r="AK1" s="178" t="s">
+      <c r="AB1" s="221"/>
+      <c r="AC1" s="221"/>
+      <c r="AD1" s="221"/>
+      <c r="AE1" s="221"/>
+      <c r="AF1" s="221"/>
+      <c r="AG1" s="221"/>
+      <c r="AH1" s="221"/>
+      <c r="AI1" s="221"/>
+      <c r="AJ1" s="221"/>
+      <c r="AK1" s="206" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="178"/>
-      <c r="AM1" s="178"/>
-      <c r="AN1" s="180" t="s">
+      <c r="AL1" s="206"/>
+      <c r="AM1" s="206"/>
+      <c r="AN1" s="207" t="s">
         <v>31</v>
       </c>
-      <c r="AO1" s="180"/>
-      <c r="AP1" s="180"/>
-      <c r="AQ1" s="178" t="s">
+      <c r="AO1" s="207"/>
+      <c r="AP1" s="207"/>
+      <c r="AQ1" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="AR1" s="178"/>
-      <c r="AS1" s="178"/>
-      <c r="AT1" s="181">
+      <c r="AR1" s="206"/>
+      <c r="AS1" s="206"/>
+      <c r="AT1" s="209">
         <f>AL7</f>
         <v>46163</v>
       </c>
-      <c r="AU1" s="181"/>
-      <c r="AV1" s="181"/>
-      <c r="AW1" s="181"/>
-      <c r="AX1" s="185" t="s">
+      <c r="AU1" s="209"/>
+      <c r="AV1" s="209"/>
+      <c r="AW1" s="209"/>
+      <c r="AX1" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="AY1" s="186"/>
-      <c r="AZ1" s="186"/>
-      <c r="BA1" s="187"/>
+      <c r="AY1" s="199"/>
+      <c r="AZ1" s="199"/>
+      <c r="BA1" s="200"/>
     </row>
     <row r="2" spans="1:53">
-      <c r="A2" s="188" t="s">
+      <c r="A2" s="201" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="188"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="188"/>
-      <c r="I2" s="189" t="s">
+      <c r="B2" s="201"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="201"/>
+      <c r="G2" s="201"/>
+      <c r="H2" s="201"/>
+      <c r="I2" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="189"/>
-      <c r="K2" s="189"/>
-      <c r="L2" s="189"/>
-      <c r="M2" s="190" t="s">
+      <c r="J2" s="202"/>
+      <c r="K2" s="202"/>
+      <c r="L2" s="202"/>
+      <c r="M2" s="203" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="191"/>
-      <c r="O2" s="191"/>
-      <c r="P2" s="191"/>
-      <c r="Q2" s="191"/>
-      <c r="R2" s="191"/>
-      <c r="S2" s="191"/>
-      <c r="T2" s="191"/>
-      <c r="U2" s="191"/>
-      <c r="V2" s="191"/>
-      <c r="W2" s="192"/>
-      <c r="X2" s="189"/>
-      <c r="Y2" s="189"/>
-      <c r="Z2" s="189"/>
-      <c r="AA2" s="204"/>
-      <c r="AB2" s="204"/>
-      <c r="AC2" s="204"/>
-      <c r="AD2" s="204"/>
-      <c r="AE2" s="204"/>
-      <c r="AF2" s="204"/>
-      <c r="AG2" s="204"/>
-      <c r="AH2" s="204"/>
-      <c r="AI2" s="204"/>
-      <c r="AJ2" s="204"/>
-      <c r="AK2" s="178" t="s">
+      <c r="N2" s="204"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="204"/>
+      <c r="Q2" s="204"/>
+      <c r="R2" s="204"/>
+      <c r="S2" s="204"/>
+      <c r="T2" s="204"/>
+      <c r="U2" s="204"/>
+      <c r="V2" s="204"/>
+      <c r="W2" s="205"/>
+      <c r="X2" s="202"/>
+      <c r="Y2" s="202"/>
+      <c r="Z2" s="202"/>
+      <c r="AA2" s="221"/>
+      <c r="AB2" s="221"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="221"/>
+      <c r="AE2" s="221"/>
+      <c r="AF2" s="221"/>
+      <c r="AG2" s="221"/>
+      <c r="AH2" s="221"/>
+      <c r="AI2" s="221"/>
+      <c r="AJ2" s="221"/>
+      <c r="AK2" s="206" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="178"/>
-      <c r="AM2" s="178"/>
-      <c r="AN2" s="180" t="s">
+      <c r="AL2" s="206"/>
+      <c r="AM2" s="206"/>
+      <c r="AN2" s="207" t="s">
         <v>31</v>
       </c>
-      <c r="AO2" s="180"/>
-      <c r="AP2" s="180"/>
-      <c r="AQ2" s="178" t="s">
+      <c r="AO2" s="207"/>
+      <c r="AP2" s="207"/>
+      <c r="AQ2" s="206" t="s">
         <v>13</v>
       </c>
-      <c r="AR2" s="178"/>
-      <c r="AS2" s="178"/>
-      <c r="AT2" s="181"/>
-      <c r="AU2" s="181"/>
-      <c r="AV2" s="181"/>
-      <c r="AW2" s="181"/>
-      <c r="AX2" s="193" t="s">
+      <c r="AR2" s="206"/>
+      <c r="AS2" s="206"/>
+      <c r="AT2" s="209">
+        <v>46177</v>
+      </c>
+      <c r="AU2" s="209"/>
+      <c r="AV2" s="209"/>
+      <c r="AW2" s="209"/>
+      <c r="AX2" s="210" t="s">
         <v>29</v>
       </c>
-      <c r="AY2" s="194"/>
-      <c r="AZ2" s="194"/>
-      <c r="BA2" s="195"/>
+      <c r="AY2" s="211"/>
+      <c r="AZ2" s="211"/>
+      <c r="BA2" s="212"/>
     </row>
     <row r="3" spans="1:53" ht="12" customHeight="1">
-      <c r="A3" s="199" t="s">
+      <c r="A3" s="216" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="199"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="189" t="s">
+      <c r="B3" s="216"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="216"/>
+      <c r="F3" s="216"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="189"/>
-      <c r="K3" s="189"/>
-      <c r="L3" s="189"/>
-      <c r="M3" s="200"/>
-      <c r="N3" s="200"/>
-      <c r="O3" s="200"/>
-      <c r="P3" s="200"/>
-      <c r="Q3" s="200"/>
-      <c r="R3" s="200"/>
-      <c r="S3" s="200"/>
-      <c r="T3" s="200"/>
-      <c r="U3" s="200"/>
-      <c r="V3" s="200"/>
-      <c r="W3" s="200"/>
-      <c r="X3" s="189" t="s">
+      <c r="J3" s="202"/>
+      <c r="K3" s="202"/>
+      <c r="L3" s="202"/>
+      <c r="M3" s="217"/>
+      <c r="N3" s="217"/>
+      <c r="O3" s="217"/>
+      <c r="P3" s="217"/>
+      <c r="Q3" s="217"/>
+      <c r="R3" s="217"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="202" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="189"/>
-      <c r="Z3" s="189"/>
-      <c r="AA3" s="201" t="s">
+      <c r="Y3" s="202"/>
+      <c r="Z3" s="202"/>
+      <c r="AA3" s="218" t="s">
         <v>45</v>
       </c>
-      <c r="AB3" s="201"/>
-      <c r="AC3" s="201"/>
-      <c r="AD3" s="201"/>
-      <c r="AE3" s="201"/>
-      <c r="AF3" s="201"/>
-      <c r="AG3" s="201"/>
-      <c r="AH3" s="201"/>
-      <c r="AI3" s="201"/>
-      <c r="AJ3" s="201"/>
-      <c r="AK3" s="201"/>
-      <c r="AL3" s="201"/>
-      <c r="AM3" s="201"/>
-      <c r="AN3" s="201"/>
-      <c r="AO3" s="201"/>
-      <c r="AP3" s="201"/>
-      <c r="AQ3" s="178" t="s">
+      <c r="AB3" s="218"/>
+      <c r="AC3" s="218"/>
+      <c r="AD3" s="218"/>
+      <c r="AE3" s="218"/>
+      <c r="AF3" s="218"/>
+      <c r="AG3" s="218"/>
+      <c r="AH3" s="218"/>
+      <c r="AI3" s="218"/>
+      <c r="AJ3" s="218"/>
+      <c r="AK3" s="218"/>
+      <c r="AL3" s="218"/>
+      <c r="AM3" s="218"/>
+      <c r="AN3" s="218"/>
+      <c r="AO3" s="218"/>
+      <c r="AP3" s="218"/>
+      <c r="AQ3" s="206" t="s">
         <v>15</v>
       </c>
-      <c r="AR3" s="178"/>
-      <c r="AS3" s="178"/>
-      <c r="AT3" s="179" t="str">
+      <c r="AR3" s="206"/>
+      <c r="AS3" s="206"/>
+      <c r="AT3" s="222" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
-        <v>ｒ1.0</v>
+        <v>ｒ1.1</v>
       </c>
-      <c r="AU3" s="179"/>
-      <c r="AV3" s="179"/>
-      <c r="AW3" s="179"/>
-      <c r="AX3" s="196"/>
-      <c r="AY3" s="197"/>
-      <c r="AZ3" s="197"/>
-      <c r="BA3" s="198"/>
+      <c r="AU3" s="222"/>
+      <c r="AV3" s="222"/>
+      <c r="AW3" s="222"/>
+      <c r="AX3" s="213"/>
+      <c r="AY3" s="214"/>
+      <c r="AZ3" s="214"/>
+      <c r="BA3" s="215"/>
     </row>
     <row r="4" spans="1:53" ht="5.9" customHeight="1"/>
     <row r="5" spans="1:53" ht="14">
-      <c r="A5" s="203" t="s">
+      <c r="A5" s="220" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="203"/>
-      <c r="C5" s="203"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="203"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="203"/>
-      <c r="I5" s="203"/>
-      <c r="J5" s="203"/>
-      <c r="K5" s="203"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="203"/>
-      <c r="N5" s="203"/>
-      <c r="O5" s="203"/>
-      <c r="P5" s="203"/>
-      <c r="Q5" s="203"/>
-      <c r="R5" s="203"/>
-      <c r="S5" s="203"/>
-      <c r="T5" s="203"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="203"/>
-      <c r="W5" s="203"/>
-      <c r="X5" s="203"/>
-      <c r="Y5" s="203"/>
-      <c r="Z5" s="203"/>
-      <c r="AA5" s="203"/>
-      <c r="AB5" s="203"/>
-      <c r="AC5" s="203"/>
-      <c r="AD5" s="203"/>
-      <c r="AE5" s="203"/>
-      <c r="AF5" s="203"/>
-      <c r="AG5" s="203"/>
-      <c r="AH5" s="203"/>
-      <c r="AI5" s="203"/>
-      <c r="AJ5" s="203"/>
-      <c r="AK5" s="203"/>
-      <c r="AL5" s="203"/>
-      <c r="AM5" s="203"/>
-      <c r="AN5" s="203"/>
-      <c r="AO5" s="203"/>
-      <c r="AP5" s="203"/>
-      <c r="AQ5" s="203"/>
-      <c r="AR5" s="203"/>
-      <c r="AS5" s="203"/>
-      <c r="AT5" s="203"/>
-      <c r="AU5" s="203"/>
-      <c r="AV5" s="203"/>
-      <c r="AW5" s="203"/>
-      <c r="AX5" s="203"/>
-      <c r="AY5" s="203"/>
-      <c r="AZ5" s="203"/>
-      <c r="BA5" s="203"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="220"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="220"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="220"/>
+      <c r="I5" s="220"/>
+      <c r="J5" s="220"/>
+      <c r="K5" s="220"/>
+      <c r="L5" s="220"/>
+      <c r="M5" s="220"/>
+      <c r="N5" s="220"/>
+      <c r="O5" s="220"/>
+      <c r="P5" s="220"/>
+      <c r="Q5" s="220"/>
+      <c r="R5" s="220"/>
+      <c r="S5" s="220"/>
+      <c r="T5" s="220"/>
+      <c r="U5" s="220"/>
+      <c r="V5" s="220"/>
+      <c r="W5" s="220"/>
+      <c r="X5" s="220"/>
+      <c r="Y5" s="220"/>
+      <c r="Z5" s="220"/>
+      <c r="AA5" s="220"/>
+      <c r="AB5" s="220"/>
+      <c r="AC5" s="220"/>
+      <c r="AD5" s="220"/>
+      <c r="AE5" s="220"/>
+      <c r="AF5" s="220"/>
+      <c r="AG5" s="220"/>
+      <c r="AH5" s="220"/>
+      <c r="AI5" s="220"/>
+      <c r="AJ5" s="220"/>
+      <c r="AK5" s="220"/>
+      <c r="AL5" s="220"/>
+      <c r="AM5" s="220"/>
+      <c r="AN5" s="220"/>
+      <c r="AO5" s="220"/>
+      <c r="AP5" s="220"/>
+      <c r="AQ5" s="220"/>
+      <c r="AR5" s="220"/>
+      <c r="AS5" s="220"/>
+      <c r="AT5" s="220"/>
+      <c r="AU5" s="220"/>
+      <c r="AV5" s="220"/>
+      <c r="AW5" s="220"/>
+      <c r="AX5" s="220"/>
+      <c r="AY5" s="220"/>
+      <c r="AZ5" s="220"/>
+      <c r="BA5" s="220"/>
     </row>
     <row r="6" spans="1:53">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="223" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="183"/>
-      <c r="C6" s="184" t="s">
+      <c r="B6" s="224"/>
+      <c r="C6" s="208" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="184"/>
-      <c r="I6" s="184"/>
-      <c r="J6" s="184"/>
-      <c r="K6" s="184"/>
-      <c r="L6" s="184"/>
-      <c r="M6" s="184"/>
-      <c r="N6" s="184"/>
-      <c r="O6" s="184"/>
-      <c r="P6" s="184"/>
-      <c r="Q6" s="184" t="s">
+      <c r="D6" s="208"/>
+      <c r="E6" s="208"/>
+      <c r="F6" s="208"/>
+      <c r="G6" s="208"/>
+      <c r="H6" s="208"/>
+      <c r="I6" s="208"/>
+      <c r="J6" s="208"/>
+      <c r="K6" s="208"/>
+      <c r="L6" s="208"/>
+      <c r="M6" s="208"/>
+      <c r="N6" s="208"/>
+      <c r="O6" s="208"/>
+      <c r="P6" s="208"/>
+      <c r="Q6" s="208" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="184"/>
-      <c r="S6" s="184"/>
-      <c r="T6" s="184"/>
-      <c r="U6" s="184"/>
-      <c r="V6" s="184"/>
-      <c r="W6" s="184"/>
-      <c r="X6" s="184"/>
-      <c r="Y6" s="184"/>
-      <c r="Z6" s="184"/>
-      <c r="AA6" s="184"/>
-      <c r="AB6" s="184"/>
-      <c r="AC6" s="184"/>
-      <c r="AD6" s="184"/>
-      <c r="AE6" s="184"/>
-      <c r="AF6" s="184"/>
-      <c r="AG6" s="184"/>
-      <c r="AH6" s="184"/>
-      <c r="AI6" s="184"/>
-      <c r="AJ6" s="184"/>
-      <c r="AK6" s="184"/>
-      <c r="AL6" s="184" t="s">
+      <c r="R6" s="208"/>
+      <c r="S6" s="208"/>
+      <c r="T6" s="208"/>
+      <c r="U6" s="208"/>
+      <c r="V6" s="208"/>
+      <c r="W6" s="208"/>
+      <c r="X6" s="208"/>
+      <c r="Y6" s="208"/>
+      <c r="Z6" s="208"/>
+      <c r="AA6" s="208"/>
+      <c r="AB6" s="208"/>
+      <c r="AC6" s="208"/>
+      <c r="AD6" s="208"/>
+      <c r="AE6" s="208"/>
+      <c r="AF6" s="208"/>
+      <c r="AG6" s="208"/>
+      <c r="AH6" s="208"/>
+      <c r="AI6" s="208"/>
+      <c r="AJ6" s="208"/>
+      <c r="AK6" s="208"/>
+      <c r="AL6" s="208" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="184"/>
-      <c r="AN6" s="184"/>
-      <c r="AO6" s="184"/>
-      <c r="AP6" s="184" t="s">
+      <c r="AM6" s="208"/>
+      <c r="AN6" s="208"/>
+      <c r="AO6" s="208"/>
+      <c r="AP6" s="208" t="s">
         <v>20</v>
       </c>
-      <c r="AQ6" s="184"/>
-      <c r="AR6" s="184"/>
-      <c r="AS6" s="184" t="s">
+      <c r="AQ6" s="208"/>
+      <c r="AR6" s="208"/>
+      <c r="AS6" s="208" t="s">
         <v>21</v>
       </c>
-      <c r="AT6" s="184"/>
-      <c r="AU6" s="184"/>
-      <c r="AV6" s="184" t="s">
+      <c r="AT6" s="208"/>
+      <c r="AU6" s="208"/>
+      <c r="AV6" s="208" t="s">
         <v>22</v>
       </c>
-      <c r="AW6" s="184"/>
-      <c r="AX6" s="184"/>
-      <c r="AY6" s="184"/>
-      <c r="AZ6" s="184"/>
-      <c r="BA6" s="184"/>
+      <c r="AW6" s="208"/>
+      <c r="AX6" s="208"/>
+      <c r="AY6" s="208"/>
+      <c r="AZ6" s="208"/>
+      <c r="BA6" s="208"/>
     </row>
     <row r="7" spans="1:53">
-      <c r="A7" s="207" t="s">
+      <c r="A7" s="180" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="207"/>
-      <c r="C7" s="210" t="s">
+      <c r="B7" s="180"/>
+      <c r="C7" s="181" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="210"/>
-      <c r="E7" s="210"/>
-      <c r="F7" s="210"/>
-      <c r="G7" s="210"/>
-      <c r="H7" s="210"/>
-      <c r="I7" s="210"/>
-      <c r="J7" s="210"/>
-      <c r="K7" s="210"/>
-      <c r="L7" s="210"/>
-      <c r="M7" s="210"/>
-      <c r="N7" s="210"/>
-      <c r="O7" s="210"/>
-      <c r="P7" s="210"/>
-      <c r="Q7" s="210"/>
-      <c r="R7" s="210"/>
-      <c r="S7" s="210"/>
-      <c r="T7" s="210"/>
-      <c r="U7" s="210"/>
-      <c r="V7" s="210"/>
-      <c r="W7" s="210"/>
-      <c r="X7" s="210"/>
-      <c r="Y7" s="210"/>
-      <c r="Z7" s="210"/>
-      <c r="AA7" s="210"/>
-      <c r="AB7" s="210"/>
-      <c r="AC7" s="210"/>
-      <c r="AD7" s="210"/>
-      <c r="AE7" s="210"/>
-      <c r="AF7" s="210"/>
-      <c r="AG7" s="210"/>
-      <c r="AH7" s="210"/>
-      <c r="AI7" s="210"/>
-      <c r="AJ7" s="210"/>
-      <c r="AK7" s="210"/>
-      <c r="AL7" s="218">
+      <c r="D7" s="181"/>
+      <c r="E7" s="181"/>
+      <c r="F7" s="181"/>
+      <c r="G7" s="181"/>
+      <c r="H7" s="181"/>
+      <c r="I7" s="181"/>
+      <c r="J7" s="181"/>
+      <c r="K7" s="181"/>
+      <c r="L7" s="181"/>
+      <c r="M7" s="181"/>
+      <c r="N7" s="181"/>
+      <c r="O7" s="181"/>
+      <c r="P7" s="181"/>
+      <c r="Q7" s="181"/>
+      <c r="R7" s="181"/>
+      <c r="S7" s="181"/>
+      <c r="T7" s="181"/>
+      <c r="U7" s="181"/>
+      <c r="V7" s="181"/>
+      <c r="W7" s="181"/>
+      <c r="X7" s="181"/>
+      <c r="Y7" s="181"/>
+      <c r="Z7" s="181"/>
+      <c r="AA7" s="181"/>
+      <c r="AB7" s="181"/>
+      <c r="AC7" s="181"/>
+      <c r="AD7" s="181"/>
+      <c r="AE7" s="181"/>
+      <c r="AF7" s="181"/>
+      <c r="AG7" s="181"/>
+      <c r="AH7" s="181"/>
+      <c r="AI7" s="181"/>
+      <c r="AJ7" s="181"/>
+      <c r="AK7" s="181"/>
+      <c r="AL7" s="185">
         <v>46163</v>
       </c>
-      <c r="AM7" s="219"/>
-      <c r="AN7" s="219"/>
-      <c r="AO7" s="219"/>
-      <c r="AP7" s="210" t="s">
+      <c r="AM7" s="186"/>
+      <c r="AN7" s="186"/>
+      <c r="AO7" s="186"/>
+      <c r="AP7" s="181" t="s">
         <v>31</v>
       </c>
-      <c r="AQ7" s="210"/>
-      <c r="AR7" s="210"/>
-      <c r="AS7" s="210"/>
-      <c r="AT7" s="210"/>
-      <c r="AU7" s="210"/>
-      <c r="AV7" s="210"/>
-      <c r="AW7" s="210"/>
-      <c r="AX7" s="210"/>
-      <c r="AY7" s="210"/>
-      <c r="AZ7" s="210"/>
-      <c r="BA7" s="210"/>
+      <c r="AQ7" s="181"/>
+      <c r="AR7" s="181"/>
+      <c r="AS7" s="181"/>
+      <c r="AT7" s="181"/>
+      <c r="AU7" s="181"/>
+      <c r="AV7" s="181"/>
+      <c r="AW7" s="181"/>
+      <c r="AX7" s="181"/>
+      <c r="AY7" s="181"/>
+      <c r="AZ7" s="181"/>
+      <c r="BA7" s="181"/>
     </row>
     <row r="8" spans="1:53" ht="26.5" customHeight="1">
-      <c r="A8" s="205"/>
-      <c r="B8" s="206"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="211"/>
-      <c r="E8" s="211"/>
-      <c r="F8" s="211"/>
-      <c r="G8" s="211"/>
-      <c r="H8" s="211"/>
-      <c r="I8" s="211"/>
-      <c r="J8" s="211"/>
-      <c r="K8" s="211"/>
-      <c r="L8" s="211"/>
-      <c r="M8" s="211"/>
-      <c r="N8" s="211"/>
-      <c r="O8" s="211"/>
-      <c r="P8" s="211"/>
-      <c r="Q8" s="213"/>
-      <c r="R8" s="214"/>
-      <c r="S8" s="214"/>
-      <c r="T8" s="214"/>
-      <c r="U8" s="214"/>
-      <c r="V8" s="214"/>
-      <c r="W8" s="214"/>
-      <c r="X8" s="214"/>
-      <c r="Y8" s="214"/>
-      <c r="Z8" s="214"/>
-      <c r="AA8" s="214"/>
-      <c r="AB8" s="214"/>
-      <c r="AC8" s="214"/>
-      <c r="AD8" s="214"/>
-      <c r="AE8" s="214"/>
-      <c r="AF8" s="214"/>
-      <c r="AG8" s="214"/>
-      <c r="AH8" s="214"/>
-      <c r="AI8" s="214"/>
-      <c r="AJ8" s="214"/>
-      <c r="AK8" s="215"/>
-      <c r="AL8" s="220"/>
-      <c r="AM8" s="221"/>
-      <c r="AN8" s="221"/>
-      <c r="AO8" s="222"/>
-      <c r="AP8" s="210"/>
-      <c r="AQ8" s="210"/>
-      <c r="AR8" s="210"/>
-      <c r="AS8" s="210"/>
-      <c r="AT8" s="210"/>
-      <c r="AU8" s="210"/>
-      <c r="AV8" s="210"/>
-      <c r="AW8" s="210"/>
-      <c r="AX8" s="210"/>
-      <c r="AY8" s="210"/>
-      <c r="AZ8" s="210"/>
-      <c r="BA8" s="210"/>
+      <c r="A8" s="180" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="180"/>
+      <c r="C8" s="182" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="182"/>
+      <c r="E8" s="182"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="182"/>
+      <c r="M8" s="182"/>
+      <c r="N8" s="182"/>
+      <c r="O8" s="182"/>
+      <c r="P8" s="182"/>
+      <c r="Q8" s="192" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="193"/>
+      <c r="S8" s="193"/>
+      <c r="T8" s="193"/>
+      <c r="U8" s="193"/>
+      <c r="V8" s="193"/>
+      <c r="W8" s="193"/>
+      <c r="X8" s="193"/>
+      <c r="Y8" s="193"/>
+      <c r="Z8" s="193"/>
+      <c r="AA8" s="193"/>
+      <c r="AB8" s="193"/>
+      <c r="AC8" s="193"/>
+      <c r="AD8" s="193"/>
+      <c r="AE8" s="193"/>
+      <c r="AF8" s="193"/>
+      <c r="AG8" s="193"/>
+      <c r="AH8" s="193"/>
+      <c r="AI8" s="193"/>
+      <c r="AJ8" s="193"/>
+      <c r="AK8" s="194"/>
+      <c r="AL8" s="187">
+        <v>46177</v>
+      </c>
+      <c r="AM8" s="188"/>
+      <c r="AN8" s="188"/>
+      <c r="AO8" s="189"/>
+      <c r="AP8" s="181" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ8" s="181"/>
+      <c r="AR8" s="181"/>
+      <c r="AS8" s="181"/>
+      <c r="AT8" s="181"/>
+      <c r="AU8" s="181"/>
+      <c r="AV8" s="181"/>
+      <c r="AW8" s="181"/>
+      <c r="AX8" s="181"/>
+      <c r="AY8" s="181"/>
+      <c r="AZ8" s="181"/>
+      <c r="BA8" s="181"/>
     </row>
     <row r="9" spans="1:53">
-      <c r="A9" s="205"/>
-      <c r="B9" s="206"/>
-      <c r="C9" s="210"/>
-      <c r="D9" s="210"/>
-      <c r="E9" s="210"/>
-      <c r="F9" s="210"/>
-      <c r="G9" s="210"/>
-      <c r="H9" s="210"/>
-      <c r="I9" s="210"/>
-      <c r="J9" s="210"/>
-      <c r="K9" s="210"/>
-      <c r="L9" s="210"/>
-      <c r="M9" s="210"/>
-      <c r="N9" s="210"/>
-      <c r="O9" s="210"/>
-      <c r="P9" s="210"/>
-      <c r="Q9" s="213"/>
-      <c r="R9" s="214"/>
-      <c r="S9" s="214"/>
-      <c r="T9" s="214"/>
-      <c r="U9" s="214"/>
-      <c r="V9" s="214"/>
-      <c r="W9" s="214"/>
-      <c r="X9" s="214"/>
-      <c r="Y9" s="214"/>
-      <c r="Z9" s="214"/>
-      <c r="AA9" s="214"/>
-      <c r="AB9" s="214"/>
-      <c r="AC9" s="214"/>
-      <c r="AD9" s="214"/>
-      <c r="AE9" s="214"/>
-      <c r="AF9" s="214"/>
-      <c r="AG9" s="214"/>
-      <c r="AH9" s="214"/>
-      <c r="AI9" s="214"/>
-      <c r="AJ9" s="214"/>
-      <c r="AK9" s="215"/>
-      <c r="AL9" s="220"/>
-      <c r="AM9" s="221"/>
-      <c r="AN9" s="221"/>
-      <c r="AO9" s="222"/>
-      <c r="AP9" s="210"/>
-      <c r="AQ9" s="210"/>
-      <c r="AR9" s="210"/>
-      <c r="AS9" s="210"/>
-      <c r="AT9" s="210"/>
-      <c r="AU9" s="210"/>
-      <c r="AV9" s="210"/>
-      <c r="AW9" s="210"/>
-      <c r="AX9" s="210"/>
-      <c r="AY9" s="210"/>
-      <c r="AZ9" s="210"/>
-      <c r="BA9" s="210"/>
+      <c r="A9" s="196"/>
+      <c r="B9" s="197"/>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
+      <c r="G9" s="181"/>
+      <c r="H9" s="181"/>
+      <c r="I9" s="181"/>
+      <c r="J9" s="181"/>
+      <c r="K9" s="181"/>
+      <c r="L9" s="181"/>
+      <c r="M9" s="181"/>
+      <c r="N9" s="181"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="181"/>
+      <c r="Q9" s="192"/>
+      <c r="R9" s="193"/>
+      <c r="S9" s="193"/>
+      <c r="T9" s="193"/>
+      <c r="U9" s="193"/>
+      <c r="V9" s="193"/>
+      <c r="W9" s="193"/>
+      <c r="X9" s="193"/>
+      <c r="Y9" s="193"/>
+      <c r="Z9" s="193"/>
+      <c r="AA9" s="193"/>
+      <c r="AB9" s="193"/>
+      <c r="AC9" s="193"/>
+      <c r="AD9" s="193"/>
+      <c r="AE9" s="193"/>
+      <c r="AF9" s="193"/>
+      <c r="AG9" s="193"/>
+      <c r="AH9" s="193"/>
+      <c r="AI9" s="193"/>
+      <c r="AJ9" s="193"/>
+      <c r="AK9" s="194"/>
+      <c r="AL9" s="187"/>
+      <c r="AM9" s="188"/>
+      <c r="AN9" s="188"/>
+      <c r="AO9" s="189"/>
+      <c r="AP9" s="181"/>
+      <c r="AQ9" s="181"/>
+      <c r="AR9" s="181"/>
+      <c r="AS9" s="181"/>
+      <c r="AT9" s="181"/>
+      <c r="AU9" s="181"/>
+      <c r="AV9" s="181"/>
+      <c r="AW9" s="181"/>
+      <c r="AX9" s="181"/>
+      <c r="AY9" s="181"/>
+      <c r="AZ9" s="181"/>
+      <c r="BA9" s="181"/>
     </row>
     <row r="10" spans="1:53">
-      <c r="A10" s="207"/>
-      <c r="B10" s="207"/>
-      <c r="C10" s="210"/>
-      <c r="D10" s="210"/>
-      <c r="E10" s="210"/>
-      <c r="F10" s="210"/>
-      <c r="G10" s="210"/>
-      <c r="H10" s="210"/>
-      <c r="I10" s="210"/>
-      <c r="J10" s="210"/>
-      <c r="K10" s="210"/>
-      <c r="L10" s="210"/>
-      <c r="M10" s="210"/>
-      <c r="N10" s="210"/>
-      <c r="O10" s="210"/>
-      <c r="P10" s="210"/>
-      <c r="Q10" s="211"/>
-      <c r="R10" s="210"/>
-      <c r="S10" s="210"/>
-      <c r="T10" s="210"/>
-      <c r="U10" s="210"/>
-      <c r="V10" s="210"/>
-      <c r="W10" s="210"/>
-      <c r="X10" s="210"/>
-      <c r="Y10" s="210"/>
-      <c r="Z10" s="210"/>
-      <c r="AA10" s="210"/>
-      <c r="AB10" s="210"/>
-      <c r="AC10" s="210"/>
-      <c r="AD10" s="210"/>
-      <c r="AE10" s="210"/>
-      <c r="AF10" s="210"/>
-      <c r="AG10" s="210"/>
-      <c r="AH10" s="210"/>
-      <c r="AI10" s="210"/>
-      <c r="AJ10" s="210"/>
-      <c r="AK10" s="210"/>
-      <c r="AL10" s="217"/>
-      <c r="AM10" s="207"/>
-      <c r="AN10" s="207"/>
-      <c r="AO10" s="207"/>
-      <c r="AP10" s="210"/>
-      <c r="AQ10" s="210"/>
-      <c r="AR10" s="210"/>
-      <c r="AS10" s="210"/>
-      <c r="AT10" s="210"/>
-      <c r="AU10" s="210"/>
-      <c r="AV10" s="210"/>
-      <c r="AW10" s="210"/>
-      <c r="AX10" s="210"/>
-      <c r="AY10" s="210"/>
-      <c r="AZ10" s="210"/>
-      <c r="BA10" s="210"/>
+      <c r="A10" s="180"/>
+      <c r="B10" s="180"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
+      <c r="G10" s="181"/>
+      <c r="H10" s="181"/>
+      <c r="I10" s="181"/>
+      <c r="J10" s="181"/>
+      <c r="K10" s="181"/>
+      <c r="L10" s="181"/>
+      <c r="M10" s="181"/>
+      <c r="N10" s="181"/>
+      <c r="O10" s="181"/>
+      <c r="P10" s="181"/>
+      <c r="Q10" s="182"/>
+      <c r="R10" s="181"/>
+      <c r="S10" s="181"/>
+      <c r="T10" s="181"/>
+      <c r="U10" s="181"/>
+      <c r="V10" s="181"/>
+      <c r="W10" s="181"/>
+      <c r="X10" s="181"/>
+      <c r="Y10" s="181"/>
+      <c r="Z10" s="181"/>
+      <c r="AA10" s="181"/>
+      <c r="AB10" s="181"/>
+      <c r="AC10" s="181"/>
+      <c r="AD10" s="181"/>
+      <c r="AE10" s="181"/>
+      <c r="AF10" s="181"/>
+      <c r="AG10" s="181"/>
+      <c r="AH10" s="181"/>
+      <c r="AI10" s="181"/>
+      <c r="AJ10" s="181"/>
+      <c r="AK10" s="181"/>
+      <c r="AL10" s="179"/>
+      <c r="AM10" s="180"/>
+      <c r="AN10" s="180"/>
+      <c r="AO10" s="180"/>
+      <c r="AP10" s="181"/>
+      <c r="AQ10" s="181"/>
+      <c r="AR10" s="181"/>
+      <c r="AS10" s="181"/>
+      <c r="AT10" s="181"/>
+      <c r="AU10" s="181"/>
+      <c r="AV10" s="181"/>
+      <c r="AW10" s="181"/>
+      <c r="AX10" s="181"/>
+      <c r="AY10" s="181"/>
+      <c r="AZ10" s="181"/>
+      <c r="BA10" s="181"/>
     </row>
     <row r="11" spans="1:53">
-      <c r="A11" s="207"/>
-      <c r="B11" s="207"/>
-      <c r="C11" s="211"/>
-      <c r="D11" s="210"/>
-      <c r="E11" s="210"/>
-      <c r="F11" s="210"/>
-      <c r="G11" s="210"/>
-      <c r="H11" s="210"/>
-      <c r="I11" s="210"/>
-      <c r="J11" s="210"/>
-      <c r="K11" s="210"/>
-      <c r="L11" s="210"/>
-      <c r="M11" s="210"/>
-      <c r="N11" s="210"/>
-      <c r="O11" s="210"/>
-      <c r="P11" s="210"/>
-      <c r="Q11" s="211"/>
-      <c r="R11" s="210"/>
-      <c r="S11" s="210"/>
-      <c r="T11" s="210"/>
-      <c r="U11" s="210"/>
-      <c r="V11" s="210"/>
-      <c r="W11" s="210"/>
-      <c r="X11" s="210"/>
-      <c r="Y11" s="210"/>
-      <c r="Z11" s="210"/>
-      <c r="AA11" s="210"/>
-      <c r="AB11" s="210"/>
-      <c r="AC11" s="210"/>
-      <c r="AD11" s="210"/>
-      <c r="AE11" s="210"/>
-      <c r="AF11" s="210"/>
-      <c r="AG11" s="210"/>
-      <c r="AH11" s="210"/>
-      <c r="AI11" s="210"/>
-      <c r="AJ11" s="210"/>
-      <c r="AK11" s="210"/>
-      <c r="AL11" s="217"/>
-      <c r="AM11" s="207"/>
-      <c r="AN11" s="207"/>
-      <c r="AO11" s="207"/>
-      <c r="AP11" s="210"/>
-      <c r="AQ11" s="210"/>
-      <c r="AR11" s="210"/>
-      <c r="AS11" s="210"/>
-      <c r="AT11" s="210"/>
-      <c r="AU11" s="210"/>
-      <c r="AV11" s="210"/>
-      <c r="AW11" s="210"/>
-      <c r="AX11" s="210"/>
-      <c r="AY11" s="210"/>
-      <c r="AZ11" s="210"/>
-      <c r="BA11" s="210"/>
+      <c r="A11" s="180"/>
+      <c r="B11" s="180"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="181"/>
+      <c r="F11" s="181"/>
+      <c r="G11" s="181"/>
+      <c r="H11" s="181"/>
+      <c r="I11" s="181"/>
+      <c r="J11" s="181"/>
+      <c r="K11" s="181"/>
+      <c r="L11" s="181"/>
+      <c r="M11" s="181"/>
+      <c r="N11" s="181"/>
+      <c r="O11" s="181"/>
+      <c r="P11" s="181"/>
+      <c r="Q11" s="182"/>
+      <c r="R11" s="181"/>
+      <c r="S11" s="181"/>
+      <c r="T11" s="181"/>
+      <c r="U11" s="181"/>
+      <c r="V11" s="181"/>
+      <c r="W11" s="181"/>
+      <c r="X11" s="181"/>
+      <c r="Y11" s="181"/>
+      <c r="Z11" s="181"/>
+      <c r="AA11" s="181"/>
+      <c r="AB11" s="181"/>
+      <c r="AC11" s="181"/>
+      <c r="AD11" s="181"/>
+      <c r="AE11" s="181"/>
+      <c r="AF11" s="181"/>
+      <c r="AG11" s="181"/>
+      <c r="AH11" s="181"/>
+      <c r="AI11" s="181"/>
+      <c r="AJ11" s="181"/>
+      <c r="AK11" s="181"/>
+      <c r="AL11" s="179"/>
+      <c r="AM11" s="180"/>
+      <c r="AN11" s="180"/>
+      <c r="AO11" s="180"/>
+      <c r="AP11" s="181"/>
+      <c r="AQ11" s="181"/>
+      <c r="AR11" s="181"/>
+      <c r="AS11" s="181"/>
+      <c r="AT11" s="181"/>
+      <c r="AU11" s="181"/>
+      <c r="AV11" s="181"/>
+      <c r="AW11" s="181"/>
+      <c r="AX11" s="181"/>
+      <c r="AY11" s="181"/>
+      <c r="AZ11" s="181"/>
+      <c r="BA11" s="181"/>
     </row>
     <row r="12" spans="1:53">
-      <c r="A12" s="207"/>
-      <c r="B12" s="207"/>
-      <c r="C12" s="210"/>
-      <c r="D12" s="210"/>
-      <c r="E12" s="210"/>
-      <c r="F12" s="210"/>
-      <c r="G12" s="210"/>
-      <c r="H12" s="210"/>
-      <c r="I12" s="210"/>
-      <c r="J12" s="210"/>
-      <c r="K12" s="210"/>
-      <c r="L12" s="210"/>
-      <c r="M12" s="210"/>
-      <c r="N12" s="210"/>
-      <c r="O12" s="210"/>
-      <c r="P12" s="210"/>
-      <c r="Q12" s="210"/>
-      <c r="R12" s="210"/>
-      <c r="S12" s="210"/>
-      <c r="T12" s="210"/>
-      <c r="U12" s="210"/>
-      <c r="V12" s="210"/>
-      <c r="W12" s="210"/>
-      <c r="X12" s="210"/>
-      <c r="Y12" s="210"/>
-      <c r="Z12" s="210"/>
-      <c r="AA12" s="210"/>
-      <c r="AB12" s="210"/>
-      <c r="AC12" s="210"/>
-      <c r="AD12" s="210"/>
-      <c r="AE12" s="210"/>
-      <c r="AF12" s="210"/>
-      <c r="AG12" s="210"/>
-      <c r="AH12" s="210"/>
-      <c r="AI12" s="210"/>
-      <c r="AJ12" s="210"/>
-      <c r="AK12" s="210"/>
-      <c r="AL12" s="217"/>
-      <c r="AM12" s="207"/>
-      <c r="AN12" s="207"/>
-      <c r="AO12" s="207"/>
-      <c r="AP12" s="210"/>
-      <c r="AQ12" s="210"/>
-      <c r="AR12" s="210"/>
-      <c r="AS12" s="210"/>
-      <c r="AT12" s="210"/>
-      <c r="AU12" s="210"/>
-      <c r="AV12" s="210"/>
-      <c r="AW12" s="210"/>
-      <c r="AX12" s="210"/>
-      <c r="AY12" s="210"/>
-      <c r="AZ12" s="210"/>
-      <c r="BA12" s="210"/>
+      <c r="A12" s="180"/>
+      <c r="B12" s="180"/>
+      <c r="C12" s="181"/>
+      <c r="D12" s="181"/>
+      <c r="E12" s="181"/>
+      <c r="F12" s="181"/>
+      <c r="G12" s="181"/>
+      <c r="H12" s="181"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="181"/>
+      <c r="K12" s="181"/>
+      <c r="L12" s="181"/>
+      <c r="M12" s="181"/>
+      <c r="N12" s="181"/>
+      <c r="O12" s="181"/>
+      <c r="P12" s="181"/>
+      <c r="Q12" s="181"/>
+      <c r="R12" s="181"/>
+      <c r="S12" s="181"/>
+      <c r="T12" s="181"/>
+      <c r="U12" s="181"/>
+      <c r="V12" s="181"/>
+      <c r="W12" s="181"/>
+      <c r="X12" s="181"/>
+      <c r="Y12" s="181"/>
+      <c r="Z12" s="181"/>
+      <c r="AA12" s="181"/>
+      <c r="AB12" s="181"/>
+      <c r="AC12" s="181"/>
+      <c r="AD12" s="181"/>
+      <c r="AE12" s="181"/>
+      <c r="AF12" s="181"/>
+      <c r="AG12" s="181"/>
+      <c r="AH12" s="181"/>
+      <c r="AI12" s="181"/>
+      <c r="AJ12" s="181"/>
+      <c r="AK12" s="181"/>
+      <c r="AL12" s="179"/>
+      <c r="AM12" s="180"/>
+      <c r="AN12" s="180"/>
+      <c r="AO12" s="180"/>
+      <c r="AP12" s="181"/>
+      <c r="AQ12" s="181"/>
+      <c r="AR12" s="181"/>
+      <c r="AS12" s="181"/>
+      <c r="AT12" s="181"/>
+      <c r="AU12" s="181"/>
+      <c r="AV12" s="181"/>
+      <c r="AW12" s="181"/>
+      <c r="AX12" s="181"/>
+      <c r="AY12" s="181"/>
+      <c r="AZ12" s="181"/>
+      <c r="BA12" s="181"/>
     </row>
     <row r="13" spans="1:53">
-      <c r="A13" s="209"/>
-      <c r="B13" s="209"/>
-      <c r="C13" s="212"/>
-      <c r="D13" s="212"/>
-      <c r="E13" s="212"/>
-      <c r="F13" s="212"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="212"/>
-      <c r="I13" s="212"/>
-      <c r="J13" s="212"/>
-      <c r="K13" s="212"/>
-      <c r="L13" s="212"/>
-      <c r="M13" s="212"/>
-      <c r="N13" s="212"/>
-      <c r="O13" s="212"/>
-      <c r="P13" s="212"/>
-      <c r="Q13" s="211"/>
-      <c r="R13" s="210"/>
-      <c r="S13" s="210"/>
-      <c r="T13" s="210"/>
-      <c r="U13" s="210"/>
-      <c r="V13" s="210"/>
-      <c r="W13" s="210"/>
-      <c r="X13" s="210"/>
-      <c r="Y13" s="210"/>
-      <c r="Z13" s="210"/>
-      <c r="AA13" s="210"/>
-      <c r="AB13" s="210"/>
-      <c r="AC13" s="210"/>
-      <c r="AD13" s="210"/>
-      <c r="AE13" s="210"/>
-      <c r="AF13" s="210"/>
-      <c r="AG13" s="210"/>
-      <c r="AH13" s="210"/>
-      <c r="AI13" s="210"/>
-      <c r="AJ13" s="210"/>
-      <c r="AK13" s="210"/>
-      <c r="AL13" s="223"/>
-      <c r="AM13" s="209"/>
-      <c r="AN13" s="209"/>
-      <c r="AO13" s="209"/>
-      <c r="AP13" s="210"/>
-      <c r="AQ13" s="210"/>
-      <c r="AR13" s="210"/>
-      <c r="AS13" s="212"/>
-      <c r="AT13" s="212"/>
-      <c r="AU13" s="212"/>
-      <c r="AV13" s="212"/>
-      <c r="AW13" s="212"/>
-      <c r="AX13" s="212"/>
-      <c r="AY13" s="212"/>
-      <c r="AZ13" s="212"/>
-      <c r="BA13" s="212"/>
+      <c r="A13" s="191"/>
+      <c r="B13" s="191"/>
+      <c r="C13" s="183"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="183"/>
+      <c r="F13" s="183"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="183"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="183"/>
+      <c r="K13" s="183"/>
+      <c r="L13" s="183"/>
+      <c r="M13" s="183"/>
+      <c r="N13" s="183"/>
+      <c r="O13" s="183"/>
+      <c r="P13" s="183"/>
+      <c r="Q13" s="182"/>
+      <c r="R13" s="181"/>
+      <c r="S13" s="181"/>
+      <c r="T13" s="181"/>
+      <c r="U13" s="181"/>
+      <c r="V13" s="181"/>
+      <c r="W13" s="181"/>
+      <c r="X13" s="181"/>
+      <c r="Y13" s="181"/>
+      <c r="Z13" s="181"/>
+      <c r="AA13" s="181"/>
+      <c r="AB13" s="181"/>
+      <c r="AC13" s="181"/>
+      <c r="AD13" s="181"/>
+      <c r="AE13" s="181"/>
+      <c r="AF13" s="181"/>
+      <c r="AG13" s="181"/>
+      <c r="AH13" s="181"/>
+      <c r="AI13" s="181"/>
+      <c r="AJ13" s="181"/>
+      <c r="AK13" s="181"/>
+      <c r="AL13" s="190"/>
+      <c r="AM13" s="191"/>
+      <c r="AN13" s="191"/>
+      <c r="AO13" s="191"/>
+      <c r="AP13" s="181"/>
+      <c r="AQ13" s="181"/>
+      <c r="AR13" s="181"/>
+      <c r="AS13" s="183"/>
+      <c r="AT13" s="183"/>
+      <c r="AU13" s="183"/>
+      <c r="AV13" s="183"/>
+      <c r="AW13" s="183"/>
+      <c r="AX13" s="183"/>
+      <c r="AY13" s="183"/>
+      <c r="AZ13" s="183"/>
+      <c r="BA13" s="183"/>
     </row>
     <row r="14" spans="1:53">
-      <c r="A14" s="207"/>
-      <c r="B14" s="207"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
-      <c r="F14" s="210"/>
-      <c r="G14" s="210"/>
-      <c r="H14" s="210"/>
-      <c r="I14" s="210"/>
-      <c r="J14" s="210"/>
-      <c r="K14" s="210"/>
-      <c r="L14" s="210"/>
-      <c r="M14" s="210"/>
-      <c r="N14" s="210"/>
-      <c r="O14" s="210"/>
-      <c r="P14" s="210"/>
-      <c r="Q14" s="211"/>
-      <c r="R14" s="210"/>
-      <c r="S14" s="210"/>
-      <c r="T14" s="210"/>
-      <c r="U14" s="210"/>
-      <c r="V14" s="210"/>
-      <c r="W14" s="210"/>
-      <c r="X14" s="210"/>
-      <c r="Y14" s="210"/>
-      <c r="Z14" s="210"/>
-      <c r="AA14" s="210"/>
-      <c r="AB14" s="210"/>
-      <c r="AC14" s="210"/>
-      <c r="AD14" s="210"/>
-      <c r="AE14" s="210"/>
-      <c r="AF14" s="210"/>
-      <c r="AG14" s="210"/>
-      <c r="AH14" s="210"/>
-      <c r="AI14" s="210"/>
-      <c r="AJ14" s="210"/>
-      <c r="AK14" s="210"/>
-      <c r="AL14" s="217"/>
-      <c r="AM14" s="207"/>
-      <c r="AN14" s="207"/>
-      <c r="AO14" s="207"/>
-      <c r="AP14" s="210"/>
-      <c r="AQ14" s="210"/>
-      <c r="AR14" s="210"/>
-      <c r="AS14" s="210"/>
-      <c r="AT14" s="210"/>
-      <c r="AU14" s="210"/>
-      <c r="AV14" s="210"/>
-      <c r="AW14" s="210"/>
-      <c r="AX14" s="210"/>
-      <c r="AY14" s="210"/>
-      <c r="AZ14" s="210"/>
-      <c r="BA14" s="210"/>
+      <c r="A14" s="180"/>
+      <c r="B14" s="180"/>
+      <c r="C14" s="181"/>
+      <c r="D14" s="181"/>
+      <c r="E14" s="181"/>
+      <c r="F14" s="181"/>
+      <c r="G14" s="181"/>
+      <c r="H14" s="181"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="181"/>
+      <c r="K14" s="181"/>
+      <c r="L14" s="181"/>
+      <c r="M14" s="181"/>
+      <c r="N14" s="181"/>
+      <c r="O14" s="181"/>
+      <c r="P14" s="181"/>
+      <c r="Q14" s="182"/>
+      <c r="R14" s="181"/>
+      <c r="S14" s="181"/>
+      <c r="T14" s="181"/>
+      <c r="U14" s="181"/>
+      <c r="V14" s="181"/>
+      <c r="W14" s="181"/>
+      <c r="X14" s="181"/>
+      <c r="Y14" s="181"/>
+      <c r="Z14" s="181"/>
+      <c r="AA14" s="181"/>
+      <c r="AB14" s="181"/>
+      <c r="AC14" s="181"/>
+      <c r="AD14" s="181"/>
+      <c r="AE14" s="181"/>
+      <c r="AF14" s="181"/>
+      <c r="AG14" s="181"/>
+      <c r="AH14" s="181"/>
+      <c r="AI14" s="181"/>
+      <c r="AJ14" s="181"/>
+      <c r="AK14" s="181"/>
+      <c r="AL14" s="179"/>
+      <c r="AM14" s="180"/>
+      <c r="AN14" s="180"/>
+      <c r="AO14" s="180"/>
+      <c r="AP14" s="181"/>
+      <c r="AQ14" s="181"/>
+      <c r="AR14" s="181"/>
+      <c r="AS14" s="181"/>
+      <c r="AT14" s="181"/>
+      <c r="AU14" s="181"/>
+      <c r="AV14" s="181"/>
+      <c r="AW14" s="181"/>
+      <c r="AX14" s="181"/>
+      <c r="AY14" s="181"/>
+      <c r="AZ14" s="181"/>
+      <c r="BA14" s="181"/>
     </row>
     <row r="15" spans="1:53">
-      <c r="A15" s="207"/>
-      <c r="B15" s="207"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
-      <c r="F15" s="210"/>
-      <c r="G15" s="210"/>
-      <c r="H15" s="210"/>
-      <c r="I15" s="210"/>
-      <c r="J15" s="210"/>
-      <c r="K15" s="210"/>
-      <c r="L15" s="210"/>
-      <c r="M15" s="210"/>
-      <c r="N15" s="210"/>
-      <c r="O15" s="210"/>
-      <c r="P15" s="210"/>
-      <c r="Q15" s="211"/>
-      <c r="R15" s="210"/>
-      <c r="S15" s="210"/>
-      <c r="T15" s="210"/>
-      <c r="U15" s="210"/>
-      <c r="V15" s="210"/>
-      <c r="W15" s="210"/>
-      <c r="X15" s="210"/>
-      <c r="Y15" s="210"/>
-      <c r="Z15" s="210"/>
-      <c r="AA15" s="210"/>
-      <c r="AB15" s="210"/>
-      <c r="AC15" s="210"/>
-      <c r="AD15" s="210"/>
-      <c r="AE15" s="210"/>
-      <c r="AF15" s="210"/>
-      <c r="AG15" s="210"/>
-      <c r="AH15" s="210"/>
-      <c r="AI15" s="210"/>
-      <c r="AJ15" s="210"/>
-      <c r="AK15" s="210"/>
-      <c r="AL15" s="217"/>
-      <c r="AM15" s="207"/>
-      <c r="AN15" s="207"/>
-      <c r="AO15" s="207"/>
-      <c r="AP15" s="210"/>
-      <c r="AQ15" s="210"/>
-      <c r="AR15" s="210"/>
-      <c r="AS15" s="210"/>
-      <c r="AT15" s="210"/>
-      <c r="AU15" s="210"/>
-      <c r="AV15" s="210"/>
-      <c r="AW15" s="210"/>
-      <c r="AX15" s="210"/>
-      <c r="AY15" s="210"/>
-      <c r="AZ15" s="210"/>
-      <c r="BA15" s="210"/>
+      <c r="A15" s="180"/>
+      <c r="B15" s="180"/>
+      <c r="C15" s="181"/>
+      <c r="D15" s="181"/>
+      <c r="E15" s="181"/>
+      <c r="F15" s="181"/>
+      <c r="G15" s="181"/>
+      <c r="H15" s="181"/>
+      <c r="I15" s="181"/>
+      <c r="J15" s="181"/>
+      <c r="K15" s="181"/>
+      <c r="L15" s="181"/>
+      <c r="M15" s="181"/>
+      <c r="N15" s="181"/>
+      <c r="O15" s="181"/>
+      <c r="P15" s="181"/>
+      <c r="Q15" s="182"/>
+      <c r="R15" s="181"/>
+      <c r="S15" s="181"/>
+      <c r="T15" s="181"/>
+      <c r="U15" s="181"/>
+      <c r="V15" s="181"/>
+      <c r="W15" s="181"/>
+      <c r="X15" s="181"/>
+      <c r="Y15" s="181"/>
+      <c r="Z15" s="181"/>
+      <c r="AA15" s="181"/>
+      <c r="AB15" s="181"/>
+      <c r="AC15" s="181"/>
+      <c r="AD15" s="181"/>
+      <c r="AE15" s="181"/>
+      <c r="AF15" s="181"/>
+      <c r="AG15" s="181"/>
+      <c r="AH15" s="181"/>
+      <c r="AI15" s="181"/>
+      <c r="AJ15" s="181"/>
+      <c r="AK15" s="181"/>
+      <c r="AL15" s="179"/>
+      <c r="AM15" s="180"/>
+      <c r="AN15" s="180"/>
+      <c r="AO15" s="180"/>
+      <c r="AP15" s="181"/>
+      <c r="AQ15" s="181"/>
+      <c r="AR15" s="181"/>
+      <c r="AS15" s="181"/>
+      <c r="AT15" s="181"/>
+      <c r="AU15" s="181"/>
+      <c r="AV15" s="181"/>
+      <c r="AW15" s="181"/>
+      <c r="AX15" s="181"/>
+      <c r="AY15" s="181"/>
+      <c r="AZ15" s="181"/>
+      <c r="BA15" s="181"/>
     </row>
     <row r="16" spans="1:53">
-      <c r="A16" s="207"/>
-      <c r="B16" s="207"/>
-      <c r="C16" s="210"/>
-      <c r="D16" s="210"/>
-      <c r="E16" s="210"/>
-      <c r="F16" s="210"/>
-      <c r="G16" s="210"/>
-      <c r="H16" s="210"/>
-      <c r="I16" s="210"/>
-      <c r="J16" s="210"/>
-      <c r="K16" s="210"/>
-      <c r="L16" s="210"/>
-      <c r="M16" s="210"/>
-      <c r="N16" s="210"/>
-      <c r="O16" s="210"/>
-      <c r="P16" s="210"/>
-      <c r="Q16" s="211"/>
-      <c r="R16" s="210"/>
-      <c r="S16" s="210"/>
-      <c r="T16" s="210"/>
-      <c r="U16" s="210"/>
-      <c r="V16" s="210"/>
-      <c r="W16" s="210"/>
-      <c r="X16" s="210"/>
-      <c r="Y16" s="210"/>
-      <c r="Z16" s="210"/>
-      <c r="AA16" s="210"/>
-      <c r="AB16" s="210"/>
-      <c r="AC16" s="210"/>
-      <c r="AD16" s="210"/>
-      <c r="AE16" s="210"/>
-      <c r="AF16" s="210"/>
-      <c r="AG16" s="210"/>
-      <c r="AH16" s="210"/>
-      <c r="AI16" s="210"/>
-      <c r="AJ16" s="210"/>
-      <c r="AK16" s="210"/>
-      <c r="AL16" s="217"/>
-      <c r="AM16" s="207"/>
-      <c r="AN16" s="207"/>
-      <c r="AO16" s="207"/>
-      <c r="AP16" s="210"/>
-      <c r="AQ16" s="210"/>
-      <c r="AR16" s="210"/>
-      <c r="AS16" s="210"/>
-      <c r="AT16" s="210"/>
-      <c r="AU16" s="210"/>
-      <c r="AV16" s="210"/>
-      <c r="AW16" s="210"/>
-      <c r="AX16" s="210"/>
-      <c r="AY16" s="210"/>
-      <c r="AZ16" s="210"/>
-      <c r="BA16" s="210"/>
+      <c r="A16" s="180"/>
+      <c r="B16" s="180"/>
+      <c r="C16" s="181"/>
+      <c r="D16" s="181"/>
+      <c r="E16" s="181"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="181"/>
+      <c r="H16" s="181"/>
+      <c r="I16" s="181"/>
+      <c r="J16" s="181"/>
+      <c r="K16" s="181"/>
+      <c r="L16" s="181"/>
+      <c r="M16" s="181"/>
+      <c r="N16" s="181"/>
+      <c r="O16" s="181"/>
+      <c r="P16" s="181"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="181"/>
+      <c r="S16" s="181"/>
+      <c r="T16" s="181"/>
+      <c r="U16" s="181"/>
+      <c r="V16" s="181"/>
+      <c r="W16" s="181"/>
+      <c r="X16" s="181"/>
+      <c r="Y16" s="181"/>
+      <c r="Z16" s="181"/>
+      <c r="AA16" s="181"/>
+      <c r="AB16" s="181"/>
+      <c r="AC16" s="181"/>
+      <c r="AD16" s="181"/>
+      <c r="AE16" s="181"/>
+      <c r="AF16" s="181"/>
+      <c r="AG16" s="181"/>
+      <c r="AH16" s="181"/>
+      <c r="AI16" s="181"/>
+      <c r="AJ16" s="181"/>
+      <c r="AK16" s="181"/>
+      <c r="AL16" s="179"/>
+      <c r="AM16" s="180"/>
+      <c r="AN16" s="180"/>
+      <c r="AO16" s="180"/>
+      <c r="AP16" s="181"/>
+      <c r="AQ16" s="181"/>
+      <c r="AR16" s="181"/>
+      <c r="AS16" s="181"/>
+      <c r="AT16" s="181"/>
+      <c r="AU16" s="181"/>
+      <c r="AV16" s="181"/>
+      <c r="AW16" s="181"/>
+      <c r="AX16" s="181"/>
+      <c r="AY16" s="181"/>
+      <c r="AZ16" s="181"/>
+      <c r="BA16" s="181"/>
     </row>
     <row r="17" spans="1:53">
-      <c r="A17" s="208"/>
-      <c r="B17" s="208"/>
-      <c r="C17" s="210"/>
-      <c r="D17" s="210"/>
-      <c r="E17" s="210"/>
-      <c r="F17" s="210"/>
-      <c r="G17" s="210"/>
-      <c r="H17" s="210"/>
-      <c r="I17" s="210"/>
-      <c r="J17" s="210"/>
-      <c r="K17" s="210"/>
-      <c r="L17" s="210"/>
-      <c r="M17" s="210"/>
-      <c r="N17" s="210"/>
-      <c r="O17" s="210"/>
-      <c r="P17" s="210"/>
-      <c r="Q17" s="210"/>
-      <c r="R17" s="216"/>
-      <c r="S17" s="216"/>
-      <c r="T17" s="216"/>
-      <c r="U17" s="216"/>
-      <c r="V17" s="216"/>
-      <c r="W17" s="216"/>
-      <c r="X17" s="216"/>
-      <c r="Y17" s="216"/>
-      <c r="Z17" s="216"/>
-      <c r="AA17" s="216"/>
-      <c r="AB17" s="216"/>
-      <c r="AC17" s="216"/>
-      <c r="AD17" s="216"/>
-      <c r="AE17" s="216"/>
-      <c r="AF17" s="216"/>
-      <c r="AG17" s="216"/>
-      <c r="AH17" s="216"/>
-      <c r="AI17" s="216"/>
-      <c r="AJ17" s="216"/>
-      <c r="AK17" s="216"/>
-      <c r="AL17" s="217"/>
-      <c r="AM17" s="207"/>
-      <c r="AN17" s="207"/>
-      <c r="AO17" s="207"/>
-      <c r="AP17" s="210"/>
-      <c r="AQ17" s="216"/>
-      <c r="AR17" s="216"/>
-      <c r="AS17" s="216"/>
-      <c r="AT17" s="216"/>
-      <c r="AU17" s="216"/>
-      <c r="AV17" s="216"/>
-      <c r="AW17" s="216"/>
-      <c r="AX17" s="216"/>
-      <c r="AY17" s="216"/>
-      <c r="AZ17" s="216"/>
-      <c r="BA17" s="216"/>
+      <c r="A17" s="195"/>
+      <c r="B17" s="195"/>
+      <c r="C17" s="181"/>
+      <c r="D17" s="181"/>
+      <c r="E17" s="181"/>
+      <c r="F17" s="181"/>
+      <c r="G17" s="181"/>
+      <c r="H17" s="181"/>
+      <c r="I17" s="181"/>
+      <c r="J17" s="181"/>
+      <c r="K17" s="181"/>
+      <c r="L17" s="181"/>
+      <c r="M17" s="181"/>
+      <c r="N17" s="181"/>
+      <c r="O17" s="181"/>
+      <c r="P17" s="181"/>
+      <c r="Q17" s="181"/>
+      <c r="R17" s="184"/>
+      <c r="S17" s="184"/>
+      <c r="T17" s="184"/>
+      <c r="U17" s="184"/>
+      <c r="V17" s="184"/>
+      <c r="W17" s="184"/>
+      <c r="X17" s="184"/>
+      <c r="Y17" s="184"/>
+      <c r="Z17" s="184"/>
+      <c r="AA17" s="184"/>
+      <c r="AB17" s="184"/>
+      <c r="AC17" s="184"/>
+      <c r="AD17" s="184"/>
+      <c r="AE17" s="184"/>
+      <c r="AF17" s="184"/>
+      <c r="AG17" s="184"/>
+      <c r="AH17" s="184"/>
+      <c r="AI17" s="184"/>
+      <c r="AJ17" s="184"/>
+      <c r="AK17" s="184"/>
+      <c r="AL17" s="179"/>
+      <c r="AM17" s="180"/>
+      <c r="AN17" s="180"/>
+      <c r="AO17" s="180"/>
+      <c r="AP17" s="181"/>
+      <c r="AQ17" s="184"/>
+      <c r="AR17" s="184"/>
+      <c r="AS17" s="184"/>
+      <c r="AT17" s="184"/>
+      <c r="AU17" s="184"/>
+      <c r="AV17" s="184"/>
+      <c r="AW17" s="184"/>
+      <c r="AX17" s="184"/>
+      <c r="AY17" s="184"/>
+      <c r="AZ17" s="184"/>
+      <c r="BA17" s="184"/>
     </row>
     <row r="18" spans="1:53">
-      <c r="A18" s="208"/>
-      <c r="B18" s="208"/>
-      <c r="C18" s="210"/>
-      <c r="D18" s="210"/>
-      <c r="E18" s="210"/>
-      <c r="F18" s="210"/>
-      <c r="G18" s="210"/>
-      <c r="H18" s="210"/>
-      <c r="I18" s="210"/>
-      <c r="J18" s="210"/>
-      <c r="K18" s="210"/>
-      <c r="L18" s="210"/>
-      <c r="M18" s="210"/>
-      <c r="N18" s="210"/>
-      <c r="O18" s="210"/>
-      <c r="P18" s="210"/>
-      <c r="Q18" s="210"/>
-      <c r="R18" s="216"/>
-      <c r="S18" s="216"/>
-      <c r="T18" s="216"/>
-      <c r="U18" s="216"/>
-      <c r="V18" s="216"/>
-      <c r="W18" s="216"/>
-      <c r="X18" s="216"/>
-      <c r="Y18" s="216"/>
-      <c r="Z18" s="216"/>
-      <c r="AA18" s="216"/>
-      <c r="AB18" s="216"/>
-      <c r="AC18" s="216"/>
-      <c r="AD18" s="216"/>
-      <c r="AE18" s="216"/>
-      <c r="AF18" s="216"/>
-      <c r="AG18" s="216"/>
-      <c r="AH18" s="216"/>
-      <c r="AI18" s="216"/>
-      <c r="AJ18" s="216"/>
-      <c r="AK18" s="216"/>
-      <c r="AL18" s="217"/>
-      <c r="AM18" s="207"/>
-      <c r="AN18" s="207"/>
-      <c r="AO18" s="207"/>
-      <c r="AP18" s="210"/>
-      <c r="AQ18" s="216"/>
-      <c r="AR18" s="216"/>
-      <c r="AS18" s="216"/>
-      <c r="AT18" s="216"/>
-      <c r="AU18" s="216"/>
-      <c r="AV18" s="216"/>
-      <c r="AW18" s="216"/>
-      <c r="AX18" s="216"/>
-      <c r="AY18" s="216"/>
-      <c r="AZ18" s="216"/>
-      <c r="BA18" s="216"/>
+      <c r="A18" s="195"/>
+      <c r="B18" s="195"/>
+      <c r="C18" s="181"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="181"/>
+      <c r="F18" s="181"/>
+      <c r="G18" s="181"/>
+      <c r="H18" s="181"/>
+      <c r="I18" s="181"/>
+      <c r="J18" s="181"/>
+      <c r="K18" s="181"/>
+      <c r="L18" s="181"/>
+      <c r="M18" s="181"/>
+      <c r="N18" s="181"/>
+      <c r="O18" s="181"/>
+      <c r="P18" s="181"/>
+      <c r="Q18" s="181"/>
+      <c r="R18" s="184"/>
+      <c r="S18" s="184"/>
+      <c r="T18" s="184"/>
+      <c r="U18" s="184"/>
+      <c r="V18" s="184"/>
+      <c r="W18" s="184"/>
+      <c r="X18" s="184"/>
+      <c r="Y18" s="184"/>
+      <c r="Z18" s="184"/>
+      <c r="AA18" s="184"/>
+      <c r="AB18" s="184"/>
+      <c r="AC18" s="184"/>
+      <c r="AD18" s="184"/>
+      <c r="AE18" s="184"/>
+      <c r="AF18" s="184"/>
+      <c r="AG18" s="184"/>
+      <c r="AH18" s="184"/>
+      <c r="AI18" s="184"/>
+      <c r="AJ18" s="184"/>
+      <c r="AK18" s="184"/>
+      <c r="AL18" s="179"/>
+      <c r="AM18" s="180"/>
+      <c r="AN18" s="180"/>
+      <c r="AO18" s="180"/>
+      <c r="AP18" s="181"/>
+      <c r="AQ18" s="184"/>
+      <c r="AR18" s="184"/>
+      <c r="AS18" s="184"/>
+      <c r="AT18" s="184"/>
+      <c r="AU18" s="184"/>
+      <c r="AV18" s="184"/>
+      <c r="AW18" s="184"/>
+      <c r="AX18" s="184"/>
+      <c r="AY18" s="184"/>
+      <c r="AZ18" s="184"/>
+      <c r="BA18" s="184"/>
     </row>
     <row r="19" spans="1:53">
-      <c r="A19" s="207"/>
-      <c r="B19" s="207"/>
-      <c r="C19" s="210"/>
-      <c r="D19" s="210"/>
-      <c r="E19" s="210"/>
-      <c r="F19" s="210"/>
-      <c r="G19" s="210"/>
-      <c r="H19" s="210"/>
-      <c r="I19" s="210"/>
-      <c r="J19" s="210"/>
-      <c r="K19" s="210"/>
-      <c r="L19" s="210"/>
-      <c r="M19" s="210"/>
-      <c r="N19" s="210"/>
-      <c r="O19" s="210"/>
-      <c r="P19" s="210"/>
-      <c r="Q19" s="210"/>
-      <c r="R19" s="210"/>
-      <c r="S19" s="210"/>
-      <c r="T19" s="210"/>
-      <c r="U19" s="210"/>
-      <c r="V19" s="210"/>
-      <c r="W19" s="210"/>
-      <c r="X19" s="210"/>
-      <c r="Y19" s="210"/>
-      <c r="Z19" s="210"/>
-      <c r="AA19" s="210"/>
-      <c r="AB19" s="210"/>
-      <c r="AC19" s="210"/>
-      <c r="AD19" s="210"/>
-      <c r="AE19" s="210"/>
-      <c r="AF19" s="210"/>
-      <c r="AG19" s="210"/>
-      <c r="AH19" s="210"/>
-      <c r="AI19" s="210"/>
-      <c r="AJ19" s="210"/>
-      <c r="AK19" s="210"/>
-      <c r="AL19" s="217"/>
-      <c r="AM19" s="217"/>
-      <c r="AN19" s="217"/>
-      <c r="AO19" s="217"/>
-      <c r="AP19" s="210"/>
-      <c r="AQ19" s="210"/>
-      <c r="AR19" s="210"/>
-      <c r="AS19" s="210"/>
-      <c r="AT19" s="210"/>
-      <c r="AU19" s="210"/>
-      <c r="AV19" s="210"/>
-      <c r="AW19" s="210"/>
-      <c r="AX19" s="210"/>
-      <c r="AY19" s="210"/>
-      <c r="AZ19" s="210"/>
-      <c r="BA19" s="210"/>
+      <c r="A19" s="180"/>
+      <c r="B19" s="180"/>
+      <c r="C19" s="181"/>
+      <c r="D19" s="181"/>
+      <c r="E19" s="181"/>
+      <c r="F19" s="181"/>
+      <c r="G19" s="181"/>
+      <c r="H19" s="181"/>
+      <c r="I19" s="181"/>
+      <c r="J19" s="181"/>
+      <c r="K19" s="181"/>
+      <c r="L19" s="181"/>
+      <c r="M19" s="181"/>
+      <c r="N19" s="181"/>
+      <c r="O19" s="181"/>
+      <c r="P19" s="181"/>
+      <c r="Q19" s="181"/>
+      <c r="R19" s="181"/>
+      <c r="S19" s="181"/>
+      <c r="T19" s="181"/>
+      <c r="U19" s="181"/>
+      <c r="V19" s="181"/>
+      <c r="W19" s="181"/>
+      <c r="X19" s="181"/>
+      <c r="Y19" s="181"/>
+      <c r="Z19" s="181"/>
+      <c r="AA19" s="181"/>
+      <c r="AB19" s="181"/>
+      <c r="AC19" s="181"/>
+      <c r="AD19" s="181"/>
+      <c r="AE19" s="181"/>
+      <c r="AF19" s="181"/>
+      <c r="AG19" s="181"/>
+      <c r="AH19" s="181"/>
+      <c r="AI19" s="181"/>
+      <c r="AJ19" s="181"/>
+      <c r="AK19" s="181"/>
+      <c r="AL19" s="179"/>
+      <c r="AM19" s="179"/>
+      <c r="AN19" s="179"/>
+      <c r="AO19" s="179"/>
+      <c r="AP19" s="181"/>
+      <c r="AQ19" s="181"/>
+      <c r="AR19" s="181"/>
+      <c r="AS19" s="181"/>
+      <c r="AT19" s="181"/>
+      <c r="AU19" s="181"/>
+      <c r="AV19" s="181"/>
+      <c r="AW19" s="181"/>
+      <c r="AX19" s="181"/>
+      <c r="AY19" s="181"/>
+      <c r="AZ19" s="181"/>
+      <c r="BA19" s="181"/>
     </row>
     <row r="20" spans="1:53">
-      <c r="A20" s="207"/>
-      <c r="B20" s="207"/>
-      <c r="C20" s="210"/>
-      <c r="D20" s="210"/>
-      <c r="E20" s="210"/>
-      <c r="F20" s="210"/>
-      <c r="G20" s="210"/>
-      <c r="H20" s="210"/>
-      <c r="I20" s="210"/>
-      <c r="J20" s="210"/>
-      <c r="K20" s="210"/>
-      <c r="L20" s="210"/>
-      <c r="M20" s="210"/>
-      <c r="N20" s="210"/>
-      <c r="O20" s="210"/>
-      <c r="P20" s="210"/>
-      <c r="Q20" s="210"/>
-      <c r="R20" s="210"/>
-      <c r="S20" s="210"/>
-      <c r="T20" s="210"/>
-      <c r="U20" s="210"/>
-      <c r="V20" s="210"/>
-      <c r="W20" s="210"/>
-      <c r="X20" s="210"/>
-      <c r="Y20" s="210"/>
-      <c r="Z20" s="210"/>
-      <c r="AA20" s="210"/>
-      <c r="AB20" s="210"/>
-      <c r="AC20" s="210"/>
-      <c r="AD20" s="210"/>
-      <c r="AE20" s="210"/>
-      <c r="AF20" s="210"/>
-      <c r="AG20" s="210"/>
-      <c r="AH20" s="210"/>
-      <c r="AI20" s="210"/>
-      <c r="AJ20" s="210"/>
-      <c r="AK20" s="210"/>
-      <c r="AL20" s="217"/>
-      <c r="AM20" s="217"/>
-      <c r="AN20" s="217"/>
-      <c r="AO20" s="217"/>
-      <c r="AP20" s="210"/>
-      <c r="AQ20" s="210"/>
-      <c r="AR20" s="210"/>
-      <c r="AS20" s="210"/>
-      <c r="AT20" s="210"/>
-      <c r="AU20" s="210"/>
-      <c r="AV20" s="210"/>
-      <c r="AW20" s="210"/>
-      <c r="AX20" s="210"/>
-      <c r="AY20" s="210"/>
-      <c r="AZ20" s="210"/>
-      <c r="BA20" s="210"/>
+      <c r="A20" s="180"/>
+      <c r="B20" s="180"/>
+      <c r="C20" s="181"/>
+      <c r="D20" s="181"/>
+      <c r="E20" s="181"/>
+      <c r="F20" s="181"/>
+      <c r="G20" s="181"/>
+      <c r="H20" s="181"/>
+      <c r="I20" s="181"/>
+      <c r="J20" s="181"/>
+      <c r="K20" s="181"/>
+      <c r="L20" s="181"/>
+      <c r="M20" s="181"/>
+      <c r="N20" s="181"/>
+      <c r="O20" s="181"/>
+      <c r="P20" s="181"/>
+      <c r="Q20" s="181"/>
+      <c r="R20" s="181"/>
+      <c r="S20" s="181"/>
+      <c r="T20" s="181"/>
+      <c r="U20" s="181"/>
+      <c r="V20" s="181"/>
+      <c r="W20" s="181"/>
+      <c r="X20" s="181"/>
+      <c r="Y20" s="181"/>
+      <c r="Z20" s="181"/>
+      <c r="AA20" s="181"/>
+      <c r="AB20" s="181"/>
+      <c r="AC20" s="181"/>
+      <c r="AD20" s="181"/>
+      <c r="AE20" s="181"/>
+      <c r="AF20" s="181"/>
+      <c r="AG20" s="181"/>
+      <c r="AH20" s="181"/>
+      <c r="AI20" s="181"/>
+      <c r="AJ20" s="181"/>
+      <c r="AK20" s="181"/>
+      <c r="AL20" s="179"/>
+      <c r="AM20" s="179"/>
+      <c r="AN20" s="179"/>
+      <c r="AO20" s="179"/>
+      <c r="AP20" s="181"/>
+      <c r="AQ20" s="181"/>
+      <c r="AR20" s="181"/>
+      <c r="AS20" s="181"/>
+      <c r="AT20" s="181"/>
+      <c r="AU20" s="181"/>
+      <c r="AV20" s="181"/>
+      <c r="AW20" s="181"/>
+      <c r="AX20" s="181"/>
+      <c r="AY20" s="181"/>
+      <c r="AZ20" s="181"/>
+      <c r="BA20" s="181"/>
     </row>
     <row r="21" spans="1:53" ht="13.5" customHeight="1">
-      <c r="A21" s="207"/>
-      <c r="B21" s="207"/>
-      <c r="C21" s="210"/>
-      <c r="D21" s="210"/>
-      <c r="E21" s="210"/>
-      <c r="F21" s="210"/>
-      <c r="G21" s="210"/>
-      <c r="H21" s="210"/>
-      <c r="I21" s="210"/>
-      <c r="J21" s="210"/>
-      <c r="K21" s="210"/>
-      <c r="L21" s="210"/>
-      <c r="M21" s="210"/>
-      <c r="N21" s="210"/>
-      <c r="O21" s="210"/>
-      <c r="P21" s="210"/>
-      <c r="Q21" s="210"/>
-      <c r="R21" s="216"/>
-      <c r="S21" s="216"/>
-      <c r="T21" s="216"/>
-      <c r="U21" s="216"/>
-      <c r="V21" s="216"/>
-      <c r="W21" s="216"/>
-      <c r="X21" s="216"/>
-      <c r="Y21" s="216"/>
-      <c r="Z21" s="216"/>
-      <c r="AA21" s="216"/>
-      <c r="AB21" s="216"/>
-      <c r="AC21" s="216"/>
-      <c r="AD21" s="216"/>
-      <c r="AE21" s="216"/>
-      <c r="AF21" s="216"/>
-      <c r="AG21" s="216"/>
-      <c r="AH21" s="216"/>
-      <c r="AI21" s="216"/>
-      <c r="AJ21" s="216"/>
-      <c r="AK21" s="216"/>
-      <c r="AL21" s="217"/>
-      <c r="AM21" s="217"/>
-      <c r="AN21" s="217"/>
-      <c r="AO21" s="217"/>
-      <c r="AP21" s="210"/>
-      <c r="AQ21" s="210"/>
-      <c r="AR21" s="210"/>
-      <c r="AS21" s="210"/>
-      <c r="AT21" s="210"/>
-      <c r="AU21" s="210"/>
-      <c r="AV21" s="210"/>
-      <c r="AW21" s="210"/>
-      <c r="AX21" s="210"/>
-      <c r="AY21" s="210"/>
-      <c r="AZ21" s="210"/>
-      <c r="BA21" s="210"/>
+      <c r="A21" s="180"/>
+      <c r="B21" s="180"/>
+      <c r="C21" s="181"/>
+      <c r="D21" s="181"/>
+      <c r="E21" s="181"/>
+      <c r="F21" s="181"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="181"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="181"/>
+      <c r="L21" s="181"/>
+      <c r="M21" s="181"/>
+      <c r="N21" s="181"/>
+      <c r="O21" s="181"/>
+      <c r="P21" s="181"/>
+      <c r="Q21" s="181"/>
+      <c r="R21" s="184"/>
+      <c r="S21" s="184"/>
+      <c r="T21" s="184"/>
+      <c r="U21" s="184"/>
+      <c r="V21" s="184"/>
+      <c r="W21" s="184"/>
+      <c r="X21" s="184"/>
+      <c r="Y21" s="184"/>
+      <c r="Z21" s="184"/>
+      <c r="AA21" s="184"/>
+      <c r="AB21" s="184"/>
+      <c r="AC21" s="184"/>
+      <c r="AD21" s="184"/>
+      <c r="AE21" s="184"/>
+      <c r="AF21" s="184"/>
+      <c r="AG21" s="184"/>
+      <c r="AH21" s="184"/>
+      <c r="AI21" s="184"/>
+      <c r="AJ21" s="184"/>
+      <c r="AK21" s="184"/>
+      <c r="AL21" s="179"/>
+      <c r="AM21" s="179"/>
+      <c r="AN21" s="179"/>
+      <c r="AO21" s="179"/>
+      <c r="AP21" s="181"/>
+      <c r="AQ21" s="181"/>
+      <c r="AR21" s="181"/>
+      <c r="AS21" s="181"/>
+      <c r="AT21" s="181"/>
+      <c r="AU21" s="181"/>
+      <c r="AV21" s="181"/>
+      <c r="AW21" s="181"/>
+      <c r="AX21" s="181"/>
+      <c r="AY21" s="181"/>
+      <c r="AZ21" s="181"/>
+      <c r="BA21" s="181"/>
     </row>
     <row r="22" spans="1:53">
-      <c r="A22" s="207"/>
-      <c r="B22" s="207"/>
-      <c r="C22" s="210"/>
-      <c r="D22" s="210"/>
-      <c r="E22" s="210"/>
-      <c r="F22" s="210"/>
-      <c r="G22" s="210"/>
-      <c r="H22" s="210"/>
-      <c r="I22" s="210"/>
-      <c r="J22" s="210"/>
-      <c r="K22" s="210"/>
-      <c r="L22" s="210"/>
-      <c r="M22" s="210"/>
-      <c r="N22" s="210"/>
-      <c r="O22" s="210"/>
-      <c r="P22" s="210"/>
-      <c r="Q22" s="210"/>
-      <c r="R22" s="210"/>
-      <c r="S22" s="210"/>
-      <c r="T22" s="210"/>
-      <c r="U22" s="210"/>
-      <c r="V22" s="210"/>
-      <c r="W22" s="210"/>
-      <c r="X22" s="210"/>
-      <c r="Y22" s="210"/>
-      <c r="Z22" s="210"/>
-      <c r="AA22" s="210"/>
-      <c r="AB22" s="210"/>
-      <c r="AC22" s="210"/>
-      <c r="AD22" s="210"/>
-      <c r="AE22" s="210"/>
-      <c r="AF22" s="210"/>
-      <c r="AG22" s="210"/>
-      <c r="AH22" s="210"/>
-      <c r="AI22" s="210"/>
-      <c r="AJ22" s="210"/>
-      <c r="AK22" s="210"/>
-      <c r="AL22" s="217"/>
-      <c r="AM22" s="217"/>
-      <c r="AN22" s="217"/>
-      <c r="AO22" s="217"/>
-      <c r="AP22" s="210"/>
-      <c r="AQ22" s="210"/>
-      <c r="AR22" s="210"/>
-      <c r="AS22" s="210"/>
-      <c r="AT22" s="210"/>
-      <c r="AU22" s="210"/>
-      <c r="AV22" s="210"/>
-      <c r="AW22" s="210"/>
-      <c r="AX22" s="210"/>
-      <c r="AY22" s="210"/>
-      <c r="AZ22" s="210"/>
-      <c r="BA22" s="210"/>
+      <c r="A22" s="180"/>
+      <c r="B22" s="180"/>
+      <c r="C22" s="181"/>
+      <c r="D22" s="181"/>
+      <c r="E22" s="181"/>
+      <c r="F22" s="181"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="181"/>
+      <c r="I22" s="181"/>
+      <c r="J22" s="181"/>
+      <c r="K22" s="181"/>
+      <c r="L22" s="181"/>
+      <c r="M22" s="181"/>
+      <c r="N22" s="181"/>
+      <c r="O22" s="181"/>
+      <c r="P22" s="181"/>
+      <c r="Q22" s="181"/>
+      <c r="R22" s="181"/>
+      <c r="S22" s="181"/>
+      <c r="T22" s="181"/>
+      <c r="U22" s="181"/>
+      <c r="V22" s="181"/>
+      <c r="W22" s="181"/>
+      <c r="X22" s="181"/>
+      <c r="Y22" s="181"/>
+      <c r="Z22" s="181"/>
+      <c r="AA22" s="181"/>
+      <c r="AB22" s="181"/>
+      <c r="AC22" s="181"/>
+      <c r="AD22" s="181"/>
+      <c r="AE22" s="181"/>
+      <c r="AF22" s="181"/>
+      <c r="AG22" s="181"/>
+      <c r="AH22" s="181"/>
+      <c r="AI22" s="181"/>
+      <c r="AJ22" s="181"/>
+      <c r="AK22" s="181"/>
+      <c r="AL22" s="179"/>
+      <c r="AM22" s="179"/>
+      <c r="AN22" s="179"/>
+      <c r="AO22" s="179"/>
+      <c r="AP22" s="181"/>
+      <c r="AQ22" s="181"/>
+      <c r="AR22" s="181"/>
+      <c r="AS22" s="181"/>
+      <c r="AT22" s="181"/>
+      <c r="AU22" s="181"/>
+      <c r="AV22" s="181"/>
+      <c r="AW22" s="181"/>
+      <c r="AX22" s="181"/>
+      <c r="AY22" s="181"/>
+      <c r="AZ22" s="181"/>
+      <c r="BA22" s="181"/>
     </row>
     <row r="23" spans="1:53">
-      <c r="A23" s="207"/>
-      <c r="B23" s="207"/>
-      <c r="C23" s="210"/>
-      <c r="D23" s="210"/>
-      <c r="E23" s="210"/>
-      <c r="F23" s="210"/>
-      <c r="G23" s="210"/>
-      <c r="H23" s="210"/>
-      <c r="I23" s="210"/>
-      <c r="J23" s="210"/>
-      <c r="K23" s="210"/>
-      <c r="L23" s="210"/>
-      <c r="M23" s="210"/>
-      <c r="N23" s="210"/>
-      <c r="O23" s="210"/>
-      <c r="P23" s="210"/>
-      <c r="Q23" s="210"/>
-      <c r="R23" s="216"/>
-      <c r="S23" s="216"/>
-      <c r="T23" s="216"/>
-      <c r="U23" s="216"/>
-      <c r="V23" s="216"/>
-      <c r="W23" s="216"/>
-      <c r="X23" s="216"/>
-      <c r="Y23" s="216"/>
-      <c r="Z23" s="216"/>
-      <c r="AA23" s="216"/>
-      <c r="AB23" s="216"/>
-      <c r="AC23" s="216"/>
-      <c r="AD23" s="216"/>
-      <c r="AE23" s="216"/>
-      <c r="AF23" s="216"/>
-      <c r="AG23" s="216"/>
-      <c r="AH23" s="216"/>
-      <c r="AI23" s="216"/>
-      <c r="AJ23" s="216"/>
-      <c r="AK23" s="216"/>
-      <c r="AL23" s="217"/>
-      <c r="AM23" s="217"/>
-      <c r="AN23" s="217"/>
-      <c r="AO23" s="217"/>
-      <c r="AP23" s="210"/>
-      <c r="AQ23" s="210"/>
-      <c r="AR23" s="210"/>
-      <c r="AS23" s="210"/>
-      <c r="AT23" s="210"/>
-      <c r="AU23" s="210"/>
-      <c r="AV23" s="210"/>
-      <c r="AW23" s="210"/>
-      <c r="AX23" s="210"/>
-      <c r="AY23" s="210"/>
-      <c r="AZ23" s="210"/>
-      <c r="BA23" s="210"/>
+      <c r="A23" s="180"/>
+      <c r="B23" s="180"/>
+      <c r="C23" s="181"/>
+      <c r="D23" s="181"/>
+      <c r="E23" s="181"/>
+      <c r="F23" s="181"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="181"/>
+      <c r="I23" s="181"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="181"/>
+      <c r="L23" s="181"/>
+      <c r="M23" s="181"/>
+      <c r="N23" s="181"/>
+      <c r="O23" s="181"/>
+      <c r="P23" s="181"/>
+      <c r="Q23" s="181"/>
+      <c r="R23" s="184"/>
+      <c r="S23" s="184"/>
+      <c r="T23" s="184"/>
+      <c r="U23" s="184"/>
+      <c r="V23" s="184"/>
+      <c r="W23" s="184"/>
+      <c r="X23" s="184"/>
+      <c r="Y23" s="184"/>
+      <c r="Z23" s="184"/>
+      <c r="AA23" s="184"/>
+      <c r="AB23" s="184"/>
+      <c r="AC23" s="184"/>
+      <c r="AD23" s="184"/>
+      <c r="AE23" s="184"/>
+      <c r="AF23" s="184"/>
+      <c r="AG23" s="184"/>
+      <c r="AH23" s="184"/>
+      <c r="AI23" s="184"/>
+      <c r="AJ23" s="184"/>
+      <c r="AK23" s="184"/>
+      <c r="AL23" s="179"/>
+      <c r="AM23" s="179"/>
+      <c r="AN23" s="179"/>
+      <c r="AO23" s="179"/>
+      <c r="AP23" s="181"/>
+      <c r="AQ23" s="181"/>
+      <c r="AR23" s="181"/>
+      <c r="AS23" s="181"/>
+      <c r="AT23" s="181"/>
+      <c r="AU23" s="181"/>
+      <c r="AV23" s="181"/>
+      <c r="AW23" s="181"/>
+      <c r="AX23" s="181"/>
+      <c r="AY23" s="181"/>
+      <c r="AZ23" s="181"/>
+      <c r="BA23" s="181"/>
     </row>
     <row r="24" spans="1:53">
-      <c r="A24" s="207"/>
-      <c r="B24" s="207"/>
-      <c r="C24" s="210"/>
-      <c r="D24" s="210"/>
-      <c r="E24" s="210"/>
-      <c r="F24" s="210"/>
-      <c r="G24" s="210"/>
-      <c r="H24" s="210"/>
-      <c r="I24" s="210"/>
-      <c r="J24" s="210"/>
-      <c r="K24" s="210"/>
-      <c r="L24" s="210"/>
-      <c r="M24" s="210"/>
-      <c r="N24" s="210"/>
-      <c r="O24" s="210"/>
-      <c r="P24" s="210"/>
-      <c r="Q24" s="210"/>
-      <c r="R24" s="210"/>
-      <c r="S24" s="210"/>
-      <c r="T24" s="210"/>
-      <c r="U24" s="210"/>
-      <c r="V24" s="210"/>
-      <c r="W24" s="210"/>
-      <c r="X24" s="210"/>
-      <c r="Y24" s="210"/>
-      <c r="Z24" s="210"/>
-      <c r="AA24" s="210"/>
-      <c r="AB24" s="210"/>
-      <c r="AC24" s="210"/>
-      <c r="AD24" s="210"/>
-      <c r="AE24" s="210"/>
-      <c r="AF24" s="210"/>
-      <c r="AG24" s="210"/>
-      <c r="AH24" s="210"/>
-      <c r="AI24" s="210"/>
-      <c r="AJ24" s="210"/>
-      <c r="AK24" s="210"/>
-      <c r="AL24" s="217"/>
-      <c r="AM24" s="217"/>
-      <c r="AN24" s="217"/>
-      <c r="AO24" s="217"/>
-      <c r="AP24" s="210"/>
-      <c r="AQ24" s="210"/>
-      <c r="AR24" s="210"/>
-      <c r="AS24" s="210"/>
-      <c r="AT24" s="210"/>
-      <c r="AU24" s="210"/>
-      <c r="AV24" s="210"/>
-      <c r="AW24" s="210"/>
-      <c r="AX24" s="210"/>
-      <c r="AY24" s="210"/>
-      <c r="AZ24" s="210"/>
-      <c r="BA24" s="210"/>
+      <c r="A24" s="180"/>
+      <c r="B24" s="180"/>
+      <c r="C24" s="181"/>
+      <c r="D24" s="181"/>
+      <c r="E24" s="181"/>
+      <c r="F24" s="181"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="181"/>
+      <c r="I24" s="181"/>
+      <c r="J24" s="181"/>
+      <c r="K24" s="181"/>
+      <c r="L24" s="181"/>
+      <c r="M24" s="181"/>
+      <c r="N24" s="181"/>
+      <c r="O24" s="181"/>
+      <c r="P24" s="181"/>
+      <c r="Q24" s="181"/>
+      <c r="R24" s="181"/>
+      <c r="S24" s="181"/>
+      <c r="T24" s="181"/>
+      <c r="U24" s="181"/>
+      <c r="V24" s="181"/>
+      <c r="W24" s="181"/>
+      <c r="X24" s="181"/>
+      <c r="Y24" s="181"/>
+      <c r="Z24" s="181"/>
+      <c r="AA24" s="181"/>
+      <c r="AB24" s="181"/>
+      <c r="AC24" s="181"/>
+      <c r="AD24" s="181"/>
+      <c r="AE24" s="181"/>
+      <c r="AF24" s="181"/>
+      <c r="AG24" s="181"/>
+      <c r="AH24" s="181"/>
+      <c r="AI24" s="181"/>
+      <c r="AJ24" s="181"/>
+      <c r="AK24" s="181"/>
+      <c r="AL24" s="179"/>
+      <c r="AM24" s="179"/>
+      <c r="AN24" s="179"/>
+      <c r="AO24" s="179"/>
+      <c r="AP24" s="181"/>
+      <c r="AQ24" s="181"/>
+      <c r="AR24" s="181"/>
+      <c r="AS24" s="181"/>
+      <c r="AT24" s="181"/>
+      <c r="AU24" s="181"/>
+      <c r="AV24" s="181"/>
+      <c r="AW24" s="181"/>
+      <c r="AX24" s="181"/>
+      <c r="AY24" s="181"/>
+      <c r="AZ24" s="181"/>
+      <c r="BA24" s="181"/>
     </row>
     <row r="25" spans="1:53">
-      <c r="A25" s="207"/>
-      <c r="B25" s="207"/>
-      <c r="C25" s="210"/>
-      <c r="D25" s="210"/>
-      <c r="E25" s="210"/>
-      <c r="F25" s="210"/>
-      <c r="G25" s="210"/>
-      <c r="H25" s="210"/>
-      <c r="I25" s="210"/>
-      <c r="J25" s="210"/>
-      <c r="K25" s="210"/>
-      <c r="L25" s="210"/>
-      <c r="M25" s="210"/>
-      <c r="N25" s="210"/>
-      <c r="O25" s="210"/>
-      <c r="P25" s="210"/>
-      <c r="Q25" s="210"/>
-      <c r="R25" s="210"/>
-      <c r="S25" s="210"/>
-      <c r="T25" s="210"/>
-      <c r="U25" s="210"/>
-      <c r="V25" s="210"/>
-      <c r="W25" s="210"/>
-      <c r="X25" s="210"/>
-      <c r="Y25" s="210"/>
-      <c r="Z25" s="210"/>
-      <c r="AA25" s="210"/>
-      <c r="AB25" s="210"/>
-      <c r="AC25" s="210"/>
-      <c r="AD25" s="210"/>
-      <c r="AE25" s="210"/>
-      <c r="AF25" s="210"/>
-      <c r="AG25" s="210"/>
-      <c r="AH25" s="210"/>
-      <c r="AI25" s="210"/>
-      <c r="AJ25" s="210"/>
-      <c r="AK25" s="210"/>
-      <c r="AL25" s="217"/>
-      <c r="AM25" s="207"/>
-      <c r="AN25" s="207"/>
-      <c r="AO25" s="207"/>
-      <c r="AP25" s="210"/>
-      <c r="AQ25" s="210"/>
-      <c r="AR25" s="210"/>
-      <c r="AS25" s="210"/>
-      <c r="AT25" s="210"/>
-      <c r="AU25" s="210"/>
-      <c r="AV25" s="210"/>
-      <c r="AW25" s="210"/>
-      <c r="AX25" s="210"/>
-      <c r="AY25" s="210"/>
-      <c r="AZ25" s="210"/>
-      <c r="BA25" s="210"/>
+      <c r="A25" s="180"/>
+      <c r="B25" s="180"/>
+      <c r="C25" s="181"/>
+      <c r="D25" s="181"/>
+      <c r="E25" s="181"/>
+      <c r="F25" s="181"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="181"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="181"/>
+      <c r="L25" s="181"/>
+      <c r="M25" s="181"/>
+      <c r="N25" s="181"/>
+      <c r="O25" s="181"/>
+      <c r="P25" s="181"/>
+      <c r="Q25" s="181"/>
+      <c r="R25" s="181"/>
+      <c r="S25" s="181"/>
+      <c r="T25" s="181"/>
+      <c r="U25" s="181"/>
+      <c r="V25" s="181"/>
+      <c r="W25" s="181"/>
+      <c r="X25" s="181"/>
+      <c r="Y25" s="181"/>
+      <c r="Z25" s="181"/>
+      <c r="AA25" s="181"/>
+      <c r="AB25" s="181"/>
+      <c r="AC25" s="181"/>
+      <c r="AD25" s="181"/>
+      <c r="AE25" s="181"/>
+      <c r="AF25" s="181"/>
+      <c r="AG25" s="181"/>
+      <c r="AH25" s="181"/>
+      <c r="AI25" s="181"/>
+      <c r="AJ25" s="181"/>
+      <c r="AK25" s="181"/>
+      <c r="AL25" s="179"/>
+      <c r="AM25" s="180"/>
+      <c r="AN25" s="180"/>
+      <c r="AO25" s="180"/>
+      <c r="AP25" s="181"/>
+      <c r="AQ25" s="181"/>
+      <c r="AR25" s="181"/>
+      <c r="AS25" s="181"/>
+      <c r="AT25" s="181"/>
+      <c r="AU25" s="181"/>
+      <c r="AV25" s="181"/>
+      <c r="AW25" s="181"/>
+      <c r="AX25" s="181"/>
+      <c r="AY25" s="181"/>
+      <c r="AZ25" s="181"/>
+      <c r="BA25" s="181"/>
     </row>
     <row r="26" spans="1:53">
-      <c r="A26" s="207"/>
-      <c r="B26" s="207"/>
-      <c r="C26" s="210"/>
-      <c r="D26" s="210"/>
-      <c r="E26" s="210"/>
-      <c r="F26" s="210"/>
-      <c r="G26" s="210"/>
-      <c r="H26" s="210"/>
-      <c r="I26" s="210"/>
-      <c r="J26" s="210"/>
-      <c r="K26" s="210"/>
-      <c r="L26" s="210"/>
-      <c r="M26" s="210"/>
-      <c r="N26" s="210"/>
-      <c r="O26" s="210"/>
-      <c r="P26" s="210"/>
-      <c r="Q26" s="210"/>
-      <c r="R26" s="210"/>
-      <c r="S26" s="210"/>
-      <c r="T26" s="210"/>
-      <c r="U26" s="210"/>
-      <c r="V26" s="210"/>
-      <c r="W26" s="210"/>
-      <c r="X26" s="210"/>
-      <c r="Y26" s="210"/>
-      <c r="Z26" s="210"/>
-      <c r="AA26" s="210"/>
-      <c r="AB26" s="210"/>
-      <c r="AC26" s="210"/>
-      <c r="AD26" s="210"/>
-      <c r="AE26" s="210"/>
-      <c r="AF26" s="210"/>
-      <c r="AG26" s="210"/>
-      <c r="AH26" s="210"/>
-      <c r="AI26" s="210"/>
-      <c r="AJ26" s="210"/>
-      <c r="AK26" s="210"/>
-      <c r="AL26" s="217"/>
-      <c r="AM26" s="207"/>
-      <c r="AN26" s="207"/>
-      <c r="AO26" s="207"/>
-      <c r="AP26" s="210"/>
-      <c r="AQ26" s="210"/>
-      <c r="AR26" s="210"/>
-      <c r="AS26" s="210"/>
-      <c r="AT26" s="210"/>
-      <c r="AU26" s="210"/>
-      <c r="AV26" s="210"/>
-      <c r="AW26" s="210"/>
-      <c r="AX26" s="210"/>
-      <c r="AY26" s="210"/>
-      <c r="AZ26" s="210"/>
-      <c r="BA26" s="210"/>
+      <c r="A26" s="180"/>
+      <c r="B26" s="180"/>
+      <c r="C26" s="181"/>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="181"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="181"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="181"/>
+      <c r="L26" s="181"/>
+      <c r="M26" s="181"/>
+      <c r="N26" s="181"/>
+      <c r="O26" s="181"/>
+      <c r="P26" s="181"/>
+      <c r="Q26" s="181"/>
+      <c r="R26" s="181"/>
+      <c r="S26" s="181"/>
+      <c r="T26" s="181"/>
+      <c r="U26" s="181"/>
+      <c r="V26" s="181"/>
+      <c r="W26" s="181"/>
+      <c r="X26" s="181"/>
+      <c r="Y26" s="181"/>
+      <c r="Z26" s="181"/>
+      <c r="AA26" s="181"/>
+      <c r="AB26" s="181"/>
+      <c r="AC26" s="181"/>
+      <c r="AD26" s="181"/>
+      <c r="AE26" s="181"/>
+      <c r="AF26" s="181"/>
+      <c r="AG26" s="181"/>
+      <c r="AH26" s="181"/>
+      <c r="AI26" s="181"/>
+      <c r="AJ26" s="181"/>
+      <c r="AK26" s="181"/>
+      <c r="AL26" s="179"/>
+      <c r="AM26" s="180"/>
+      <c r="AN26" s="180"/>
+      <c r="AO26" s="180"/>
+      <c r="AP26" s="181"/>
+      <c r="AQ26" s="181"/>
+      <c r="AR26" s="181"/>
+      <c r="AS26" s="181"/>
+      <c r="AT26" s="181"/>
+      <c r="AU26" s="181"/>
+      <c r="AV26" s="181"/>
+      <c r="AW26" s="181"/>
+      <c r="AX26" s="181"/>
+      <c r="AY26" s="181"/>
+      <c r="AZ26" s="181"/>
+      <c r="BA26" s="181"/>
     </row>
     <row r="27" spans="1:53">
-      <c r="A27" s="207"/>
-      <c r="B27" s="207"/>
-      <c r="C27" s="210"/>
-      <c r="D27" s="210"/>
-      <c r="E27" s="210"/>
-      <c r="F27" s="210"/>
-      <c r="G27" s="210"/>
-      <c r="H27" s="210"/>
-      <c r="I27" s="210"/>
-      <c r="J27" s="210"/>
-      <c r="K27" s="210"/>
-      <c r="L27" s="210"/>
-      <c r="M27" s="210"/>
-      <c r="N27" s="210"/>
-      <c r="O27" s="210"/>
-      <c r="P27" s="210"/>
-      <c r="Q27" s="210"/>
-      <c r="R27" s="210"/>
-      <c r="S27" s="210"/>
-      <c r="T27" s="210"/>
-      <c r="U27" s="210"/>
-      <c r="V27" s="210"/>
-      <c r="W27" s="210"/>
-      <c r="X27" s="210"/>
-      <c r="Y27" s="210"/>
-      <c r="Z27" s="210"/>
-      <c r="AA27" s="210"/>
-      <c r="AB27" s="210"/>
-      <c r="AC27" s="210"/>
-      <c r="AD27" s="210"/>
-      <c r="AE27" s="210"/>
-      <c r="AF27" s="210"/>
-      <c r="AG27" s="210"/>
-      <c r="AH27" s="210"/>
-      <c r="AI27" s="210"/>
-      <c r="AJ27" s="210"/>
-      <c r="AK27" s="210"/>
-      <c r="AL27" s="217"/>
-      <c r="AM27" s="207"/>
-      <c r="AN27" s="207"/>
-      <c r="AO27" s="207"/>
-      <c r="AP27" s="210"/>
-      <c r="AQ27" s="210"/>
-      <c r="AR27" s="210"/>
-      <c r="AS27" s="210"/>
-      <c r="AT27" s="210"/>
-      <c r="AU27" s="210"/>
-      <c r="AV27" s="210"/>
-      <c r="AW27" s="210"/>
-      <c r="AX27" s="210"/>
-      <c r="AY27" s="210"/>
-      <c r="AZ27" s="210"/>
-      <c r="BA27" s="210"/>
+      <c r="A27" s="180"/>
+      <c r="B27" s="180"/>
+      <c r="C27" s="181"/>
+      <c r="D27" s="181"/>
+      <c r="E27" s="181"/>
+      <c r="F27" s="181"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="181"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="181"/>
+      <c r="K27" s="181"/>
+      <c r="L27" s="181"/>
+      <c r="M27" s="181"/>
+      <c r="N27" s="181"/>
+      <c r="O27" s="181"/>
+      <c r="P27" s="181"/>
+      <c r="Q27" s="181"/>
+      <c r="R27" s="181"/>
+      <c r="S27" s="181"/>
+      <c r="T27" s="181"/>
+      <c r="U27" s="181"/>
+      <c r="V27" s="181"/>
+      <c r="W27" s="181"/>
+      <c r="X27" s="181"/>
+      <c r="Y27" s="181"/>
+      <c r="Z27" s="181"/>
+      <c r="AA27" s="181"/>
+      <c r="AB27" s="181"/>
+      <c r="AC27" s="181"/>
+      <c r="AD27" s="181"/>
+      <c r="AE27" s="181"/>
+      <c r="AF27" s="181"/>
+      <c r="AG27" s="181"/>
+      <c r="AH27" s="181"/>
+      <c r="AI27" s="181"/>
+      <c r="AJ27" s="181"/>
+      <c r="AK27" s="181"/>
+      <c r="AL27" s="179"/>
+      <c r="AM27" s="180"/>
+      <c r="AN27" s="180"/>
+      <c r="AO27" s="180"/>
+      <c r="AP27" s="181"/>
+      <c r="AQ27" s="181"/>
+      <c r="AR27" s="181"/>
+      <c r="AS27" s="181"/>
+      <c r="AT27" s="181"/>
+      <c r="AU27" s="181"/>
+      <c r="AV27" s="181"/>
+      <c r="AW27" s="181"/>
+      <c r="AX27" s="181"/>
+      <c r="AY27" s="181"/>
+      <c r="AZ27" s="181"/>
+      <c r="BA27" s="181"/>
     </row>
     <row r="28" spans="1:53">
-      <c r="A28" s="207"/>
-      <c r="B28" s="207"/>
-      <c r="C28" s="210"/>
-      <c r="D28" s="210"/>
-      <c r="E28" s="210"/>
-      <c r="F28" s="210"/>
-      <c r="G28" s="210"/>
-      <c r="H28" s="210"/>
-      <c r="I28" s="210"/>
-      <c r="J28" s="210"/>
-      <c r="K28" s="210"/>
-      <c r="L28" s="210"/>
-      <c r="M28" s="210"/>
-      <c r="N28" s="210"/>
-      <c r="O28" s="210"/>
-      <c r="P28" s="210"/>
-      <c r="Q28" s="210"/>
-      <c r="R28" s="210"/>
-      <c r="S28" s="210"/>
-      <c r="T28" s="210"/>
-      <c r="U28" s="210"/>
-      <c r="V28" s="210"/>
-      <c r="W28" s="210"/>
-      <c r="X28" s="210"/>
-      <c r="Y28" s="210"/>
-      <c r="Z28" s="210"/>
-      <c r="AA28" s="210"/>
-      <c r="AB28" s="210"/>
-      <c r="AC28" s="210"/>
-      <c r="AD28" s="210"/>
-      <c r="AE28" s="210"/>
-      <c r="AF28" s="210"/>
-      <c r="AG28" s="210"/>
-      <c r="AH28" s="210"/>
-      <c r="AI28" s="210"/>
-      <c r="AJ28" s="210"/>
-      <c r="AK28" s="210"/>
-      <c r="AL28" s="217"/>
-      <c r="AM28" s="207"/>
-      <c r="AN28" s="207"/>
-      <c r="AO28" s="207"/>
-      <c r="AP28" s="210"/>
-      <c r="AQ28" s="210"/>
-      <c r="AR28" s="210"/>
-      <c r="AS28" s="210"/>
-      <c r="AT28" s="210"/>
-      <c r="AU28" s="210"/>
-      <c r="AV28" s="210"/>
-      <c r="AW28" s="210"/>
-      <c r="AX28" s="210"/>
-      <c r="AY28" s="210"/>
-      <c r="AZ28" s="210"/>
-      <c r="BA28" s="210"/>
+      <c r="A28" s="180"/>
+      <c r="B28" s="180"/>
+      <c r="C28" s="181"/>
+      <c r="D28" s="181"/>
+      <c r="E28" s="181"/>
+      <c r="F28" s="181"/>
+      <c r="G28" s="181"/>
+      <c r="H28" s="181"/>
+      <c r="I28" s="181"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="181"/>
+      <c r="L28" s="181"/>
+      <c r="M28" s="181"/>
+      <c r="N28" s="181"/>
+      <c r="O28" s="181"/>
+      <c r="P28" s="181"/>
+      <c r="Q28" s="181"/>
+      <c r="R28" s="181"/>
+      <c r="S28" s="181"/>
+      <c r="T28" s="181"/>
+      <c r="U28" s="181"/>
+      <c r="V28" s="181"/>
+      <c r="W28" s="181"/>
+      <c r="X28" s="181"/>
+      <c r="Y28" s="181"/>
+      <c r="Z28" s="181"/>
+      <c r="AA28" s="181"/>
+      <c r="AB28" s="181"/>
+      <c r="AC28" s="181"/>
+      <c r="AD28" s="181"/>
+      <c r="AE28" s="181"/>
+      <c r="AF28" s="181"/>
+      <c r="AG28" s="181"/>
+      <c r="AH28" s="181"/>
+      <c r="AI28" s="181"/>
+      <c r="AJ28" s="181"/>
+      <c r="AK28" s="181"/>
+      <c r="AL28" s="179"/>
+      <c r="AM28" s="180"/>
+      <c r="AN28" s="180"/>
+      <c r="AO28" s="180"/>
+      <c r="AP28" s="181"/>
+      <c r="AQ28" s="181"/>
+      <c r="AR28" s="181"/>
+      <c r="AS28" s="181"/>
+      <c r="AT28" s="181"/>
+      <c r="AU28" s="181"/>
+      <c r="AV28" s="181"/>
+      <c r="AW28" s="181"/>
+      <c r="AX28" s="181"/>
+      <c r="AY28" s="181"/>
+      <c r="AZ28" s="181"/>
+      <c r="BA28" s="181"/>
     </row>
     <row r="29" spans="1:53">
-      <c r="A29" s="207"/>
-      <c r="B29" s="207"/>
-      <c r="C29" s="210"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="210"/>
-      <c r="G29" s="210"/>
-      <c r="H29" s="210"/>
-      <c r="I29" s="210"/>
-      <c r="J29" s="210"/>
-      <c r="K29" s="210"/>
-      <c r="L29" s="210"/>
-      <c r="M29" s="210"/>
-      <c r="N29" s="210"/>
-      <c r="O29" s="210"/>
-      <c r="P29" s="210"/>
-      <c r="Q29" s="210"/>
-      <c r="R29" s="210"/>
-      <c r="S29" s="210"/>
-      <c r="T29" s="210"/>
-      <c r="U29" s="210"/>
-      <c r="V29" s="210"/>
-      <c r="W29" s="210"/>
-      <c r="X29" s="210"/>
-      <c r="Y29" s="210"/>
-      <c r="Z29" s="210"/>
-      <c r="AA29" s="210"/>
-      <c r="AB29" s="210"/>
-      <c r="AC29" s="210"/>
-      <c r="AD29" s="210"/>
-      <c r="AE29" s="210"/>
-      <c r="AF29" s="210"/>
-      <c r="AG29" s="210"/>
-      <c r="AH29" s="210"/>
-      <c r="AI29" s="210"/>
-      <c r="AJ29" s="210"/>
-      <c r="AK29" s="210"/>
-      <c r="AL29" s="217"/>
-      <c r="AM29" s="207"/>
-      <c r="AN29" s="207"/>
-      <c r="AO29" s="207"/>
-      <c r="AP29" s="210"/>
-      <c r="AQ29" s="210"/>
-      <c r="AR29" s="210"/>
-      <c r="AS29" s="210"/>
-      <c r="AT29" s="210"/>
-      <c r="AU29" s="210"/>
-      <c r="AV29" s="210"/>
-      <c r="AW29" s="210"/>
-      <c r="AX29" s="210"/>
-      <c r="AY29" s="210"/>
-      <c r="AZ29" s="210"/>
-      <c r="BA29" s="210"/>
+      <c r="A29" s="180"/>
+      <c r="B29" s="180"/>
+      <c r="C29" s="181"/>
+      <c r="D29" s="181"/>
+      <c r="E29" s="181"/>
+      <c r="F29" s="181"/>
+      <c r="G29" s="181"/>
+      <c r="H29" s="181"/>
+      <c r="I29" s="181"/>
+      <c r="J29" s="181"/>
+      <c r="K29" s="181"/>
+      <c r="L29" s="181"/>
+      <c r="M29" s="181"/>
+      <c r="N29" s="181"/>
+      <c r="O29" s="181"/>
+      <c r="P29" s="181"/>
+      <c r="Q29" s="181"/>
+      <c r="R29" s="181"/>
+      <c r="S29" s="181"/>
+      <c r="T29" s="181"/>
+      <c r="U29" s="181"/>
+      <c r="V29" s="181"/>
+      <c r="W29" s="181"/>
+      <c r="X29" s="181"/>
+      <c r="Y29" s="181"/>
+      <c r="Z29" s="181"/>
+      <c r="AA29" s="181"/>
+      <c r="AB29" s="181"/>
+      <c r="AC29" s="181"/>
+      <c r="AD29" s="181"/>
+      <c r="AE29" s="181"/>
+      <c r="AF29" s="181"/>
+      <c r="AG29" s="181"/>
+      <c r="AH29" s="181"/>
+      <c r="AI29" s="181"/>
+      <c r="AJ29" s="181"/>
+      <c r="AK29" s="181"/>
+      <c r="AL29" s="179"/>
+      <c r="AM29" s="180"/>
+      <c r="AN29" s="180"/>
+      <c r="AO29" s="180"/>
+      <c r="AP29" s="181"/>
+      <c r="AQ29" s="181"/>
+      <c r="AR29" s="181"/>
+      <c r="AS29" s="181"/>
+      <c r="AT29" s="181"/>
+      <c r="AU29" s="181"/>
+      <c r="AV29" s="181"/>
+      <c r="AW29" s="181"/>
+      <c r="AX29" s="181"/>
+      <c r="AY29" s="181"/>
+      <c r="AZ29" s="181"/>
+      <c r="BA29" s="181"/>
     </row>
     <row r="30" spans="1:53">
-      <c r="A30" s="207"/>
-      <c r="B30" s="207"/>
-      <c r="C30" s="210"/>
-      <c r="D30" s="210"/>
-      <c r="E30" s="210"/>
-      <c r="F30" s="210"/>
-      <c r="G30" s="210"/>
-      <c r="H30" s="210"/>
-      <c r="I30" s="210"/>
-      <c r="J30" s="210"/>
-      <c r="K30" s="210"/>
-      <c r="L30" s="210"/>
-      <c r="M30" s="210"/>
-      <c r="N30" s="210"/>
-      <c r="O30" s="210"/>
-      <c r="P30" s="210"/>
-      <c r="Q30" s="210"/>
-      <c r="R30" s="210"/>
-      <c r="S30" s="210"/>
-      <c r="T30" s="210"/>
-      <c r="U30" s="210"/>
-      <c r="V30" s="210"/>
-      <c r="W30" s="210"/>
-      <c r="X30" s="210"/>
-      <c r="Y30" s="210"/>
-      <c r="Z30" s="210"/>
-      <c r="AA30" s="210"/>
-      <c r="AB30" s="210"/>
-      <c r="AC30" s="210"/>
-      <c r="AD30" s="210"/>
-      <c r="AE30" s="210"/>
-      <c r="AF30" s="210"/>
-      <c r="AG30" s="210"/>
-      <c r="AH30" s="210"/>
-      <c r="AI30" s="210"/>
-      <c r="AJ30" s="210"/>
-      <c r="AK30" s="210"/>
-      <c r="AL30" s="207"/>
-      <c r="AM30" s="207"/>
-      <c r="AN30" s="207"/>
-      <c r="AO30" s="207"/>
-      <c r="AP30" s="210"/>
-      <c r="AQ30" s="210"/>
-      <c r="AR30" s="210"/>
-      <c r="AS30" s="210"/>
-      <c r="AT30" s="210"/>
-      <c r="AU30" s="210"/>
-      <c r="AV30" s="210"/>
-      <c r="AW30" s="210"/>
-      <c r="AX30" s="210"/>
-      <c r="AY30" s="210"/>
-      <c r="AZ30" s="210"/>
-      <c r="BA30" s="210"/>
+      <c r="A30" s="180"/>
+      <c r="B30" s="180"/>
+      <c r="C30" s="181"/>
+      <c r="D30" s="181"/>
+      <c r="E30" s="181"/>
+      <c r="F30" s="181"/>
+      <c r="G30" s="181"/>
+      <c r="H30" s="181"/>
+      <c r="I30" s="181"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="181"/>
+      <c r="L30" s="181"/>
+      <c r="M30" s="181"/>
+      <c r="N30" s="181"/>
+      <c r="O30" s="181"/>
+      <c r="P30" s="181"/>
+      <c r="Q30" s="181"/>
+      <c r="R30" s="181"/>
+      <c r="S30" s="181"/>
+      <c r="T30" s="181"/>
+      <c r="U30" s="181"/>
+      <c r="V30" s="181"/>
+      <c r="W30" s="181"/>
+      <c r="X30" s="181"/>
+      <c r="Y30" s="181"/>
+      <c r="Z30" s="181"/>
+      <c r="AA30" s="181"/>
+      <c r="AB30" s="181"/>
+      <c r="AC30" s="181"/>
+      <c r="AD30" s="181"/>
+      <c r="AE30" s="181"/>
+      <c r="AF30" s="181"/>
+      <c r="AG30" s="181"/>
+      <c r="AH30" s="181"/>
+      <c r="AI30" s="181"/>
+      <c r="AJ30" s="181"/>
+      <c r="AK30" s="181"/>
+      <c r="AL30" s="180"/>
+      <c r="AM30" s="180"/>
+      <c r="AN30" s="180"/>
+      <c r="AO30" s="180"/>
+      <c r="AP30" s="181"/>
+      <c r="AQ30" s="181"/>
+      <c r="AR30" s="181"/>
+      <c r="AS30" s="181"/>
+      <c r="AT30" s="181"/>
+      <c r="AU30" s="181"/>
+      <c r="AV30" s="181"/>
+      <c r="AW30" s="181"/>
+      <c r="AX30" s="181"/>
+      <c r="AY30" s="181"/>
+      <c r="AZ30" s="181"/>
+      <c r="BA30" s="181"/>
     </row>
     <row r="31" spans="1:53">
-      <c r="A31" s="207"/>
-      <c r="B31" s="207"/>
-      <c r="C31" s="210"/>
-      <c r="D31" s="210"/>
-      <c r="E31" s="210"/>
-      <c r="F31" s="210"/>
-      <c r="G31" s="210"/>
-      <c r="H31" s="210"/>
-      <c r="I31" s="210"/>
-      <c r="J31" s="210"/>
-      <c r="K31" s="210"/>
-      <c r="L31" s="210"/>
-      <c r="M31" s="210"/>
-      <c r="N31" s="210"/>
-      <c r="O31" s="210"/>
-      <c r="P31" s="210"/>
-      <c r="Q31" s="210"/>
-      <c r="R31" s="210"/>
-      <c r="S31" s="210"/>
-      <c r="T31" s="210"/>
-      <c r="U31" s="210"/>
-      <c r="V31" s="210"/>
-      <c r="W31" s="210"/>
-      <c r="X31" s="210"/>
-      <c r="Y31" s="210"/>
-      <c r="Z31" s="210"/>
-      <c r="AA31" s="210"/>
-      <c r="AB31" s="210"/>
-      <c r="AC31" s="210"/>
-      <c r="AD31" s="210"/>
-      <c r="AE31" s="210"/>
-      <c r="AF31" s="210"/>
-      <c r="AG31" s="210"/>
-      <c r="AH31" s="210"/>
-      <c r="AI31" s="210"/>
-      <c r="AJ31" s="210"/>
-      <c r="AK31" s="210"/>
-      <c r="AL31" s="207"/>
-      <c r="AM31" s="207"/>
-      <c r="AN31" s="207"/>
-      <c r="AO31" s="207"/>
-      <c r="AP31" s="210"/>
-      <c r="AQ31" s="210"/>
-      <c r="AR31" s="210"/>
-      <c r="AS31" s="210"/>
-      <c r="AT31" s="210"/>
-      <c r="AU31" s="210"/>
-      <c r="AV31" s="210"/>
-      <c r="AW31" s="210"/>
-      <c r="AX31" s="210"/>
-      <c r="AY31" s="210"/>
-      <c r="AZ31" s="210"/>
-      <c r="BA31" s="210"/>
+      <c r="A31" s="180"/>
+      <c r="B31" s="180"/>
+      <c r="C31" s="181"/>
+      <c r="D31" s="181"/>
+      <c r="E31" s="181"/>
+      <c r="F31" s="181"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="181"/>
+      <c r="I31" s="181"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="181"/>
+      <c r="L31" s="181"/>
+      <c r="M31" s="181"/>
+      <c r="N31" s="181"/>
+      <c r="O31" s="181"/>
+      <c r="P31" s="181"/>
+      <c r="Q31" s="181"/>
+      <c r="R31" s="181"/>
+      <c r="S31" s="181"/>
+      <c r="T31" s="181"/>
+      <c r="U31" s="181"/>
+      <c r="V31" s="181"/>
+      <c r="W31" s="181"/>
+      <c r="X31" s="181"/>
+      <c r="Y31" s="181"/>
+      <c r="Z31" s="181"/>
+      <c r="AA31" s="181"/>
+      <c r="AB31" s="181"/>
+      <c r="AC31" s="181"/>
+      <c r="AD31" s="181"/>
+      <c r="AE31" s="181"/>
+      <c r="AF31" s="181"/>
+      <c r="AG31" s="181"/>
+      <c r="AH31" s="181"/>
+      <c r="AI31" s="181"/>
+      <c r="AJ31" s="181"/>
+      <c r="AK31" s="181"/>
+      <c r="AL31" s="180"/>
+      <c r="AM31" s="180"/>
+      <c r="AN31" s="180"/>
+      <c r="AO31" s="180"/>
+      <c r="AP31" s="181"/>
+      <c r="AQ31" s="181"/>
+      <c r="AR31" s="181"/>
+      <c r="AS31" s="181"/>
+      <c r="AT31" s="181"/>
+      <c r="AU31" s="181"/>
+      <c r="AV31" s="181"/>
+      <c r="AW31" s="181"/>
+      <c r="AX31" s="181"/>
+      <c r="AY31" s="181"/>
+      <c r="AZ31" s="181"/>
+      <c r="BA31" s="181"/>
     </row>
     <row r="32" spans="1:53">
-      <c r="A32" s="207"/>
-      <c r="B32" s="207"/>
-      <c r="C32" s="210"/>
-      <c r="D32" s="210"/>
-      <c r="E32" s="210"/>
-      <c r="F32" s="210"/>
-      <c r="G32" s="210"/>
-      <c r="H32" s="210"/>
-      <c r="I32" s="210"/>
-      <c r="J32" s="210"/>
-      <c r="K32" s="210"/>
-      <c r="L32" s="210"/>
-      <c r="M32" s="210"/>
-      <c r="N32" s="210"/>
-      <c r="O32" s="210"/>
-      <c r="P32" s="210"/>
-      <c r="Q32" s="210"/>
-      <c r="R32" s="210"/>
-      <c r="S32" s="210"/>
-      <c r="T32" s="210"/>
-      <c r="U32" s="210"/>
-      <c r="V32" s="210"/>
-      <c r="W32" s="210"/>
-      <c r="X32" s="210"/>
-      <c r="Y32" s="210"/>
-      <c r="Z32" s="210"/>
-      <c r="AA32" s="210"/>
-      <c r="AB32" s="210"/>
-      <c r="AC32" s="210"/>
-      <c r="AD32" s="210"/>
-      <c r="AE32" s="210"/>
-      <c r="AF32" s="210"/>
-      <c r="AG32" s="210"/>
-      <c r="AH32" s="210"/>
-      <c r="AI32" s="210"/>
-      <c r="AJ32" s="210"/>
-      <c r="AK32" s="210"/>
-      <c r="AL32" s="207"/>
-      <c r="AM32" s="207"/>
-      <c r="AN32" s="207"/>
-      <c r="AO32" s="207"/>
-      <c r="AP32" s="210"/>
-      <c r="AQ32" s="210"/>
-      <c r="AR32" s="210"/>
-      <c r="AS32" s="210"/>
-      <c r="AT32" s="210"/>
-      <c r="AU32" s="210"/>
-      <c r="AV32" s="210"/>
-      <c r="AW32" s="210"/>
-      <c r="AX32" s="210"/>
-      <c r="AY32" s="210"/>
-      <c r="AZ32" s="210"/>
-      <c r="BA32" s="210"/>
+      <c r="A32" s="180"/>
+      <c r="B32" s="180"/>
+      <c r="C32" s="181"/>
+      <c r="D32" s="181"/>
+      <c r="E32" s="181"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="181"/>
+      <c r="L32" s="181"/>
+      <c r="M32" s="181"/>
+      <c r="N32" s="181"/>
+      <c r="O32" s="181"/>
+      <c r="P32" s="181"/>
+      <c r="Q32" s="181"/>
+      <c r="R32" s="181"/>
+      <c r="S32" s="181"/>
+      <c r="T32" s="181"/>
+      <c r="U32" s="181"/>
+      <c r="V32" s="181"/>
+      <c r="W32" s="181"/>
+      <c r="X32" s="181"/>
+      <c r="Y32" s="181"/>
+      <c r="Z32" s="181"/>
+      <c r="AA32" s="181"/>
+      <c r="AB32" s="181"/>
+      <c r="AC32" s="181"/>
+      <c r="AD32" s="181"/>
+      <c r="AE32" s="181"/>
+      <c r="AF32" s="181"/>
+      <c r="AG32" s="181"/>
+      <c r="AH32" s="181"/>
+      <c r="AI32" s="181"/>
+      <c r="AJ32" s="181"/>
+      <c r="AK32" s="181"/>
+      <c r="AL32" s="180"/>
+      <c r="AM32" s="180"/>
+      <c r="AN32" s="180"/>
+      <c r="AO32" s="180"/>
+      <c r="AP32" s="181"/>
+      <c r="AQ32" s="181"/>
+      <c r="AR32" s="181"/>
+      <c r="AS32" s="181"/>
+      <c r="AT32" s="181"/>
+      <c r="AU32" s="181"/>
+      <c r="AV32" s="181"/>
+      <c r="AW32" s="181"/>
+      <c r="AX32" s="181"/>
+      <c r="AY32" s="181"/>
+      <c r="AZ32" s="181"/>
+      <c r="BA32" s="181"/>
     </row>
     <row r="33" spans="1:53">
-      <c r="A33" s="207"/>
-      <c r="B33" s="207"/>
-      <c r="C33" s="210"/>
-      <c r="D33" s="210"/>
-      <c r="E33" s="210"/>
-      <c r="F33" s="210"/>
-      <c r="G33" s="210"/>
-      <c r="H33" s="210"/>
-      <c r="I33" s="210"/>
-      <c r="J33" s="210"/>
-      <c r="K33" s="210"/>
-      <c r="L33" s="210"/>
-      <c r="M33" s="210"/>
-      <c r="N33" s="210"/>
-      <c r="O33" s="210"/>
-      <c r="P33" s="210"/>
-      <c r="Q33" s="210"/>
-      <c r="R33" s="210"/>
-      <c r="S33" s="210"/>
-      <c r="T33" s="210"/>
-      <c r="U33" s="210"/>
-      <c r="V33" s="210"/>
-      <c r="W33" s="210"/>
-      <c r="X33" s="210"/>
-      <c r="Y33" s="210"/>
-      <c r="Z33" s="210"/>
-      <c r="AA33" s="210"/>
-      <c r="AB33" s="210"/>
-      <c r="AC33" s="210"/>
-      <c r="AD33" s="210"/>
-      <c r="AE33" s="210"/>
-      <c r="AF33" s="210"/>
-      <c r="AG33" s="210"/>
-      <c r="AH33" s="210"/>
-      <c r="AI33" s="210"/>
-      <c r="AJ33" s="210"/>
-      <c r="AK33" s="210"/>
-      <c r="AL33" s="207"/>
-      <c r="AM33" s="207"/>
-      <c r="AN33" s="207"/>
-      <c r="AO33" s="207"/>
-      <c r="AP33" s="210"/>
-      <c r="AQ33" s="210"/>
-      <c r="AR33" s="210"/>
-      <c r="AS33" s="210"/>
-      <c r="AT33" s="210"/>
-      <c r="AU33" s="210"/>
-      <c r="AV33" s="210"/>
-      <c r="AW33" s="210"/>
-      <c r="AX33" s="210"/>
-      <c r="AY33" s="210"/>
-      <c r="AZ33" s="210"/>
-      <c r="BA33" s="210"/>
+      <c r="A33" s="180"/>
+      <c r="B33" s="180"/>
+      <c r="C33" s="181"/>
+      <c r="D33" s="181"/>
+      <c r="E33" s="181"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="181"/>
+      <c r="L33" s="181"/>
+      <c r="M33" s="181"/>
+      <c r="N33" s="181"/>
+      <c r="O33" s="181"/>
+      <c r="P33" s="181"/>
+      <c r="Q33" s="181"/>
+      <c r="R33" s="181"/>
+      <c r="S33" s="181"/>
+      <c r="T33" s="181"/>
+      <c r="U33" s="181"/>
+      <c r="V33" s="181"/>
+      <c r="W33" s="181"/>
+      <c r="X33" s="181"/>
+      <c r="Y33" s="181"/>
+      <c r="Z33" s="181"/>
+      <c r="AA33" s="181"/>
+      <c r="AB33" s="181"/>
+      <c r="AC33" s="181"/>
+      <c r="AD33" s="181"/>
+      <c r="AE33" s="181"/>
+      <c r="AF33" s="181"/>
+      <c r="AG33" s="181"/>
+      <c r="AH33" s="181"/>
+      <c r="AI33" s="181"/>
+      <c r="AJ33" s="181"/>
+      <c r="AK33" s="181"/>
+      <c r="AL33" s="180"/>
+      <c r="AM33" s="180"/>
+      <c r="AN33" s="180"/>
+      <c r="AO33" s="180"/>
+      <c r="AP33" s="181"/>
+      <c r="AQ33" s="181"/>
+      <c r="AR33" s="181"/>
+      <c r="AS33" s="181"/>
+      <c r="AT33" s="181"/>
+      <c r="AU33" s="181"/>
+      <c r="AV33" s="181"/>
+      <c r="AW33" s="181"/>
+      <c r="AX33" s="181"/>
+      <c r="AY33" s="181"/>
+      <c r="AZ33" s="181"/>
+      <c r="BA33" s="181"/>
     </row>
     <row r="34" spans="1:53">
-      <c r="A34" s="207"/>
-      <c r="B34" s="207"/>
-      <c r="C34" s="210"/>
-      <c r="D34" s="210"/>
-      <c r="E34" s="210"/>
-      <c r="F34" s="210"/>
-      <c r="G34" s="210"/>
-      <c r="H34" s="210"/>
-      <c r="I34" s="210"/>
-      <c r="J34" s="210"/>
-      <c r="K34" s="210"/>
-      <c r="L34" s="210"/>
-      <c r="M34" s="210"/>
-      <c r="N34" s="210"/>
-      <c r="O34" s="210"/>
-      <c r="P34" s="210"/>
-      <c r="Q34" s="210"/>
-      <c r="R34" s="210"/>
-      <c r="S34" s="210"/>
-      <c r="T34" s="210"/>
-      <c r="U34" s="210"/>
-      <c r="V34" s="210"/>
-      <c r="W34" s="210"/>
-      <c r="X34" s="210"/>
-      <c r="Y34" s="210"/>
-      <c r="Z34" s="210"/>
-      <c r="AA34" s="210"/>
-      <c r="AB34" s="210"/>
-      <c r="AC34" s="210"/>
-      <c r="AD34" s="210"/>
-      <c r="AE34" s="210"/>
-      <c r="AF34" s="210"/>
-      <c r="AG34" s="210"/>
-      <c r="AH34" s="210"/>
-      <c r="AI34" s="210"/>
-      <c r="AJ34" s="210"/>
-      <c r="AK34" s="210"/>
-      <c r="AL34" s="207"/>
-      <c r="AM34" s="207"/>
-      <c r="AN34" s="207"/>
-      <c r="AO34" s="207"/>
-      <c r="AP34" s="210"/>
-      <c r="AQ34" s="210"/>
-      <c r="AR34" s="210"/>
-      <c r="AS34" s="210"/>
-      <c r="AT34" s="210"/>
-      <c r="AU34" s="210"/>
-      <c r="AV34" s="210"/>
-      <c r="AW34" s="210"/>
-      <c r="AX34" s="210"/>
-      <c r="AY34" s="210"/>
-      <c r="AZ34" s="210"/>
-      <c r="BA34" s="210"/>
+      <c r="A34" s="180"/>
+      <c r="B34" s="180"/>
+      <c r="C34" s="181"/>
+      <c r="D34" s="181"/>
+      <c r="E34" s="181"/>
+      <c r="F34" s="181"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="181"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="181"/>
+      <c r="K34" s="181"/>
+      <c r="L34" s="181"/>
+      <c r="M34" s="181"/>
+      <c r="N34" s="181"/>
+      <c r="O34" s="181"/>
+      <c r="P34" s="181"/>
+      <c r="Q34" s="181"/>
+      <c r="R34" s="181"/>
+      <c r="S34" s="181"/>
+      <c r="T34" s="181"/>
+      <c r="U34" s="181"/>
+      <c r="V34" s="181"/>
+      <c r="W34" s="181"/>
+      <c r="X34" s="181"/>
+      <c r="Y34" s="181"/>
+      <c r="Z34" s="181"/>
+      <c r="AA34" s="181"/>
+      <c r="AB34" s="181"/>
+      <c r="AC34" s="181"/>
+      <c r="AD34" s="181"/>
+      <c r="AE34" s="181"/>
+      <c r="AF34" s="181"/>
+      <c r="AG34" s="181"/>
+      <c r="AH34" s="181"/>
+      <c r="AI34" s="181"/>
+      <c r="AJ34" s="181"/>
+      <c r="AK34" s="181"/>
+      <c r="AL34" s="180"/>
+      <c r="AM34" s="180"/>
+      <c r="AN34" s="180"/>
+      <c r="AO34" s="180"/>
+      <c r="AP34" s="181"/>
+      <c r="AQ34" s="181"/>
+      <c r="AR34" s="181"/>
+      <c r="AS34" s="181"/>
+      <c r="AT34" s="181"/>
+      <c r="AU34" s="181"/>
+      <c r="AV34" s="181"/>
+      <c r="AW34" s="181"/>
+      <c r="AX34" s="181"/>
+      <c r="AY34" s="181"/>
+      <c r="AZ34" s="181"/>
+      <c r="BA34" s="181"/>
     </row>
   </sheetData>
   <mergeCells count="229">
-    <mergeCell ref="AL22:AO22"/>
-    <mergeCell ref="AL23:AO23"/>
-    <mergeCell ref="AL24:AO24"/>
-    <mergeCell ref="AL25:AO25"/>
-    <mergeCell ref="AL26:AO26"/>
-    <mergeCell ref="Q24:AK24"/>
-    <mergeCell ref="Q25:AK25"/>
-    <mergeCell ref="Q26:AK26"/>
-    <mergeCell ref="AP14:AR14"/>
-    <mergeCell ref="Q16:AK16"/>
-    <mergeCell ref="AL16:AO16"/>
-    <mergeCell ref="AP16:AR16"/>
-    <mergeCell ref="AV20:BA20"/>
-    <mergeCell ref="AV21:BA21"/>
-    <mergeCell ref="AV14:BA14"/>
-    <mergeCell ref="AV15:BA15"/>
-    <mergeCell ref="AS28:AU28"/>
-    <mergeCell ref="AS30:AU30"/>
-    <mergeCell ref="AS31:AU31"/>
-    <mergeCell ref="AS25:AU25"/>
-    <mergeCell ref="AP31:AR31"/>
-    <mergeCell ref="AP27:AR27"/>
-    <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS16:AU16"/>
-    <mergeCell ref="AP15:AR15"/>
-    <mergeCell ref="AS26:AU26"/>
-    <mergeCell ref="AS14:AU14"/>
-    <mergeCell ref="AS15:AU15"/>
+    <mergeCell ref="AK1:AM1"/>
+    <mergeCell ref="AT3:AW3"/>
+    <mergeCell ref="AN1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="Q6:AK6"/>
+    <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AX1:BA1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:W2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AP6:AR6"/>
+    <mergeCell ref="AS6:AU6"/>
+    <mergeCell ref="AT2:AW2"/>
+    <mergeCell ref="AX2:BA3"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="AA3:AP3"/>
+    <mergeCell ref="AQ3:AS3"/>
+    <mergeCell ref="AV6:BA6"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A5:BA5"/>
+    <mergeCell ref="M1:W1"/>
+    <mergeCell ref="X1:Z2"/>
+    <mergeCell ref="AA1:AJ2"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C33:P33"/>
+    <mergeCell ref="C27:P27"/>
+    <mergeCell ref="C28:P28"/>
+    <mergeCell ref="C24:P24"/>
+    <mergeCell ref="C25:P25"/>
+    <mergeCell ref="C26:P26"/>
+    <mergeCell ref="C29:P29"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="C23:P23"/>
+    <mergeCell ref="C7:P7"/>
+    <mergeCell ref="C8:P8"/>
+    <mergeCell ref="C9:P9"/>
+    <mergeCell ref="C10:P10"/>
+    <mergeCell ref="C18:P18"/>
+    <mergeCell ref="C19:P19"/>
+    <mergeCell ref="C20:P20"/>
+    <mergeCell ref="C21:P21"/>
+    <mergeCell ref="C11:P11"/>
+    <mergeCell ref="C12:P12"/>
+    <mergeCell ref="C13:P13"/>
+    <mergeCell ref="C34:P34"/>
+    <mergeCell ref="Q7:AK7"/>
+    <mergeCell ref="Q8:AK8"/>
+    <mergeCell ref="Q9:AK9"/>
+    <mergeCell ref="Q10:AK10"/>
+    <mergeCell ref="Q11:AK11"/>
+    <mergeCell ref="Q12:AK12"/>
+    <mergeCell ref="Q19:AK19"/>
+    <mergeCell ref="Q20:AK20"/>
+    <mergeCell ref="Q21:AK21"/>
+    <mergeCell ref="Q13:AK13"/>
+    <mergeCell ref="Q34:AK34"/>
+    <mergeCell ref="Q30:AK30"/>
+    <mergeCell ref="Q31:AK31"/>
+    <mergeCell ref="Q32:AK32"/>
+    <mergeCell ref="Q33:AK33"/>
+    <mergeCell ref="Q23:AK23"/>
+    <mergeCell ref="C17:P17"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="C15:P15"/>
+    <mergeCell ref="C16:P16"/>
+    <mergeCell ref="C30:P30"/>
+    <mergeCell ref="C31:P31"/>
+    <mergeCell ref="C32:P32"/>
+    <mergeCell ref="AL29:AO29"/>
+    <mergeCell ref="AL27:AO27"/>
+    <mergeCell ref="AL28:AO28"/>
+    <mergeCell ref="Q29:AK29"/>
+    <mergeCell ref="Q27:AK27"/>
+    <mergeCell ref="Q28:AK28"/>
+    <mergeCell ref="AL7:AO7"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL17:AO17"/>
+    <mergeCell ref="AL18:AO18"/>
+    <mergeCell ref="AL19:AO19"/>
+    <mergeCell ref="AL9:AO9"/>
+    <mergeCell ref="AL10:AO10"/>
+    <mergeCell ref="AL11:AO11"/>
+    <mergeCell ref="AL12:AO12"/>
+    <mergeCell ref="AL13:AO13"/>
+    <mergeCell ref="AL21:AO21"/>
+    <mergeCell ref="Q17:AK17"/>
+    <mergeCell ref="Q18:AK18"/>
+    <mergeCell ref="Q22:AK22"/>
+    <mergeCell ref="Q14:AK14"/>
+    <mergeCell ref="AL14:AO14"/>
+    <mergeCell ref="Q15:AK15"/>
+    <mergeCell ref="AL15:AO15"/>
+    <mergeCell ref="AL32:AO32"/>
+    <mergeCell ref="AL33:AO33"/>
+    <mergeCell ref="AL34:AO34"/>
+    <mergeCell ref="AP7:AR7"/>
+    <mergeCell ref="AP8:AR8"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="AP10:AR10"/>
+    <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AP20:AR20"/>
+    <mergeCell ref="AP21:AR21"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="AP12:AR12"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AL30:AO30"/>
+    <mergeCell ref="AL31:AO31"/>
+    <mergeCell ref="AL20:AO20"/>
+    <mergeCell ref="AP26:AR26"/>
+    <mergeCell ref="AP29:AR29"/>
+    <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AP33:AR33"/>
+    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="AP34:AR34"/>
+    <mergeCell ref="AS7:AU7"/>
+    <mergeCell ref="AS8:AU8"/>
+    <mergeCell ref="AS9:AU9"/>
+    <mergeCell ref="AS10:AU10"/>
+    <mergeCell ref="AS11:AU11"/>
+    <mergeCell ref="AS12:AU12"/>
+    <mergeCell ref="AS19:AU19"/>
+    <mergeCell ref="AS20:AU20"/>
+    <mergeCell ref="AS21:AU21"/>
+    <mergeCell ref="AS13:AU13"/>
+    <mergeCell ref="AS17:AU17"/>
+    <mergeCell ref="AS18:AU18"/>
+    <mergeCell ref="AS22:AU22"/>
+    <mergeCell ref="AS23:AU23"/>
+    <mergeCell ref="AS24:AU24"/>
+    <mergeCell ref="AS29:AU29"/>
+    <mergeCell ref="AS27:AU27"/>
+    <mergeCell ref="AS32:AU32"/>
+    <mergeCell ref="AS33:AU33"/>
+    <mergeCell ref="AP24:AR24"/>
+    <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="AV7:BA7"/>
     <mergeCell ref="AV8:BA8"/>
     <mergeCell ref="AV9:BA9"/>
@@ -9230,183 +9278,34 @@
     <mergeCell ref="AV18:BA18"/>
     <mergeCell ref="AV19:BA19"/>
     <mergeCell ref="AV16:BA16"/>
-    <mergeCell ref="AS34:AU34"/>
-    <mergeCell ref="AP34:AR34"/>
-    <mergeCell ref="AS7:AU7"/>
-    <mergeCell ref="AS8:AU8"/>
-    <mergeCell ref="AS9:AU9"/>
-    <mergeCell ref="AS10:AU10"/>
-    <mergeCell ref="AS11:AU11"/>
-    <mergeCell ref="AS12:AU12"/>
-    <mergeCell ref="AS19:AU19"/>
-    <mergeCell ref="AS20:AU20"/>
-    <mergeCell ref="AS21:AU21"/>
-    <mergeCell ref="AS13:AU13"/>
-    <mergeCell ref="AS17:AU17"/>
-    <mergeCell ref="AS18:AU18"/>
-    <mergeCell ref="AS22:AU22"/>
-    <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="AS24:AU24"/>
-    <mergeCell ref="AS29:AU29"/>
-    <mergeCell ref="AS27:AU27"/>
-    <mergeCell ref="AS32:AU32"/>
-    <mergeCell ref="AS33:AU33"/>
-    <mergeCell ref="AP24:AR24"/>
-    <mergeCell ref="AP25:AR25"/>
-    <mergeCell ref="AP32:AR32"/>
-    <mergeCell ref="AL32:AO32"/>
-    <mergeCell ref="AL33:AO33"/>
-    <mergeCell ref="AL34:AO34"/>
-    <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="AP8:AR8"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="AP10:AR10"/>
-    <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="AP19:AR19"/>
-    <mergeCell ref="AP20:AR20"/>
-    <mergeCell ref="AP21:AR21"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="AP12:AR12"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="AP17:AR17"/>
-    <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AL30:AO30"/>
-    <mergeCell ref="AL31:AO31"/>
-    <mergeCell ref="AL20:AO20"/>
-    <mergeCell ref="AP26:AR26"/>
-    <mergeCell ref="AP29:AR29"/>
-    <mergeCell ref="AP30:AR30"/>
-    <mergeCell ref="AP33:AR33"/>
-    <mergeCell ref="AL29:AO29"/>
-    <mergeCell ref="AL27:AO27"/>
-    <mergeCell ref="AL28:AO28"/>
-    <mergeCell ref="Q29:AK29"/>
-    <mergeCell ref="Q27:AK27"/>
-    <mergeCell ref="Q28:AK28"/>
-    <mergeCell ref="AL7:AO7"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AL18:AO18"/>
-    <mergeCell ref="AL19:AO19"/>
-    <mergeCell ref="AL9:AO9"/>
-    <mergeCell ref="AL10:AO10"/>
-    <mergeCell ref="AL11:AO11"/>
-    <mergeCell ref="AL12:AO12"/>
-    <mergeCell ref="AL13:AO13"/>
-    <mergeCell ref="AL21:AO21"/>
-    <mergeCell ref="Q17:AK17"/>
-    <mergeCell ref="Q18:AK18"/>
-    <mergeCell ref="Q22:AK22"/>
-    <mergeCell ref="Q14:AK14"/>
-    <mergeCell ref="AL14:AO14"/>
-    <mergeCell ref="Q15:AK15"/>
-    <mergeCell ref="AL15:AO15"/>
-    <mergeCell ref="C34:P34"/>
-    <mergeCell ref="Q7:AK7"/>
-    <mergeCell ref="Q8:AK8"/>
-    <mergeCell ref="Q9:AK9"/>
-    <mergeCell ref="Q10:AK10"/>
-    <mergeCell ref="Q11:AK11"/>
-    <mergeCell ref="Q12:AK12"/>
-    <mergeCell ref="Q19:AK19"/>
-    <mergeCell ref="Q20:AK20"/>
-    <mergeCell ref="Q21:AK21"/>
-    <mergeCell ref="Q13:AK13"/>
-    <mergeCell ref="Q34:AK34"/>
-    <mergeCell ref="Q30:AK30"/>
-    <mergeCell ref="Q31:AK31"/>
-    <mergeCell ref="Q32:AK32"/>
-    <mergeCell ref="Q33:AK33"/>
-    <mergeCell ref="Q23:AK23"/>
-    <mergeCell ref="C17:P17"/>
-    <mergeCell ref="C14:P14"/>
-    <mergeCell ref="C15:P15"/>
-    <mergeCell ref="C16:P16"/>
-    <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C31:P31"/>
-    <mergeCell ref="C32:P32"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C33:P33"/>
-    <mergeCell ref="C27:P27"/>
-    <mergeCell ref="C28:P28"/>
-    <mergeCell ref="C24:P24"/>
-    <mergeCell ref="C25:P25"/>
-    <mergeCell ref="C26:P26"/>
-    <mergeCell ref="C29:P29"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="C23:P23"/>
-    <mergeCell ref="C7:P7"/>
-    <mergeCell ref="C8:P8"/>
-    <mergeCell ref="C9:P9"/>
-    <mergeCell ref="C10:P10"/>
-    <mergeCell ref="C18:P18"/>
-    <mergeCell ref="C19:P19"/>
-    <mergeCell ref="C20:P20"/>
-    <mergeCell ref="C21:P21"/>
-    <mergeCell ref="C11:P11"/>
-    <mergeCell ref="C12:P12"/>
-    <mergeCell ref="C13:P13"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="AX1:BA1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:W2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AP6:AR6"/>
-    <mergeCell ref="AS6:AU6"/>
-    <mergeCell ref="AT2:AW2"/>
-    <mergeCell ref="AX2:BA3"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="AA3:AP3"/>
-    <mergeCell ref="AQ3:AS3"/>
-    <mergeCell ref="AV6:BA6"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="A5:BA5"/>
-    <mergeCell ref="M1:W1"/>
-    <mergeCell ref="X1:Z2"/>
-    <mergeCell ref="AA1:AJ2"/>
-    <mergeCell ref="AK1:AM1"/>
-    <mergeCell ref="AT3:AW3"/>
-    <mergeCell ref="AN1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="Q6:AK6"/>
-    <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AV20:BA20"/>
+    <mergeCell ref="AV21:BA21"/>
+    <mergeCell ref="AV14:BA14"/>
+    <mergeCell ref="AV15:BA15"/>
+    <mergeCell ref="AS28:AU28"/>
+    <mergeCell ref="AS30:AU30"/>
+    <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="AS25:AU25"/>
+    <mergeCell ref="AP31:AR31"/>
+    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AS16:AU16"/>
+    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AS15:AU15"/>
+    <mergeCell ref="AL22:AO22"/>
+    <mergeCell ref="AL23:AO23"/>
+    <mergeCell ref="AL24:AO24"/>
+    <mergeCell ref="AL25:AO25"/>
+    <mergeCell ref="AL26:AO26"/>
+    <mergeCell ref="Q24:AK24"/>
+    <mergeCell ref="Q25:AK25"/>
+    <mergeCell ref="Q26:AK26"/>
+    <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="Q16:AK16"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="AP16:AR16"/>
   </mergeCells>
   <phoneticPr fontId="51"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -9434,300 +9333,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" ht="12" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="219" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="189" t="s">
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="189"/>
-      <c r="K1" s="189"/>
-      <c r="L1" s="189"/>
-      <c r="M1" s="200" t="str">
+      <c r="J1" s="202"/>
+      <c r="K1" s="202"/>
+      <c r="L1" s="202"/>
+      <c r="M1" s="217" t="str">
         <f>変更来歴!M1</f>
         <v>ヒロセ電機株式会社</v>
       </c>
-      <c r="N1" s="200"/>
-      <c r="O1" s="200"/>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="200"/>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="189" t="s">
+      <c r="N1" s="217"/>
+      <c r="O1" s="217"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="189"/>
-      <c r="AA1" s="204" t="str">
+      <c r="Y1" s="202"/>
+      <c r="Z1" s="202"/>
+      <c r="AA1" s="221" t="str">
         <f>変更来歴!AA1</f>
         <v>お知らせ登録</v>
       </c>
-      <c r="AB1" s="204"/>
-      <c r="AC1" s="204"/>
-      <c r="AD1" s="204"/>
-      <c r="AE1" s="204"/>
-      <c r="AF1" s="204"/>
-      <c r="AG1" s="204"/>
-      <c r="AH1" s="204"/>
-      <c r="AI1" s="204"/>
-      <c r="AJ1" s="204"/>
-      <c r="AK1" s="178" t="s">
+      <c r="AB1" s="221"/>
+      <c r="AC1" s="221"/>
+      <c r="AD1" s="221"/>
+      <c r="AE1" s="221"/>
+      <c r="AF1" s="221"/>
+      <c r="AG1" s="221"/>
+      <c r="AH1" s="221"/>
+      <c r="AI1" s="221"/>
+      <c r="AJ1" s="221"/>
+      <c r="AK1" s="206" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="178"/>
-      <c r="AM1" s="178"/>
-      <c r="AN1" s="180" t="str">
+      <c r="AL1" s="206"/>
+      <c r="AM1" s="206"/>
+      <c r="AN1" s="207" t="str">
         <f>変更来歴!AP7</f>
         <v>古竹</v>
       </c>
-      <c r="AO1" s="180"/>
-      <c r="AP1" s="180"/>
-      <c r="AQ1" s="180"/>
-      <c r="AR1" s="180"/>
-      <c r="AS1" s="178" t="s">
+      <c r="AO1" s="207"/>
+      <c r="AP1" s="207"/>
+      <c r="AQ1" s="207"/>
+      <c r="AR1" s="207"/>
+      <c r="AS1" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="AT1" s="178"/>
-      <c r="AU1" s="178"/>
-      <c r="AV1" s="181">
+      <c r="AT1" s="206"/>
+      <c r="AU1" s="206"/>
+      <c r="AV1" s="209">
         <f>変更来歴!AL7</f>
         <v>46163</v>
       </c>
-      <c r="AW1" s="179"/>
-      <c r="AX1" s="179"/>
-      <c r="AY1" s="179"/>
-      <c r="AZ1" s="185" t="s">
+      <c r="AW1" s="222"/>
+      <c r="AX1" s="222"/>
+      <c r="AY1" s="222"/>
+      <c r="AZ1" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="BA1" s="186"/>
-      <c r="BB1" s="186"/>
-      <c r="BC1" s="187"/>
+      <c r="BA1" s="199"/>
+      <c r="BB1" s="199"/>
+      <c r="BC1" s="200"/>
     </row>
     <row r="2" spans="1:78">
-      <c r="A2" s="188" t="s">
+      <c r="A2" s="201" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="188"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="188"/>
-      <c r="I2" s="189" t="s">
+      <c r="B2" s="201"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="201"/>
+      <c r="G2" s="201"/>
+      <c r="H2" s="201"/>
+      <c r="I2" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="189"/>
-      <c r="K2" s="189"/>
-      <c r="L2" s="189"/>
-      <c r="M2" s="224" t="str">
+      <c r="J2" s="202"/>
+      <c r="K2" s="202"/>
+      <c r="L2" s="202"/>
+      <c r="M2" s="225" t="str">
         <f>変更来歴!M2</f>
         <v>新環境証明書</v>
       </c>
-      <c r="N2" s="224"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="224"/>
-      <c r="Q2" s="224"/>
-      <c r="R2" s="224"/>
-      <c r="S2" s="224"/>
-      <c r="T2" s="224"/>
-      <c r="U2" s="224"/>
-      <c r="V2" s="224"/>
-      <c r="W2" s="224"/>
-      <c r="X2" s="189"/>
-      <c r="Y2" s="189"/>
-      <c r="Z2" s="189"/>
-      <c r="AA2" s="204"/>
-      <c r="AB2" s="204"/>
-      <c r="AC2" s="204"/>
-      <c r="AD2" s="204"/>
-      <c r="AE2" s="204"/>
-      <c r="AF2" s="204"/>
-      <c r="AG2" s="204"/>
-      <c r="AH2" s="204"/>
-      <c r="AI2" s="204"/>
-      <c r="AJ2" s="204"/>
-      <c r="AK2" s="178" t="s">
+      <c r="N2" s="225"/>
+      <c r="O2" s="225"/>
+      <c r="P2" s="225"/>
+      <c r="Q2" s="225"/>
+      <c r="R2" s="225"/>
+      <c r="S2" s="225"/>
+      <c r="T2" s="225"/>
+      <c r="U2" s="225"/>
+      <c r="V2" s="225"/>
+      <c r="W2" s="225"/>
+      <c r="X2" s="202"/>
+      <c r="Y2" s="202"/>
+      <c r="Z2" s="202"/>
+      <c r="AA2" s="221"/>
+      <c r="AB2" s="221"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="221"/>
+      <c r="AE2" s="221"/>
+      <c r="AF2" s="221"/>
+      <c r="AG2" s="221"/>
+      <c r="AH2" s="221"/>
+      <c r="AI2" s="221"/>
+      <c r="AJ2" s="221"/>
+      <c r="AK2" s="206" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="178"/>
-      <c r="AM2" s="178"/>
-      <c r="AN2" s="180" t="str">
+      <c r="AL2" s="206"/>
+      <c r="AM2" s="206"/>
+      <c r="AN2" s="207" t="str">
         <f ca="1">INDIRECT("変更来歴!AP" &amp; COUNTA(変更来歴!AP7:'変更来歴'!AP39) + 6)</f>
         <v>古竹</v>
       </c>
-      <c r="AO2" s="180"/>
-      <c r="AP2" s="180"/>
-      <c r="AQ2" s="180"/>
-      <c r="AR2" s="180"/>
-      <c r="AS2" s="178" t="s">
+      <c r="AO2" s="207"/>
+      <c r="AP2" s="207"/>
+      <c r="AQ2" s="207"/>
+      <c r="AR2" s="207"/>
+      <c r="AS2" s="206" t="s">
         <v>13</v>
       </c>
-      <c r="AT2" s="178"/>
-      <c r="AU2" s="178"/>
-      <c r="AV2" s="181">
+      <c r="AT2" s="206"/>
+      <c r="AU2" s="206"/>
+      <c r="AV2" s="209">
         <f ca="1">INDIRECT("変更来歴!AL" &amp; COUNTA(変更来歴!AL7:'変更来歴'!AL39) + 6)</f>
-        <v>46163</v>
+        <v>46177</v>
       </c>
-      <c r="AW2" s="179"/>
-      <c r="AX2" s="179"/>
-      <c r="AY2" s="179"/>
-      <c r="AZ2" s="193" t="str">
+      <c r="AW2" s="222"/>
+      <c r="AX2" s="222"/>
+      <c r="AY2" s="222"/>
+      <c r="AZ2" s="210" t="str">
         <f>変更来歴!AX2</f>
         <v>IMWF-53</v>
       </c>
-      <c r="BA2" s="194"/>
-      <c r="BB2" s="194"/>
-      <c r="BC2" s="195"/>
+      <c r="BA2" s="211"/>
+      <c r="BB2" s="211"/>
+      <c r="BC2" s="212"/>
     </row>
     <row r="3" spans="1:78" ht="12" customHeight="1">
-      <c r="A3" s="199" t="str">
+      <c r="A3" s="216" t="str">
         <f>変更来歴!A3</f>
         <v>画面設計書</v>
       </c>
-      <c r="B3" s="199"/>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="189" t="s">
+      <c r="B3" s="216"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="216"/>
+      <c r="E3" s="216"/>
+      <c r="F3" s="216"/>
+      <c r="G3" s="216"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="189"/>
-      <c r="K3" s="189"/>
-      <c r="L3" s="189"/>
-      <c r="M3" s="200" t="str">
+      <c r="J3" s="202"/>
+      <c r="K3" s="202"/>
+      <c r="L3" s="202"/>
+      <c r="M3" s="217" t="str">
         <f ca="1">RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1)))</f>
         <v>お知らせ登録画面</v>
       </c>
-      <c r="N3" s="200"/>
-      <c r="O3" s="200"/>
-      <c r="P3" s="200"/>
-      <c r="Q3" s="200"/>
-      <c r="R3" s="200"/>
-      <c r="S3" s="200"/>
-      <c r="T3" s="200"/>
-      <c r="U3" s="200"/>
-      <c r="V3" s="200"/>
-      <c r="W3" s="200"/>
-      <c r="X3" s="189" t="s">
+      <c r="N3" s="217"/>
+      <c r="O3" s="217"/>
+      <c r="P3" s="217"/>
+      <c r="Q3" s="217"/>
+      <c r="R3" s="217"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="202" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="189"/>
-      <c r="Z3" s="189"/>
-      <c r="AA3" s="201" t="str">
+      <c r="Y3" s="202"/>
+      <c r="Z3" s="202"/>
+      <c r="AA3" s="218" t="str">
         <f ca="1">MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename"))) &amp; "画面"</f>
-        <v>お知らせ登録画面画面</v>
+        <v>変更来歴画面</v>
       </c>
-      <c r="AB3" s="201"/>
-      <c r="AC3" s="201"/>
-      <c r="AD3" s="201"/>
-      <c r="AE3" s="201"/>
-      <c r="AF3" s="201"/>
-      <c r="AG3" s="201"/>
-      <c r="AH3" s="201"/>
-      <c r="AI3" s="201"/>
-      <c r="AJ3" s="201"/>
-      <c r="AK3" s="201"/>
-      <c r="AL3" s="201"/>
-      <c r="AM3" s="201"/>
-      <c r="AN3" s="201"/>
-      <c r="AO3" s="201"/>
-      <c r="AP3" s="201"/>
-      <c r="AQ3" s="201"/>
-      <c r="AR3" s="201"/>
-      <c r="AS3" s="178" t="s">
+      <c r="AB3" s="218"/>
+      <c r="AC3" s="218"/>
+      <c r="AD3" s="218"/>
+      <c r="AE3" s="218"/>
+      <c r="AF3" s="218"/>
+      <c r="AG3" s="218"/>
+      <c r="AH3" s="218"/>
+      <c r="AI3" s="218"/>
+      <c r="AJ3" s="218"/>
+      <c r="AK3" s="218"/>
+      <c r="AL3" s="218"/>
+      <c r="AM3" s="218"/>
+      <c r="AN3" s="218"/>
+      <c r="AO3" s="218"/>
+      <c r="AP3" s="218"/>
+      <c r="AQ3" s="218"/>
+      <c r="AR3" s="218"/>
+      <c r="AS3" s="206" t="s">
         <v>15</v>
       </c>
-      <c r="AT3" s="178"/>
-      <c r="AU3" s="178"/>
-      <c r="AV3" s="179" t="str">
+      <c r="AT3" s="206"/>
+      <c r="AU3" s="206"/>
+      <c r="AV3" s="222" t="str">
         <f ca="1">INDIRECT("変更来歴!A" &amp; COUNTA(変更来歴!A7:'変更来歴'!A39) + 6)</f>
-        <v>ｒ1.0</v>
+        <v>ｒ1.1</v>
       </c>
-      <c r="AW3" s="179"/>
-      <c r="AX3" s="179"/>
-      <c r="AY3" s="179"/>
-      <c r="AZ3" s="196"/>
-      <c r="BA3" s="197"/>
-      <c r="BB3" s="197"/>
-      <c r="BC3" s="198"/>
+      <c r="AW3" s="222"/>
+      <c r="AX3" s="222"/>
+      <c r="AY3" s="222"/>
+      <c r="AZ3" s="213"/>
+      <c r="BA3" s="214"/>
+      <c r="BB3" s="214"/>
+      <c r="BC3" s="215"/>
     </row>
     <row r="4" spans="1:78" ht="5.9" customHeight="1"/>
     <row r="5" spans="1:78" ht="13.5" customHeight="1">
-      <c r="A5" s="228" t="str">
+      <c r="A5" s="229" t="str">
         <f ca="1">"画面レイアウト"&amp;"("&amp;MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename")))&amp;")"</f>
-        <v>画面レイアウト(お知らせ登録画面)</v>
+        <v>画面レイアウト(変更来歴)</v>
       </c>
-      <c r="B5" s="229"/>
-      <c r="C5" s="229"/>
-      <c r="D5" s="229"/>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="229"/>
-      <c r="J5" s="229"/>
-      <c r="K5" s="229"/>
-      <c r="L5" s="229"/>
-      <c r="M5" s="229"/>
-      <c r="N5" s="229"/>
-      <c r="O5" s="229"/>
-      <c r="P5" s="229"/>
-      <c r="Q5" s="229"/>
-      <c r="R5" s="229"/>
-      <c r="S5" s="229"/>
-      <c r="T5" s="229"/>
-      <c r="U5" s="229"/>
-      <c r="V5" s="229"/>
-      <c r="W5" s="229"/>
-      <c r="X5" s="229"/>
-      <c r="Y5" s="229"/>
-      <c r="Z5" s="229"/>
-      <c r="AA5" s="229"/>
-      <c r="AB5" s="229"/>
-      <c r="AC5" s="229"/>
-      <c r="AD5" s="229"/>
-      <c r="AE5" s="229"/>
-      <c r="AF5" s="229"/>
-      <c r="AG5" s="229"/>
-      <c r="AH5" s="229"/>
-      <c r="AI5" s="229"/>
-      <c r="AJ5" s="229"/>
-      <c r="AK5" s="229"/>
-      <c r="AL5" s="229"/>
-      <c r="AM5" s="229"/>
-      <c r="AN5" s="229"/>
-      <c r="AO5" s="229"/>
-      <c r="AP5" s="229"/>
-      <c r="AQ5" s="229"/>
-      <c r="AR5" s="229"/>
-      <c r="AS5" s="229"/>
-      <c r="AT5" s="229"/>
-      <c r="AU5" s="229"/>
-      <c r="AV5" s="229"/>
-      <c r="AW5" s="229"/>
-      <c r="AX5" s="229"/>
-      <c r="AY5" s="229"/>
-      <c r="AZ5" s="229"/>
-      <c r="BA5" s="230"/>
-      <c r="BB5" s="231" t="s">
+      <c r="B5" s="230"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="230"/>
+      <c r="E5" s="230"/>
+      <c r="F5" s="230"/>
+      <c r="G5" s="230"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="230"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="230"/>
+      <c r="L5" s="230"/>
+      <c r="M5" s="230"/>
+      <c r="N5" s="230"/>
+      <c r="O5" s="230"/>
+      <c r="P5" s="230"/>
+      <c r="Q5" s="230"/>
+      <c r="R5" s="230"/>
+      <c r="S5" s="230"/>
+      <c r="T5" s="230"/>
+      <c r="U5" s="230"/>
+      <c r="V5" s="230"/>
+      <c r="W5" s="230"/>
+      <c r="X5" s="230"/>
+      <c r="Y5" s="230"/>
+      <c r="Z5" s="230"/>
+      <c r="AA5" s="230"/>
+      <c r="AB5" s="230"/>
+      <c r="AC5" s="230"/>
+      <c r="AD5" s="230"/>
+      <c r="AE5" s="230"/>
+      <c r="AF5" s="230"/>
+      <c r="AG5" s="230"/>
+      <c r="AH5" s="230"/>
+      <c r="AI5" s="230"/>
+      <c r="AJ5" s="230"/>
+      <c r="AK5" s="230"/>
+      <c r="AL5" s="230"/>
+      <c r="AM5" s="230"/>
+      <c r="AN5" s="230"/>
+      <c r="AO5" s="230"/>
+      <c r="AP5" s="230"/>
+      <c r="AQ5" s="230"/>
+      <c r="AR5" s="230"/>
+      <c r="AS5" s="230"/>
+      <c r="AT5" s="230"/>
+      <c r="AU5" s="230"/>
+      <c r="AV5" s="230"/>
+      <c r="AW5" s="230"/>
+      <c r="AX5" s="230"/>
+      <c r="AY5" s="230"/>
+      <c r="AZ5" s="230"/>
+      <c r="BA5" s="231"/>
+      <c r="BB5" s="232" t="s">
         <v>24</v>
       </c>
-      <c r="BC5" s="232"/>
+      <c r="BC5" s="233"/>
       <c r="BD5" s="24"/>
     </row>
     <row r="6" spans="1:78" ht="13.5" customHeight="1">
@@ -9947,11 +9846,11 @@
       <c r="BB7" s="36"/>
       <c r="BC7" s="37"/>
       <c r="BD7" s="34"/>
-      <c r="BE7" s="225" t="s">
+      <c r="BE7" s="226" t="s">
         <v>54</v>
       </c>
-      <c r="BF7" s="226"/>
-      <c r="BG7" s="227"/>
+      <c r="BF7" s="227"/>
+      <c r="BG7" s="228"/>
       <c r="BH7" s="43"/>
       <c r="BI7" s="43"/>
       <c r="BJ7" s="43"/>
@@ -10025,8 +9924,8 @@
       <c r="BB8" s="36"/>
       <c r="BC8" s="37"/>
       <c r="BD8" s="34"/>
-      <c r="BE8" s="150" t="s">
-        <v>69</v>
+      <c r="BE8" s="172" t="s">
+        <v>80</v>
       </c>
       <c r="BF8" s="170"/>
       <c r="BG8" s="170"/>
@@ -10107,9 +10006,7 @@
       <c r="BB9" s="32"/>
       <c r="BC9" s="33"/>
       <c r="BD9" s="34"/>
-      <c r="BE9" s="150" t="s">
-        <v>68</v>
-      </c>
+      <c r="BE9" s="150"/>
       <c r="BF9" s="41"/>
       <c r="BG9" s="41"/>
       <c r="BH9" s="45"/>
@@ -23670,18 +23567,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AV1:AY1"/>
-    <mergeCell ref="AZ1:BC1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:W2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="BE7:BG7"/>
-    <mergeCell ref="A5:BA5"/>
-    <mergeCell ref="BB5:BC5"/>
     <mergeCell ref="AK1:AM1"/>
     <mergeCell ref="AV2:AY2"/>
     <mergeCell ref="AZ2:BC3"/>
@@ -23698,6 +23583,18 @@
     <mergeCell ref="X1:Z2"/>
     <mergeCell ref="AA1:AJ2"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:W2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="BE7:BG7"/>
+    <mergeCell ref="A5:BA5"/>
+    <mergeCell ref="BB5:BC5"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AV1:AY1"/>
+    <mergeCell ref="AZ1:BC1"/>
+    <mergeCell ref="AS2:AU2"/>
   </mergeCells>
   <phoneticPr fontId="55"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -23977,17 +23874,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" ht="12.75" customHeight="1">
-      <c r="A1" s="233" t="s">
+      <c r="A1" s="262" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
+      <c r="I1" s="262"/>
       <c r="J1" s="136"/>
       <c r="K1" s="136"/>
       <c r="L1" s="136"/>
@@ -24059,530 +23956,530 @@
       <c r="BZ1" s="137"/>
     </row>
     <row r="2" spans="1:78" ht="12.75" customHeight="1">
-      <c r="A2" s="234" t="s">
+      <c r="A2" s="263" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="234"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="234"/>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="M2" s="234"/>
-      <c r="N2" s="234"/>
-      <c r="O2" s="234"/>
-      <c r="P2" s="234"/>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235"/>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
-      <c r="AD2" s="235"/>
-      <c r="AE2" s="235"/>
-      <c r="AF2" s="235"/>
-      <c r="AG2" s="235"/>
-      <c r="AH2" s="235"/>
-      <c r="AI2" s="235"/>
-      <c r="AJ2" s="235"/>
-      <c r="AK2" s="235"/>
-      <c r="AL2" s="235"/>
-      <c r="AM2" s="235"/>
-      <c r="AN2" s="235"/>
-      <c r="AO2" s="235"/>
-      <c r="AP2" s="235"/>
-      <c r="AQ2" s="235"/>
-      <c r="AR2" s="235"/>
-      <c r="AS2" s="235"/>
-      <c r="AT2" s="235"/>
-      <c r="AU2" s="235"/>
-      <c r="AV2" s="235"/>
-      <c r="AW2" s="235"/>
-      <c r="AX2" s="235"/>
-      <c r="AY2" s="235"/>
-      <c r="AZ2" s="235"/>
-      <c r="BA2" s="235"/>
-      <c r="BB2" s="235"/>
-      <c r="BC2" s="235"/>
-      <c r="BD2" s="235"/>
-      <c r="BE2" s="235"/>
-      <c r="BF2" s="235"/>
-      <c r="BG2" s="235"/>
-      <c r="BH2" s="235"/>
-      <c r="BI2" s="235"/>
-      <c r="BJ2" s="235"/>
-      <c r="BK2" s="235"/>
-      <c r="BL2" s="235"/>
-      <c r="BM2" s="235"/>
-      <c r="BN2" s="235"/>
-      <c r="BO2" s="235"/>
-      <c r="BP2" s="235"/>
-      <c r="BQ2" s="235"/>
-      <c r="BR2" s="235"/>
-      <c r="BS2" s="235"/>
-      <c r="BT2" s="235"/>
-      <c r="BU2" s="235"/>
-      <c r="BV2" s="235"/>
-      <c r="BW2" s="235"/>
-      <c r="BX2" s="235"/>
-      <c r="BY2" s="235"/>
-      <c r="BZ2" s="235"/>
+      <c r="B2" s="263"/>
+      <c r="C2" s="263"/>
+      <c r="D2" s="263"/>
+      <c r="E2" s="263"/>
+      <c r="F2" s="263"/>
+      <c r="G2" s="263"/>
+      <c r="H2" s="263"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="263"/>
+      <c r="L2" s="263"/>
+      <c r="M2" s="263"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="263"/>
+      <c r="P2" s="263"/>
+      <c r="Q2" s="264"/>
+      <c r="R2" s="264"/>
+      <c r="S2" s="264"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="264"/>
+      <c r="V2" s="264"/>
+      <c r="W2" s="264"/>
+      <c r="X2" s="264"/>
+      <c r="Y2" s="264"/>
+      <c r="Z2" s="264"/>
+      <c r="AA2" s="264"/>
+      <c r="AB2" s="264"/>
+      <c r="AC2" s="264"/>
+      <c r="AD2" s="264"/>
+      <c r="AE2" s="264"/>
+      <c r="AF2" s="264"/>
+      <c r="AG2" s="264"/>
+      <c r="AH2" s="264"/>
+      <c r="AI2" s="264"/>
+      <c r="AJ2" s="264"/>
+      <c r="AK2" s="264"/>
+      <c r="AL2" s="264"/>
+      <c r="AM2" s="264"/>
+      <c r="AN2" s="264"/>
+      <c r="AO2" s="264"/>
+      <c r="AP2" s="264"/>
+      <c r="AQ2" s="264"/>
+      <c r="AR2" s="264"/>
+      <c r="AS2" s="264"/>
+      <c r="AT2" s="264"/>
+      <c r="AU2" s="264"/>
+      <c r="AV2" s="264"/>
+      <c r="AW2" s="264"/>
+      <c r="AX2" s="264"/>
+      <c r="AY2" s="264"/>
+      <c r="AZ2" s="264"/>
+      <c r="BA2" s="264"/>
+      <c r="BB2" s="264"/>
+      <c r="BC2" s="264"/>
+      <c r="BD2" s="264"/>
+      <c r="BE2" s="264"/>
+      <c r="BF2" s="264"/>
+      <c r="BG2" s="264"/>
+      <c r="BH2" s="264"/>
+      <c r="BI2" s="264"/>
+      <c r="BJ2" s="264"/>
+      <c r="BK2" s="264"/>
+      <c r="BL2" s="264"/>
+      <c r="BM2" s="264"/>
+      <c r="BN2" s="264"/>
+      <c r="BO2" s="264"/>
+      <c r="BP2" s="264"/>
+      <c r="BQ2" s="264"/>
+      <c r="BR2" s="264"/>
+      <c r="BS2" s="264"/>
+      <c r="BT2" s="264"/>
+      <c r="BU2" s="264"/>
+      <c r="BV2" s="264"/>
+      <c r="BW2" s="264"/>
+      <c r="BX2" s="264"/>
+      <c r="BY2" s="264"/>
+      <c r="BZ2" s="264"/>
     </row>
     <row r="3" spans="1:78" ht="27.75" customHeight="1">
-      <c r="A3" s="236" t="s">
+      <c r="A3" s="265" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="237"/>
-      <c r="C3" s="237" t="s">
+      <c r="B3" s="266"/>
+      <c r="C3" s="266" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="237"/>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="M3" s="237"/>
-      <c r="N3" s="237"/>
-      <c r="O3" s="237"/>
-      <c r="P3" s="237"/>
-      <c r="Q3" s="238" t="s">
+      <c r="D3" s="266"/>
+      <c r="E3" s="266"/>
+      <c r="F3" s="266"/>
+      <c r="G3" s="266"/>
+      <c r="H3" s="266"/>
+      <c r="I3" s="266"/>
+      <c r="J3" s="266"/>
+      <c r="K3" s="266"/>
+      <c r="L3" s="266"/>
+      <c r="M3" s="266"/>
+      <c r="N3" s="266"/>
+      <c r="O3" s="266"/>
+      <c r="P3" s="266"/>
+      <c r="Q3" s="267" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="239"/>
-      <c r="S3" s="239"/>
-      <c r="T3" s="239"/>
-      <c r="U3" s="239"/>
-      <c r="V3" s="239"/>
-      <c r="W3" s="239"/>
-      <c r="X3" s="239"/>
-      <c r="Y3" s="239"/>
-      <c r="Z3" s="239"/>
-      <c r="AA3" s="240"/>
-      <c r="AB3" s="238" t="s">
+      <c r="R3" s="268"/>
+      <c r="S3" s="268"/>
+      <c r="T3" s="268"/>
+      <c r="U3" s="268"/>
+      <c r="V3" s="268"/>
+      <c r="W3" s="268"/>
+      <c r="X3" s="268"/>
+      <c r="Y3" s="268"/>
+      <c r="Z3" s="268"/>
+      <c r="AA3" s="269"/>
+      <c r="AB3" s="267" t="s">
         <v>43</v>
       </c>
-      <c r="AC3" s="239"/>
-      <c r="AD3" s="239"/>
-      <c r="AE3" s="239"/>
-      <c r="AF3" s="239"/>
-      <c r="AG3" s="239"/>
-      <c r="AH3" s="239"/>
-      <c r="AI3" s="238" t="s">
+      <c r="AC3" s="268"/>
+      <c r="AD3" s="268"/>
+      <c r="AE3" s="268"/>
+      <c r="AF3" s="268"/>
+      <c r="AG3" s="268"/>
+      <c r="AH3" s="268"/>
+      <c r="AI3" s="267" t="s">
         <v>55</v>
       </c>
-      <c r="AJ3" s="239"/>
-      <c r="AK3" s="239"/>
-      <c r="AL3" s="239"/>
-      <c r="AM3" s="239"/>
-      <c r="AN3" s="239"/>
-      <c r="AO3" s="239"/>
-      <c r="AP3" s="239"/>
-      <c r="AQ3" s="239"/>
-      <c r="AR3" s="236" t="s">
+      <c r="AJ3" s="268"/>
+      <c r="AK3" s="268"/>
+      <c r="AL3" s="268"/>
+      <c r="AM3" s="268"/>
+      <c r="AN3" s="268"/>
+      <c r="AO3" s="268"/>
+      <c r="AP3" s="268"/>
+      <c r="AQ3" s="268"/>
+      <c r="AR3" s="265" t="s">
         <v>37</v>
       </c>
-      <c r="AS3" s="236"/>
-      <c r="AT3" s="236"/>
-      <c r="AU3" s="236"/>
-      <c r="AV3" s="236"/>
-      <c r="AW3" s="236"/>
-      <c r="AX3" s="236"/>
-      <c r="AY3" s="236"/>
-      <c r="AZ3" s="236"/>
-      <c r="BA3" s="236"/>
-      <c r="BB3" s="236"/>
-      <c r="BC3" s="236"/>
-      <c r="BD3" s="236"/>
-      <c r="BE3" s="236"/>
-      <c r="BF3" s="236"/>
-      <c r="BG3" s="236"/>
-      <c r="BH3" s="236"/>
-      <c r="BI3" s="236"/>
-      <c r="BJ3" s="236"/>
-      <c r="BK3" s="236"/>
-      <c r="BL3" s="236"/>
-      <c r="BM3" s="236"/>
-      <c r="BN3" s="236"/>
-      <c r="BO3" s="236"/>
-      <c r="BP3" s="236"/>
-      <c r="BQ3" s="236"/>
-      <c r="BR3" s="236"/>
-      <c r="BS3" s="236"/>
-      <c r="BT3" s="236"/>
-      <c r="BU3" s="236"/>
-      <c r="BV3" s="236"/>
-      <c r="BW3" s="236"/>
-      <c r="BX3" s="236"/>
-      <c r="BY3" s="236"/>
-      <c r="BZ3" s="236"/>
+      <c r="AS3" s="265"/>
+      <c r="AT3" s="265"/>
+      <c r="AU3" s="265"/>
+      <c r="AV3" s="265"/>
+      <c r="AW3" s="265"/>
+      <c r="AX3" s="265"/>
+      <c r="AY3" s="265"/>
+      <c r="AZ3" s="265"/>
+      <c r="BA3" s="265"/>
+      <c r="BB3" s="265"/>
+      <c r="BC3" s="265"/>
+      <c r="BD3" s="265"/>
+      <c r="BE3" s="265"/>
+      <c r="BF3" s="265"/>
+      <c r="BG3" s="265"/>
+      <c r="BH3" s="265"/>
+      <c r="BI3" s="265"/>
+      <c r="BJ3" s="265"/>
+      <c r="BK3" s="265"/>
+      <c r="BL3" s="265"/>
+      <c r="BM3" s="265"/>
+      <c r="BN3" s="265"/>
+      <c r="BO3" s="265"/>
+      <c r="BP3" s="265"/>
+      <c r="BQ3" s="265"/>
+      <c r="BR3" s="265"/>
+      <c r="BS3" s="265"/>
+      <c r="BT3" s="265"/>
+      <c r="BU3" s="265"/>
+      <c r="BV3" s="265"/>
+      <c r="BW3" s="265"/>
+      <c r="BX3" s="265"/>
+      <c r="BY3" s="265"/>
+      <c r="BZ3" s="265"/>
     </row>
     <row r="4" spans="1:78" ht="27.75" customHeight="1">
-      <c r="A4" s="237"/>
-      <c r="B4" s="237"/>
-      <c r="C4" s="244" t="s">
+      <c r="A4" s="266"/>
+      <c r="B4" s="266"/>
+      <c r="C4" s="273" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244" t="s">
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="J4" s="273" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244"/>
-      <c r="N4" s="244"/>
-      <c r="O4" s="244"/>
-      <c r="P4" s="244"/>
-      <c r="Q4" s="241"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
-      <c r="AA4" s="243"/>
-      <c r="AB4" s="241"/>
-      <c r="AC4" s="242"/>
-      <c r="AD4" s="242"/>
-      <c r="AE4" s="242"/>
-      <c r="AF4" s="242"/>
-      <c r="AG4" s="242"/>
-      <c r="AH4" s="242"/>
-      <c r="AI4" s="241"/>
-      <c r="AJ4" s="242"/>
-      <c r="AK4" s="242"/>
-      <c r="AL4" s="242"/>
-      <c r="AM4" s="242"/>
-      <c r="AN4" s="242"/>
-      <c r="AO4" s="242"/>
-      <c r="AP4" s="242"/>
-      <c r="AQ4" s="242"/>
-      <c r="AR4" s="236"/>
-      <c r="AS4" s="236"/>
-      <c r="AT4" s="236"/>
-      <c r="AU4" s="236"/>
-      <c r="AV4" s="236"/>
-      <c r="AW4" s="236"/>
-      <c r="AX4" s="236"/>
-      <c r="AY4" s="236"/>
-      <c r="AZ4" s="236"/>
-      <c r="BA4" s="236"/>
-      <c r="BB4" s="236"/>
-      <c r="BC4" s="236"/>
-      <c r="BD4" s="236"/>
-      <c r="BE4" s="236"/>
-      <c r="BF4" s="236"/>
-      <c r="BG4" s="236"/>
-      <c r="BH4" s="236"/>
-      <c r="BI4" s="236"/>
-      <c r="BJ4" s="236"/>
-      <c r="BK4" s="236"/>
-      <c r="BL4" s="236"/>
-      <c r="BM4" s="236"/>
-      <c r="BN4" s="236"/>
-      <c r="BO4" s="236"/>
-      <c r="BP4" s="236"/>
-      <c r="BQ4" s="236"/>
-      <c r="BR4" s="236"/>
-      <c r="BS4" s="236"/>
-      <c r="BT4" s="236"/>
-      <c r="BU4" s="236"/>
-      <c r="BV4" s="236"/>
-      <c r="BW4" s="236"/>
-      <c r="BX4" s="236"/>
-      <c r="BY4" s="236"/>
-      <c r="BZ4" s="236"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
+      <c r="M4" s="273"/>
+      <c r="N4" s="273"/>
+      <c r="O4" s="273"/>
+      <c r="P4" s="273"/>
+      <c r="Q4" s="270"/>
+      <c r="R4" s="271"/>
+      <c r="S4" s="271"/>
+      <c r="T4" s="271"/>
+      <c r="U4" s="271"/>
+      <c r="V4" s="271"/>
+      <c r="W4" s="271"/>
+      <c r="X4" s="271"/>
+      <c r="Y4" s="271"/>
+      <c r="Z4" s="271"/>
+      <c r="AA4" s="272"/>
+      <c r="AB4" s="270"/>
+      <c r="AC4" s="271"/>
+      <c r="AD4" s="271"/>
+      <c r="AE4" s="271"/>
+      <c r="AF4" s="271"/>
+      <c r="AG4" s="271"/>
+      <c r="AH4" s="271"/>
+      <c r="AI4" s="270"/>
+      <c r="AJ4" s="271"/>
+      <c r="AK4" s="271"/>
+      <c r="AL4" s="271"/>
+      <c r="AM4" s="271"/>
+      <c r="AN4" s="271"/>
+      <c r="AO4" s="271"/>
+      <c r="AP4" s="271"/>
+      <c r="AQ4" s="271"/>
+      <c r="AR4" s="265"/>
+      <c r="AS4" s="265"/>
+      <c r="AT4" s="265"/>
+      <c r="AU4" s="265"/>
+      <c r="AV4" s="265"/>
+      <c r="AW4" s="265"/>
+      <c r="AX4" s="265"/>
+      <c r="AY4" s="265"/>
+      <c r="AZ4" s="265"/>
+      <c r="BA4" s="265"/>
+      <c r="BB4" s="265"/>
+      <c r="BC4" s="265"/>
+      <c r="BD4" s="265"/>
+      <c r="BE4" s="265"/>
+      <c r="BF4" s="265"/>
+      <c r="BG4" s="265"/>
+      <c r="BH4" s="265"/>
+      <c r="BI4" s="265"/>
+      <c r="BJ4" s="265"/>
+      <c r="BK4" s="265"/>
+      <c r="BL4" s="265"/>
+      <c r="BM4" s="265"/>
+      <c r="BN4" s="265"/>
+      <c r="BO4" s="265"/>
+      <c r="BP4" s="265"/>
+      <c r="BQ4" s="265"/>
+      <c r="BR4" s="265"/>
+      <c r="BS4" s="265"/>
+      <c r="BT4" s="265"/>
+      <c r="BU4" s="265"/>
+      <c r="BV4" s="265"/>
+      <c r="BW4" s="265"/>
+      <c r="BX4" s="265"/>
+      <c r="BY4" s="265"/>
+      <c r="BZ4" s="265"/>
     </row>
     <row r="5" spans="1:78" ht="40" customHeight="1">
-      <c r="A5" s="248" t="s">
+      <c r="A5" s="242" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="249"/>
-      <c r="C5" s="250" t="s">
+      <c r="B5" s="243"/>
+      <c r="C5" s="259" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="251"/>
-      <c r="E5" s="251"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="252"/>
-      <c r="J5" s="253"/>
-      <c r="K5" s="254"/>
-      <c r="L5" s="254"/>
-      <c r="M5" s="254"/>
-      <c r="N5" s="254"/>
-      <c r="O5" s="254"/>
-      <c r="P5" s="255"/>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
-      <c r="AA5" s="258"/>
-      <c r="AB5" s="259"/>
-      <c r="AC5" s="246"/>
-      <c r="AD5" s="246"/>
-      <c r="AE5" s="246"/>
-      <c r="AF5" s="246"/>
-      <c r="AG5" s="246"/>
-      <c r="AH5" s="246"/>
-      <c r="AI5" s="259"/>
-      <c r="AJ5" s="246"/>
-      <c r="AK5" s="246"/>
-      <c r="AL5" s="246"/>
-      <c r="AM5" s="246"/>
-      <c r="AN5" s="246"/>
-      <c r="AO5" s="246"/>
-      <c r="AP5" s="246"/>
-      <c r="AQ5" s="246"/>
-      <c r="AR5" s="245" t="s">
-        <v>78</v>
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="260"/>
+      <c r="G5" s="260"/>
+      <c r="H5" s="260"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="256"/>
+      <c r="K5" s="257"/>
+      <c r="L5" s="257"/>
+      <c r="M5" s="257"/>
+      <c r="N5" s="257"/>
+      <c r="O5" s="257"/>
+      <c r="P5" s="258"/>
+      <c r="Q5" s="239"/>
+      <c r="R5" s="240"/>
+      <c r="S5" s="240"/>
+      <c r="T5" s="240"/>
+      <c r="U5" s="240"/>
+      <c r="V5" s="240"/>
+      <c r="W5" s="240"/>
+      <c r="X5" s="240"/>
+      <c r="Y5" s="240"/>
+      <c r="Z5" s="240"/>
+      <c r="AA5" s="241"/>
+      <c r="AB5" s="250"/>
+      <c r="AC5" s="237"/>
+      <c r="AD5" s="237"/>
+      <c r="AE5" s="237"/>
+      <c r="AF5" s="237"/>
+      <c r="AG5" s="237"/>
+      <c r="AH5" s="237"/>
+      <c r="AI5" s="250"/>
+      <c r="AJ5" s="237"/>
+      <c r="AK5" s="237"/>
+      <c r="AL5" s="237"/>
+      <c r="AM5" s="237"/>
+      <c r="AN5" s="237"/>
+      <c r="AO5" s="237"/>
+      <c r="AP5" s="237"/>
+      <c r="AQ5" s="237"/>
+      <c r="AR5" s="236" t="s">
+        <v>83</v>
       </c>
-      <c r="AS5" s="246"/>
-      <c r="AT5" s="246"/>
-      <c r="AU5" s="246"/>
-      <c r="AV5" s="246"/>
-      <c r="AW5" s="246"/>
-      <c r="AX5" s="246"/>
-      <c r="AY5" s="246"/>
-      <c r="AZ5" s="246"/>
-      <c r="BA5" s="246"/>
-      <c r="BB5" s="246"/>
-      <c r="BC5" s="246"/>
-      <c r="BD5" s="246"/>
-      <c r="BE5" s="246"/>
-      <c r="BF5" s="246"/>
-      <c r="BG5" s="246"/>
-      <c r="BH5" s="246"/>
-      <c r="BI5" s="246"/>
-      <c r="BJ5" s="246"/>
-      <c r="BK5" s="246"/>
-      <c r="BL5" s="246"/>
-      <c r="BM5" s="246"/>
-      <c r="BN5" s="246"/>
-      <c r="BO5" s="246"/>
-      <c r="BP5" s="246"/>
-      <c r="BQ5" s="246"/>
-      <c r="BR5" s="246"/>
-      <c r="BS5" s="246"/>
-      <c r="BT5" s="246"/>
-      <c r="BU5" s="246"/>
-      <c r="BV5" s="246"/>
-      <c r="BW5" s="246"/>
-      <c r="BX5" s="246"/>
-      <c r="BY5" s="246"/>
-      <c r="BZ5" s="247"/>
+      <c r="AS5" s="237"/>
+      <c r="AT5" s="237"/>
+      <c r="AU5" s="237"/>
+      <c r="AV5" s="237"/>
+      <c r="AW5" s="237"/>
+      <c r="AX5" s="237"/>
+      <c r="AY5" s="237"/>
+      <c r="AZ5" s="237"/>
+      <c r="BA5" s="237"/>
+      <c r="BB5" s="237"/>
+      <c r="BC5" s="237"/>
+      <c r="BD5" s="237"/>
+      <c r="BE5" s="237"/>
+      <c r="BF5" s="237"/>
+      <c r="BG5" s="237"/>
+      <c r="BH5" s="237"/>
+      <c r="BI5" s="237"/>
+      <c r="BJ5" s="237"/>
+      <c r="BK5" s="237"/>
+      <c r="BL5" s="237"/>
+      <c r="BM5" s="237"/>
+      <c r="BN5" s="237"/>
+      <c r="BO5" s="237"/>
+      <c r="BP5" s="237"/>
+      <c r="BQ5" s="237"/>
+      <c r="BR5" s="237"/>
+      <c r="BS5" s="237"/>
+      <c r="BT5" s="237"/>
+      <c r="BU5" s="237"/>
+      <c r="BV5" s="237"/>
+      <c r="BW5" s="237"/>
+      <c r="BX5" s="237"/>
+      <c r="BY5" s="237"/>
+      <c r="BZ5" s="238"/>
     </row>
     <row r="6" spans="1:78">
-      <c r="A6" s="248" t="s">
+      <c r="A6" s="242" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="249"/>
-      <c r="C6" s="250"/>
-      <c r="D6" s="251"/>
-      <c r="E6" s="251"/>
-      <c r="F6" s="251"/>
-      <c r="G6" s="251"/>
-      <c r="H6" s="251"/>
-      <c r="I6" s="252"/>
-      <c r="J6" s="253" t="s">
+      <c r="B6" s="243"/>
+      <c r="C6" s="259"/>
+      <c r="D6" s="260"/>
+      <c r="E6" s="260"/>
+      <c r="F6" s="260"/>
+      <c r="G6" s="260"/>
+      <c r="H6" s="260"/>
+      <c r="I6" s="261"/>
+      <c r="J6" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="K6" s="254"/>
-      <c r="L6" s="254"/>
-      <c r="M6" s="254"/>
-      <c r="N6" s="254"/>
-      <c r="O6" s="254"/>
-      <c r="P6" s="255"/>
-      <c r="Q6" s="256" t="s">
-        <v>71</v>
+      <c r="K6" s="257"/>
+      <c r="L6" s="257"/>
+      <c r="M6" s="257"/>
+      <c r="N6" s="257"/>
+      <c r="O6" s="257"/>
+      <c r="P6" s="258"/>
+      <c r="Q6" s="239" t="s">
+        <v>69</v>
       </c>
-      <c r="R6" s="257"/>
-      <c r="S6" s="257"/>
-      <c r="T6" s="257"/>
-      <c r="U6" s="257"/>
-      <c r="V6" s="257"/>
-      <c r="W6" s="257"/>
-      <c r="X6" s="257"/>
-      <c r="Y6" s="257"/>
-      <c r="Z6" s="257"/>
-      <c r="AA6" s="258"/>
-      <c r="AB6" s="259"/>
-      <c r="AC6" s="246"/>
-      <c r="AD6" s="246"/>
-      <c r="AE6" s="246"/>
-      <c r="AF6" s="246"/>
-      <c r="AG6" s="246"/>
-      <c r="AH6" s="246"/>
-      <c r="AI6" s="259"/>
-      <c r="AJ6" s="246"/>
-      <c r="AK6" s="246"/>
-      <c r="AL6" s="246"/>
-      <c r="AM6" s="246"/>
-      <c r="AN6" s="246"/>
-      <c r="AO6" s="246"/>
-      <c r="AP6" s="246"/>
-      <c r="AQ6" s="246"/>
-      <c r="AR6" s="245" t="s">
+      <c r="R6" s="240"/>
+      <c r="S6" s="240"/>
+      <c r="T6" s="240"/>
+      <c r="U6" s="240"/>
+      <c r="V6" s="240"/>
+      <c r="W6" s="240"/>
+      <c r="X6" s="240"/>
+      <c r="Y6" s="240"/>
+      <c r="Z6" s="240"/>
+      <c r="AA6" s="241"/>
+      <c r="AB6" s="250"/>
+      <c r="AC6" s="237"/>
+      <c r="AD6" s="237"/>
+      <c r="AE6" s="237"/>
+      <c r="AF6" s="237"/>
+      <c r="AG6" s="237"/>
+      <c r="AH6" s="237"/>
+      <c r="AI6" s="250"/>
+      <c r="AJ6" s="237"/>
+      <c r="AK6" s="237"/>
+      <c r="AL6" s="237"/>
+      <c r="AM6" s="237"/>
+      <c r="AN6" s="237"/>
+      <c r="AO6" s="237"/>
+      <c r="AP6" s="237"/>
+      <c r="AQ6" s="237"/>
+      <c r="AR6" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="AS6" s="246"/>
-      <c r="AT6" s="246"/>
-      <c r="AU6" s="246"/>
-      <c r="AV6" s="246"/>
-      <c r="AW6" s="246"/>
-      <c r="AX6" s="246"/>
-      <c r="AY6" s="246"/>
-      <c r="AZ6" s="246"/>
-      <c r="BA6" s="246"/>
-      <c r="BB6" s="246"/>
-      <c r="BC6" s="246"/>
-      <c r="BD6" s="246"/>
-      <c r="BE6" s="246"/>
-      <c r="BF6" s="246"/>
-      <c r="BG6" s="246"/>
-      <c r="BH6" s="246"/>
-      <c r="BI6" s="246"/>
-      <c r="BJ6" s="246"/>
-      <c r="BK6" s="246"/>
-      <c r="BL6" s="246"/>
-      <c r="BM6" s="246"/>
-      <c r="BN6" s="246"/>
-      <c r="BO6" s="246"/>
-      <c r="BP6" s="246"/>
-      <c r="BQ6" s="246"/>
-      <c r="BR6" s="246"/>
-      <c r="BS6" s="246"/>
-      <c r="BT6" s="246"/>
-      <c r="BU6" s="246"/>
-      <c r="BV6" s="246"/>
-      <c r="BW6" s="246"/>
-      <c r="BX6" s="246"/>
-      <c r="BY6" s="246"/>
-      <c r="BZ6" s="247"/>
+      <c r="AS6" s="237"/>
+      <c r="AT6" s="237"/>
+      <c r="AU6" s="237"/>
+      <c r="AV6" s="237"/>
+      <c r="AW6" s="237"/>
+      <c r="AX6" s="237"/>
+      <c r="AY6" s="237"/>
+      <c r="AZ6" s="237"/>
+      <c r="BA6" s="237"/>
+      <c r="BB6" s="237"/>
+      <c r="BC6" s="237"/>
+      <c r="BD6" s="237"/>
+      <c r="BE6" s="237"/>
+      <c r="BF6" s="237"/>
+      <c r="BG6" s="237"/>
+      <c r="BH6" s="237"/>
+      <c r="BI6" s="237"/>
+      <c r="BJ6" s="237"/>
+      <c r="BK6" s="237"/>
+      <c r="BL6" s="237"/>
+      <c r="BM6" s="237"/>
+      <c r="BN6" s="237"/>
+      <c r="BO6" s="237"/>
+      <c r="BP6" s="237"/>
+      <c r="BQ6" s="237"/>
+      <c r="BR6" s="237"/>
+      <c r="BS6" s="237"/>
+      <c r="BT6" s="237"/>
+      <c r="BU6" s="237"/>
+      <c r="BV6" s="237"/>
+      <c r="BW6" s="237"/>
+      <c r="BX6" s="237"/>
+      <c r="BY6" s="237"/>
+      <c r="BZ6" s="238"/>
     </row>
     <row r="7" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A7" s="268">
+      <c r="A7" s="254">
         <v>1.2</v>
       </c>
-      <c r="B7" s="269"/>
-      <c r="C7" s="260"/>
-      <c r="D7" s="261"/>
-      <c r="E7" s="261"/>
-      <c r="F7" s="261"/>
-      <c r="G7" s="261"/>
-      <c r="H7" s="261"/>
-      <c r="I7" s="262"/>
-      <c r="J7" s="253" t="s">
+      <c r="B7" s="255"/>
+      <c r="C7" s="244"/>
+      <c r="D7" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
+      <c r="I7" s="246"/>
+      <c r="J7" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="K7" s="254"/>
-      <c r="L7" s="254"/>
-      <c r="M7" s="254"/>
-      <c r="N7" s="254"/>
-      <c r="O7" s="254"/>
-      <c r="P7" s="255"/>
-      <c r="Q7" s="256" t="s">
-        <v>71</v>
+      <c r="K7" s="257"/>
+      <c r="L7" s="257"/>
+      <c r="M7" s="257"/>
+      <c r="N7" s="257"/>
+      <c r="O7" s="257"/>
+      <c r="P7" s="258"/>
+      <c r="Q7" s="239" t="s">
+        <v>69</v>
       </c>
-      <c r="R7" s="257"/>
-      <c r="S7" s="257"/>
-      <c r="T7" s="257"/>
-      <c r="U7" s="257"/>
-      <c r="V7" s="257"/>
-      <c r="W7" s="257"/>
-      <c r="X7" s="257"/>
-      <c r="Y7" s="257"/>
-      <c r="Z7" s="257"/>
-      <c r="AA7" s="258"/>
-      <c r="AB7" s="259"/>
-      <c r="AC7" s="246"/>
-      <c r="AD7" s="246"/>
-      <c r="AE7" s="246"/>
-      <c r="AF7" s="246"/>
-      <c r="AG7" s="246"/>
-      <c r="AH7" s="246"/>
-      <c r="AI7" s="259"/>
-      <c r="AJ7" s="246"/>
-      <c r="AK7" s="246"/>
-      <c r="AL7" s="246"/>
-      <c r="AM7" s="246"/>
-      <c r="AN7" s="246"/>
-      <c r="AO7" s="246"/>
-      <c r="AP7" s="246"/>
-      <c r="AQ7" s="246"/>
-      <c r="AR7" s="245" t="s">
+      <c r="R7" s="240"/>
+      <c r="S7" s="240"/>
+      <c r="T7" s="240"/>
+      <c r="U7" s="240"/>
+      <c r="V7" s="240"/>
+      <c r="W7" s="240"/>
+      <c r="X7" s="240"/>
+      <c r="Y7" s="240"/>
+      <c r="Z7" s="240"/>
+      <c r="AA7" s="241"/>
+      <c r="AB7" s="250"/>
+      <c r="AC7" s="237"/>
+      <c r="AD7" s="237"/>
+      <c r="AE7" s="237"/>
+      <c r="AF7" s="237"/>
+      <c r="AG7" s="237"/>
+      <c r="AH7" s="237"/>
+      <c r="AI7" s="250"/>
+      <c r="AJ7" s="237"/>
+      <c r="AK7" s="237"/>
+      <c r="AL7" s="237"/>
+      <c r="AM7" s="237"/>
+      <c r="AN7" s="237"/>
+      <c r="AO7" s="237"/>
+      <c r="AP7" s="237"/>
+      <c r="AQ7" s="237"/>
+      <c r="AR7" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="AS7" s="246"/>
-      <c r="AT7" s="246"/>
-      <c r="AU7" s="246"/>
-      <c r="AV7" s="246"/>
-      <c r="AW7" s="246"/>
-      <c r="AX7" s="246"/>
-      <c r="AY7" s="246"/>
-      <c r="AZ7" s="246"/>
-      <c r="BA7" s="246"/>
-      <c r="BB7" s="246"/>
-      <c r="BC7" s="246"/>
-      <c r="BD7" s="246"/>
-      <c r="BE7" s="246"/>
-      <c r="BF7" s="246"/>
-      <c r="BG7" s="246"/>
-      <c r="BH7" s="246"/>
-      <c r="BI7" s="246"/>
-      <c r="BJ7" s="246"/>
-      <c r="BK7" s="246"/>
-      <c r="BL7" s="246"/>
-      <c r="BM7" s="246"/>
-      <c r="BN7" s="246"/>
-      <c r="BO7" s="246"/>
-      <c r="BP7" s="246"/>
-      <c r="BQ7" s="246"/>
-      <c r="BR7" s="246"/>
-      <c r="BS7" s="246"/>
-      <c r="BT7" s="246"/>
-      <c r="BU7" s="246"/>
-      <c r="BV7" s="246"/>
-      <c r="BW7" s="246"/>
-      <c r="BX7" s="246"/>
-      <c r="BY7" s="246"/>
-      <c r="BZ7" s="247"/>
+      <c r="AS7" s="237"/>
+      <c r="AT7" s="237"/>
+      <c r="AU7" s="237"/>
+      <c r="AV7" s="237"/>
+      <c r="AW7" s="237"/>
+      <c r="AX7" s="237"/>
+      <c r="AY7" s="237"/>
+      <c r="AZ7" s="237"/>
+      <c r="BA7" s="237"/>
+      <c r="BB7" s="237"/>
+      <c r="BC7" s="237"/>
+      <c r="BD7" s="237"/>
+      <c r="BE7" s="237"/>
+      <c r="BF7" s="237"/>
+      <c r="BG7" s="237"/>
+      <c r="BH7" s="237"/>
+      <c r="BI7" s="237"/>
+      <c r="BJ7" s="237"/>
+      <c r="BK7" s="237"/>
+      <c r="BL7" s="237"/>
+      <c r="BM7" s="237"/>
+      <c r="BN7" s="237"/>
+      <c r="BO7" s="237"/>
+      <c r="BP7" s="237"/>
+      <c r="BQ7" s="237"/>
+      <c r="BR7" s="237"/>
+      <c r="BS7" s="237"/>
+      <c r="BT7" s="237"/>
+      <c r="BU7" s="237"/>
+      <c r="BV7" s="237"/>
+      <c r="BW7" s="237"/>
+      <c r="BX7" s="237"/>
+      <c r="BY7" s="237"/>
+      <c r="BZ7" s="238"/>
     </row>
     <row r="8" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A8" s="248" t="s">
+      <c r="A8" s="242" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="249"/>
+      <c r="B8" s="243"/>
       <c r="C8" s="139"/>
       <c r="D8" s="140"/>
       <c r="E8" s="140"/>
@@ -24590,85 +24487,85 @@
       <c r="G8" s="140"/>
       <c r="H8" s="140"/>
       <c r="I8" s="141"/>
-      <c r="J8" s="260" t="s">
+      <c r="J8" s="244" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="261"/>
-      <c r="L8" s="261"/>
-      <c r="M8" s="261"/>
-      <c r="N8" s="261"/>
-      <c r="O8" s="261"/>
-      <c r="P8" s="262"/>
-      <c r="Q8" s="265"/>
-      <c r="R8" s="266"/>
-      <c r="S8" s="266"/>
-      <c r="T8" s="266"/>
-      <c r="U8" s="266"/>
-      <c r="V8" s="266"/>
-      <c r="W8" s="266"/>
-      <c r="X8" s="266"/>
-      <c r="Y8" s="266"/>
-      <c r="Z8" s="266"/>
-      <c r="AA8" s="267"/>
-      <c r="AB8" s="263"/>
-      <c r="AC8" s="264"/>
-      <c r="AD8" s="264"/>
-      <c r="AE8" s="264"/>
-      <c r="AF8" s="264"/>
-      <c r="AG8" s="264"/>
-      <c r="AH8" s="264"/>
-      <c r="AI8" s="263"/>
-      <c r="AJ8" s="264"/>
-      <c r="AK8" s="264"/>
-      <c r="AL8" s="264"/>
-      <c r="AM8" s="264"/>
-      <c r="AN8" s="264"/>
-      <c r="AO8" s="264"/>
-      <c r="AP8" s="264"/>
-      <c r="AQ8" s="264"/>
-      <c r="AR8" s="245" t="s">
+      <c r="K8" s="245"/>
+      <c r="L8" s="245"/>
+      <c r="M8" s="245"/>
+      <c r="N8" s="245"/>
+      <c r="O8" s="245"/>
+      <c r="P8" s="246"/>
+      <c r="Q8" s="247"/>
+      <c r="R8" s="248"/>
+      <c r="S8" s="248"/>
+      <c r="T8" s="248"/>
+      <c r="U8" s="248"/>
+      <c r="V8" s="248"/>
+      <c r="W8" s="248"/>
+      <c r="X8" s="248"/>
+      <c r="Y8" s="248"/>
+      <c r="Z8" s="248"/>
+      <c r="AA8" s="249"/>
+      <c r="AB8" s="234"/>
+      <c r="AC8" s="235"/>
+      <c r="AD8" s="235"/>
+      <c r="AE8" s="235"/>
+      <c r="AF8" s="235"/>
+      <c r="AG8" s="235"/>
+      <c r="AH8" s="235"/>
+      <c r="AI8" s="234"/>
+      <c r="AJ8" s="235"/>
+      <c r="AK8" s="235"/>
+      <c r="AL8" s="235"/>
+      <c r="AM8" s="235"/>
+      <c r="AN8" s="235"/>
+      <c r="AO8" s="235"/>
+      <c r="AP8" s="235"/>
+      <c r="AQ8" s="235"/>
+      <c r="AR8" s="236" t="s">
         <v>63</v>
       </c>
-      <c r="AS8" s="246"/>
-      <c r="AT8" s="246"/>
-      <c r="AU8" s="246"/>
-      <c r="AV8" s="246"/>
-      <c r="AW8" s="246"/>
-      <c r="AX8" s="246"/>
-      <c r="AY8" s="246"/>
-      <c r="AZ8" s="246"/>
-      <c r="BA8" s="246"/>
-      <c r="BB8" s="246"/>
-      <c r="BC8" s="246"/>
-      <c r="BD8" s="246"/>
-      <c r="BE8" s="246"/>
-      <c r="BF8" s="246"/>
-      <c r="BG8" s="246"/>
-      <c r="BH8" s="246"/>
-      <c r="BI8" s="246"/>
-      <c r="BJ8" s="246"/>
-      <c r="BK8" s="246"/>
-      <c r="BL8" s="246"/>
-      <c r="BM8" s="246"/>
-      <c r="BN8" s="246"/>
-      <c r="BO8" s="246"/>
-      <c r="BP8" s="246"/>
-      <c r="BQ8" s="246"/>
-      <c r="BR8" s="246"/>
-      <c r="BS8" s="246"/>
-      <c r="BT8" s="246"/>
-      <c r="BU8" s="246"/>
-      <c r="BV8" s="246"/>
-      <c r="BW8" s="246"/>
-      <c r="BX8" s="246"/>
-      <c r="BY8" s="246"/>
-      <c r="BZ8" s="247"/>
+      <c r="AS8" s="237"/>
+      <c r="AT8" s="237"/>
+      <c r="AU8" s="237"/>
+      <c r="AV8" s="237"/>
+      <c r="AW8" s="237"/>
+      <c r="AX8" s="237"/>
+      <c r="AY8" s="237"/>
+      <c r="AZ8" s="237"/>
+      <c r="BA8" s="237"/>
+      <c r="BB8" s="237"/>
+      <c r="BC8" s="237"/>
+      <c r="BD8" s="237"/>
+      <c r="BE8" s="237"/>
+      <c r="BF8" s="237"/>
+      <c r="BG8" s="237"/>
+      <c r="BH8" s="237"/>
+      <c r="BI8" s="237"/>
+      <c r="BJ8" s="237"/>
+      <c r="BK8" s="237"/>
+      <c r="BL8" s="237"/>
+      <c r="BM8" s="237"/>
+      <c r="BN8" s="237"/>
+      <c r="BO8" s="237"/>
+      <c r="BP8" s="237"/>
+      <c r="BQ8" s="237"/>
+      <c r="BR8" s="237"/>
+      <c r="BS8" s="237"/>
+      <c r="BT8" s="237"/>
+      <c r="BU8" s="237"/>
+      <c r="BV8" s="237"/>
+      <c r="BW8" s="237"/>
+      <c r="BX8" s="237"/>
+      <c r="BY8" s="237"/>
+      <c r="BZ8" s="238"/>
     </row>
     <row r="9" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A9" s="248" t="s">
+      <c r="A9" s="242" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="249"/>
+      <c r="B9" s="243"/>
       <c r="C9" s="139"/>
       <c r="D9" s="140"/>
       <c r="E9" s="140"/>
@@ -24676,343 +24573,343 @@
       <c r="G9" s="140"/>
       <c r="H9" s="140"/>
       <c r="I9" s="141"/>
-      <c r="J9" s="260" t="s">
+      <c r="J9" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="261"/>
-      <c r="L9" s="261"/>
-      <c r="M9" s="261"/>
-      <c r="N9" s="261"/>
-      <c r="O9" s="261"/>
-      <c r="P9" s="262"/>
-      <c r="Q9" s="265"/>
-      <c r="R9" s="266"/>
-      <c r="S9" s="266"/>
-      <c r="T9" s="266"/>
-      <c r="U9" s="266"/>
-      <c r="V9" s="266"/>
-      <c r="W9" s="266"/>
-      <c r="X9" s="266"/>
-      <c r="Y9" s="266"/>
-      <c r="Z9" s="266"/>
-      <c r="AA9" s="267"/>
-      <c r="AB9" s="263"/>
-      <c r="AC9" s="264"/>
-      <c r="AD9" s="264"/>
-      <c r="AE9" s="264"/>
-      <c r="AF9" s="264"/>
-      <c r="AG9" s="264"/>
-      <c r="AH9" s="264"/>
-      <c r="AI9" s="263"/>
-      <c r="AJ9" s="264"/>
-      <c r="AK9" s="264"/>
-      <c r="AL9" s="264"/>
-      <c r="AM9" s="264"/>
-      <c r="AN9" s="264"/>
-      <c r="AO9" s="264"/>
-      <c r="AP9" s="264"/>
-      <c r="AQ9" s="264"/>
-      <c r="AR9" s="245"/>
-      <c r="AS9" s="246"/>
-      <c r="AT9" s="246"/>
-      <c r="AU9" s="246"/>
-      <c r="AV9" s="246"/>
-      <c r="AW9" s="246"/>
-      <c r="AX9" s="246"/>
-      <c r="AY9" s="246"/>
-      <c r="AZ9" s="246"/>
-      <c r="BA9" s="246"/>
-      <c r="BB9" s="246"/>
-      <c r="BC9" s="246"/>
-      <c r="BD9" s="246"/>
-      <c r="BE9" s="246"/>
-      <c r="BF9" s="246"/>
-      <c r="BG9" s="246"/>
-      <c r="BH9" s="246"/>
-      <c r="BI9" s="246"/>
-      <c r="BJ9" s="246"/>
-      <c r="BK9" s="246"/>
-      <c r="BL9" s="246"/>
-      <c r="BM9" s="246"/>
-      <c r="BN9" s="246"/>
-      <c r="BO9" s="246"/>
-      <c r="BP9" s="246"/>
-      <c r="BQ9" s="246"/>
-      <c r="BR9" s="246"/>
-      <c r="BS9" s="246"/>
-      <c r="BT9" s="246"/>
-      <c r="BU9" s="246"/>
-      <c r="BV9" s="246"/>
-      <c r="BW9" s="246"/>
-      <c r="BX9" s="246"/>
-      <c r="BY9" s="246"/>
-      <c r="BZ9" s="247"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
+      <c r="M9" s="245"/>
+      <c r="N9" s="245"/>
+      <c r="O9" s="245"/>
+      <c r="P9" s="246"/>
+      <c r="Q9" s="247"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
+      <c r="AA9" s="249"/>
+      <c r="AB9" s="234"/>
+      <c r="AC9" s="235"/>
+      <c r="AD9" s="235"/>
+      <c r="AE9" s="235"/>
+      <c r="AF9" s="235"/>
+      <c r="AG9" s="235"/>
+      <c r="AH9" s="235"/>
+      <c r="AI9" s="234"/>
+      <c r="AJ9" s="235"/>
+      <c r="AK9" s="235"/>
+      <c r="AL9" s="235"/>
+      <c r="AM9" s="235"/>
+      <c r="AN9" s="235"/>
+      <c r="AO9" s="235"/>
+      <c r="AP9" s="235"/>
+      <c r="AQ9" s="235"/>
+      <c r="AR9" s="236"/>
+      <c r="AS9" s="237"/>
+      <c r="AT9" s="237"/>
+      <c r="AU9" s="237"/>
+      <c r="AV9" s="237"/>
+      <c r="AW9" s="237"/>
+      <c r="AX9" s="237"/>
+      <c r="AY9" s="237"/>
+      <c r="AZ9" s="237"/>
+      <c r="BA9" s="237"/>
+      <c r="BB9" s="237"/>
+      <c r="BC9" s="237"/>
+      <c r="BD9" s="237"/>
+      <c r="BE9" s="237"/>
+      <c r="BF9" s="237"/>
+      <c r="BG9" s="237"/>
+      <c r="BH9" s="237"/>
+      <c r="BI9" s="237"/>
+      <c r="BJ9" s="237"/>
+      <c r="BK9" s="237"/>
+      <c r="BL9" s="237"/>
+      <c r="BM9" s="237"/>
+      <c r="BN9" s="237"/>
+      <c r="BO9" s="237"/>
+      <c r="BP9" s="237"/>
+      <c r="BQ9" s="237"/>
+      <c r="BR9" s="237"/>
+      <c r="BS9" s="237"/>
+      <c r="BT9" s="237"/>
+      <c r="BU9" s="237"/>
+      <c r="BV9" s="237"/>
+      <c r="BW9" s="237"/>
+      <c r="BX9" s="237"/>
+      <c r="BY9" s="237"/>
+      <c r="BZ9" s="238"/>
     </row>
     <row r="10" spans="1:78" ht="26" customHeight="1">
-      <c r="A10" s="248" t="s">
+      <c r="A10" s="242" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="249"/>
-      <c r="C10" s="250" t="s">
+      <c r="B10" s="243"/>
+      <c r="C10" s="259" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="251"/>
-      <c r="E10" s="251"/>
-      <c r="F10" s="251"/>
-      <c r="G10" s="251"/>
-      <c r="H10" s="251"/>
-      <c r="I10" s="252"/>
-      <c r="J10" s="253"/>
-      <c r="K10" s="254"/>
-      <c r="L10" s="254"/>
-      <c r="M10" s="254"/>
-      <c r="N10" s="254"/>
-      <c r="O10" s="254"/>
-      <c r="P10" s="255"/>
-      <c r="Q10" s="265"/>
-      <c r="R10" s="266"/>
-      <c r="S10" s="266"/>
-      <c r="T10" s="266"/>
-      <c r="U10" s="266"/>
-      <c r="V10" s="266"/>
-      <c r="W10" s="266"/>
-      <c r="X10" s="266"/>
-      <c r="Y10" s="266"/>
-      <c r="Z10" s="266"/>
-      <c r="AA10" s="267"/>
-      <c r="AB10" s="263"/>
-      <c r="AC10" s="264"/>
-      <c r="AD10" s="264"/>
-      <c r="AE10" s="264"/>
-      <c r="AF10" s="264"/>
-      <c r="AG10" s="264"/>
-      <c r="AH10" s="264"/>
-      <c r="AI10" s="263"/>
-      <c r="AJ10" s="264"/>
-      <c r="AK10" s="264"/>
-      <c r="AL10" s="264"/>
-      <c r="AM10" s="264"/>
-      <c r="AN10" s="264"/>
-      <c r="AO10" s="264"/>
-      <c r="AP10" s="264"/>
-      <c r="AQ10" s="264"/>
-      <c r="AR10" s="245"/>
-      <c r="AS10" s="246"/>
-      <c r="AT10" s="246"/>
-      <c r="AU10" s="246"/>
-      <c r="AV10" s="246"/>
-      <c r="AW10" s="246"/>
-      <c r="AX10" s="246"/>
-      <c r="AY10" s="246"/>
-      <c r="AZ10" s="246"/>
-      <c r="BA10" s="246"/>
-      <c r="BB10" s="246"/>
-      <c r="BC10" s="246"/>
-      <c r="BD10" s="246"/>
-      <c r="BE10" s="246"/>
-      <c r="BF10" s="246"/>
-      <c r="BG10" s="246"/>
-      <c r="BH10" s="246"/>
-      <c r="BI10" s="246"/>
-      <c r="BJ10" s="246"/>
-      <c r="BK10" s="246"/>
-      <c r="BL10" s="246"/>
-      <c r="BM10" s="246"/>
-      <c r="BN10" s="246"/>
-      <c r="BO10" s="246"/>
-      <c r="BP10" s="246"/>
-      <c r="BQ10" s="246"/>
-      <c r="BR10" s="246"/>
-      <c r="BS10" s="246"/>
-      <c r="BT10" s="246"/>
-      <c r="BU10" s="246"/>
-      <c r="BV10" s="246"/>
-      <c r="BW10" s="246"/>
-      <c r="BX10" s="246"/>
-      <c r="BY10" s="246"/>
-      <c r="BZ10" s="247"/>
+      <c r="D10" s="260"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="260"/>
+      <c r="I10" s="261"/>
+      <c r="J10" s="256"/>
+      <c r="K10" s="257"/>
+      <c r="L10" s="257"/>
+      <c r="M10" s="257"/>
+      <c r="N10" s="257"/>
+      <c r="O10" s="257"/>
+      <c r="P10" s="258"/>
+      <c r="Q10" s="247"/>
+      <c r="R10" s="248"/>
+      <c r="S10" s="248"/>
+      <c r="T10" s="248"/>
+      <c r="U10" s="248"/>
+      <c r="V10" s="248"/>
+      <c r="W10" s="248"/>
+      <c r="X10" s="248"/>
+      <c r="Y10" s="248"/>
+      <c r="Z10" s="248"/>
+      <c r="AA10" s="249"/>
+      <c r="AB10" s="234"/>
+      <c r="AC10" s="235"/>
+      <c r="AD10" s="235"/>
+      <c r="AE10" s="235"/>
+      <c r="AF10" s="235"/>
+      <c r="AG10" s="235"/>
+      <c r="AH10" s="235"/>
+      <c r="AI10" s="234"/>
+      <c r="AJ10" s="235"/>
+      <c r="AK10" s="235"/>
+      <c r="AL10" s="235"/>
+      <c r="AM10" s="235"/>
+      <c r="AN10" s="235"/>
+      <c r="AO10" s="235"/>
+      <c r="AP10" s="235"/>
+      <c r="AQ10" s="235"/>
+      <c r="AR10" s="236"/>
+      <c r="AS10" s="237"/>
+      <c r="AT10" s="237"/>
+      <c r="AU10" s="237"/>
+      <c r="AV10" s="237"/>
+      <c r="AW10" s="237"/>
+      <c r="AX10" s="237"/>
+      <c r="AY10" s="237"/>
+      <c r="AZ10" s="237"/>
+      <c r="BA10" s="237"/>
+      <c r="BB10" s="237"/>
+      <c r="BC10" s="237"/>
+      <c r="BD10" s="237"/>
+      <c r="BE10" s="237"/>
+      <c r="BF10" s="237"/>
+      <c r="BG10" s="237"/>
+      <c r="BH10" s="237"/>
+      <c r="BI10" s="237"/>
+      <c r="BJ10" s="237"/>
+      <c r="BK10" s="237"/>
+      <c r="BL10" s="237"/>
+      <c r="BM10" s="237"/>
+      <c r="BN10" s="237"/>
+      <c r="BO10" s="237"/>
+      <c r="BP10" s="237"/>
+      <c r="BQ10" s="237"/>
+      <c r="BR10" s="237"/>
+      <c r="BS10" s="237"/>
+      <c r="BT10" s="237"/>
+      <c r="BU10" s="237"/>
+      <c r="BV10" s="237"/>
+      <c r="BW10" s="237"/>
+      <c r="BX10" s="237"/>
+      <c r="BY10" s="237"/>
+      <c r="BZ10" s="238"/>
     </row>
     <row r="11" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A11" s="248" t="s">
+      <c r="A11" s="242" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="249"/>
-      <c r="C11" s="250"/>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="252"/>
-      <c r="J11" s="253" t="s">
+      <c r="B11" s="243"/>
+      <c r="C11" s="259"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="261"/>
+      <c r="J11" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="254"/>
-      <c r="L11" s="254"/>
-      <c r="M11" s="254"/>
-      <c r="N11" s="254"/>
-      <c r="O11" s="254"/>
-      <c r="P11" s="255"/>
-      <c r="Q11" s="256" t="s">
-        <v>71</v>
+      <c r="K11" s="257"/>
+      <c r="L11" s="257"/>
+      <c r="M11" s="257"/>
+      <c r="N11" s="257"/>
+      <c r="O11" s="257"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="239" t="s">
+        <v>69</v>
       </c>
-      <c r="R11" s="257"/>
-      <c r="S11" s="257"/>
-      <c r="T11" s="257"/>
-      <c r="U11" s="257"/>
-      <c r="V11" s="257"/>
-      <c r="W11" s="257"/>
-      <c r="X11" s="257"/>
-      <c r="Y11" s="257"/>
-      <c r="Z11" s="257"/>
-      <c r="AA11" s="258"/>
-      <c r="AB11" s="259"/>
-      <c r="AC11" s="246"/>
-      <c r="AD11" s="246"/>
-      <c r="AE11" s="246"/>
-      <c r="AF11" s="246"/>
-      <c r="AG11" s="246"/>
-      <c r="AH11" s="246"/>
-      <c r="AI11" s="259"/>
-      <c r="AJ11" s="246"/>
-      <c r="AK11" s="246"/>
-      <c r="AL11" s="246"/>
-      <c r="AM11" s="246"/>
-      <c r="AN11" s="246"/>
-      <c r="AO11" s="246"/>
-      <c r="AP11" s="246"/>
-      <c r="AQ11" s="246"/>
-      <c r="AR11" s="245" t="s">
+      <c r="R11" s="240"/>
+      <c r="S11" s="240"/>
+      <c r="T11" s="240"/>
+      <c r="U11" s="240"/>
+      <c r="V11" s="240"/>
+      <c r="W11" s="240"/>
+      <c r="X11" s="240"/>
+      <c r="Y11" s="240"/>
+      <c r="Z11" s="240"/>
+      <c r="AA11" s="241"/>
+      <c r="AB11" s="250"/>
+      <c r="AC11" s="237"/>
+      <c r="AD11" s="237"/>
+      <c r="AE11" s="237"/>
+      <c r="AF11" s="237"/>
+      <c r="AG11" s="237"/>
+      <c r="AH11" s="237"/>
+      <c r="AI11" s="250"/>
+      <c r="AJ11" s="237"/>
+      <c r="AK11" s="237"/>
+      <c r="AL11" s="237"/>
+      <c r="AM11" s="237"/>
+      <c r="AN11" s="237"/>
+      <c r="AO11" s="237"/>
+      <c r="AP11" s="237"/>
+      <c r="AQ11" s="237"/>
+      <c r="AR11" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="AS11" s="246"/>
-      <c r="AT11" s="246"/>
-      <c r="AU11" s="246"/>
-      <c r="AV11" s="246"/>
-      <c r="AW11" s="246"/>
-      <c r="AX11" s="246"/>
-      <c r="AY11" s="246"/>
-      <c r="AZ11" s="246"/>
-      <c r="BA11" s="246"/>
-      <c r="BB11" s="246"/>
-      <c r="BC11" s="246"/>
-      <c r="BD11" s="246"/>
-      <c r="BE11" s="246"/>
-      <c r="BF11" s="246"/>
-      <c r="BG11" s="246"/>
-      <c r="BH11" s="246"/>
-      <c r="BI11" s="246"/>
-      <c r="BJ11" s="246"/>
-      <c r="BK11" s="246"/>
-      <c r="BL11" s="246"/>
-      <c r="BM11" s="246"/>
-      <c r="BN11" s="246"/>
-      <c r="BO11" s="246"/>
-      <c r="BP11" s="246"/>
-      <c r="BQ11" s="246"/>
-      <c r="BR11" s="246"/>
-      <c r="BS11" s="246"/>
-      <c r="BT11" s="246"/>
-      <c r="BU11" s="246"/>
-      <c r="BV11" s="246"/>
-      <c r="BW11" s="246"/>
-      <c r="BX11" s="246"/>
-      <c r="BY11" s="246"/>
-      <c r="BZ11" s="247"/>
+      <c r="AS11" s="237"/>
+      <c r="AT11" s="237"/>
+      <c r="AU11" s="237"/>
+      <c r="AV11" s="237"/>
+      <c r="AW11" s="237"/>
+      <c r="AX11" s="237"/>
+      <c r="AY11" s="237"/>
+      <c r="AZ11" s="237"/>
+      <c r="BA11" s="237"/>
+      <c r="BB11" s="237"/>
+      <c r="BC11" s="237"/>
+      <c r="BD11" s="237"/>
+      <c r="BE11" s="237"/>
+      <c r="BF11" s="237"/>
+      <c r="BG11" s="237"/>
+      <c r="BH11" s="237"/>
+      <c r="BI11" s="237"/>
+      <c r="BJ11" s="237"/>
+      <c r="BK11" s="237"/>
+      <c r="BL11" s="237"/>
+      <c r="BM11" s="237"/>
+      <c r="BN11" s="237"/>
+      <c r="BO11" s="237"/>
+      <c r="BP11" s="237"/>
+      <c r="BQ11" s="237"/>
+      <c r="BR11" s="237"/>
+      <c r="BS11" s="237"/>
+      <c r="BT11" s="237"/>
+      <c r="BU11" s="237"/>
+      <c r="BV11" s="237"/>
+      <c r="BW11" s="237"/>
+      <c r="BX11" s="237"/>
+      <c r="BY11" s="237"/>
+      <c r="BZ11" s="238"/>
     </row>
     <row r="12" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A12" s="268">
+      <c r="A12" s="254">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B12" s="269"/>
-      <c r="C12" s="260"/>
-      <c r="D12" s="261"/>
-      <c r="E12" s="261"/>
-      <c r="F12" s="261"/>
-      <c r="G12" s="261"/>
-      <c r="H12" s="261"/>
-      <c r="I12" s="262"/>
-      <c r="J12" s="253" t="s">
+      <c r="B12" s="255"/>
+      <c r="C12" s="244"/>
+      <c r="D12" s="245"/>
+      <c r="E12" s="245"/>
+      <c r="F12" s="245"/>
+      <c r="G12" s="245"/>
+      <c r="H12" s="245"/>
+      <c r="I12" s="246"/>
+      <c r="J12" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="K12" s="254"/>
-      <c r="L12" s="254"/>
-      <c r="M12" s="254"/>
-      <c r="N12" s="254"/>
-      <c r="O12" s="254"/>
-      <c r="P12" s="255"/>
-      <c r="Q12" s="256" t="s">
-        <v>71</v>
+      <c r="K12" s="257"/>
+      <c r="L12" s="257"/>
+      <c r="M12" s="257"/>
+      <c r="N12" s="257"/>
+      <c r="O12" s="257"/>
+      <c r="P12" s="258"/>
+      <c r="Q12" s="239" t="s">
+        <v>69</v>
       </c>
-      <c r="R12" s="257"/>
-      <c r="S12" s="257"/>
-      <c r="T12" s="257"/>
-      <c r="U12" s="257"/>
-      <c r="V12" s="257"/>
-      <c r="W12" s="257"/>
-      <c r="X12" s="257"/>
-      <c r="Y12" s="257"/>
-      <c r="Z12" s="257"/>
-      <c r="AA12" s="258"/>
-      <c r="AB12" s="263"/>
-      <c r="AC12" s="264"/>
-      <c r="AD12" s="264"/>
-      <c r="AE12" s="264"/>
-      <c r="AF12" s="264"/>
-      <c r="AG12" s="264"/>
-      <c r="AH12" s="264"/>
-      <c r="AI12" s="263"/>
-      <c r="AJ12" s="264"/>
-      <c r="AK12" s="264"/>
-      <c r="AL12" s="264"/>
-      <c r="AM12" s="264"/>
-      <c r="AN12" s="264"/>
-      <c r="AO12" s="264"/>
-      <c r="AP12" s="264"/>
-      <c r="AQ12" s="264"/>
-      <c r="AR12" s="245" t="s">
+      <c r="R12" s="240"/>
+      <c r="S12" s="240"/>
+      <c r="T12" s="240"/>
+      <c r="U12" s="240"/>
+      <c r="V12" s="240"/>
+      <c r="W12" s="240"/>
+      <c r="X12" s="240"/>
+      <c r="Y12" s="240"/>
+      <c r="Z12" s="240"/>
+      <c r="AA12" s="241"/>
+      <c r="AB12" s="234"/>
+      <c r="AC12" s="235"/>
+      <c r="AD12" s="235"/>
+      <c r="AE12" s="235"/>
+      <c r="AF12" s="235"/>
+      <c r="AG12" s="235"/>
+      <c r="AH12" s="235"/>
+      <c r="AI12" s="234"/>
+      <c r="AJ12" s="235"/>
+      <c r="AK12" s="235"/>
+      <c r="AL12" s="235"/>
+      <c r="AM12" s="235"/>
+      <c r="AN12" s="235"/>
+      <c r="AO12" s="235"/>
+      <c r="AP12" s="235"/>
+      <c r="AQ12" s="235"/>
+      <c r="AR12" s="236" t="s">
         <v>60</v>
       </c>
-      <c r="AS12" s="246"/>
-      <c r="AT12" s="246"/>
-      <c r="AU12" s="246"/>
-      <c r="AV12" s="246"/>
-      <c r="AW12" s="246"/>
-      <c r="AX12" s="246"/>
-      <c r="AY12" s="246"/>
-      <c r="AZ12" s="246"/>
-      <c r="BA12" s="246"/>
-      <c r="BB12" s="246"/>
-      <c r="BC12" s="246"/>
-      <c r="BD12" s="246"/>
-      <c r="BE12" s="246"/>
-      <c r="BF12" s="246"/>
-      <c r="BG12" s="246"/>
-      <c r="BH12" s="246"/>
-      <c r="BI12" s="246"/>
-      <c r="BJ12" s="246"/>
-      <c r="BK12" s="246"/>
-      <c r="BL12" s="246"/>
-      <c r="BM12" s="246"/>
-      <c r="BN12" s="246"/>
-      <c r="BO12" s="246"/>
-      <c r="BP12" s="246"/>
-      <c r="BQ12" s="246"/>
-      <c r="BR12" s="246"/>
-      <c r="BS12" s="246"/>
-      <c r="BT12" s="246"/>
-      <c r="BU12" s="246"/>
-      <c r="BV12" s="246"/>
-      <c r="BW12" s="246"/>
-      <c r="BX12" s="246"/>
-      <c r="BY12" s="246"/>
-      <c r="BZ12" s="247"/>
+      <c r="AS12" s="237"/>
+      <c r="AT12" s="237"/>
+      <c r="AU12" s="237"/>
+      <c r="AV12" s="237"/>
+      <c r="AW12" s="237"/>
+      <c r="AX12" s="237"/>
+      <c r="AY12" s="237"/>
+      <c r="AZ12" s="237"/>
+      <c r="BA12" s="237"/>
+      <c r="BB12" s="237"/>
+      <c r="BC12" s="237"/>
+      <c r="BD12" s="237"/>
+      <c r="BE12" s="237"/>
+      <c r="BF12" s="237"/>
+      <c r="BG12" s="237"/>
+      <c r="BH12" s="237"/>
+      <c r="BI12" s="237"/>
+      <c r="BJ12" s="237"/>
+      <c r="BK12" s="237"/>
+      <c r="BL12" s="237"/>
+      <c r="BM12" s="237"/>
+      <c r="BN12" s="237"/>
+      <c r="BO12" s="237"/>
+      <c r="BP12" s="237"/>
+      <c r="BQ12" s="237"/>
+      <c r="BR12" s="237"/>
+      <c r="BS12" s="237"/>
+      <c r="BT12" s="237"/>
+      <c r="BU12" s="237"/>
+      <c r="BV12" s="237"/>
+      <c r="BW12" s="237"/>
+      <c r="BX12" s="237"/>
+      <c r="BY12" s="237"/>
+      <c r="BZ12" s="238"/>
     </row>
     <row r="13" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A13" s="248" t="s">
+      <c r="A13" s="242" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="249"/>
+      <c r="B13" s="243"/>
       <c r="C13" s="139"/>
       <c r="D13" s="140"/>
       <c r="E13" s="140"/>
@@ -25020,15 +24917,15 @@
       <c r="G13" s="140"/>
       <c r="H13" s="140"/>
       <c r="I13" s="141"/>
-      <c r="J13" s="260" t="s">
+      <c r="J13" s="244" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="261"/>
-      <c r="L13" s="261"/>
-      <c r="M13" s="261"/>
-      <c r="N13" s="261"/>
-      <c r="O13" s="261"/>
-      <c r="P13" s="262"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="245"/>
+      <c r="M13" s="245"/>
+      <c r="N13" s="245"/>
+      <c r="O13" s="245"/>
+      <c r="P13" s="246"/>
       <c r="Q13" s="166"/>
       <c r="R13" s="167"/>
       <c r="S13" s="167"/>
@@ -25040,65 +24937,65 @@
       <c r="Y13" s="167"/>
       <c r="Z13" s="167"/>
       <c r="AA13" s="168"/>
-      <c r="AB13" s="263"/>
-      <c r="AC13" s="264"/>
-      <c r="AD13" s="264"/>
-      <c r="AE13" s="264"/>
-      <c r="AF13" s="264"/>
-      <c r="AG13" s="264"/>
-      <c r="AH13" s="264"/>
-      <c r="AI13" s="263"/>
-      <c r="AJ13" s="264"/>
-      <c r="AK13" s="264"/>
-      <c r="AL13" s="264"/>
-      <c r="AM13" s="264"/>
-      <c r="AN13" s="264"/>
-      <c r="AO13" s="264"/>
-      <c r="AP13" s="264"/>
-      <c r="AQ13" s="264"/>
-      <c r="AR13" s="245" t="s">
+      <c r="AB13" s="234"/>
+      <c r="AC13" s="235"/>
+      <c r="AD13" s="235"/>
+      <c r="AE13" s="235"/>
+      <c r="AF13" s="235"/>
+      <c r="AG13" s="235"/>
+      <c r="AH13" s="235"/>
+      <c r="AI13" s="234"/>
+      <c r="AJ13" s="235"/>
+      <c r="AK13" s="235"/>
+      <c r="AL13" s="235"/>
+      <c r="AM13" s="235"/>
+      <c r="AN13" s="235"/>
+      <c r="AO13" s="235"/>
+      <c r="AP13" s="235"/>
+      <c r="AQ13" s="235"/>
+      <c r="AR13" s="236" t="s">
         <v>63</v>
       </c>
-      <c r="AS13" s="246"/>
-      <c r="AT13" s="246"/>
-      <c r="AU13" s="246"/>
-      <c r="AV13" s="246"/>
-      <c r="AW13" s="246"/>
-      <c r="AX13" s="246"/>
-      <c r="AY13" s="246"/>
-      <c r="AZ13" s="246"/>
-      <c r="BA13" s="246"/>
-      <c r="BB13" s="246"/>
-      <c r="BC13" s="246"/>
-      <c r="BD13" s="246"/>
-      <c r="BE13" s="246"/>
-      <c r="BF13" s="246"/>
-      <c r="BG13" s="246"/>
-      <c r="BH13" s="246"/>
-      <c r="BI13" s="246"/>
-      <c r="BJ13" s="246"/>
-      <c r="BK13" s="246"/>
-      <c r="BL13" s="246"/>
-      <c r="BM13" s="246"/>
-      <c r="BN13" s="246"/>
-      <c r="BO13" s="246"/>
-      <c r="BP13" s="246"/>
-      <c r="BQ13" s="246"/>
-      <c r="BR13" s="246"/>
-      <c r="BS13" s="246"/>
-      <c r="BT13" s="246"/>
-      <c r="BU13" s="246"/>
-      <c r="BV13" s="246"/>
-      <c r="BW13" s="246"/>
-      <c r="BX13" s="246"/>
-      <c r="BY13" s="246"/>
-      <c r="BZ13" s="247"/>
+      <c r="AS13" s="237"/>
+      <c r="AT13" s="237"/>
+      <c r="AU13" s="237"/>
+      <c r="AV13" s="237"/>
+      <c r="AW13" s="237"/>
+      <c r="AX13" s="237"/>
+      <c r="AY13" s="237"/>
+      <c r="AZ13" s="237"/>
+      <c r="BA13" s="237"/>
+      <c r="BB13" s="237"/>
+      <c r="BC13" s="237"/>
+      <c r="BD13" s="237"/>
+      <c r="BE13" s="237"/>
+      <c r="BF13" s="237"/>
+      <c r="BG13" s="237"/>
+      <c r="BH13" s="237"/>
+      <c r="BI13" s="237"/>
+      <c r="BJ13" s="237"/>
+      <c r="BK13" s="237"/>
+      <c r="BL13" s="237"/>
+      <c r="BM13" s="237"/>
+      <c r="BN13" s="237"/>
+      <c r="BO13" s="237"/>
+      <c r="BP13" s="237"/>
+      <c r="BQ13" s="237"/>
+      <c r="BR13" s="237"/>
+      <c r="BS13" s="237"/>
+      <c r="BT13" s="237"/>
+      <c r="BU13" s="237"/>
+      <c r="BV13" s="237"/>
+      <c r="BW13" s="237"/>
+      <c r="BX13" s="237"/>
+      <c r="BY13" s="237"/>
+      <c r="BZ13" s="238"/>
     </row>
     <row r="14" spans="1:78" ht="14" customHeight="1">
-      <c r="A14" s="248" t="s">
+      <c r="A14" s="242" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="249"/>
+      <c r="B14" s="243"/>
       <c r="C14" s="139"/>
       <c r="D14" s="140"/>
       <c r="E14" s="140"/>
@@ -25106,81 +25003,81 @@
       <c r="G14" s="140"/>
       <c r="H14" s="140"/>
       <c r="I14" s="141"/>
-      <c r="J14" s="260" t="s">
+      <c r="J14" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="K14" s="261"/>
-      <c r="L14" s="261"/>
-      <c r="M14" s="261"/>
-      <c r="N14" s="261"/>
-      <c r="O14" s="261"/>
-      <c r="P14" s="262"/>
-      <c r="Q14" s="256"/>
-      <c r="R14" s="257"/>
-      <c r="S14" s="257"/>
-      <c r="T14" s="257"/>
-      <c r="U14" s="257"/>
-      <c r="V14" s="257"/>
-      <c r="W14" s="257"/>
-      <c r="X14" s="257"/>
-      <c r="Y14" s="257"/>
-      <c r="Z14" s="257"/>
-      <c r="AA14" s="258"/>
-      <c r="AB14" s="259"/>
-      <c r="AC14" s="246"/>
-      <c r="AD14" s="246"/>
-      <c r="AE14" s="246"/>
-      <c r="AF14" s="246"/>
-      <c r="AG14" s="246"/>
-      <c r="AH14" s="246"/>
-      <c r="AI14" s="259"/>
-      <c r="AJ14" s="246"/>
-      <c r="AK14" s="246"/>
-      <c r="AL14" s="246"/>
-      <c r="AM14" s="246"/>
-      <c r="AN14" s="246"/>
-      <c r="AO14" s="246"/>
-      <c r="AP14" s="246"/>
-      <c r="AQ14" s="246"/>
-      <c r="AR14" s="270"/>
-      <c r="AS14" s="271"/>
-      <c r="AT14" s="271"/>
-      <c r="AU14" s="271"/>
-      <c r="AV14" s="271"/>
-      <c r="AW14" s="271"/>
-      <c r="AX14" s="271"/>
-      <c r="AY14" s="271"/>
-      <c r="AZ14" s="271"/>
-      <c r="BA14" s="271"/>
-      <c r="BB14" s="271"/>
-      <c r="BC14" s="271"/>
-      <c r="BD14" s="271"/>
-      <c r="BE14" s="271"/>
-      <c r="BF14" s="271"/>
-      <c r="BG14" s="271"/>
-      <c r="BH14" s="271"/>
-      <c r="BI14" s="271"/>
-      <c r="BJ14" s="271"/>
-      <c r="BK14" s="271"/>
-      <c r="BL14" s="271"/>
-      <c r="BM14" s="271"/>
-      <c r="BN14" s="271"/>
-      <c r="BO14" s="271"/>
-      <c r="BP14" s="271"/>
-      <c r="BQ14" s="271"/>
-      <c r="BR14" s="271"/>
-      <c r="BS14" s="271"/>
-      <c r="BT14" s="271"/>
-      <c r="BU14" s="271"/>
-      <c r="BV14" s="271"/>
-      <c r="BW14" s="271"/>
-      <c r="BX14" s="271"/>
-      <c r="BY14" s="271"/>
-      <c r="BZ14" s="272"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="245"/>
+      <c r="N14" s="245"/>
+      <c r="O14" s="245"/>
+      <c r="P14" s="246"/>
+      <c r="Q14" s="239"/>
+      <c r="R14" s="240"/>
+      <c r="S14" s="240"/>
+      <c r="T14" s="240"/>
+      <c r="U14" s="240"/>
+      <c r="V14" s="240"/>
+      <c r="W14" s="240"/>
+      <c r="X14" s="240"/>
+      <c r="Y14" s="240"/>
+      <c r="Z14" s="240"/>
+      <c r="AA14" s="241"/>
+      <c r="AB14" s="250"/>
+      <c r="AC14" s="237"/>
+      <c r="AD14" s="237"/>
+      <c r="AE14" s="237"/>
+      <c r="AF14" s="237"/>
+      <c r="AG14" s="237"/>
+      <c r="AH14" s="237"/>
+      <c r="AI14" s="250"/>
+      <c r="AJ14" s="237"/>
+      <c r="AK14" s="237"/>
+      <c r="AL14" s="237"/>
+      <c r="AM14" s="237"/>
+      <c r="AN14" s="237"/>
+      <c r="AO14" s="237"/>
+      <c r="AP14" s="237"/>
+      <c r="AQ14" s="237"/>
+      <c r="AR14" s="251"/>
+      <c r="AS14" s="252"/>
+      <c r="AT14" s="252"/>
+      <c r="AU14" s="252"/>
+      <c r="AV14" s="252"/>
+      <c r="AW14" s="252"/>
+      <c r="AX14" s="252"/>
+      <c r="AY14" s="252"/>
+      <c r="AZ14" s="252"/>
+      <c r="BA14" s="252"/>
+      <c r="BB14" s="252"/>
+      <c r="BC14" s="252"/>
+      <c r="BD14" s="252"/>
+      <c r="BE14" s="252"/>
+      <c r="BF14" s="252"/>
+      <c r="BG14" s="252"/>
+      <c r="BH14" s="252"/>
+      <c r="BI14" s="252"/>
+      <c r="BJ14" s="252"/>
+      <c r="BK14" s="252"/>
+      <c r="BL14" s="252"/>
+      <c r="BM14" s="252"/>
+      <c r="BN14" s="252"/>
+      <c r="BO14" s="252"/>
+      <c r="BP14" s="252"/>
+      <c r="BQ14" s="252"/>
+      <c r="BR14" s="252"/>
+      <c r="BS14" s="252"/>
+      <c r="BT14" s="252"/>
+      <c r="BU14" s="252"/>
+      <c r="BV14" s="252"/>
+      <c r="BW14" s="252"/>
+      <c r="BX14" s="252"/>
+      <c r="BY14" s="252"/>
+      <c r="BZ14" s="253"/>
     </row>
     <row r="15" spans="1:78" ht="25" customHeight="1">
-      <c r="A15" s="248"/>
-      <c r="B15" s="249"/>
+      <c r="A15" s="242"/>
+      <c r="B15" s="243"/>
       <c r="C15" s="139"/>
       <c r="D15" s="140"/>
       <c r="E15" s="140"/>
@@ -25188,40 +25085,40 @@
       <c r="G15" s="140"/>
       <c r="H15" s="140"/>
       <c r="I15" s="141"/>
-      <c r="J15" s="260"/>
-      <c r="K15" s="261"/>
-      <c r="L15" s="261"/>
-      <c r="M15" s="261"/>
-      <c r="N15" s="261"/>
-      <c r="O15" s="261"/>
-      <c r="P15" s="262"/>
-      <c r="Q15" s="256"/>
-      <c r="R15" s="257"/>
-      <c r="S15" s="257"/>
-      <c r="T15" s="257"/>
-      <c r="U15" s="257"/>
-      <c r="V15" s="257"/>
-      <c r="W15" s="257"/>
-      <c r="X15" s="257"/>
-      <c r="Y15" s="257"/>
-      <c r="Z15" s="257"/>
-      <c r="AA15" s="258"/>
-      <c r="AB15" s="259"/>
-      <c r="AC15" s="246"/>
-      <c r="AD15" s="246"/>
-      <c r="AE15" s="246"/>
-      <c r="AF15" s="246"/>
-      <c r="AG15" s="246"/>
-      <c r="AH15" s="246"/>
-      <c r="AI15" s="259"/>
-      <c r="AJ15" s="246"/>
-      <c r="AK15" s="246"/>
-      <c r="AL15" s="246"/>
-      <c r="AM15" s="246"/>
-      <c r="AN15" s="246"/>
-      <c r="AO15" s="246"/>
-      <c r="AP15" s="246"/>
-      <c r="AQ15" s="246"/>
+      <c r="J15" s="244"/>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
+      <c r="M15" s="245"/>
+      <c r="N15" s="245"/>
+      <c r="O15" s="245"/>
+      <c r="P15" s="246"/>
+      <c r="Q15" s="239"/>
+      <c r="R15" s="240"/>
+      <c r="S15" s="240"/>
+      <c r="T15" s="240"/>
+      <c r="U15" s="240"/>
+      <c r="V15" s="240"/>
+      <c r="W15" s="240"/>
+      <c r="X15" s="240"/>
+      <c r="Y15" s="240"/>
+      <c r="Z15" s="240"/>
+      <c r="AA15" s="241"/>
+      <c r="AB15" s="250"/>
+      <c r="AC15" s="237"/>
+      <c r="AD15" s="237"/>
+      <c r="AE15" s="237"/>
+      <c r="AF15" s="237"/>
+      <c r="AG15" s="237"/>
+      <c r="AH15" s="237"/>
+      <c r="AI15" s="250"/>
+      <c r="AJ15" s="237"/>
+      <c r="AK15" s="237"/>
+      <c r="AL15" s="237"/>
+      <c r="AM15" s="237"/>
+      <c r="AN15" s="237"/>
+      <c r="AO15" s="237"/>
+      <c r="AP15" s="237"/>
+      <c r="AQ15" s="237"/>
       <c r="AR15" s="144"/>
       <c r="AS15" s="143"/>
       <c r="AT15" s="143"/>
@@ -25259,8 +25156,8 @@
       <c r="BZ15" s="145"/>
     </row>
     <row r="16" spans="1:78" ht="26.5" customHeight="1">
-      <c r="A16" s="248"/>
-      <c r="B16" s="249"/>
+      <c r="A16" s="242"/>
+      <c r="B16" s="243"/>
       <c r="C16" s="139"/>
       <c r="D16" s="140"/>
       <c r="E16" s="140"/>
@@ -25268,24 +25165,24 @@
       <c r="G16" s="140"/>
       <c r="H16" s="140"/>
       <c r="I16" s="141"/>
-      <c r="J16" s="260"/>
-      <c r="K16" s="261"/>
-      <c r="L16" s="261"/>
-      <c r="M16" s="261"/>
-      <c r="N16" s="261"/>
-      <c r="O16" s="261"/>
-      <c r="P16" s="262"/>
-      <c r="Q16" s="256"/>
-      <c r="R16" s="257"/>
-      <c r="S16" s="257"/>
-      <c r="T16" s="257"/>
-      <c r="U16" s="257"/>
-      <c r="V16" s="257"/>
-      <c r="W16" s="257"/>
-      <c r="X16" s="257"/>
-      <c r="Y16" s="257"/>
-      <c r="Z16" s="257"/>
-      <c r="AA16" s="258"/>
+      <c r="J16" s="244"/>
+      <c r="K16" s="245"/>
+      <c r="L16" s="245"/>
+      <c r="M16" s="245"/>
+      <c r="N16" s="245"/>
+      <c r="O16" s="245"/>
+      <c r="P16" s="246"/>
+      <c r="Q16" s="239"/>
+      <c r="R16" s="240"/>
+      <c r="S16" s="240"/>
+      <c r="T16" s="240"/>
+      <c r="U16" s="240"/>
+      <c r="V16" s="240"/>
+      <c r="W16" s="240"/>
+      <c r="X16" s="240"/>
+      <c r="Y16" s="240"/>
+      <c r="Z16" s="240"/>
+      <c r="AA16" s="241"/>
       <c r="AB16" s="142"/>
       <c r="AC16" s="143"/>
       <c r="AD16" s="143"/>
@@ -25293,15 +25190,15 @@
       <c r="AF16" s="143"/>
       <c r="AG16" s="143"/>
       <c r="AH16" s="143"/>
-      <c r="AI16" s="259"/>
-      <c r="AJ16" s="246"/>
-      <c r="AK16" s="246"/>
-      <c r="AL16" s="246"/>
-      <c r="AM16" s="246"/>
-      <c r="AN16" s="246"/>
-      <c r="AO16" s="246"/>
-      <c r="AP16" s="246"/>
-      <c r="AQ16" s="246"/>
+      <c r="AI16" s="250"/>
+      <c r="AJ16" s="237"/>
+      <c r="AK16" s="237"/>
+      <c r="AL16" s="237"/>
+      <c r="AM16" s="237"/>
+      <c r="AN16" s="237"/>
+      <c r="AO16" s="237"/>
+      <c r="AP16" s="237"/>
+      <c r="AQ16" s="237"/>
       <c r="AR16" s="144"/>
       <c r="AS16" s="143"/>
       <c r="AT16" s="143"/>
@@ -25340,6 +25237,75 @@
     </row>
   </sheetData>
   <mergeCells count="85">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="Q2:BZ2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:P3"/>
+    <mergeCell ref="Q3:AA4"/>
+    <mergeCell ref="AB3:AH4"/>
+    <mergeCell ref="AI3:AQ4"/>
+    <mergeCell ref="AR3:BZ4"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="J4:P4"/>
+    <mergeCell ref="AR5:BZ5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="J6:P6"/>
+    <mergeCell ref="Q6:AA6"/>
+    <mergeCell ref="AB6:AH6"/>
+    <mergeCell ref="AI6:AQ6"/>
+    <mergeCell ref="AR6:BZ6"/>
+    <mergeCell ref="AB5:AH5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="J5:P5"/>
+    <mergeCell ref="Q5:AA5"/>
+    <mergeCell ref="AI5:AQ5"/>
+    <mergeCell ref="AR7:BZ7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="AB8:AH8"/>
+    <mergeCell ref="AI8:AQ8"/>
+    <mergeCell ref="AR8:BZ8"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="Q8:AA8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="Q7:AA7"/>
+    <mergeCell ref="AB7:AH7"/>
+    <mergeCell ref="AI7:AQ7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="AB10:AH10"/>
+    <mergeCell ref="AI10:AQ10"/>
+    <mergeCell ref="AR10:BZ10"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="Q10:AA10"/>
+    <mergeCell ref="AR11:BZ11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="AB12:AH12"/>
+    <mergeCell ref="AI12:AQ12"/>
+    <mergeCell ref="AR12:BZ12"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="Q12:AA12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="Q11:AA11"/>
+    <mergeCell ref="AB11:AH11"/>
+    <mergeCell ref="AI11:AQ11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="AB13:AH13"/>
+    <mergeCell ref="AI13:AQ13"/>
+    <mergeCell ref="AR13:BZ13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AB15:AH15"/>
+    <mergeCell ref="AI15:AQ15"/>
+    <mergeCell ref="Q14:AA14"/>
     <mergeCell ref="AI9:AQ9"/>
     <mergeCell ref="AR9:BZ9"/>
     <mergeCell ref="Q15:AA15"/>
@@ -25356,75 +25322,6 @@
     <mergeCell ref="AB14:AH14"/>
     <mergeCell ref="AI14:AQ14"/>
     <mergeCell ref="AR14:BZ14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="AB15:AH15"/>
-    <mergeCell ref="AI15:AQ15"/>
-    <mergeCell ref="Q14:AA14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="AB13:AH13"/>
-    <mergeCell ref="AI13:AQ13"/>
-    <mergeCell ref="AR13:BZ13"/>
-    <mergeCell ref="AR11:BZ11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="AB12:AH12"/>
-    <mergeCell ref="AI12:AQ12"/>
-    <mergeCell ref="AR12:BZ12"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="Q12:AA12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="Q11:AA11"/>
-    <mergeCell ref="AB11:AH11"/>
-    <mergeCell ref="AI11:AQ11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="AB10:AH10"/>
-    <mergeCell ref="AI10:AQ10"/>
-    <mergeCell ref="AR10:BZ10"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="Q10:AA10"/>
-    <mergeCell ref="AR7:BZ7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="AB8:AH8"/>
-    <mergeCell ref="AI8:AQ8"/>
-    <mergeCell ref="AR8:BZ8"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="Q8:AA8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="Q7:AA7"/>
-    <mergeCell ref="AB7:AH7"/>
-    <mergeCell ref="AI7:AQ7"/>
-    <mergeCell ref="AR5:BZ5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="J6:P6"/>
-    <mergeCell ref="Q6:AA6"/>
-    <mergeCell ref="AB6:AH6"/>
-    <mergeCell ref="AI6:AQ6"/>
-    <mergeCell ref="AR6:BZ6"/>
-    <mergeCell ref="AB5:AH5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="J5:P5"/>
-    <mergeCell ref="Q5:AA5"/>
-    <mergeCell ref="AI5:AQ5"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="Q2:BZ2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="Q3:AA4"/>
-    <mergeCell ref="AB3:AH4"/>
-    <mergeCell ref="AI3:AQ4"/>
-    <mergeCell ref="AR3:BZ4"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="J4:P4"/>
   </mergeCells>
   <phoneticPr fontId="55"/>
   <conditionalFormatting sqref="Q5:Q16">
@@ -25483,21 +25380,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="13.75" customHeight="1">
-      <c r="A1" s="273" t="s">
-        <v>70</v>
+      <c r="A1" s="274" t="s">
+        <v>68</v>
       </c>
-      <c r="B1" s="273"/>
-      <c r="C1" s="273"/>
-      <c r="D1" s="273"/>
-      <c r="E1" s="273"/>
-      <c r="F1" s="273"/>
-      <c r="G1" s="273"/>
-      <c r="H1" s="273"/>
-      <c r="I1" s="273"/>
-      <c r="J1" s="273"/>
-      <c r="K1" s="273"/>
-      <c r="L1" s="273"/>
-      <c r="M1" s="273"/>
+      <c r="B1" s="274"/>
+      <c r="C1" s="274"/>
+      <c r="D1" s="274"/>
+      <c r="E1" s="274"/>
+      <c r="F1" s="274"/>
+      <c r="G1" s="274"/>
+      <c r="H1" s="274"/>
+      <c r="I1" s="274"/>
+      <c r="J1" s="274"/>
+      <c r="K1" s="274"/>
+      <c r="L1" s="274"/>
+      <c r="M1" s="274"/>
     </row>
     <row r="2" spans="1:85" ht="13.75" customHeight="1">
       <c r="A2" s="158"/>
@@ -25589,44 +25486,44 @@
     <row r="3" spans="1:85">
       <c r="A3" s="161"/>
       <c r="B3" s="169" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="CG3" s="162"/>
     </row>
     <row r="4" spans="1:85">
       <c r="A4" s="161"/>
       <c r="D4" s="157" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="CG4" s="162"/>
     </row>
     <row r="5" spans="1:85">
       <c r="A5" s="161"/>
       <c r="C5" s="157" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D5" s="157" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CG5" s="162"/>
     </row>
     <row r="6" spans="1:85" ht="15" customHeight="1">
       <c r="A6" s="161"/>
       <c r="C6" s="157" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D6" s="157" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="CG6" s="162"/>
     </row>
     <row r="7" spans="1:85" ht="15" customHeight="1">
       <c r="A7" s="161"/>
       <c r="C7" s="157" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D7" s="157" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="CG7" s="162"/>
     </row>
@@ -25637,44 +25534,44 @@
     <row r="9" spans="1:85">
       <c r="A9" s="161"/>
       <c r="B9" s="169" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="CG9" s="162"/>
     </row>
     <row r="10" spans="1:85" ht="15" customHeight="1">
       <c r="A10" s="161"/>
       <c r="D10" s="157" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="CG10" s="162"/>
     </row>
     <row r="11" spans="1:85" ht="15" customHeight="1">
       <c r="A11" s="161"/>
       <c r="C11" s="157" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D11" s="157" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CG11" s="162"/>
     </row>
     <row r="12" spans="1:85" ht="13.75" customHeight="1">
       <c r="A12" s="161"/>
       <c r="C12" s="157" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D12" s="157" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="CG12" s="162"/>
     </row>
     <row r="13" spans="1:85">
       <c r="A13" s="161"/>
       <c r="C13" s="157" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D13" s="157" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="CG13" s="162"/>
     </row>

--- a/20_設計書/お知らせ登録画面.xlsx
+++ b/20_設計書/お知らせ登録画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A340AC3B-B7F7-4CDE-92A1-4232FAD805BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95B334F-97A5-49E1-842C-802D460948A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30285" yWindow="1515" windowWidth="20595" windowHeight="12375" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -221,7 +221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="88">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -460,10 +460,6 @@
     <phoneticPr fontId="51"/>
   </si>
   <si>
-    <t>ｒ1.0</t>
-    <phoneticPr fontId="51"/>
-  </si>
-  <si>
     <t>古竹</t>
     <rPh sb="0" eb="2">
       <t>フルタケ</t>
@@ -554,13 +550,6 @@
     </rPh>
     <rPh sb="4" eb="8">
       <t>トウロクガメン</t>
-    </rPh>
-    <phoneticPr fontId="51"/>
-  </si>
-  <si>
-    <t>新環境証明書</t>
-    <rPh sb="0" eb="6">
-      <t>シンカンキョウショウメイショ</t>
     </rPh>
     <phoneticPr fontId="51"/>
   </si>
@@ -802,44 +791,9 @@
     <phoneticPr fontId="55"/>
   </si>
   <si>
-    <t>1.　お知らせ登録画面</t>
-    <rPh sb="4" eb="5">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>トウロクガメン</t>
-    </rPh>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
     <t>日本語版、英語版どちらかまたは両方が未記載の際にエラーメッセージを表示</t>
     <rPh sb="33" eb="35">
       <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
-    <t>エラーがなければ、「お知らせ登録テーブル」に日本語本文と英語本文をDBに登録</t>
-    <rPh sb="11" eb="12">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>ニホンゴ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ホンブン</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>エイゴ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ホンブン</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="55"/>
   </si>
@@ -850,41 +804,6 @@
     </rPh>
     <rPh sb="9" eb="11">
       <t>オウカ</t>
-    </rPh>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
-    <t>2.　お知らせ登録画面</t>
-    <rPh sb="4" eb="5">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="7" eb="11">
-      <t>トウロクガメン</t>
-    </rPh>
-    <phoneticPr fontId="55"/>
-  </si>
-  <si>
-    <t>エラーがなければ、「バージョン情報登録テーブル」に日本語本文と英語本文をDBに登録</t>
-    <rPh sb="15" eb="17">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="25" eb="28">
-      <t>ニホンゴ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ホンブン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>エイゴ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>ホンブン</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="55"/>
   </si>
@@ -939,10 +858,6 @@
     <phoneticPr fontId="55"/>
   </si>
   <si>
-    <t>ｒ1.1</t>
-    <phoneticPr fontId="51"/>
-  </si>
-  <si>
     <t>「お知らせ登録画面」「画面項目」</t>
     <rPh sb="11" eb="15">
       <t>ガメンコウモク</t>
@@ -950,9 +865,96 @@
     <phoneticPr fontId="51"/>
   </si>
   <si>
+    <t>リッチテキストに必要な機能を修正</t>
+    <rPh sb="8" eb="10">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="51"/>
+  </si>
+  <si>
+    <t>2.　データバージョン情報登録</t>
+    <rPh sb="11" eb="13">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="55"/>
+  </si>
+  <si>
+    <t>1.　お知らせ登録</t>
+    <rPh sb="4" eb="5">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="55"/>
+  </si>
+  <si>
+    <t>エラーがなければ、「お知らせテーブル」に日本語本文と英語本文をDBに登録</t>
+    <rPh sb="11" eb="12">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>ニホンゴ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ホンブン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>エイゴ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ホンブン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="55"/>
+  </si>
+  <si>
+    <t>dr1.0</t>
+  </si>
+  <si>
+    <t>dr1.1</t>
+  </si>
+  <si>
+    <t>dr1.2</t>
+    <phoneticPr fontId="51"/>
+  </si>
+  <si>
+    <t>「処理詳細」</t>
+    <rPh sb="1" eb="5">
+      <t>ショリショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="51"/>
+  </si>
+  <si>
+    <t>テーブル情報変更に伴い修正</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="51"/>
+  </si>
+  <si>
     <t>・本設計はリッチテキストを使用
-　必要機能は文字色変更、太字を想定。
-　リンク挿入方法は検討中</t>
+　必要機能は文字色変更、太字、リンクを想定。</t>
     <rPh sb="17" eb="21">
       <t>ヒツヨウキノウ</t>
     </rPh>
@@ -965,33 +967,25 @@
     <rPh sb="28" eb="30">
       <t>フトジ</t>
     </rPh>
-    <rPh sb="31" eb="33">
+    <rPh sb="35" eb="37">
       <t>ソウテイ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ソウニュウ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ケントウ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>チュウ</t>
     </rPh>
     <phoneticPr fontId="55"/>
   </si>
   <si>
-    <t>リッチテキストに必要な機能を修正</t>
-    <rPh sb="8" eb="10">
-      <t>ヒツヨウ</t>
+    <t>新環境証明書システム</t>
+    <rPh sb="0" eb="6">
+      <t>シンカンキョウショウメイショ</t>
     </rPh>
-    <rPh sb="11" eb="13">
-      <t>キノウ</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>新環境証明書システム移行</t>
+    <rPh sb="0" eb="6">
+      <t>シンカンキョウショウメイショ</t>
     </rPh>
-    <rPh sb="14" eb="16">
-      <t>シュウセイ</t>
+    <rPh sb="10" eb="12">
+      <t>イコウ</t>
     </rPh>
     <phoneticPr fontId="51"/>
   </si>
@@ -2698,7 +2692,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="275">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3285,12 +3279,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="10" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6236,7 +6224,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
       <c r="B22" s="173" t="str">
         <f ca="1">TEXT(IF(変更来歴!AT2="",変更来歴!AT1,変更来歴!AT2),"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 06月 04日 ｒ1.1</v>
+        <v>2026年 06月 11日 dr1.2</v>
       </c>
       <c r="C22" s="174"/>
       <c r="D22" s="174"/>
@@ -7176,350 +7164,350 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="12" customHeight="1">
-      <c r="A1" s="219" t="s">
+      <c r="A1" s="217" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="202" t="s">
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="217" t="s">
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="202" t="s">
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="200" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="202"/>
-      <c r="Z1" s="202"/>
-      <c r="AA1" s="221" t="s">
-        <v>44</v>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="200"/>
+      <c r="AA1" s="219" t="s">
+        <v>43</v>
       </c>
-      <c r="AB1" s="221"/>
-      <c r="AC1" s="221"/>
-      <c r="AD1" s="221"/>
-      <c r="AE1" s="221"/>
-      <c r="AF1" s="221"/>
-      <c r="AG1" s="221"/>
-      <c r="AH1" s="221"/>
-      <c r="AI1" s="221"/>
-      <c r="AJ1" s="221"/>
-      <c r="AK1" s="206" t="s">
+      <c r="AB1" s="219"/>
+      <c r="AC1" s="219"/>
+      <c r="AD1" s="219"/>
+      <c r="AE1" s="219"/>
+      <c r="AF1" s="219"/>
+      <c r="AG1" s="219"/>
+      <c r="AH1" s="219"/>
+      <c r="AI1" s="219"/>
+      <c r="AJ1" s="219"/>
+      <c r="AK1" s="204" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="206"/>
-      <c r="AM1" s="206"/>
-      <c r="AN1" s="207" t="s">
-        <v>31</v>
+      <c r="AL1" s="204"/>
+      <c r="AM1" s="204"/>
+      <c r="AN1" s="205" t="s">
+        <v>30</v>
       </c>
-      <c r="AO1" s="207"/>
-      <c r="AP1" s="207"/>
-      <c r="AQ1" s="206" t="s">
+      <c r="AO1" s="205"/>
+      <c r="AP1" s="205"/>
+      <c r="AQ1" s="204" t="s">
         <v>9</v>
       </c>
-      <c r="AR1" s="206"/>
-      <c r="AS1" s="206"/>
-      <c r="AT1" s="209">
+      <c r="AR1" s="204"/>
+      <c r="AS1" s="204"/>
+      <c r="AT1" s="207">
         <f>AL7</f>
         <v>46163</v>
       </c>
-      <c r="AU1" s="209"/>
-      <c r="AV1" s="209"/>
-      <c r="AW1" s="209"/>
-      <c r="AX1" s="198" t="s">
+      <c r="AU1" s="207"/>
+      <c r="AV1" s="207"/>
+      <c r="AW1" s="207"/>
+      <c r="AX1" s="196" t="s">
         <v>10</v>
       </c>
-      <c r="AY1" s="199"/>
-      <c r="AZ1" s="199"/>
-      <c r="BA1" s="200"/>
+      <c r="AY1" s="197"/>
+      <c r="AZ1" s="197"/>
+      <c r="BA1" s="198"/>
     </row>
     <row r="2" spans="1:53">
-      <c r="A2" s="201" t="s">
-        <v>16</v>
+      <c r="A2" s="199" t="s">
+        <v>86</v>
       </c>
-      <c r="B2" s="201"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-      <c r="G2" s="201"/>
-      <c r="H2" s="201"/>
-      <c r="I2" s="202" t="s">
+      <c r="B2" s="199"/>
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="200" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="202"/>
-      <c r="K2" s="202"/>
-      <c r="L2" s="202"/>
-      <c r="M2" s="203" t="s">
-        <v>46</v>
+      <c r="J2" s="200"/>
+      <c r="K2" s="200"/>
+      <c r="L2" s="200"/>
+      <c r="M2" s="201" t="s">
+        <v>87</v>
       </c>
-      <c r="N2" s="204"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="204"/>
-      <c r="R2" s="204"/>
-      <c r="S2" s="204"/>
-      <c r="T2" s="204"/>
-      <c r="U2" s="204"/>
-      <c r="V2" s="204"/>
-      <c r="W2" s="205"/>
-      <c r="X2" s="202"/>
-      <c r="Y2" s="202"/>
-      <c r="Z2" s="202"/>
-      <c r="AA2" s="221"/>
-      <c r="AB2" s="221"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="221"/>
-      <c r="AE2" s="221"/>
-      <c r="AF2" s="221"/>
-      <c r="AG2" s="221"/>
-      <c r="AH2" s="221"/>
-      <c r="AI2" s="221"/>
-      <c r="AJ2" s="221"/>
-      <c r="AK2" s="206" t="s">
+      <c r="N2" s="202"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="202"/>
+      <c r="Q2" s="202"/>
+      <c r="R2" s="202"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="202"/>
+      <c r="U2" s="202"/>
+      <c r="V2" s="202"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="200"/>
+      <c r="Y2" s="200"/>
+      <c r="Z2" s="200"/>
+      <c r="AA2" s="219"/>
+      <c r="AB2" s="219"/>
+      <c r="AC2" s="219"/>
+      <c r="AD2" s="219"/>
+      <c r="AE2" s="219"/>
+      <c r="AF2" s="219"/>
+      <c r="AG2" s="219"/>
+      <c r="AH2" s="219"/>
+      <c r="AI2" s="219"/>
+      <c r="AJ2" s="219"/>
+      <c r="AK2" s="204" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="206"/>
-      <c r="AM2" s="206"/>
-      <c r="AN2" s="207" t="s">
-        <v>31</v>
+      <c r="AL2" s="204"/>
+      <c r="AM2" s="204"/>
+      <c r="AN2" s="205" t="s">
+        <v>30</v>
       </c>
-      <c r="AO2" s="207"/>
-      <c r="AP2" s="207"/>
-      <c r="AQ2" s="206" t="s">
+      <c r="AO2" s="205"/>
+      <c r="AP2" s="205"/>
+      <c r="AQ2" s="204" t="s">
         <v>13</v>
       </c>
-      <c r="AR2" s="206"/>
-      <c r="AS2" s="206"/>
-      <c r="AT2" s="209">
-        <v>46177</v>
+      <c r="AR2" s="204"/>
+      <c r="AS2" s="204"/>
+      <c r="AT2" s="207">
+        <v>46184</v>
       </c>
-      <c r="AU2" s="209"/>
-      <c r="AV2" s="209"/>
-      <c r="AW2" s="209"/>
-      <c r="AX2" s="210" t="s">
+      <c r="AU2" s="207"/>
+      <c r="AV2" s="207"/>
+      <c r="AW2" s="207"/>
+      <c r="AX2" s="208" t="s">
         <v>29</v>
       </c>
-      <c r="AY2" s="211"/>
-      <c r="AZ2" s="211"/>
-      <c r="BA2" s="212"/>
+      <c r="AY2" s="209"/>
+      <c r="AZ2" s="209"/>
+      <c r="BA2" s="210"/>
     </row>
     <row r="3" spans="1:53" ht="12" customHeight="1">
-      <c r="A3" s="216" t="s">
+      <c r="A3" s="214" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="216"/>
-      <c r="C3" s="216"/>
-      <c r="D3" s="216"/>
-      <c r="E3" s="216"/>
-      <c r="F3" s="216"/>
-      <c r="G3" s="216"/>
-      <c r="H3" s="216"/>
-      <c r="I3" s="202" t="s">
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="202"/>
-      <c r="K3" s="202"/>
-      <c r="L3" s="202"/>
-      <c r="M3" s="217"/>
-      <c r="N3" s="217"/>
-      <c r="O3" s="217"/>
-      <c r="P3" s="217"/>
-      <c r="Q3" s="217"/>
-      <c r="R3" s="217"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="217"/>
-      <c r="W3" s="217"/>
-      <c r="X3" s="202" t="s">
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
+      <c r="L3" s="200"/>
+      <c r="M3" s="215"/>
+      <c r="N3" s="215"/>
+      <c r="O3" s="215"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="200" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="202"/>
-      <c r="Z3" s="202"/>
-      <c r="AA3" s="218" t="s">
-        <v>45</v>
+      <c r="Y3" s="200"/>
+      <c r="Z3" s="200"/>
+      <c r="AA3" s="216" t="s">
+        <v>44</v>
       </c>
-      <c r="AB3" s="218"/>
-      <c r="AC3" s="218"/>
-      <c r="AD3" s="218"/>
-      <c r="AE3" s="218"/>
-      <c r="AF3" s="218"/>
-      <c r="AG3" s="218"/>
-      <c r="AH3" s="218"/>
-      <c r="AI3" s="218"/>
-      <c r="AJ3" s="218"/>
-      <c r="AK3" s="218"/>
-      <c r="AL3" s="218"/>
-      <c r="AM3" s="218"/>
-      <c r="AN3" s="218"/>
-      <c r="AO3" s="218"/>
-      <c r="AP3" s="218"/>
-      <c r="AQ3" s="206" t="s">
+      <c r="AB3" s="216"/>
+      <c r="AC3" s="216"/>
+      <c r="AD3" s="216"/>
+      <c r="AE3" s="216"/>
+      <c r="AF3" s="216"/>
+      <c r="AG3" s="216"/>
+      <c r="AH3" s="216"/>
+      <c r="AI3" s="216"/>
+      <c r="AJ3" s="216"/>
+      <c r="AK3" s="216"/>
+      <c r="AL3" s="216"/>
+      <c r="AM3" s="216"/>
+      <c r="AN3" s="216"/>
+      <c r="AO3" s="216"/>
+      <c r="AP3" s="216"/>
+      <c r="AQ3" s="204" t="s">
         <v>15</v>
       </c>
-      <c r="AR3" s="206"/>
-      <c r="AS3" s="206"/>
-      <c r="AT3" s="222" t="str">
+      <c r="AR3" s="204"/>
+      <c r="AS3" s="204"/>
+      <c r="AT3" s="220" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
-        <v>ｒ1.1</v>
+        <v>dr1.2</v>
       </c>
-      <c r="AU3" s="222"/>
-      <c r="AV3" s="222"/>
-      <c r="AW3" s="222"/>
-      <c r="AX3" s="213"/>
-      <c r="AY3" s="214"/>
-      <c r="AZ3" s="214"/>
-      <c r="BA3" s="215"/>
+      <c r="AU3" s="220"/>
+      <c r="AV3" s="220"/>
+      <c r="AW3" s="220"/>
+      <c r="AX3" s="211"/>
+      <c r="AY3" s="212"/>
+      <c r="AZ3" s="212"/>
+      <c r="BA3" s="213"/>
     </row>
     <row r="4" spans="1:53" ht="5.9" customHeight="1"/>
     <row r="5" spans="1:53" ht="14">
-      <c r="A5" s="220" t="s">
+      <c r="A5" s="218" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="220"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="220"/>
-      <c r="E5" s="220"/>
-      <c r="F5" s="220"/>
-      <c r="G5" s="220"/>
-      <c r="H5" s="220"/>
-      <c r="I5" s="220"/>
-      <c r="J5" s="220"/>
-      <c r="K5" s="220"/>
-      <c r="L5" s="220"/>
-      <c r="M5" s="220"/>
-      <c r="N5" s="220"/>
-      <c r="O5" s="220"/>
-      <c r="P5" s="220"/>
-      <c r="Q5" s="220"/>
-      <c r="R5" s="220"/>
-      <c r="S5" s="220"/>
-      <c r="T5" s="220"/>
-      <c r="U5" s="220"/>
-      <c r="V5" s="220"/>
-      <c r="W5" s="220"/>
-      <c r="X5" s="220"/>
-      <c r="Y5" s="220"/>
-      <c r="Z5" s="220"/>
-      <c r="AA5" s="220"/>
-      <c r="AB5" s="220"/>
-      <c r="AC5" s="220"/>
-      <c r="AD5" s="220"/>
-      <c r="AE5" s="220"/>
-      <c r="AF5" s="220"/>
-      <c r="AG5" s="220"/>
-      <c r="AH5" s="220"/>
-      <c r="AI5" s="220"/>
-      <c r="AJ5" s="220"/>
-      <c r="AK5" s="220"/>
-      <c r="AL5" s="220"/>
-      <c r="AM5" s="220"/>
-      <c r="AN5" s="220"/>
-      <c r="AO5" s="220"/>
-      <c r="AP5" s="220"/>
-      <c r="AQ5" s="220"/>
-      <c r="AR5" s="220"/>
-      <c r="AS5" s="220"/>
-      <c r="AT5" s="220"/>
-      <c r="AU5" s="220"/>
-      <c r="AV5" s="220"/>
-      <c r="AW5" s="220"/>
-      <c r="AX5" s="220"/>
-      <c r="AY5" s="220"/>
-      <c r="AZ5" s="220"/>
-      <c r="BA5" s="220"/>
+      <c r="B5" s="218"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="218"/>
+      <c r="E5" s="218"/>
+      <c r="F5" s="218"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="218"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="218"/>
+      <c r="K5" s="218"/>
+      <c r="L5" s="218"/>
+      <c r="M5" s="218"/>
+      <c r="N5" s="218"/>
+      <c r="O5" s="218"/>
+      <c r="P5" s="218"/>
+      <c r="Q5" s="218"/>
+      <c r="R5" s="218"/>
+      <c r="S5" s="218"/>
+      <c r="T5" s="218"/>
+      <c r="U5" s="218"/>
+      <c r="V5" s="218"/>
+      <c r="W5" s="218"/>
+      <c r="X5" s="218"/>
+      <c r="Y5" s="218"/>
+      <c r="Z5" s="218"/>
+      <c r="AA5" s="218"/>
+      <c r="AB5" s="218"/>
+      <c r="AC5" s="218"/>
+      <c r="AD5" s="218"/>
+      <c r="AE5" s="218"/>
+      <c r="AF5" s="218"/>
+      <c r="AG5" s="218"/>
+      <c r="AH5" s="218"/>
+      <c r="AI5" s="218"/>
+      <c r="AJ5" s="218"/>
+      <c r="AK5" s="218"/>
+      <c r="AL5" s="218"/>
+      <c r="AM5" s="218"/>
+      <c r="AN5" s="218"/>
+      <c r="AO5" s="218"/>
+      <c r="AP5" s="218"/>
+      <c r="AQ5" s="218"/>
+      <c r="AR5" s="218"/>
+      <c r="AS5" s="218"/>
+      <c r="AT5" s="218"/>
+      <c r="AU5" s="218"/>
+      <c r="AV5" s="218"/>
+      <c r="AW5" s="218"/>
+      <c r="AX5" s="218"/>
+      <c r="AY5" s="218"/>
+      <c r="AZ5" s="218"/>
+      <c r="BA5" s="218"/>
     </row>
     <row r="6" spans="1:53">
-      <c r="A6" s="223" t="s">
+      <c r="A6" s="221" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="224"/>
-      <c r="C6" s="208" t="s">
+      <c r="B6" s="222"/>
+      <c r="C6" s="206" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="208"/>
-      <c r="E6" s="208"/>
-      <c r="F6" s="208"/>
-      <c r="G6" s="208"/>
-      <c r="H6" s="208"/>
-      <c r="I6" s="208"/>
-      <c r="J6" s="208"/>
-      <c r="K6" s="208"/>
-      <c r="L6" s="208"/>
-      <c r="M6" s="208"/>
-      <c r="N6" s="208"/>
-      <c r="O6" s="208"/>
-      <c r="P6" s="208"/>
-      <c r="Q6" s="208" t="s">
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+      <c r="M6" s="206"/>
+      <c r="N6" s="206"/>
+      <c r="O6" s="206"/>
+      <c r="P6" s="206"/>
+      <c r="Q6" s="206" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="208"/>
-      <c r="S6" s="208"/>
-      <c r="T6" s="208"/>
-      <c r="U6" s="208"/>
-      <c r="V6" s="208"/>
-      <c r="W6" s="208"/>
-      <c r="X6" s="208"/>
-      <c r="Y6" s="208"/>
-      <c r="Z6" s="208"/>
-      <c r="AA6" s="208"/>
-      <c r="AB6" s="208"/>
-      <c r="AC6" s="208"/>
-      <c r="AD6" s="208"/>
-      <c r="AE6" s="208"/>
-      <c r="AF6" s="208"/>
-      <c r="AG6" s="208"/>
-      <c r="AH6" s="208"/>
-      <c r="AI6" s="208"/>
-      <c r="AJ6" s="208"/>
-      <c r="AK6" s="208"/>
-      <c r="AL6" s="208" t="s">
+      <c r="R6" s="206"/>
+      <c r="S6" s="206"/>
+      <c r="T6" s="206"/>
+      <c r="U6" s="206"/>
+      <c r="V6" s="206"/>
+      <c r="W6" s="206"/>
+      <c r="X6" s="206"/>
+      <c r="Y6" s="206"/>
+      <c r="Z6" s="206"/>
+      <c r="AA6" s="206"/>
+      <c r="AB6" s="206"/>
+      <c r="AC6" s="206"/>
+      <c r="AD6" s="206"/>
+      <c r="AE6" s="206"/>
+      <c r="AF6" s="206"/>
+      <c r="AG6" s="206"/>
+      <c r="AH6" s="206"/>
+      <c r="AI6" s="206"/>
+      <c r="AJ6" s="206"/>
+      <c r="AK6" s="206"/>
+      <c r="AL6" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="208"/>
-      <c r="AN6" s="208"/>
-      <c r="AO6" s="208"/>
-      <c r="AP6" s="208" t="s">
+      <c r="AM6" s="206"/>
+      <c r="AN6" s="206"/>
+      <c r="AO6" s="206"/>
+      <c r="AP6" s="206" t="s">
         <v>20</v>
       </c>
-      <c r="AQ6" s="208"/>
-      <c r="AR6" s="208"/>
-      <c r="AS6" s="208" t="s">
+      <c r="AQ6" s="206"/>
+      <c r="AR6" s="206"/>
+      <c r="AS6" s="206" t="s">
         <v>21</v>
       </c>
-      <c r="AT6" s="208"/>
-      <c r="AU6" s="208"/>
-      <c r="AV6" s="208" t="s">
+      <c r="AT6" s="206"/>
+      <c r="AU6" s="206"/>
+      <c r="AV6" s="206" t="s">
         <v>22</v>
       </c>
-      <c r="AW6" s="208"/>
-      <c r="AX6" s="208"/>
-      <c r="AY6" s="208"/>
-      <c r="AZ6" s="208"/>
-      <c r="BA6" s="208"/>
+      <c r="AW6" s="206"/>
+      <c r="AX6" s="206"/>
+      <c r="AY6" s="206"/>
+      <c r="AZ6" s="206"/>
+      <c r="BA6" s="206"/>
     </row>
     <row r="7" spans="1:53">
       <c r="A7" s="180" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="B7" s="180"/>
       <c r="C7" s="181" t="s">
@@ -7566,7 +7554,7 @@
       <c r="AN7" s="186"/>
       <c r="AO7" s="186"/>
       <c r="AP7" s="181" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AQ7" s="181"/>
       <c r="AR7" s="181"/>
@@ -7580,13 +7568,13 @@
       <c r="AZ7" s="181"/>
       <c r="BA7" s="181"/>
     </row>
-    <row r="8" spans="1:53" ht="26.5" customHeight="1">
+    <row r="8" spans="1:53">
       <c r="A8" s="180" t="s">
         <v>81</v>
       </c>
       <c r="B8" s="180"/>
       <c r="C8" s="182" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D8" s="182"/>
       <c r="E8" s="182"/>
@@ -7602,7 +7590,7 @@
       <c r="O8" s="182"/>
       <c r="P8" s="182"/>
       <c r="Q8" s="192" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R8" s="193"/>
       <c r="S8" s="193"/>
@@ -7631,7 +7619,7 @@
       <c r="AN8" s="188"/>
       <c r="AO8" s="189"/>
       <c r="AP8" s="181" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AQ8" s="181"/>
       <c r="AR8" s="181"/>
@@ -7646,9 +7634,13 @@
       <c r="BA8" s="181"/>
     </row>
     <row r="9" spans="1:53">
-      <c r="A9" s="196"/>
-      <c r="B9" s="197"/>
-      <c r="C9" s="181"/>
+      <c r="A9" s="180" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="180"/>
+      <c r="C9" s="181" t="s">
+        <v>83</v>
+      </c>
       <c r="D9" s="181"/>
       <c r="E9" s="181"/>
       <c r="F9" s="181"/>
@@ -7662,7 +7654,9 @@
       <c r="N9" s="181"/>
       <c r="O9" s="181"/>
       <c r="P9" s="181"/>
-      <c r="Q9" s="192"/>
+      <c r="Q9" s="192" t="s">
+        <v>84</v>
+      </c>
       <c r="R9" s="193"/>
       <c r="S9" s="193"/>
       <c r="T9" s="193"/>
@@ -7683,11 +7677,15 @@
       <c r="AI9" s="193"/>
       <c r="AJ9" s="193"/>
       <c r="AK9" s="194"/>
-      <c r="AL9" s="187"/>
+      <c r="AL9" s="187">
+        <v>46184</v>
+      </c>
       <c r="AM9" s="188"/>
       <c r="AN9" s="188"/>
       <c r="AO9" s="189"/>
-      <c r="AP9" s="181"/>
+      <c r="AP9" s="181" t="s">
+        <v>30</v>
+      </c>
       <c r="AQ9" s="181"/>
       <c r="AR9" s="181"/>
       <c r="AS9" s="181"/>
@@ -9333,300 +9331,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" ht="12" customHeight="1">
-      <c r="A1" s="219" t="s">
+      <c r="A1" s="217" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="202" t="s">
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="217" t="str">
+      <c r="J1" s="200"/>
+      <c r="K1" s="200"/>
+      <c r="L1" s="200"/>
+      <c r="M1" s="215" t="str">
         <f>変更来歴!M1</f>
         <v>ヒロセ電機株式会社</v>
       </c>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="202" t="s">
+      <c r="N1" s="215"/>
+      <c r="O1" s="215"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="215"/>
+      <c r="T1" s="215"/>
+      <c r="U1" s="215"/>
+      <c r="V1" s="215"/>
+      <c r="W1" s="215"/>
+      <c r="X1" s="200" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="202"/>
-      <c r="Z1" s="202"/>
-      <c r="AA1" s="221" t="str">
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="200"/>
+      <c r="AA1" s="219" t="str">
         <f>変更来歴!AA1</f>
         <v>お知らせ登録</v>
       </c>
-      <c r="AB1" s="221"/>
-      <c r="AC1" s="221"/>
-      <c r="AD1" s="221"/>
-      <c r="AE1" s="221"/>
-      <c r="AF1" s="221"/>
-      <c r="AG1" s="221"/>
-      <c r="AH1" s="221"/>
-      <c r="AI1" s="221"/>
-      <c r="AJ1" s="221"/>
-      <c r="AK1" s="206" t="s">
+      <c r="AB1" s="219"/>
+      <c r="AC1" s="219"/>
+      <c r="AD1" s="219"/>
+      <c r="AE1" s="219"/>
+      <c r="AF1" s="219"/>
+      <c r="AG1" s="219"/>
+      <c r="AH1" s="219"/>
+      <c r="AI1" s="219"/>
+      <c r="AJ1" s="219"/>
+      <c r="AK1" s="204" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="206"/>
-      <c r="AM1" s="206"/>
-      <c r="AN1" s="207" t="str">
+      <c r="AL1" s="204"/>
+      <c r="AM1" s="204"/>
+      <c r="AN1" s="205" t="str">
         <f>変更来歴!AP7</f>
         <v>古竹</v>
       </c>
-      <c r="AO1" s="207"/>
-      <c r="AP1" s="207"/>
-      <c r="AQ1" s="207"/>
-      <c r="AR1" s="207"/>
-      <c r="AS1" s="206" t="s">
+      <c r="AO1" s="205"/>
+      <c r="AP1" s="205"/>
+      <c r="AQ1" s="205"/>
+      <c r="AR1" s="205"/>
+      <c r="AS1" s="204" t="s">
         <v>9</v>
       </c>
-      <c r="AT1" s="206"/>
-      <c r="AU1" s="206"/>
-      <c r="AV1" s="209">
+      <c r="AT1" s="204"/>
+      <c r="AU1" s="204"/>
+      <c r="AV1" s="207">
         <f>変更来歴!AL7</f>
         <v>46163</v>
       </c>
-      <c r="AW1" s="222"/>
-      <c r="AX1" s="222"/>
-      <c r="AY1" s="222"/>
-      <c r="AZ1" s="198" t="s">
+      <c r="AW1" s="220"/>
+      <c r="AX1" s="220"/>
+      <c r="AY1" s="220"/>
+      <c r="AZ1" s="196" t="s">
         <v>10</v>
       </c>
-      <c r="BA1" s="199"/>
-      <c r="BB1" s="199"/>
-      <c r="BC1" s="200"/>
+      <c r="BA1" s="197"/>
+      <c r="BB1" s="197"/>
+      <c r="BC1" s="198"/>
     </row>
     <row r="2" spans="1:78">
-      <c r="A2" s="201" t="s">
+      <c r="A2" s="199" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="201"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
-      <c r="G2" s="201"/>
-      <c r="H2" s="201"/>
-      <c r="I2" s="202" t="s">
+      <c r="B2" s="199"/>
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="199"/>
+      <c r="G2" s="199"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="200" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="202"/>
-      <c r="K2" s="202"/>
-      <c r="L2" s="202"/>
-      <c r="M2" s="225" t="str">
+      <c r="J2" s="200"/>
+      <c r="K2" s="200"/>
+      <c r="L2" s="200"/>
+      <c r="M2" s="223" t="str">
         <f>変更来歴!M2</f>
-        <v>新環境証明書</v>
+        <v>新環境証明書システム移行</v>
       </c>
-      <c r="N2" s="225"/>
-      <c r="O2" s="225"/>
-      <c r="P2" s="225"/>
-      <c r="Q2" s="225"/>
-      <c r="R2" s="225"/>
-      <c r="S2" s="225"/>
-      <c r="T2" s="225"/>
-      <c r="U2" s="225"/>
-      <c r="V2" s="225"/>
-      <c r="W2" s="225"/>
-      <c r="X2" s="202"/>
-      <c r="Y2" s="202"/>
-      <c r="Z2" s="202"/>
-      <c r="AA2" s="221"/>
-      <c r="AB2" s="221"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="221"/>
-      <c r="AE2" s="221"/>
-      <c r="AF2" s="221"/>
-      <c r="AG2" s="221"/>
-      <c r="AH2" s="221"/>
-      <c r="AI2" s="221"/>
-      <c r="AJ2" s="221"/>
-      <c r="AK2" s="206" t="s">
+      <c r="N2" s="223"/>
+      <c r="O2" s="223"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="223"/>
+      <c r="T2" s="223"/>
+      <c r="U2" s="223"/>
+      <c r="V2" s="223"/>
+      <c r="W2" s="223"/>
+      <c r="X2" s="200"/>
+      <c r="Y2" s="200"/>
+      <c r="Z2" s="200"/>
+      <c r="AA2" s="219"/>
+      <c r="AB2" s="219"/>
+      <c r="AC2" s="219"/>
+      <c r="AD2" s="219"/>
+      <c r="AE2" s="219"/>
+      <c r="AF2" s="219"/>
+      <c r="AG2" s="219"/>
+      <c r="AH2" s="219"/>
+      <c r="AI2" s="219"/>
+      <c r="AJ2" s="219"/>
+      <c r="AK2" s="204" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="206"/>
-      <c r="AM2" s="206"/>
-      <c r="AN2" s="207" t="str">
+      <c r="AL2" s="204"/>
+      <c r="AM2" s="204"/>
+      <c r="AN2" s="205" t="str">
         <f ca="1">INDIRECT("変更来歴!AP" &amp; COUNTA(変更来歴!AP7:'変更来歴'!AP39) + 6)</f>
         <v>古竹</v>
       </c>
-      <c r="AO2" s="207"/>
-      <c r="AP2" s="207"/>
-      <c r="AQ2" s="207"/>
-      <c r="AR2" s="207"/>
-      <c r="AS2" s="206" t="s">
+      <c r="AO2" s="205"/>
+      <c r="AP2" s="205"/>
+      <c r="AQ2" s="205"/>
+      <c r="AR2" s="205"/>
+      <c r="AS2" s="204" t="s">
         <v>13</v>
       </c>
-      <c r="AT2" s="206"/>
-      <c r="AU2" s="206"/>
-      <c r="AV2" s="209">
+      <c r="AT2" s="204"/>
+      <c r="AU2" s="204"/>
+      <c r="AV2" s="207">
         <f ca="1">INDIRECT("変更来歴!AL" &amp; COUNTA(変更来歴!AL7:'変更来歴'!AL39) + 6)</f>
-        <v>46177</v>
+        <v>46184</v>
       </c>
-      <c r="AW2" s="222"/>
-      <c r="AX2" s="222"/>
-      <c r="AY2" s="222"/>
-      <c r="AZ2" s="210" t="str">
+      <c r="AW2" s="220"/>
+      <c r="AX2" s="220"/>
+      <c r="AY2" s="220"/>
+      <c r="AZ2" s="208" t="str">
         <f>変更来歴!AX2</f>
         <v>IMWF-53</v>
       </c>
-      <c r="BA2" s="211"/>
-      <c r="BB2" s="211"/>
-      <c r="BC2" s="212"/>
+      <c r="BA2" s="209"/>
+      <c r="BB2" s="209"/>
+      <c r="BC2" s="210"/>
     </row>
     <row r="3" spans="1:78" ht="12" customHeight="1">
-      <c r="A3" s="216" t="str">
+      <c r="A3" s="214" t="str">
         <f>変更来歴!A3</f>
         <v>画面設計書</v>
       </c>
-      <c r="B3" s="216"/>
-      <c r="C3" s="216"/>
-      <c r="D3" s="216"/>
-      <c r="E3" s="216"/>
-      <c r="F3" s="216"/>
-      <c r="G3" s="216"/>
-      <c r="H3" s="216"/>
-      <c r="I3" s="202" t="s">
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="202"/>
-      <c r="K3" s="202"/>
-      <c r="L3" s="202"/>
-      <c r="M3" s="217" t="str">
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
+      <c r="L3" s="200"/>
+      <c r="M3" s="215" t="str">
         <f ca="1">RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1)))</f>
         <v>お知らせ登録画面</v>
       </c>
-      <c r="N3" s="217"/>
-      <c r="O3" s="217"/>
-      <c r="P3" s="217"/>
-      <c r="Q3" s="217"/>
-      <c r="R3" s="217"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="217"/>
-      <c r="W3" s="217"/>
-      <c r="X3" s="202" t="s">
+      <c r="N3" s="215"/>
+      <c r="O3" s="215"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="200" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="202"/>
-      <c r="Z3" s="202"/>
-      <c r="AA3" s="218" t="str">
+      <c r="Y3" s="200"/>
+      <c r="Z3" s="200"/>
+      <c r="AA3" s="216" t="str">
         <f ca="1">MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename"))) &amp; "画面"</f>
         <v>変更来歴画面</v>
       </c>
-      <c r="AB3" s="218"/>
-      <c r="AC3" s="218"/>
-      <c r="AD3" s="218"/>
-      <c r="AE3" s="218"/>
-      <c r="AF3" s="218"/>
-      <c r="AG3" s="218"/>
-      <c r="AH3" s="218"/>
-      <c r="AI3" s="218"/>
-      <c r="AJ3" s="218"/>
-      <c r="AK3" s="218"/>
-      <c r="AL3" s="218"/>
-      <c r="AM3" s="218"/>
-      <c r="AN3" s="218"/>
-      <c r="AO3" s="218"/>
-      <c r="AP3" s="218"/>
-      <c r="AQ3" s="218"/>
-      <c r="AR3" s="218"/>
-      <c r="AS3" s="206" t="s">
+      <c r="AB3" s="216"/>
+      <c r="AC3" s="216"/>
+      <c r="AD3" s="216"/>
+      <c r="AE3" s="216"/>
+      <c r="AF3" s="216"/>
+      <c r="AG3" s="216"/>
+      <c r="AH3" s="216"/>
+      <c r="AI3" s="216"/>
+      <c r="AJ3" s="216"/>
+      <c r="AK3" s="216"/>
+      <c r="AL3" s="216"/>
+      <c r="AM3" s="216"/>
+      <c r="AN3" s="216"/>
+      <c r="AO3" s="216"/>
+      <c r="AP3" s="216"/>
+      <c r="AQ3" s="216"/>
+      <c r="AR3" s="216"/>
+      <c r="AS3" s="204" t="s">
         <v>15</v>
       </c>
-      <c r="AT3" s="206"/>
-      <c r="AU3" s="206"/>
-      <c r="AV3" s="222" t="str">
+      <c r="AT3" s="204"/>
+      <c r="AU3" s="204"/>
+      <c r="AV3" s="220" t="str">
         <f ca="1">INDIRECT("変更来歴!A" &amp; COUNTA(変更来歴!A7:'変更来歴'!A39) + 6)</f>
-        <v>ｒ1.1</v>
+        <v>dr1.2</v>
       </c>
-      <c r="AW3" s="222"/>
-      <c r="AX3" s="222"/>
-      <c r="AY3" s="222"/>
-      <c r="AZ3" s="213"/>
-      <c r="BA3" s="214"/>
-      <c r="BB3" s="214"/>
-      <c r="BC3" s="215"/>
+      <c r="AW3" s="220"/>
+      <c r="AX3" s="220"/>
+      <c r="AY3" s="220"/>
+      <c r="AZ3" s="211"/>
+      <c r="BA3" s="212"/>
+      <c r="BB3" s="212"/>
+      <c r="BC3" s="213"/>
     </row>
     <row r="4" spans="1:78" ht="5.9" customHeight="1"/>
     <row r="5" spans="1:78" ht="13.5" customHeight="1">
-      <c r="A5" s="229" t="str">
+      <c r="A5" s="227" t="str">
         <f ca="1">"画面レイアウト"&amp;"("&amp;MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename")))&amp;")"</f>
         <v>画面レイアウト(変更来歴)</v>
       </c>
-      <c r="B5" s="230"/>
-      <c r="C5" s="230"/>
-      <c r="D5" s="230"/>
-      <c r="E5" s="230"/>
-      <c r="F5" s="230"/>
-      <c r="G5" s="230"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="230"/>
-      <c r="K5" s="230"/>
-      <c r="L5" s="230"/>
-      <c r="M5" s="230"/>
-      <c r="N5" s="230"/>
-      <c r="O5" s="230"/>
-      <c r="P5" s="230"/>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="230"/>
-      <c r="S5" s="230"/>
-      <c r="T5" s="230"/>
-      <c r="U5" s="230"/>
-      <c r="V5" s="230"/>
-      <c r="W5" s="230"/>
-      <c r="X5" s="230"/>
-      <c r="Y5" s="230"/>
-      <c r="Z5" s="230"/>
-      <c r="AA5" s="230"/>
-      <c r="AB5" s="230"/>
-      <c r="AC5" s="230"/>
-      <c r="AD5" s="230"/>
-      <c r="AE5" s="230"/>
-      <c r="AF5" s="230"/>
-      <c r="AG5" s="230"/>
-      <c r="AH5" s="230"/>
-      <c r="AI5" s="230"/>
-      <c r="AJ5" s="230"/>
-      <c r="AK5" s="230"/>
-      <c r="AL5" s="230"/>
-      <c r="AM5" s="230"/>
-      <c r="AN5" s="230"/>
-      <c r="AO5" s="230"/>
-      <c r="AP5" s="230"/>
-      <c r="AQ5" s="230"/>
-      <c r="AR5" s="230"/>
-      <c r="AS5" s="230"/>
-      <c r="AT5" s="230"/>
-      <c r="AU5" s="230"/>
-      <c r="AV5" s="230"/>
-      <c r="AW5" s="230"/>
-      <c r="AX5" s="230"/>
-      <c r="AY5" s="230"/>
-      <c r="AZ5" s="230"/>
-      <c r="BA5" s="231"/>
-      <c r="BB5" s="232" t="s">
+      <c r="B5" s="228"/>
+      <c r="C5" s="228"/>
+      <c r="D5" s="228"/>
+      <c r="E5" s="228"/>
+      <c r="F5" s="228"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="228"/>
+      <c r="K5" s="228"/>
+      <c r="L5" s="228"/>
+      <c r="M5" s="228"/>
+      <c r="N5" s="228"/>
+      <c r="O5" s="228"/>
+      <c r="P5" s="228"/>
+      <c r="Q5" s="228"/>
+      <c r="R5" s="228"/>
+      <c r="S5" s="228"/>
+      <c r="T5" s="228"/>
+      <c r="U5" s="228"/>
+      <c r="V5" s="228"/>
+      <c r="W5" s="228"/>
+      <c r="X5" s="228"/>
+      <c r="Y5" s="228"/>
+      <c r="Z5" s="228"/>
+      <c r="AA5" s="228"/>
+      <c r="AB5" s="228"/>
+      <c r="AC5" s="228"/>
+      <c r="AD5" s="228"/>
+      <c r="AE5" s="228"/>
+      <c r="AF5" s="228"/>
+      <c r="AG5" s="228"/>
+      <c r="AH5" s="228"/>
+      <c r="AI5" s="228"/>
+      <c r="AJ5" s="228"/>
+      <c r="AK5" s="228"/>
+      <c r="AL5" s="228"/>
+      <c r="AM5" s="228"/>
+      <c r="AN5" s="228"/>
+      <c r="AO5" s="228"/>
+      <c r="AP5" s="228"/>
+      <c r="AQ5" s="228"/>
+      <c r="AR5" s="228"/>
+      <c r="AS5" s="228"/>
+      <c r="AT5" s="228"/>
+      <c r="AU5" s="228"/>
+      <c r="AV5" s="228"/>
+      <c r="AW5" s="228"/>
+      <c r="AX5" s="228"/>
+      <c r="AY5" s="228"/>
+      <c r="AZ5" s="228"/>
+      <c r="BA5" s="229"/>
+      <c r="BB5" s="230" t="s">
         <v>24</v>
       </c>
-      <c r="BC5" s="233"/>
+      <c r="BC5" s="231"/>
       <c r="BD5" s="24"/>
     </row>
     <row r="6" spans="1:78" ht="13.5" customHeight="1">
@@ -9846,11 +9844,11 @@
       <c r="BB7" s="36"/>
       <c r="BC7" s="37"/>
       <c r="BD7" s="34"/>
-      <c r="BE7" s="226" t="s">
-        <v>54</v>
+      <c r="BE7" s="224" t="s">
+        <v>52</v>
       </c>
-      <c r="BF7" s="227"/>
-      <c r="BG7" s="228"/>
+      <c r="BF7" s="225"/>
+      <c r="BG7" s="226"/>
       <c r="BH7" s="43"/>
       <c r="BI7" s="43"/>
       <c r="BJ7" s="43"/>
@@ -9868,7 +9866,7 @@
     <row r="8" spans="1:78" ht="19.5" customHeight="1">
       <c r="A8" s="49"/>
       <c r="B8" s="101" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="60"/>
       <c r="D8" s="41"/>
@@ -9925,7 +9923,7 @@
       <c r="BC8" s="37"/>
       <c r="BD8" s="34"/>
       <c r="BE8" s="172" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="BF8" s="170"/>
       <c r="BG8" s="170"/>
@@ -10103,7 +10101,7 @@
       <c r="A11" s="49"/>
       <c r="B11" s="107"/>
       <c r="C11" s="128" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" s="75"/>
       <c r="E11" s="75"/>
@@ -10180,7 +10178,7 @@
       <c r="A12" s="49"/>
       <c r="B12" s="107"/>
       <c r="C12" s="100" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" s="75"/>
       <c r="E12" s="75"/>
@@ -10336,7 +10334,7 @@
       <c r="A14" s="49"/>
       <c r="B14" s="107"/>
       <c r="C14" s="129" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
@@ -11064,7 +11062,7 @@
       <c r="A24" s="49"/>
       <c r="B24" s="107"/>
       <c r="C24" s="129" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
@@ -12155,7 +12153,7 @@
       <c r="A39" s="49"/>
       <c r="B39" s="130"/>
       <c r="C39" s="131" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D39" s="132"/>
       <c r="E39" s="132"/>
@@ -12231,7 +12229,7 @@
       <c r="A40" s="49"/>
       <c r="B40" s="107"/>
       <c r="C40" s="100" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D40" s="75"/>
       <c r="E40" s="75"/>
@@ -12381,7 +12379,7 @@
       <c r="A42" s="49"/>
       <c r="B42" s="107"/>
       <c r="C42" s="129" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D42" s="51"/>
       <c r="E42" s="51"/>
@@ -13109,7 +13107,7 @@
       <c r="A52" s="49"/>
       <c r="B52" s="107"/>
       <c r="C52" s="129" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D52" s="51"/>
       <c r="E52" s="51"/>
@@ -23874,17 +23872,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:78" ht="12.75" customHeight="1">
-      <c r="A1" s="262" t="s">
-        <v>32</v>
+      <c r="A1" s="260" t="s">
+        <v>31</v>
       </c>
-      <c r="B1" s="262"/>
-      <c r="C1" s="262"/>
-      <c r="D1" s="262"/>
-      <c r="E1" s="262"/>
-      <c r="F1" s="262"/>
-      <c r="G1" s="262"/>
-      <c r="H1" s="262"/>
-      <c r="I1" s="262"/>
+      <c r="B1" s="260"/>
+      <c r="C1" s="260"/>
+      <c r="D1" s="260"/>
+      <c r="E1" s="260"/>
+      <c r="F1" s="260"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
       <c r="J1" s="136"/>
       <c r="K1" s="136"/>
       <c r="L1" s="136"/>
@@ -23956,530 +23954,530 @@
       <c r="BZ1" s="137"/>
     </row>
     <row r="2" spans="1:78" ht="12.75" customHeight="1">
-      <c r="A2" s="263" t="s">
+      <c r="A2" s="261" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="261"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="261"/>
+      <c r="G2" s="261"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="261"/>
+      <c r="J2" s="261"/>
+      <c r="K2" s="261"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="261"/>
+      <c r="O2" s="261"/>
+      <c r="P2" s="261"/>
+      <c r="Q2" s="262"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="262"/>
+      <c r="AA2" s="262"/>
+      <c r="AB2" s="262"/>
+      <c r="AC2" s="262"/>
+      <c r="AD2" s="262"/>
+      <c r="AE2" s="262"/>
+      <c r="AF2" s="262"/>
+      <c r="AG2" s="262"/>
+      <c r="AH2" s="262"/>
+      <c r="AI2" s="262"/>
+      <c r="AJ2" s="262"/>
+      <c r="AK2" s="262"/>
+      <c r="AL2" s="262"/>
+      <c r="AM2" s="262"/>
+      <c r="AN2" s="262"/>
+      <c r="AO2" s="262"/>
+      <c r="AP2" s="262"/>
+      <c r="AQ2" s="262"/>
+      <c r="AR2" s="262"/>
+      <c r="AS2" s="262"/>
+      <c r="AT2" s="262"/>
+      <c r="AU2" s="262"/>
+      <c r="AV2" s="262"/>
+      <c r="AW2" s="262"/>
+      <c r="AX2" s="262"/>
+      <c r="AY2" s="262"/>
+      <c r="AZ2" s="262"/>
+      <c r="BA2" s="262"/>
+      <c r="BB2" s="262"/>
+      <c r="BC2" s="262"/>
+      <c r="BD2" s="262"/>
+      <c r="BE2" s="262"/>
+      <c r="BF2" s="262"/>
+      <c r="BG2" s="262"/>
+      <c r="BH2" s="262"/>
+      <c r="BI2" s="262"/>
+      <c r="BJ2" s="262"/>
+      <c r="BK2" s="262"/>
+      <c r="BL2" s="262"/>
+      <c r="BM2" s="262"/>
+      <c r="BN2" s="262"/>
+      <c r="BO2" s="262"/>
+      <c r="BP2" s="262"/>
+      <c r="BQ2" s="262"/>
+      <c r="BR2" s="262"/>
+      <c r="BS2" s="262"/>
+      <c r="BT2" s="262"/>
+      <c r="BU2" s="262"/>
+      <c r="BV2" s="262"/>
+      <c r="BW2" s="262"/>
+      <c r="BX2" s="262"/>
+      <c r="BY2" s="262"/>
+      <c r="BZ2" s="262"/>
+    </row>
+    <row r="3" spans="1:78" ht="27.75" customHeight="1">
+      <c r="A3" s="263" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="263"/>
-      <c r="C2" s="263"/>
-      <c r="D2" s="263"/>
-      <c r="E2" s="263"/>
-      <c r="F2" s="263"/>
-      <c r="G2" s="263"/>
-      <c r="H2" s="263"/>
-      <c r="I2" s="263"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="263"/>
-      <c r="L2" s="263"/>
-      <c r="M2" s="263"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="263"/>
-      <c r="P2" s="263"/>
-      <c r="Q2" s="264"/>
-      <c r="R2" s="264"/>
-      <c r="S2" s="264"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="264"/>
-      <c r="V2" s="264"/>
-      <c r="W2" s="264"/>
-      <c r="X2" s="264"/>
-      <c r="Y2" s="264"/>
-      <c r="Z2" s="264"/>
-      <c r="AA2" s="264"/>
-      <c r="AB2" s="264"/>
-      <c r="AC2" s="264"/>
-      <c r="AD2" s="264"/>
-      <c r="AE2" s="264"/>
-      <c r="AF2" s="264"/>
-      <c r="AG2" s="264"/>
-      <c r="AH2" s="264"/>
-      <c r="AI2" s="264"/>
-      <c r="AJ2" s="264"/>
-      <c r="AK2" s="264"/>
-      <c r="AL2" s="264"/>
-      <c r="AM2" s="264"/>
-      <c r="AN2" s="264"/>
-      <c r="AO2" s="264"/>
-      <c r="AP2" s="264"/>
-      <c r="AQ2" s="264"/>
-      <c r="AR2" s="264"/>
-      <c r="AS2" s="264"/>
-      <c r="AT2" s="264"/>
-      <c r="AU2" s="264"/>
-      <c r="AV2" s="264"/>
-      <c r="AW2" s="264"/>
-      <c r="AX2" s="264"/>
-      <c r="AY2" s="264"/>
-      <c r="AZ2" s="264"/>
-      <c r="BA2" s="264"/>
-      <c r="BB2" s="264"/>
-      <c r="BC2" s="264"/>
-      <c r="BD2" s="264"/>
-      <c r="BE2" s="264"/>
-      <c r="BF2" s="264"/>
-      <c r="BG2" s="264"/>
-      <c r="BH2" s="264"/>
-      <c r="BI2" s="264"/>
-      <c r="BJ2" s="264"/>
-      <c r="BK2" s="264"/>
-      <c r="BL2" s="264"/>
-      <c r="BM2" s="264"/>
-      <c r="BN2" s="264"/>
-      <c r="BO2" s="264"/>
-      <c r="BP2" s="264"/>
-      <c r="BQ2" s="264"/>
-      <c r="BR2" s="264"/>
-      <c r="BS2" s="264"/>
-      <c r="BT2" s="264"/>
-      <c r="BU2" s="264"/>
-      <c r="BV2" s="264"/>
-      <c r="BW2" s="264"/>
-      <c r="BX2" s="264"/>
-      <c r="BY2" s="264"/>
-      <c r="BZ2" s="264"/>
-    </row>
-    <row r="3" spans="1:78" ht="27.75" customHeight="1">
-      <c r="A3" s="265" t="s">
+      <c r="B3" s="264"/>
+      <c r="C3" s="264" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="266"/>
-      <c r="C3" s="266" t="s">
+      <c r="D3" s="264"/>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="264"/>
+      <c r="I3" s="264"/>
+      <c r="J3" s="264"/>
+      <c r="K3" s="264"/>
+      <c r="L3" s="264"/>
+      <c r="M3" s="264"/>
+      <c r="N3" s="264"/>
+      <c r="O3" s="264"/>
+      <c r="P3" s="264"/>
+      <c r="Q3" s="265" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="266"/>
-      <c r="E3" s="266"/>
-      <c r="F3" s="266"/>
-      <c r="G3" s="266"/>
-      <c r="H3" s="266"/>
-      <c r="I3" s="266"/>
-      <c r="J3" s="266"/>
-      <c r="K3" s="266"/>
-      <c r="L3" s="266"/>
-      <c r="M3" s="266"/>
-      <c r="N3" s="266"/>
-      <c r="O3" s="266"/>
-      <c r="P3" s="266"/>
-      <c r="Q3" s="267" t="s">
+      <c r="R3" s="266"/>
+      <c r="S3" s="266"/>
+      <c r="T3" s="266"/>
+      <c r="U3" s="266"/>
+      <c r="V3" s="266"/>
+      <c r="W3" s="266"/>
+      <c r="X3" s="266"/>
+      <c r="Y3" s="266"/>
+      <c r="Z3" s="266"/>
+      <c r="AA3" s="267"/>
+      <c r="AB3" s="265" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC3" s="266"/>
+      <c r="AD3" s="266"/>
+      <c r="AE3" s="266"/>
+      <c r="AF3" s="266"/>
+      <c r="AG3" s="266"/>
+      <c r="AH3" s="266"/>
+      <c r="AI3" s="265" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ3" s="266"/>
+      <c r="AK3" s="266"/>
+      <c r="AL3" s="266"/>
+      <c r="AM3" s="266"/>
+      <c r="AN3" s="266"/>
+      <c r="AO3" s="266"/>
+      <c r="AP3" s="266"/>
+      <c r="AQ3" s="266"/>
+      <c r="AR3" s="263" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="268"/>
-      <c r="S3" s="268"/>
-      <c r="T3" s="268"/>
-      <c r="U3" s="268"/>
-      <c r="V3" s="268"/>
-      <c r="W3" s="268"/>
-      <c r="X3" s="268"/>
-      <c r="Y3" s="268"/>
-      <c r="Z3" s="268"/>
-      <c r="AA3" s="269"/>
-      <c r="AB3" s="267" t="s">
-        <v>43</v>
+      <c r="AS3" s="263"/>
+      <c r="AT3" s="263"/>
+      <c r="AU3" s="263"/>
+      <c r="AV3" s="263"/>
+      <c r="AW3" s="263"/>
+      <c r="AX3" s="263"/>
+      <c r="AY3" s="263"/>
+      <c r="AZ3" s="263"/>
+      <c r="BA3" s="263"/>
+      <c r="BB3" s="263"/>
+      <c r="BC3" s="263"/>
+      <c r="BD3" s="263"/>
+      <c r="BE3" s="263"/>
+      <c r="BF3" s="263"/>
+      <c r="BG3" s="263"/>
+      <c r="BH3" s="263"/>
+      <c r="BI3" s="263"/>
+      <c r="BJ3" s="263"/>
+      <c r="BK3" s="263"/>
+      <c r="BL3" s="263"/>
+      <c r="BM3" s="263"/>
+      <c r="BN3" s="263"/>
+      <c r="BO3" s="263"/>
+      <c r="BP3" s="263"/>
+      <c r="BQ3" s="263"/>
+      <c r="BR3" s="263"/>
+      <c r="BS3" s="263"/>
+      <c r="BT3" s="263"/>
+      <c r="BU3" s="263"/>
+      <c r="BV3" s="263"/>
+      <c r="BW3" s="263"/>
+      <c r="BX3" s="263"/>
+      <c r="BY3" s="263"/>
+      <c r="BZ3" s="263"/>
+    </row>
+    <row r="4" spans="1:78" ht="27.75" customHeight="1">
+      <c r="A4" s="264"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="271" t="s">
+        <v>37</v>
       </c>
-      <c r="AC3" s="268"/>
-      <c r="AD3" s="268"/>
-      <c r="AE3" s="268"/>
-      <c r="AF3" s="268"/>
-      <c r="AG3" s="268"/>
-      <c r="AH3" s="268"/>
-      <c r="AI3" s="267" t="s">
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="271"/>
+      <c r="L4" s="271"/>
+      <c r="M4" s="271"/>
+      <c r="N4" s="271"/>
+      <c r="O4" s="271"/>
+      <c r="P4" s="271"/>
+      <c r="Q4" s="268"/>
+      <c r="R4" s="269"/>
+      <c r="S4" s="269"/>
+      <c r="T4" s="269"/>
+      <c r="U4" s="269"/>
+      <c r="V4" s="269"/>
+      <c r="W4" s="269"/>
+      <c r="X4" s="269"/>
+      <c r="Y4" s="269"/>
+      <c r="Z4" s="269"/>
+      <c r="AA4" s="270"/>
+      <c r="AB4" s="268"/>
+      <c r="AC4" s="269"/>
+      <c r="AD4" s="269"/>
+      <c r="AE4" s="269"/>
+      <c r="AF4" s="269"/>
+      <c r="AG4" s="269"/>
+      <c r="AH4" s="269"/>
+      <c r="AI4" s="268"/>
+      <c r="AJ4" s="269"/>
+      <c r="AK4" s="269"/>
+      <c r="AL4" s="269"/>
+      <c r="AM4" s="269"/>
+      <c r="AN4" s="269"/>
+      <c r="AO4" s="269"/>
+      <c r="AP4" s="269"/>
+      <c r="AQ4" s="269"/>
+      <c r="AR4" s="263"/>
+      <c r="AS4" s="263"/>
+      <c r="AT4" s="263"/>
+      <c r="AU4" s="263"/>
+      <c r="AV4" s="263"/>
+      <c r="AW4" s="263"/>
+      <c r="AX4" s="263"/>
+      <c r="AY4" s="263"/>
+      <c r="AZ4" s="263"/>
+      <c r="BA4" s="263"/>
+      <c r="BB4" s="263"/>
+      <c r="BC4" s="263"/>
+      <c r="BD4" s="263"/>
+      <c r="BE4" s="263"/>
+      <c r="BF4" s="263"/>
+      <c r="BG4" s="263"/>
+      <c r="BH4" s="263"/>
+      <c r="BI4" s="263"/>
+      <c r="BJ4" s="263"/>
+      <c r="BK4" s="263"/>
+      <c r="BL4" s="263"/>
+      <c r="BM4" s="263"/>
+      <c r="BN4" s="263"/>
+      <c r="BO4" s="263"/>
+      <c r="BP4" s="263"/>
+      <c r="BQ4" s="263"/>
+      <c r="BR4" s="263"/>
+      <c r="BS4" s="263"/>
+      <c r="BT4" s="263"/>
+      <c r="BU4" s="263"/>
+      <c r="BV4" s="263"/>
+      <c r="BW4" s="263"/>
+      <c r="BX4" s="263"/>
+      <c r="BY4" s="263"/>
+      <c r="BZ4" s="263"/>
+    </row>
+    <row r="5" spans="1:78" ht="29" customHeight="1">
+      <c r="A5" s="240" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="241"/>
+      <c r="C5" s="257" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="254"/>
+      <c r="K5" s="255"/>
+      <c r="L5" s="255"/>
+      <c r="M5" s="255"/>
+      <c r="N5" s="255"/>
+      <c r="O5" s="255"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="237"/>
+      <c r="R5" s="238"/>
+      <c r="S5" s="238"/>
+      <c r="T5" s="238"/>
+      <c r="U5" s="238"/>
+      <c r="V5" s="238"/>
+      <c r="W5" s="238"/>
+      <c r="X5" s="238"/>
+      <c r="Y5" s="238"/>
+      <c r="Z5" s="238"/>
+      <c r="AA5" s="239"/>
+      <c r="AB5" s="248"/>
+      <c r="AC5" s="235"/>
+      <c r="AD5" s="235"/>
+      <c r="AE5" s="235"/>
+      <c r="AF5" s="235"/>
+      <c r="AG5" s="235"/>
+      <c r="AH5" s="235"/>
+      <c r="AI5" s="248"/>
+      <c r="AJ5" s="235"/>
+      <c r="AK5" s="235"/>
+      <c r="AL5" s="235"/>
+      <c r="AM5" s="235"/>
+      <c r="AN5" s="235"/>
+      <c r="AO5" s="235"/>
+      <c r="AP5" s="235"/>
+      <c r="AQ5" s="235"/>
+      <c r="AR5" s="234" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS5" s="235"/>
+      <c r="AT5" s="235"/>
+      <c r="AU5" s="235"/>
+      <c r="AV5" s="235"/>
+      <c r="AW5" s="235"/>
+      <c r="AX5" s="235"/>
+      <c r="AY5" s="235"/>
+      <c r="AZ5" s="235"/>
+      <c r="BA5" s="235"/>
+      <c r="BB5" s="235"/>
+      <c r="BC5" s="235"/>
+      <c r="BD5" s="235"/>
+      <c r="BE5" s="235"/>
+      <c r="BF5" s="235"/>
+      <c r="BG5" s="235"/>
+      <c r="BH5" s="235"/>
+      <c r="BI5" s="235"/>
+      <c r="BJ5" s="235"/>
+      <c r="BK5" s="235"/>
+      <c r="BL5" s="235"/>
+      <c r="BM5" s="235"/>
+      <c r="BN5" s="235"/>
+      <c r="BO5" s="235"/>
+      <c r="BP5" s="235"/>
+      <c r="BQ5" s="235"/>
+      <c r="BR5" s="235"/>
+      <c r="BS5" s="235"/>
+      <c r="BT5" s="235"/>
+      <c r="BU5" s="235"/>
+      <c r="BV5" s="235"/>
+      <c r="BW5" s="235"/>
+      <c r="BX5" s="235"/>
+      <c r="BY5" s="235"/>
+      <c r="BZ5" s="236"/>
+    </row>
+    <row r="6" spans="1:78">
+      <c r="A6" s="240" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="241"/>
+      <c r="C6" s="257"/>
+      <c r="D6" s="258"/>
+      <c r="E6" s="258"/>
+      <c r="F6" s="258"/>
+      <c r="G6" s="258"/>
+      <c r="H6" s="258"/>
+      <c r="I6" s="259"/>
+      <c r="J6" s="254" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="255"/>
+      <c r="L6" s="255"/>
+      <c r="M6" s="255"/>
+      <c r="N6" s="255"/>
+      <c r="O6" s="255"/>
+      <c r="P6" s="256"/>
+      <c r="Q6" s="237" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6" s="238"/>
+      <c r="S6" s="238"/>
+      <c r="T6" s="238"/>
+      <c r="U6" s="238"/>
+      <c r="V6" s="238"/>
+      <c r="W6" s="238"/>
+      <c r="X6" s="238"/>
+      <c r="Y6" s="238"/>
+      <c r="Z6" s="238"/>
+      <c r="AA6" s="239"/>
+      <c r="AB6" s="248"/>
+      <c r="AC6" s="235"/>
+      <c r="AD6" s="235"/>
+      <c r="AE6" s="235"/>
+      <c r="AF6" s="235"/>
+      <c r="AG6" s="235"/>
+      <c r="AH6" s="235"/>
+      <c r="AI6" s="248"/>
+      <c r="AJ6" s="235"/>
+      <c r="AK6" s="235"/>
+      <c r="AL6" s="235"/>
+      <c r="AM6" s="235"/>
+      <c r="AN6" s="235"/>
+      <c r="AO6" s="235"/>
+      <c r="AP6" s="235"/>
+      <c r="AQ6" s="235"/>
+      <c r="AR6" s="234" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS6" s="235"/>
+      <c r="AT6" s="235"/>
+      <c r="AU6" s="235"/>
+      <c r="AV6" s="235"/>
+      <c r="AW6" s="235"/>
+      <c r="AX6" s="235"/>
+      <c r="AY6" s="235"/>
+      <c r="AZ6" s="235"/>
+      <c r="BA6" s="235"/>
+      <c r="BB6" s="235"/>
+      <c r="BC6" s="235"/>
+      <c r="BD6" s="235"/>
+      <c r="BE6" s="235"/>
+      <c r="BF6" s="235"/>
+      <c r="BG6" s="235"/>
+      <c r="BH6" s="235"/>
+      <c r="BI6" s="235"/>
+      <c r="BJ6" s="235"/>
+      <c r="BK6" s="235"/>
+      <c r="BL6" s="235"/>
+      <c r="BM6" s="235"/>
+      <c r="BN6" s="235"/>
+      <c r="BO6" s="235"/>
+      <c r="BP6" s="235"/>
+      <c r="BQ6" s="235"/>
+      <c r="BR6" s="235"/>
+      <c r="BS6" s="235"/>
+      <c r="BT6" s="235"/>
+      <c r="BU6" s="235"/>
+      <c r="BV6" s="235"/>
+      <c r="BW6" s="235"/>
+      <c r="BX6" s="235"/>
+      <c r="BY6" s="235"/>
+      <c r="BZ6" s="236"/>
+    </row>
+    <row r="7" spans="1:78" ht="15.75" customHeight="1">
+      <c r="A7" s="252">
+        <v>1.2</v>
+      </c>
+      <c r="B7" s="253"/>
+      <c r="C7" s="242"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="244"/>
+      <c r="J7" s="254" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="255"/>
+      <c r="L7" s="255"/>
+      <c r="M7" s="255"/>
+      <c r="N7" s="255"/>
+      <c r="O7" s="255"/>
+      <c r="P7" s="256"/>
+      <c r="Q7" s="237" t="s">
+        <v>67</v>
+      </c>
+      <c r="R7" s="238"/>
+      <c r="S7" s="238"/>
+      <c r="T7" s="238"/>
+      <c r="U7" s="238"/>
+      <c r="V7" s="238"/>
+      <c r="W7" s="238"/>
+      <c r="X7" s="238"/>
+      <c r="Y7" s="238"/>
+      <c r="Z7" s="238"/>
+      <c r="AA7" s="239"/>
+      <c r="AB7" s="248"/>
+      <c r="AC7" s="235"/>
+      <c r="AD7" s="235"/>
+      <c r="AE7" s="235"/>
+      <c r="AF7" s="235"/>
+      <c r="AG7" s="235"/>
+      <c r="AH7" s="235"/>
+      <c r="AI7" s="248"/>
+      <c r="AJ7" s="235"/>
+      <c r="AK7" s="235"/>
+      <c r="AL7" s="235"/>
+      <c r="AM7" s="235"/>
+      <c r="AN7" s="235"/>
+      <c r="AO7" s="235"/>
+      <c r="AP7" s="235"/>
+      <c r="AQ7" s="235"/>
+      <c r="AR7" s="234" t="s">
+        <v>58</v>
+      </c>
+      <c r="AS7" s="235"/>
+      <c r="AT7" s="235"/>
+      <c r="AU7" s="235"/>
+      <c r="AV7" s="235"/>
+      <c r="AW7" s="235"/>
+      <c r="AX7" s="235"/>
+      <c r="AY7" s="235"/>
+      <c r="AZ7" s="235"/>
+      <c r="BA7" s="235"/>
+      <c r="BB7" s="235"/>
+      <c r="BC7" s="235"/>
+      <c r="BD7" s="235"/>
+      <c r="BE7" s="235"/>
+      <c r="BF7" s="235"/>
+      <c r="BG7" s="235"/>
+      <c r="BH7" s="235"/>
+      <c r="BI7" s="235"/>
+      <c r="BJ7" s="235"/>
+      <c r="BK7" s="235"/>
+      <c r="BL7" s="235"/>
+      <c r="BM7" s="235"/>
+      <c r="BN7" s="235"/>
+      <c r="BO7" s="235"/>
+      <c r="BP7" s="235"/>
+      <c r="BQ7" s="235"/>
+      <c r="BR7" s="235"/>
+      <c r="BS7" s="235"/>
+      <c r="BT7" s="235"/>
+      <c r="BU7" s="235"/>
+      <c r="BV7" s="235"/>
+      <c r="BW7" s="235"/>
+      <c r="BX7" s="235"/>
+      <c r="BY7" s="235"/>
+      <c r="BZ7" s="236"/>
+    </row>
+    <row r="8" spans="1:78" ht="15.75" customHeight="1">
+      <c r="A8" s="240" t="s">
         <v>55</v>
       </c>
-      <c r="AJ3" s="268"/>
-      <c r="AK3" s="268"/>
-      <c r="AL3" s="268"/>
-      <c r="AM3" s="268"/>
-      <c r="AN3" s="268"/>
-      <c r="AO3" s="268"/>
-      <c r="AP3" s="268"/>
-      <c r="AQ3" s="268"/>
-      <c r="AR3" s="265" t="s">
-        <v>37</v>
-      </c>
-      <c r="AS3" s="265"/>
-      <c r="AT3" s="265"/>
-      <c r="AU3" s="265"/>
-      <c r="AV3" s="265"/>
-      <c r="AW3" s="265"/>
-      <c r="AX3" s="265"/>
-      <c r="AY3" s="265"/>
-      <c r="AZ3" s="265"/>
-      <c r="BA3" s="265"/>
-      <c r="BB3" s="265"/>
-      <c r="BC3" s="265"/>
-      <c r="BD3" s="265"/>
-      <c r="BE3" s="265"/>
-      <c r="BF3" s="265"/>
-      <c r="BG3" s="265"/>
-      <c r="BH3" s="265"/>
-      <c r="BI3" s="265"/>
-      <c r="BJ3" s="265"/>
-      <c r="BK3" s="265"/>
-      <c r="BL3" s="265"/>
-      <c r="BM3" s="265"/>
-      <c r="BN3" s="265"/>
-      <c r="BO3" s="265"/>
-      <c r="BP3" s="265"/>
-      <c r="BQ3" s="265"/>
-      <c r="BR3" s="265"/>
-      <c r="BS3" s="265"/>
-      <c r="BT3" s="265"/>
-      <c r="BU3" s="265"/>
-      <c r="BV3" s="265"/>
-      <c r="BW3" s="265"/>
-      <c r="BX3" s="265"/>
-      <c r="BY3" s="265"/>
-      <c r="BZ3" s="265"/>
-    </row>
-    <row r="4" spans="1:78" ht="27.75" customHeight="1">
-      <c r="A4" s="266"/>
-      <c r="B4" s="266"/>
-      <c r="C4" s="273" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="273"/>
-      <c r="E4" s="273"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="273"/>
-      <c r="H4" s="273"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="273" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
-      <c r="M4" s="273"/>
-      <c r="N4" s="273"/>
-      <c r="O4" s="273"/>
-      <c r="P4" s="273"/>
-      <c r="Q4" s="270"/>
-      <c r="R4" s="271"/>
-      <c r="S4" s="271"/>
-      <c r="T4" s="271"/>
-      <c r="U4" s="271"/>
-      <c r="V4" s="271"/>
-      <c r="W4" s="271"/>
-      <c r="X4" s="271"/>
-      <c r="Y4" s="271"/>
-      <c r="Z4" s="271"/>
-      <c r="AA4" s="272"/>
-      <c r="AB4" s="270"/>
-      <c r="AC4" s="271"/>
-      <c r="AD4" s="271"/>
-      <c r="AE4" s="271"/>
-      <c r="AF4" s="271"/>
-      <c r="AG4" s="271"/>
-      <c r="AH4" s="271"/>
-      <c r="AI4" s="270"/>
-      <c r="AJ4" s="271"/>
-      <c r="AK4" s="271"/>
-      <c r="AL4" s="271"/>
-      <c r="AM4" s="271"/>
-      <c r="AN4" s="271"/>
-      <c r="AO4" s="271"/>
-      <c r="AP4" s="271"/>
-      <c r="AQ4" s="271"/>
-      <c r="AR4" s="265"/>
-      <c r="AS4" s="265"/>
-      <c r="AT4" s="265"/>
-      <c r="AU4" s="265"/>
-      <c r="AV4" s="265"/>
-      <c r="AW4" s="265"/>
-      <c r="AX4" s="265"/>
-      <c r="AY4" s="265"/>
-      <c r="AZ4" s="265"/>
-      <c r="BA4" s="265"/>
-      <c r="BB4" s="265"/>
-      <c r="BC4" s="265"/>
-      <c r="BD4" s="265"/>
-      <c r="BE4" s="265"/>
-      <c r="BF4" s="265"/>
-      <c r="BG4" s="265"/>
-      <c r="BH4" s="265"/>
-      <c r="BI4" s="265"/>
-      <c r="BJ4" s="265"/>
-      <c r="BK4" s="265"/>
-      <c r="BL4" s="265"/>
-      <c r="BM4" s="265"/>
-      <c r="BN4" s="265"/>
-      <c r="BO4" s="265"/>
-      <c r="BP4" s="265"/>
-      <c r="BQ4" s="265"/>
-      <c r="BR4" s="265"/>
-      <c r="BS4" s="265"/>
-      <c r="BT4" s="265"/>
-      <c r="BU4" s="265"/>
-      <c r="BV4" s="265"/>
-      <c r="BW4" s="265"/>
-      <c r="BX4" s="265"/>
-      <c r="BY4" s="265"/>
-      <c r="BZ4" s="265"/>
-    </row>
-    <row r="5" spans="1:78" ht="40" customHeight="1">
-      <c r="A5" s="242" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="259" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="260"/>
-      <c r="E5" s="260"/>
-      <c r="F5" s="260"/>
-      <c r="G5" s="260"/>
-      <c r="H5" s="260"/>
-      <c r="I5" s="261"/>
-      <c r="J5" s="256"/>
-      <c r="K5" s="257"/>
-      <c r="L5" s="257"/>
-      <c r="M5" s="257"/>
-      <c r="N5" s="257"/>
-      <c r="O5" s="257"/>
-      <c r="P5" s="258"/>
-      <c r="Q5" s="239"/>
-      <c r="R5" s="240"/>
-      <c r="S5" s="240"/>
-      <c r="T5" s="240"/>
-      <c r="U5" s="240"/>
-      <c r="V5" s="240"/>
-      <c r="W5" s="240"/>
-      <c r="X5" s="240"/>
-      <c r="Y5" s="240"/>
-      <c r="Z5" s="240"/>
-      <c r="AA5" s="241"/>
-      <c r="AB5" s="250"/>
-      <c r="AC5" s="237"/>
-      <c r="AD5" s="237"/>
-      <c r="AE5" s="237"/>
-      <c r="AF5" s="237"/>
-      <c r="AG5" s="237"/>
-      <c r="AH5" s="237"/>
-      <c r="AI5" s="250"/>
-      <c r="AJ5" s="237"/>
-      <c r="AK5" s="237"/>
-      <c r="AL5" s="237"/>
-      <c r="AM5" s="237"/>
-      <c r="AN5" s="237"/>
-      <c r="AO5" s="237"/>
-      <c r="AP5" s="237"/>
-      <c r="AQ5" s="237"/>
-      <c r="AR5" s="236" t="s">
-        <v>83</v>
-      </c>
-      <c r="AS5" s="237"/>
-      <c r="AT5" s="237"/>
-      <c r="AU5" s="237"/>
-      <c r="AV5" s="237"/>
-      <c r="AW5" s="237"/>
-      <c r="AX5" s="237"/>
-      <c r="AY5" s="237"/>
-      <c r="AZ5" s="237"/>
-      <c r="BA5" s="237"/>
-      <c r="BB5" s="237"/>
-      <c r="BC5" s="237"/>
-      <c r="BD5" s="237"/>
-      <c r="BE5" s="237"/>
-      <c r="BF5" s="237"/>
-      <c r="BG5" s="237"/>
-      <c r="BH5" s="237"/>
-      <c r="BI5" s="237"/>
-      <c r="BJ5" s="237"/>
-      <c r="BK5" s="237"/>
-      <c r="BL5" s="237"/>
-      <c r="BM5" s="237"/>
-      <c r="BN5" s="237"/>
-      <c r="BO5" s="237"/>
-      <c r="BP5" s="237"/>
-      <c r="BQ5" s="237"/>
-      <c r="BR5" s="237"/>
-      <c r="BS5" s="237"/>
-      <c r="BT5" s="237"/>
-      <c r="BU5" s="237"/>
-      <c r="BV5" s="237"/>
-      <c r="BW5" s="237"/>
-      <c r="BX5" s="237"/>
-      <c r="BY5" s="237"/>
-      <c r="BZ5" s="238"/>
-    </row>
-    <row r="6" spans="1:78">
-      <c r="A6" s="242" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="243"/>
-      <c r="C6" s="259"/>
-      <c r="D6" s="260"/>
-      <c r="E6" s="260"/>
-      <c r="F6" s="260"/>
-      <c r="G6" s="260"/>
-      <c r="H6" s="260"/>
-      <c r="I6" s="261"/>
-      <c r="J6" s="256" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="257"/>
-      <c r="L6" s="257"/>
-      <c r="M6" s="257"/>
-      <c r="N6" s="257"/>
-      <c r="O6" s="257"/>
-      <c r="P6" s="258"/>
-      <c r="Q6" s="239" t="s">
-        <v>69</v>
-      </c>
-      <c r="R6" s="240"/>
-      <c r="S6" s="240"/>
-      <c r="T6" s="240"/>
-      <c r="U6" s="240"/>
-      <c r="V6" s="240"/>
-      <c r="W6" s="240"/>
-      <c r="X6" s="240"/>
-      <c r="Y6" s="240"/>
-      <c r="Z6" s="240"/>
-      <c r="AA6" s="241"/>
-      <c r="AB6" s="250"/>
-      <c r="AC6" s="237"/>
-      <c r="AD6" s="237"/>
-      <c r="AE6" s="237"/>
-      <c r="AF6" s="237"/>
-      <c r="AG6" s="237"/>
-      <c r="AH6" s="237"/>
-      <c r="AI6" s="250"/>
-      <c r="AJ6" s="237"/>
-      <c r="AK6" s="237"/>
-      <c r="AL6" s="237"/>
-      <c r="AM6" s="237"/>
-      <c r="AN6" s="237"/>
-      <c r="AO6" s="237"/>
-      <c r="AP6" s="237"/>
-      <c r="AQ6" s="237"/>
-      <c r="AR6" s="236" t="s">
-        <v>60</v>
-      </c>
-      <c r="AS6" s="237"/>
-      <c r="AT6" s="237"/>
-      <c r="AU6" s="237"/>
-      <c r="AV6" s="237"/>
-      <c r="AW6" s="237"/>
-      <c r="AX6" s="237"/>
-      <c r="AY6" s="237"/>
-      <c r="AZ6" s="237"/>
-      <c r="BA6" s="237"/>
-      <c r="BB6" s="237"/>
-      <c r="BC6" s="237"/>
-      <c r="BD6" s="237"/>
-      <c r="BE6" s="237"/>
-      <c r="BF6" s="237"/>
-      <c r="BG6" s="237"/>
-      <c r="BH6" s="237"/>
-      <c r="BI6" s="237"/>
-      <c r="BJ6" s="237"/>
-      <c r="BK6" s="237"/>
-      <c r="BL6" s="237"/>
-      <c r="BM6" s="237"/>
-      <c r="BN6" s="237"/>
-      <c r="BO6" s="237"/>
-      <c r="BP6" s="237"/>
-      <c r="BQ6" s="237"/>
-      <c r="BR6" s="237"/>
-      <c r="BS6" s="237"/>
-      <c r="BT6" s="237"/>
-      <c r="BU6" s="237"/>
-      <c r="BV6" s="237"/>
-      <c r="BW6" s="237"/>
-      <c r="BX6" s="237"/>
-      <c r="BY6" s="237"/>
-      <c r="BZ6" s="238"/>
-    </row>
-    <row r="7" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A7" s="254">
-        <v>1.2</v>
-      </c>
-      <c r="B7" s="255"/>
-      <c r="C7" s="244"/>
-      <c r="D7" s="245"/>
-      <c r="E7" s="245"/>
-      <c r="F7" s="245"/>
-      <c r="G7" s="245"/>
-      <c r="H7" s="245"/>
-      <c r="I7" s="246"/>
-      <c r="J7" s="256" t="s">
-        <v>62</v>
-      </c>
-      <c r="K7" s="257"/>
-      <c r="L7" s="257"/>
-      <c r="M7" s="257"/>
-      <c r="N7" s="257"/>
-      <c r="O7" s="257"/>
-      <c r="P7" s="258"/>
-      <c r="Q7" s="239" t="s">
-        <v>69</v>
-      </c>
-      <c r="R7" s="240"/>
-      <c r="S7" s="240"/>
-      <c r="T7" s="240"/>
-      <c r="U7" s="240"/>
-      <c r="V7" s="240"/>
-      <c r="W7" s="240"/>
-      <c r="X7" s="240"/>
-      <c r="Y7" s="240"/>
-      <c r="Z7" s="240"/>
-      <c r="AA7" s="241"/>
-      <c r="AB7" s="250"/>
-      <c r="AC7" s="237"/>
-      <c r="AD7" s="237"/>
-      <c r="AE7" s="237"/>
-      <c r="AF7" s="237"/>
-      <c r="AG7" s="237"/>
-      <c r="AH7" s="237"/>
-      <c r="AI7" s="250"/>
-      <c r="AJ7" s="237"/>
-      <c r="AK7" s="237"/>
-      <c r="AL7" s="237"/>
-      <c r="AM7" s="237"/>
-      <c r="AN7" s="237"/>
-      <c r="AO7" s="237"/>
-      <c r="AP7" s="237"/>
-      <c r="AQ7" s="237"/>
-      <c r="AR7" s="236" t="s">
-        <v>60</v>
-      </c>
-      <c r="AS7" s="237"/>
-      <c r="AT7" s="237"/>
-      <c r="AU7" s="237"/>
-      <c r="AV7" s="237"/>
-      <c r="AW7" s="237"/>
-      <c r="AX7" s="237"/>
-      <c r="AY7" s="237"/>
-      <c r="AZ7" s="237"/>
-      <c r="BA7" s="237"/>
-      <c r="BB7" s="237"/>
-      <c r="BC7" s="237"/>
-      <c r="BD7" s="237"/>
-      <c r="BE7" s="237"/>
-      <c r="BF7" s="237"/>
-      <c r="BG7" s="237"/>
-      <c r="BH7" s="237"/>
-      <c r="BI7" s="237"/>
-      <c r="BJ7" s="237"/>
-      <c r="BK7" s="237"/>
-      <c r="BL7" s="237"/>
-      <c r="BM7" s="237"/>
-      <c r="BN7" s="237"/>
-      <c r="BO7" s="237"/>
-      <c r="BP7" s="237"/>
-      <c r="BQ7" s="237"/>
-      <c r="BR7" s="237"/>
-      <c r="BS7" s="237"/>
-      <c r="BT7" s="237"/>
-      <c r="BU7" s="237"/>
-      <c r="BV7" s="237"/>
-      <c r="BW7" s="237"/>
-      <c r="BX7" s="237"/>
-      <c r="BY7" s="237"/>
-      <c r="BZ7" s="238"/>
-    </row>
-    <row r="8" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A8" s="242" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="243"/>
+      <c r="B8" s="241"/>
       <c r="C8" s="139"/>
       <c r="D8" s="140"/>
       <c r="E8" s="140"/>
@@ -24487,85 +24485,85 @@
       <c r="G8" s="140"/>
       <c r="H8" s="140"/>
       <c r="I8" s="141"/>
-      <c r="J8" s="244" t="s">
+      <c r="J8" s="242" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="243"/>
+      <c r="L8" s="243"/>
+      <c r="M8" s="243"/>
+      <c r="N8" s="243"/>
+      <c r="O8" s="243"/>
+      <c r="P8" s="244"/>
+      <c r="Q8" s="245"/>
+      <c r="R8" s="246"/>
+      <c r="S8" s="246"/>
+      <c r="T8" s="246"/>
+      <c r="U8" s="246"/>
+      <c r="V8" s="246"/>
+      <c r="W8" s="246"/>
+      <c r="X8" s="246"/>
+      <c r="Y8" s="246"/>
+      <c r="Z8" s="246"/>
+      <c r="AA8" s="247"/>
+      <c r="AB8" s="232"/>
+      <c r="AC8" s="233"/>
+      <c r="AD8" s="233"/>
+      <c r="AE8" s="233"/>
+      <c r="AF8" s="233"/>
+      <c r="AG8" s="233"/>
+      <c r="AH8" s="233"/>
+      <c r="AI8" s="232"/>
+      <c r="AJ8" s="233"/>
+      <c r="AK8" s="233"/>
+      <c r="AL8" s="233"/>
+      <c r="AM8" s="233"/>
+      <c r="AN8" s="233"/>
+      <c r="AO8" s="233"/>
+      <c r="AP8" s="233"/>
+      <c r="AQ8" s="233"/>
+      <c r="AR8" s="234" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS8" s="235"/>
+      <c r="AT8" s="235"/>
+      <c r="AU8" s="235"/>
+      <c r="AV8" s="235"/>
+      <c r="AW8" s="235"/>
+      <c r="AX8" s="235"/>
+      <c r="AY8" s="235"/>
+      <c r="AZ8" s="235"/>
+      <c r="BA8" s="235"/>
+      <c r="BB8" s="235"/>
+      <c r="BC8" s="235"/>
+      <c r="BD8" s="235"/>
+      <c r="BE8" s="235"/>
+      <c r="BF8" s="235"/>
+      <c r="BG8" s="235"/>
+      <c r="BH8" s="235"/>
+      <c r="BI8" s="235"/>
+      <c r="BJ8" s="235"/>
+      <c r="BK8" s="235"/>
+      <c r="BL8" s="235"/>
+      <c r="BM8" s="235"/>
+      <c r="BN8" s="235"/>
+      <c r="BO8" s="235"/>
+      <c r="BP8" s="235"/>
+      <c r="BQ8" s="235"/>
+      <c r="BR8" s="235"/>
+      <c r="BS8" s="235"/>
+      <c r="BT8" s="235"/>
+      <c r="BU8" s="235"/>
+      <c r="BV8" s="235"/>
+      <c r="BW8" s="235"/>
+      <c r="BX8" s="235"/>
+      <c r="BY8" s="235"/>
+      <c r="BZ8" s="236"/>
+    </row>
+    <row r="9" spans="1:78" ht="15.75" customHeight="1">
+      <c r="A9" s="240" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="245"/>
-      <c r="L8" s="245"/>
-      <c r="M8" s="245"/>
-      <c r="N8" s="245"/>
-      <c r="O8" s="245"/>
-      <c r="P8" s="246"/>
-      <c r="Q8" s="247"/>
-      <c r="R8" s="248"/>
-      <c r="S8" s="248"/>
-      <c r="T8" s="248"/>
-      <c r="U8" s="248"/>
-      <c r="V8" s="248"/>
-      <c r="W8" s="248"/>
-      <c r="X8" s="248"/>
-      <c r="Y8" s="248"/>
-      <c r="Z8" s="248"/>
-      <c r="AA8" s="249"/>
-      <c r="AB8" s="234"/>
-      <c r="AC8" s="235"/>
-      <c r="AD8" s="235"/>
-      <c r="AE8" s="235"/>
-      <c r="AF8" s="235"/>
-      <c r="AG8" s="235"/>
-      <c r="AH8" s="235"/>
-      <c r="AI8" s="234"/>
-      <c r="AJ8" s="235"/>
-      <c r="AK8" s="235"/>
-      <c r="AL8" s="235"/>
-      <c r="AM8" s="235"/>
-      <c r="AN8" s="235"/>
-      <c r="AO8" s="235"/>
-      <c r="AP8" s="235"/>
-      <c r="AQ8" s="235"/>
-      <c r="AR8" s="236" t="s">
-        <v>63</v>
-      </c>
-      <c r="AS8" s="237"/>
-      <c r="AT8" s="237"/>
-      <c r="AU8" s="237"/>
-      <c r="AV8" s="237"/>
-      <c r="AW8" s="237"/>
-      <c r="AX8" s="237"/>
-      <c r="AY8" s="237"/>
-      <c r="AZ8" s="237"/>
-      <c r="BA8" s="237"/>
-      <c r="BB8" s="237"/>
-      <c r="BC8" s="237"/>
-      <c r="BD8" s="237"/>
-      <c r="BE8" s="237"/>
-      <c r="BF8" s="237"/>
-      <c r="BG8" s="237"/>
-      <c r="BH8" s="237"/>
-      <c r="BI8" s="237"/>
-      <c r="BJ8" s="237"/>
-      <c r="BK8" s="237"/>
-      <c r="BL8" s="237"/>
-      <c r="BM8" s="237"/>
-      <c r="BN8" s="237"/>
-      <c r="BO8" s="237"/>
-      <c r="BP8" s="237"/>
-      <c r="BQ8" s="237"/>
-      <c r="BR8" s="237"/>
-      <c r="BS8" s="237"/>
-      <c r="BT8" s="237"/>
-      <c r="BU8" s="237"/>
-      <c r="BV8" s="237"/>
-      <c r="BW8" s="237"/>
-      <c r="BX8" s="237"/>
-      <c r="BY8" s="237"/>
-      <c r="BZ8" s="238"/>
-    </row>
-    <row r="9" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A9" s="242" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="243"/>
+      <c r="B9" s="241"/>
       <c r="C9" s="139"/>
       <c r="D9" s="140"/>
       <c r="E9" s="140"/>
@@ -24573,343 +24571,343 @@
       <c r="G9" s="140"/>
       <c r="H9" s="140"/>
       <c r="I9" s="141"/>
-      <c r="J9" s="244" t="s">
-        <v>65</v>
+      <c r="J9" s="242" t="s">
+        <v>63</v>
       </c>
-      <c r="K9" s="245"/>
-      <c r="L9" s="245"/>
-      <c r="M9" s="245"/>
-      <c r="N9" s="245"/>
-      <c r="O9" s="245"/>
-      <c r="P9" s="246"/>
-      <c r="Q9" s="247"/>
-      <c r="R9" s="248"/>
-      <c r="S9" s="248"/>
-      <c r="T9" s="248"/>
-      <c r="U9" s="248"/>
-      <c r="V9" s="248"/>
-      <c r="W9" s="248"/>
-      <c r="X9" s="248"/>
-      <c r="Y9" s="248"/>
-      <c r="Z9" s="248"/>
-      <c r="AA9" s="249"/>
-      <c r="AB9" s="234"/>
-      <c r="AC9" s="235"/>
-      <c r="AD9" s="235"/>
-      <c r="AE9" s="235"/>
-      <c r="AF9" s="235"/>
-      <c r="AG9" s="235"/>
-      <c r="AH9" s="235"/>
-      <c r="AI9" s="234"/>
-      <c r="AJ9" s="235"/>
-      <c r="AK9" s="235"/>
-      <c r="AL9" s="235"/>
-      <c r="AM9" s="235"/>
-      <c r="AN9" s="235"/>
-      <c r="AO9" s="235"/>
-      <c r="AP9" s="235"/>
-      <c r="AQ9" s="235"/>
-      <c r="AR9" s="236"/>
-      <c r="AS9" s="237"/>
-      <c r="AT9" s="237"/>
-      <c r="AU9" s="237"/>
-      <c r="AV9" s="237"/>
-      <c r="AW9" s="237"/>
-      <c r="AX9" s="237"/>
-      <c r="AY9" s="237"/>
-      <c r="AZ9" s="237"/>
-      <c r="BA9" s="237"/>
-      <c r="BB9" s="237"/>
-      <c r="BC9" s="237"/>
-      <c r="BD9" s="237"/>
-      <c r="BE9" s="237"/>
-      <c r="BF9" s="237"/>
-      <c r="BG9" s="237"/>
-      <c r="BH9" s="237"/>
-      <c r="BI9" s="237"/>
-      <c r="BJ9" s="237"/>
-      <c r="BK9" s="237"/>
-      <c r="BL9" s="237"/>
-      <c r="BM9" s="237"/>
-      <c r="BN9" s="237"/>
-      <c r="BO9" s="237"/>
-      <c r="BP9" s="237"/>
-      <c r="BQ9" s="237"/>
-      <c r="BR9" s="237"/>
-      <c r="BS9" s="237"/>
-      <c r="BT9" s="237"/>
-      <c r="BU9" s="237"/>
-      <c r="BV9" s="237"/>
-      <c r="BW9" s="237"/>
-      <c r="BX9" s="237"/>
-      <c r="BY9" s="237"/>
-      <c r="BZ9" s="238"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="243"/>
+      <c r="N9" s="243"/>
+      <c r="O9" s="243"/>
+      <c r="P9" s="244"/>
+      <c r="Q9" s="245"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
+      <c r="W9" s="246"/>
+      <c r="X9" s="246"/>
+      <c r="Y9" s="246"/>
+      <c r="Z9" s="246"/>
+      <c r="AA9" s="247"/>
+      <c r="AB9" s="232"/>
+      <c r="AC9" s="233"/>
+      <c r="AD9" s="233"/>
+      <c r="AE9" s="233"/>
+      <c r="AF9" s="233"/>
+      <c r="AG9" s="233"/>
+      <c r="AH9" s="233"/>
+      <c r="AI9" s="232"/>
+      <c r="AJ9" s="233"/>
+      <c r="AK9" s="233"/>
+      <c r="AL9" s="233"/>
+      <c r="AM9" s="233"/>
+      <c r="AN9" s="233"/>
+      <c r="AO9" s="233"/>
+      <c r="AP9" s="233"/>
+      <c r="AQ9" s="233"/>
+      <c r="AR9" s="234"/>
+      <c r="AS9" s="235"/>
+      <c r="AT9" s="235"/>
+      <c r="AU9" s="235"/>
+      <c r="AV9" s="235"/>
+      <c r="AW9" s="235"/>
+      <c r="AX9" s="235"/>
+      <c r="AY9" s="235"/>
+      <c r="AZ9" s="235"/>
+      <c r="BA9" s="235"/>
+      <c r="BB9" s="235"/>
+      <c r="BC9" s="235"/>
+      <c r="BD9" s="235"/>
+      <c r="BE9" s="235"/>
+      <c r="BF9" s="235"/>
+      <c r="BG9" s="235"/>
+      <c r="BH9" s="235"/>
+      <c r="BI9" s="235"/>
+      <c r="BJ9" s="235"/>
+      <c r="BK9" s="235"/>
+      <c r="BL9" s="235"/>
+      <c r="BM9" s="235"/>
+      <c r="BN9" s="235"/>
+      <c r="BO9" s="235"/>
+      <c r="BP9" s="235"/>
+      <c r="BQ9" s="235"/>
+      <c r="BR9" s="235"/>
+      <c r="BS9" s="235"/>
+      <c r="BT9" s="235"/>
+      <c r="BU9" s="235"/>
+      <c r="BV9" s="235"/>
+      <c r="BW9" s="235"/>
+      <c r="BX9" s="235"/>
+      <c r="BY9" s="235"/>
+      <c r="BZ9" s="236"/>
     </row>
     <row r="10" spans="1:78" ht="26" customHeight="1">
-      <c r="A10" s="242" t="s">
+      <c r="A10" s="240" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="241"/>
+      <c r="C10" s="257" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="258"/>
+      <c r="E10" s="258"/>
+      <c r="F10" s="258"/>
+      <c r="G10" s="258"/>
+      <c r="H10" s="258"/>
+      <c r="I10" s="259"/>
+      <c r="J10" s="254"/>
+      <c r="K10" s="255"/>
+      <c r="L10" s="255"/>
+      <c r="M10" s="255"/>
+      <c r="N10" s="255"/>
+      <c r="O10" s="255"/>
+      <c r="P10" s="256"/>
+      <c r="Q10" s="245"/>
+      <c r="R10" s="246"/>
+      <c r="S10" s="246"/>
+      <c r="T10" s="246"/>
+      <c r="U10" s="246"/>
+      <c r="V10" s="246"/>
+      <c r="W10" s="246"/>
+      <c r="X10" s="246"/>
+      <c r="Y10" s="246"/>
+      <c r="Z10" s="246"/>
+      <c r="AA10" s="247"/>
+      <c r="AB10" s="232"/>
+      <c r="AC10" s="233"/>
+      <c r="AD10" s="233"/>
+      <c r="AE10" s="233"/>
+      <c r="AF10" s="233"/>
+      <c r="AG10" s="233"/>
+      <c r="AH10" s="233"/>
+      <c r="AI10" s="232"/>
+      <c r="AJ10" s="233"/>
+      <c r="AK10" s="233"/>
+      <c r="AL10" s="233"/>
+      <c r="AM10" s="233"/>
+      <c r="AN10" s="233"/>
+      <c r="AO10" s="233"/>
+      <c r="AP10" s="233"/>
+      <c r="AQ10" s="233"/>
+      <c r="AR10" s="234"/>
+      <c r="AS10" s="235"/>
+      <c r="AT10" s="235"/>
+      <c r="AU10" s="235"/>
+      <c r="AV10" s="235"/>
+      <c r="AW10" s="235"/>
+      <c r="AX10" s="235"/>
+      <c r="AY10" s="235"/>
+      <c r="AZ10" s="235"/>
+      <c r="BA10" s="235"/>
+      <c r="BB10" s="235"/>
+      <c r="BC10" s="235"/>
+      <c r="BD10" s="235"/>
+      <c r="BE10" s="235"/>
+      <c r="BF10" s="235"/>
+      <c r="BG10" s="235"/>
+      <c r="BH10" s="235"/>
+      <c r="BI10" s="235"/>
+      <c r="BJ10" s="235"/>
+      <c r="BK10" s="235"/>
+      <c r="BL10" s="235"/>
+      <c r="BM10" s="235"/>
+      <c r="BN10" s="235"/>
+      <c r="BO10" s="235"/>
+      <c r="BP10" s="235"/>
+      <c r="BQ10" s="235"/>
+      <c r="BR10" s="235"/>
+      <c r="BS10" s="235"/>
+      <c r="BT10" s="235"/>
+      <c r="BU10" s="235"/>
+      <c r="BV10" s="235"/>
+      <c r="BW10" s="235"/>
+      <c r="BX10" s="235"/>
+      <c r="BY10" s="235"/>
+      <c r="BZ10" s="236"/>
+    </row>
+    <row r="11" spans="1:78" ht="15.75" customHeight="1">
+      <c r="A11" s="240" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="241"/>
+      <c r="C11" s="257"/>
+      <c r="D11" s="258"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="258"/>
+      <c r="H11" s="258"/>
+      <c r="I11" s="259"/>
+      <c r="J11" s="254" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
+      <c r="M11" s="255"/>
+      <c r="N11" s="255"/>
+      <c r="O11" s="255"/>
+      <c r="P11" s="256"/>
+      <c r="Q11" s="237" t="s">
+        <v>67</v>
+      </c>
+      <c r="R11" s="238"/>
+      <c r="S11" s="238"/>
+      <c r="T11" s="238"/>
+      <c r="U11" s="238"/>
+      <c r="V11" s="238"/>
+      <c r="W11" s="238"/>
+      <c r="X11" s="238"/>
+      <c r="Y11" s="238"/>
+      <c r="Z11" s="238"/>
+      <c r="AA11" s="239"/>
+      <c r="AB11" s="248"/>
+      <c r="AC11" s="235"/>
+      <c r="AD11" s="235"/>
+      <c r="AE11" s="235"/>
+      <c r="AF11" s="235"/>
+      <c r="AG11" s="235"/>
+      <c r="AH11" s="235"/>
+      <c r="AI11" s="248"/>
+      <c r="AJ11" s="235"/>
+      <c r="AK11" s="235"/>
+      <c r="AL11" s="235"/>
+      <c r="AM11" s="235"/>
+      <c r="AN11" s="235"/>
+      <c r="AO11" s="235"/>
+      <c r="AP11" s="235"/>
+      <c r="AQ11" s="235"/>
+      <c r="AR11" s="234" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="243"/>
-      <c r="C10" s="259" t="s">
-        <v>56</v>
+      <c r="AS11" s="235"/>
+      <c r="AT11" s="235"/>
+      <c r="AU11" s="235"/>
+      <c r="AV11" s="235"/>
+      <c r="AW11" s="235"/>
+      <c r="AX11" s="235"/>
+      <c r="AY11" s="235"/>
+      <c r="AZ11" s="235"/>
+      <c r="BA11" s="235"/>
+      <c r="BB11" s="235"/>
+      <c r="BC11" s="235"/>
+      <c r="BD11" s="235"/>
+      <c r="BE11" s="235"/>
+      <c r="BF11" s="235"/>
+      <c r="BG11" s="235"/>
+      <c r="BH11" s="235"/>
+      <c r="BI11" s="235"/>
+      <c r="BJ11" s="235"/>
+      <c r="BK11" s="235"/>
+      <c r="BL11" s="235"/>
+      <c r="BM11" s="235"/>
+      <c r="BN11" s="235"/>
+      <c r="BO11" s="235"/>
+      <c r="BP11" s="235"/>
+      <c r="BQ11" s="235"/>
+      <c r="BR11" s="235"/>
+      <c r="BS11" s="235"/>
+      <c r="BT11" s="235"/>
+      <c r="BU11" s="235"/>
+      <c r="BV11" s="235"/>
+      <c r="BW11" s="235"/>
+      <c r="BX11" s="235"/>
+      <c r="BY11" s="235"/>
+      <c r="BZ11" s="236"/>
+    </row>
+    <row r="12" spans="1:78" ht="15.75" customHeight="1">
+      <c r="A12" s="252">
+        <v>2.2000000000000002</v>
       </c>
-      <c r="D10" s="260"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="260"/>
-      <c r="H10" s="260"/>
-      <c r="I10" s="261"/>
-      <c r="J10" s="256"/>
-      <c r="K10" s="257"/>
-      <c r="L10" s="257"/>
-      <c r="M10" s="257"/>
-      <c r="N10" s="257"/>
-      <c r="O10" s="257"/>
-      <c r="P10" s="258"/>
-      <c r="Q10" s="247"/>
-      <c r="R10" s="248"/>
-      <c r="S10" s="248"/>
-      <c r="T10" s="248"/>
-      <c r="U10" s="248"/>
-      <c r="V10" s="248"/>
-      <c r="W10" s="248"/>
-      <c r="X10" s="248"/>
-      <c r="Y10" s="248"/>
-      <c r="Z10" s="248"/>
-      <c r="AA10" s="249"/>
-      <c r="AB10" s="234"/>
-      <c r="AC10" s="235"/>
-      <c r="AD10" s="235"/>
-      <c r="AE10" s="235"/>
-      <c r="AF10" s="235"/>
-      <c r="AG10" s="235"/>
-      <c r="AH10" s="235"/>
-      <c r="AI10" s="234"/>
-      <c r="AJ10" s="235"/>
-      <c r="AK10" s="235"/>
-      <c r="AL10" s="235"/>
-      <c r="AM10" s="235"/>
-      <c r="AN10" s="235"/>
-      <c r="AO10" s="235"/>
-      <c r="AP10" s="235"/>
-      <c r="AQ10" s="235"/>
-      <c r="AR10" s="236"/>
-      <c r="AS10" s="237"/>
-      <c r="AT10" s="237"/>
-      <c r="AU10" s="237"/>
-      <c r="AV10" s="237"/>
-      <c r="AW10" s="237"/>
-      <c r="AX10" s="237"/>
-      <c r="AY10" s="237"/>
-      <c r="AZ10" s="237"/>
-      <c r="BA10" s="237"/>
-      <c r="BB10" s="237"/>
-      <c r="BC10" s="237"/>
-      <c r="BD10" s="237"/>
-      <c r="BE10" s="237"/>
-      <c r="BF10" s="237"/>
-      <c r="BG10" s="237"/>
-      <c r="BH10" s="237"/>
-      <c r="BI10" s="237"/>
-      <c r="BJ10" s="237"/>
-      <c r="BK10" s="237"/>
-      <c r="BL10" s="237"/>
-      <c r="BM10" s="237"/>
-      <c r="BN10" s="237"/>
-      <c r="BO10" s="237"/>
-      <c r="BP10" s="237"/>
-      <c r="BQ10" s="237"/>
-      <c r="BR10" s="237"/>
-      <c r="BS10" s="237"/>
-      <c r="BT10" s="237"/>
-      <c r="BU10" s="237"/>
-      <c r="BV10" s="237"/>
-      <c r="BW10" s="237"/>
-      <c r="BX10" s="237"/>
-      <c r="BY10" s="237"/>
-      <c r="BZ10" s="238"/>
-    </row>
-    <row r="11" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A11" s="242" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="243"/>
-      <c r="C11" s="259"/>
-      <c r="D11" s="260"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="260"/>
-      <c r="G11" s="260"/>
-      <c r="H11" s="260"/>
-      <c r="I11" s="261"/>
-      <c r="J11" s="256" t="s">
-        <v>61</v>
-      </c>
-      <c r="K11" s="257"/>
-      <c r="L11" s="257"/>
-      <c r="M11" s="257"/>
-      <c r="N11" s="257"/>
-      <c r="O11" s="257"/>
-      <c r="P11" s="258"/>
-      <c r="Q11" s="239" t="s">
-        <v>69</v>
-      </c>
-      <c r="R11" s="240"/>
-      <c r="S11" s="240"/>
-      <c r="T11" s="240"/>
-      <c r="U11" s="240"/>
-      <c r="V11" s="240"/>
-      <c r="W11" s="240"/>
-      <c r="X11" s="240"/>
-      <c r="Y11" s="240"/>
-      <c r="Z11" s="240"/>
-      <c r="AA11" s="241"/>
-      <c r="AB11" s="250"/>
-      <c r="AC11" s="237"/>
-      <c r="AD11" s="237"/>
-      <c r="AE11" s="237"/>
-      <c r="AF11" s="237"/>
-      <c r="AG11" s="237"/>
-      <c r="AH11" s="237"/>
-      <c r="AI11" s="250"/>
-      <c r="AJ11" s="237"/>
-      <c r="AK11" s="237"/>
-      <c r="AL11" s="237"/>
-      <c r="AM11" s="237"/>
-      <c r="AN11" s="237"/>
-      <c r="AO11" s="237"/>
-      <c r="AP11" s="237"/>
-      <c r="AQ11" s="237"/>
-      <c r="AR11" s="236" t="s">
+      <c r="B12" s="253"/>
+      <c r="C12" s="242"/>
+      <c r="D12" s="243"/>
+      <c r="E12" s="243"/>
+      <c r="F12" s="243"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="244"/>
+      <c r="J12" s="254" t="s">
         <v>60</v>
       </c>
-      <c r="AS11" s="237"/>
-      <c r="AT11" s="237"/>
-      <c r="AU11" s="237"/>
-      <c r="AV11" s="237"/>
-      <c r="AW11" s="237"/>
-      <c r="AX11" s="237"/>
-      <c r="AY11" s="237"/>
-      <c r="AZ11" s="237"/>
-      <c r="BA11" s="237"/>
-      <c r="BB11" s="237"/>
-      <c r="BC11" s="237"/>
-      <c r="BD11" s="237"/>
-      <c r="BE11" s="237"/>
-      <c r="BF11" s="237"/>
-      <c r="BG11" s="237"/>
-      <c r="BH11" s="237"/>
-      <c r="BI11" s="237"/>
-      <c r="BJ11" s="237"/>
-      <c r="BK11" s="237"/>
-      <c r="BL11" s="237"/>
-      <c r="BM11" s="237"/>
-      <c r="BN11" s="237"/>
-      <c r="BO11" s="237"/>
-      <c r="BP11" s="237"/>
-      <c r="BQ11" s="237"/>
-      <c r="BR11" s="237"/>
-      <c r="BS11" s="237"/>
-      <c r="BT11" s="237"/>
-      <c r="BU11" s="237"/>
-      <c r="BV11" s="237"/>
-      <c r="BW11" s="237"/>
-      <c r="BX11" s="237"/>
-      <c r="BY11" s="237"/>
-      <c r="BZ11" s="238"/>
-    </row>
-    <row r="12" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A12" s="254">
-        <v>2.2000000000000002</v>
+      <c r="K12" s="255"/>
+      <c r="L12" s="255"/>
+      <c r="M12" s="255"/>
+      <c r="N12" s="255"/>
+      <c r="O12" s="255"/>
+      <c r="P12" s="256"/>
+      <c r="Q12" s="237" t="s">
+        <v>67</v>
       </c>
-      <c r="B12" s="255"/>
-      <c r="C12" s="244"/>
-      <c r="D12" s="245"/>
-      <c r="E12" s="245"/>
-      <c r="F12" s="245"/>
-      <c r="G12" s="245"/>
-      <c r="H12" s="245"/>
-      <c r="I12" s="246"/>
-      <c r="J12" s="256" t="s">
-        <v>62</v>
+      <c r="R12" s="238"/>
+      <c r="S12" s="238"/>
+      <c r="T12" s="238"/>
+      <c r="U12" s="238"/>
+      <c r="V12" s="238"/>
+      <c r="W12" s="238"/>
+      <c r="X12" s="238"/>
+      <c r="Y12" s="238"/>
+      <c r="Z12" s="238"/>
+      <c r="AA12" s="239"/>
+      <c r="AB12" s="232"/>
+      <c r="AC12" s="233"/>
+      <c r="AD12" s="233"/>
+      <c r="AE12" s="233"/>
+      <c r="AF12" s="233"/>
+      <c r="AG12" s="233"/>
+      <c r="AH12" s="233"/>
+      <c r="AI12" s="232"/>
+      <c r="AJ12" s="233"/>
+      <c r="AK12" s="233"/>
+      <c r="AL12" s="233"/>
+      <c r="AM12" s="233"/>
+      <c r="AN12" s="233"/>
+      <c r="AO12" s="233"/>
+      <c r="AP12" s="233"/>
+      <c r="AQ12" s="233"/>
+      <c r="AR12" s="234" t="s">
+        <v>58</v>
       </c>
-      <c r="K12" s="257"/>
-      <c r="L12" s="257"/>
-      <c r="M12" s="257"/>
-      <c r="N12" s="257"/>
-      <c r="O12" s="257"/>
-      <c r="P12" s="258"/>
-      <c r="Q12" s="239" t="s">
-        <v>69</v>
+      <c r="AS12" s="235"/>
+      <c r="AT12" s="235"/>
+      <c r="AU12" s="235"/>
+      <c r="AV12" s="235"/>
+      <c r="AW12" s="235"/>
+      <c r="AX12" s="235"/>
+      <c r="AY12" s="235"/>
+      <c r="AZ12" s="235"/>
+      <c r="BA12" s="235"/>
+      <c r="BB12" s="235"/>
+      <c r="BC12" s="235"/>
+      <c r="BD12" s="235"/>
+      <c r="BE12" s="235"/>
+      <c r="BF12" s="235"/>
+      <c r="BG12" s="235"/>
+      <c r="BH12" s="235"/>
+      <c r="BI12" s="235"/>
+      <c r="BJ12" s="235"/>
+      <c r="BK12" s="235"/>
+      <c r="BL12" s="235"/>
+      <c r="BM12" s="235"/>
+      <c r="BN12" s="235"/>
+      <c r="BO12" s="235"/>
+      <c r="BP12" s="235"/>
+      <c r="BQ12" s="235"/>
+      <c r="BR12" s="235"/>
+      <c r="BS12" s="235"/>
+      <c r="BT12" s="235"/>
+      <c r="BU12" s="235"/>
+      <c r="BV12" s="235"/>
+      <c r="BW12" s="235"/>
+      <c r="BX12" s="235"/>
+      <c r="BY12" s="235"/>
+      <c r="BZ12" s="236"/>
+    </row>
+    <row r="13" spans="1:78" ht="15.75" customHeight="1">
+      <c r="A13" s="240" t="s">
+        <v>57</v>
       </c>
-      <c r="R12" s="240"/>
-      <c r="S12" s="240"/>
-      <c r="T12" s="240"/>
-      <c r="U12" s="240"/>
-      <c r="V12" s="240"/>
-      <c r="W12" s="240"/>
-      <c r="X12" s="240"/>
-      <c r="Y12" s="240"/>
-      <c r="Z12" s="240"/>
-      <c r="AA12" s="241"/>
-      <c r="AB12" s="234"/>
-      <c r="AC12" s="235"/>
-      <c r="AD12" s="235"/>
-      <c r="AE12" s="235"/>
-      <c r="AF12" s="235"/>
-      <c r="AG12" s="235"/>
-      <c r="AH12" s="235"/>
-      <c r="AI12" s="234"/>
-      <c r="AJ12" s="235"/>
-      <c r="AK12" s="235"/>
-      <c r="AL12" s="235"/>
-      <c r="AM12" s="235"/>
-      <c r="AN12" s="235"/>
-      <c r="AO12" s="235"/>
-      <c r="AP12" s="235"/>
-      <c r="AQ12" s="235"/>
-      <c r="AR12" s="236" t="s">
-        <v>60</v>
-      </c>
-      <c r="AS12" s="237"/>
-      <c r="AT12" s="237"/>
-      <c r="AU12" s="237"/>
-      <c r="AV12" s="237"/>
-      <c r="AW12" s="237"/>
-      <c r="AX12" s="237"/>
-      <c r="AY12" s="237"/>
-      <c r="AZ12" s="237"/>
-      <c r="BA12" s="237"/>
-      <c r="BB12" s="237"/>
-      <c r="BC12" s="237"/>
-      <c r="BD12" s="237"/>
-      <c r="BE12" s="237"/>
-      <c r="BF12" s="237"/>
-      <c r="BG12" s="237"/>
-      <c r="BH12" s="237"/>
-      <c r="BI12" s="237"/>
-      <c r="BJ12" s="237"/>
-      <c r="BK12" s="237"/>
-      <c r="BL12" s="237"/>
-      <c r="BM12" s="237"/>
-      <c r="BN12" s="237"/>
-      <c r="BO12" s="237"/>
-      <c r="BP12" s="237"/>
-      <c r="BQ12" s="237"/>
-      <c r="BR12" s="237"/>
-      <c r="BS12" s="237"/>
-      <c r="BT12" s="237"/>
-      <c r="BU12" s="237"/>
-      <c r="BV12" s="237"/>
-      <c r="BW12" s="237"/>
-      <c r="BX12" s="237"/>
-      <c r="BY12" s="237"/>
-      <c r="BZ12" s="238"/>
-    </row>
-    <row r="13" spans="1:78" ht="15.75" customHeight="1">
-      <c r="A13" s="242" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="243"/>
+      <c r="B13" s="241"/>
       <c r="C13" s="139"/>
       <c r="D13" s="140"/>
       <c r="E13" s="140"/>
@@ -24917,15 +24915,15 @@
       <c r="G13" s="140"/>
       <c r="H13" s="140"/>
       <c r="I13" s="141"/>
-      <c r="J13" s="244" t="s">
-        <v>64</v>
+      <c r="J13" s="242" t="s">
+        <v>62</v>
       </c>
-      <c r="K13" s="245"/>
-      <c r="L13" s="245"/>
-      <c r="M13" s="245"/>
-      <c r="N13" s="245"/>
-      <c r="O13" s="245"/>
-      <c r="P13" s="246"/>
+      <c r="K13" s="243"/>
+      <c r="L13" s="243"/>
+      <c r="M13" s="243"/>
+      <c r="N13" s="243"/>
+      <c r="O13" s="243"/>
+      <c r="P13" s="244"/>
       <c r="Q13" s="166"/>
       <c r="R13" s="167"/>
       <c r="S13" s="167"/>
@@ -24937,65 +24935,65 @@
       <c r="Y13" s="167"/>
       <c r="Z13" s="167"/>
       <c r="AA13" s="168"/>
-      <c r="AB13" s="234"/>
-      <c r="AC13" s="235"/>
-      <c r="AD13" s="235"/>
-      <c r="AE13" s="235"/>
-      <c r="AF13" s="235"/>
-      <c r="AG13" s="235"/>
-      <c r="AH13" s="235"/>
-      <c r="AI13" s="234"/>
-      <c r="AJ13" s="235"/>
-      <c r="AK13" s="235"/>
-      <c r="AL13" s="235"/>
-      <c r="AM13" s="235"/>
-      <c r="AN13" s="235"/>
-      <c r="AO13" s="235"/>
-      <c r="AP13" s="235"/>
-      <c r="AQ13" s="235"/>
-      <c r="AR13" s="236" t="s">
-        <v>63</v>
+      <c r="AB13" s="232"/>
+      <c r="AC13" s="233"/>
+      <c r="AD13" s="233"/>
+      <c r="AE13" s="233"/>
+      <c r="AF13" s="233"/>
+      <c r="AG13" s="233"/>
+      <c r="AH13" s="233"/>
+      <c r="AI13" s="232"/>
+      <c r="AJ13" s="233"/>
+      <c r="AK13" s="233"/>
+      <c r="AL13" s="233"/>
+      <c r="AM13" s="233"/>
+      <c r="AN13" s="233"/>
+      <c r="AO13" s="233"/>
+      <c r="AP13" s="233"/>
+      <c r="AQ13" s="233"/>
+      <c r="AR13" s="234" t="s">
+        <v>61</v>
       </c>
-      <c r="AS13" s="237"/>
-      <c r="AT13" s="237"/>
-      <c r="AU13" s="237"/>
-      <c r="AV13" s="237"/>
-      <c r="AW13" s="237"/>
-      <c r="AX13" s="237"/>
-      <c r="AY13" s="237"/>
-      <c r="AZ13" s="237"/>
-      <c r="BA13" s="237"/>
-      <c r="BB13" s="237"/>
-      <c r="BC13" s="237"/>
-      <c r="BD13" s="237"/>
-      <c r="BE13" s="237"/>
-      <c r="BF13" s="237"/>
-      <c r="BG13" s="237"/>
-      <c r="BH13" s="237"/>
-      <c r="BI13" s="237"/>
-      <c r="BJ13" s="237"/>
-      <c r="BK13" s="237"/>
-      <c r="BL13" s="237"/>
-      <c r="BM13" s="237"/>
-      <c r="BN13" s="237"/>
-      <c r="BO13" s="237"/>
-      <c r="BP13" s="237"/>
-      <c r="BQ13" s="237"/>
-      <c r="BR13" s="237"/>
-      <c r="BS13" s="237"/>
-      <c r="BT13" s="237"/>
-      <c r="BU13" s="237"/>
-      <c r="BV13" s="237"/>
-      <c r="BW13" s="237"/>
-      <c r="BX13" s="237"/>
-      <c r="BY13" s="237"/>
-      <c r="BZ13" s="238"/>
+      <c r="AS13" s="235"/>
+      <c r="AT13" s="235"/>
+      <c r="AU13" s="235"/>
+      <c r="AV13" s="235"/>
+      <c r="AW13" s="235"/>
+      <c r="AX13" s="235"/>
+      <c r="AY13" s="235"/>
+      <c r="AZ13" s="235"/>
+      <c r="BA13" s="235"/>
+      <c r="BB13" s="235"/>
+      <c r="BC13" s="235"/>
+      <c r="BD13" s="235"/>
+      <c r="BE13" s="235"/>
+      <c r="BF13" s="235"/>
+      <c r="BG13" s="235"/>
+      <c r="BH13" s="235"/>
+      <c r="BI13" s="235"/>
+      <c r="BJ13" s="235"/>
+      <c r="BK13" s="235"/>
+      <c r="BL13" s="235"/>
+      <c r="BM13" s="235"/>
+      <c r="BN13" s="235"/>
+      <c r="BO13" s="235"/>
+      <c r="BP13" s="235"/>
+      <c r="BQ13" s="235"/>
+      <c r="BR13" s="235"/>
+      <c r="BS13" s="235"/>
+      <c r="BT13" s="235"/>
+      <c r="BU13" s="235"/>
+      <c r="BV13" s="235"/>
+      <c r="BW13" s="235"/>
+      <c r="BX13" s="235"/>
+      <c r="BY13" s="235"/>
+      <c r="BZ13" s="236"/>
     </row>
     <row r="14" spans="1:78" ht="14" customHeight="1">
-      <c r="A14" s="242" t="s">
-        <v>67</v>
+      <c r="A14" s="240" t="s">
+        <v>65</v>
       </c>
-      <c r="B14" s="243"/>
+      <c r="B14" s="241"/>
       <c r="C14" s="139"/>
       <c r="D14" s="140"/>
       <c r="E14" s="140"/>
@@ -25003,81 +25001,81 @@
       <c r="G14" s="140"/>
       <c r="H14" s="140"/>
       <c r="I14" s="141"/>
-      <c r="J14" s="244" t="s">
-        <v>65</v>
+      <c r="J14" s="242" t="s">
+        <v>63</v>
       </c>
-      <c r="K14" s="245"/>
-      <c r="L14" s="245"/>
-      <c r="M14" s="245"/>
-      <c r="N14" s="245"/>
-      <c r="O14" s="245"/>
-      <c r="P14" s="246"/>
-      <c r="Q14" s="239"/>
-      <c r="R14" s="240"/>
-      <c r="S14" s="240"/>
-      <c r="T14" s="240"/>
-      <c r="U14" s="240"/>
-      <c r="V14" s="240"/>
-      <c r="W14" s="240"/>
-      <c r="X14" s="240"/>
-      <c r="Y14" s="240"/>
-      <c r="Z14" s="240"/>
-      <c r="AA14" s="241"/>
-      <c r="AB14" s="250"/>
-      <c r="AC14" s="237"/>
-      <c r="AD14" s="237"/>
-      <c r="AE14" s="237"/>
-      <c r="AF14" s="237"/>
-      <c r="AG14" s="237"/>
-      <c r="AH14" s="237"/>
-      <c r="AI14" s="250"/>
-      <c r="AJ14" s="237"/>
-      <c r="AK14" s="237"/>
-      <c r="AL14" s="237"/>
-      <c r="AM14" s="237"/>
-      <c r="AN14" s="237"/>
-      <c r="AO14" s="237"/>
-      <c r="AP14" s="237"/>
-      <c r="AQ14" s="237"/>
-      <c r="AR14" s="251"/>
-      <c r="AS14" s="252"/>
-      <c r="AT14" s="252"/>
-      <c r="AU14" s="252"/>
-      <c r="AV14" s="252"/>
-      <c r="AW14" s="252"/>
-      <c r="AX14" s="252"/>
-      <c r="AY14" s="252"/>
-      <c r="AZ14" s="252"/>
-      <c r="BA14" s="252"/>
-      <c r="BB14" s="252"/>
-      <c r="BC14" s="252"/>
-      <c r="BD14" s="252"/>
-      <c r="BE14" s="252"/>
-      <c r="BF14" s="252"/>
-      <c r="BG14" s="252"/>
-      <c r="BH14" s="252"/>
-      <c r="BI14" s="252"/>
-      <c r="BJ14" s="252"/>
-      <c r="BK14" s="252"/>
-      <c r="BL14" s="252"/>
-      <c r="BM14" s="252"/>
-      <c r="BN14" s="252"/>
-      <c r="BO14" s="252"/>
-      <c r="BP14" s="252"/>
-      <c r="BQ14" s="252"/>
-      <c r="BR14" s="252"/>
-      <c r="BS14" s="252"/>
-      <c r="BT14" s="252"/>
-      <c r="BU14" s="252"/>
-      <c r="BV14" s="252"/>
-      <c r="BW14" s="252"/>
-      <c r="BX14" s="252"/>
-      <c r="BY14" s="252"/>
-      <c r="BZ14" s="253"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="243"/>
+      <c r="M14" s="243"/>
+      <c r="N14" s="243"/>
+      <c r="O14" s="243"/>
+      <c r="P14" s="244"/>
+      <c r="Q14" s="237"/>
+      <c r="R14" s="238"/>
+      <c r="S14" s="238"/>
+      <c r="T14" s="238"/>
+      <c r="U14" s="238"/>
+      <c r="V14" s="238"/>
+      <c r="W14" s="238"/>
+      <c r="X14" s="238"/>
+      <c r="Y14" s="238"/>
+      <c r="Z14" s="238"/>
+      <c r="AA14" s="239"/>
+      <c r="AB14" s="248"/>
+      <c r="AC14" s="235"/>
+      <c r="AD14" s="235"/>
+      <c r="AE14" s="235"/>
+      <c r="AF14" s="235"/>
+      <c r="AG14" s="235"/>
+      <c r="AH14" s="235"/>
+      <c r="AI14" s="248"/>
+      <c r="AJ14" s="235"/>
+      <c r="AK14" s="235"/>
+      <c r="AL14" s="235"/>
+      <c r="AM14" s="235"/>
+      <c r="AN14" s="235"/>
+      <c r="AO14" s="235"/>
+      <c r="AP14" s="235"/>
+      <c r="AQ14" s="235"/>
+      <c r="AR14" s="249"/>
+      <c r="AS14" s="250"/>
+      <c r="AT14" s="250"/>
+      <c r="AU14" s="250"/>
+      <c r="AV14" s="250"/>
+      <c r="AW14" s="250"/>
+      <c r="AX14" s="250"/>
+      <c r="AY14" s="250"/>
+      <c r="AZ14" s="250"/>
+      <c r="BA14" s="250"/>
+      <c r="BB14" s="250"/>
+      <c r="BC14" s="250"/>
+      <c r="BD14" s="250"/>
+      <c r="BE14" s="250"/>
+      <c r="BF14" s="250"/>
+      <c r="BG14" s="250"/>
+      <c r="BH14" s="250"/>
+      <c r="BI14" s="250"/>
+      <c r="BJ14" s="250"/>
+      <c r="BK14" s="250"/>
+      <c r="BL14" s="250"/>
+      <c r="BM14" s="250"/>
+      <c r="BN14" s="250"/>
+      <c r="BO14" s="250"/>
+      <c r="BP14" s="250"/>
+      <c r="BQ14" s="250"/>
+      <c r="BR14" s="250"/>
+      <c r="BS14" s="250"/>
+      <c r="BT14" s="250"/>
+      <c r="BU14" s="250"/>
+      <c r="BV14" s="250"/>
+      <c r="BW14" s="250"/>
+      <c r="BX14" s="250"/>
+      <c r="BY14" s="250"/>
+      <c r="BZ14" s="251"/>
     </row>
     <row r="15" spans="1:78" ht="25" customHeight="1">
-      <c r="A15" s="242"/>
-      <c r="B15" s="243"/>
+      <c r="A15" s="240"/>
+      <c r="B15" s="241"/>
       <c r="C15" s="139"/>
       <c r="D15" s="140"/>
       <c r="E15" s="140"/>
@@ -25085,40 +25083,40 @@
       <c r="G15" s="140"/>
       <c r="H15" s="140"/>
       <c r="I15" s="141"/>
-      <c r="J15" s="244"/>
-      <c r="K15" s="245"/>
-      <c r="L15" s="245"/>
-      <c r="M15" s="245"/>
-      <c r="N15" s="245"/>
-      <c r="O15" s="245"/>
-      <c r="P15" s="246"/>
-      <c r="Q15" s="239"/>
-      <c r="R15" s="240"/>
-      <c r="S15" s="240"/>
-      <c r="T15" s="240"/>
-      <c r="U15" s="240"/>
-      <c r="V15" s="240"/>
-      <c r="W15" s="240"/>
-      <c r="X15" s="240"/>
-      <c r="Y15" s="240"/>
-      <c r="Z15" s="240"/>
-      <c r="AA15" s="241"/>
-      <c r="AB15" s="250"/>
-      <c r="AC15" s="237"/>
-      <c r="AD15" s="237"/>
-      <c r="AE15" s="237"/>
-      <c r="AF15" s="237"/>
-      <c r="AG15" s="237"/>
-      <c r="AH15" s="237"/>
-      <c r="AI15" s="250"/>
-      <c r="AJ15" s="237"/>
-      <c r="AK15" s="237"/>
-      <c r="AL15" s="237"/>
-      <c r="AM15" s="237"/>
-      <c r="AN15" s="237"/>
-      <c r="AO15" s="237"/>
-      <c r="AP15" s="237"/>
-      <c r="AQ15" s="237"/>
+      <c r="J15" s="242"/>
+      <c r="K15" s="243"/>
+      <c r="L15" s="243"/>
+      <c r="M15" s="243"/>
+      <c r="N15" s="243"/>
+      <c r="O15" s="243"/>
+      <c r="P15" s="244"/>
+      <c r="Q15" s="237"/>
+      <c r="R15" s="238"/>
+      <c r="S15" s="238"/>
+      <c r="T15" s="238"/>
+      <c r="U15" s="238"/>
+      <c r="V15" s="238"/>
+      <c r="W15" s="238"/>
+      <c r="X15" s="238"/>
+      <c r="Y15" s="238"/>
+      <c r="Z15" s="238"/>
+      <c r="AA15" s="239"/>
+      <c r="AB15" s="248"/>
+      <c r="AC15" s="235"/>
+      <c r="AD15" s="235"/>
+      <c r="AE15" s="235"/>
+      <c r="AF15" s="235"/>
+      <c r="AG15" s="235"/>
+      <c r="AH15" s="235"/>
+      <c r="AI15" s="248"/>
+      <c r="AJ15" s="235"/>
+      <c r="AK15" s="235"/>
+      <c r="AL15" s="235"/>
+      <c r="AM15" s="235"/>
+      <c r="AN15" s="235"/>
+      <c r="AO15" s="235"/>
+      <c r="AP15" s="235"/>
+      <c r="AQ15" s="235"/>
       <c r="AR15" s="144"/>
       <c r="AS15" s="143"/>
       <c r="AT15" s="143"/>
@@ -25156,8 +25154,8 @@
       <c r="BZ15" s="145"/>
     </row>
     <row r="16" spans="1:78" ht="26.5" customHeight="1">
-      <c r="A16" s="242"/>
-      <c r="B16" s="243"/>
+      <c r="A16" s="240"/>
+      <c r="B16" s="241"/>
       <c r="C16" s="139"/>
       <c r="D16" s="140"/>
       <c r="E16" s="140"/>
@@ -25165,24 +25163,24 @@
       <c r="G16" s="140"/>
       <c r="H16" s="140"/>
       <c r="I16" s="141"/>
-      <c r="J16" s="244"/>
-      <c r="K16" s="245"/>
-      <c r="L16" s="245"/>
-      <c r="M16" s="245"/>
-      <c r="N16" s="245"/>
-      <c r="O16" s="245"/>
-      <c r="P16" s="246"/>
-      <c r="Q16" s="239"/>
-      <c r="R16" s="240"/>
-      <c r="S16" s="240"/>
-      <c r="T16" s="240"/>
-      <c r="U16" s="240"/>
-      <c r="V16" s="240"/>
-      <c r="W16" s="240"/>
-      <c r="X16" s="240"/>
-      <c r="Y16" s="240"/>
-      <c r="Z16" s="240"/>
-      <c r="AA16" s="241"/>
+      <c r="J16" s="242"/>
+      <c r="K16" s="243"/>
+      <c r="L16" s="243"/>
+      <c r="M16" s="243"/>
+      <c r="N16" s="243"/>
+      <c r="O16" s="243"/>
+      <c r="P16" s="244"/>
+      <c r="Q16" s="237"/>
+      <c r="R16" s="238"/>
+      <c r="S16" s="238"/>
+      <c r="T16" s="238"/>
+      <c r="U16" s="238"/>
+      <c r="V16" s="238"/>
+      <c r="W16" s="238"/>
+      <c r="X16" s="238"/>
+      <c r="Y16" s="238"/>
+      <c r="Z16" s="238"/>
+      <c r="AA16" s="239"/>
       <c r="AB16" s="142"/>
       <c r="AC16" s="143"/>
       <c r="AD16" s="143"/>
@@ -25190,15 +25188,15 @@
       <c r="AF16" s="143"/>
       <c r="AG16" s="143"/>
       <c r="AH16" s="143"/>
-      <c r="AI16" s="250"/>
-      <c r="AJ16" s="237"/>
-      <c r="AK16" s="237"/>
-      <c r="AL16" s="237"/>
-      <c r="AM16" s="237"/>
-      <c r="AN16" s="237"/>
-      <c r="AO16" s="237"/>
-      <c r="AP16" s="237"/>
-      <c r="AQ16" s="237"/>
+      <c r="AI16" s="248"/>
+      <c r="AJ16" s="235"/>
+      <c r="AK16" s="235"/>
+      <c r="AL16" s="235"/>
+      <c r="AM16" s="235"/>
+      <c r="AN16" s="235"/>
+      <c r="AO16" s="235"/>
+      <c r="AP16" s="235"/>
+      <c r="AQ16" s="235"/>
       <c r="AR16" s="144"/>
       <c r="AS16" s="143"/>
       <c r="AT16" s="143"/>
@@ -25380,21 +25378,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="13.75" customHeight="1">
-      <c r="A1" s="274" t="s">
-        <v>68</v>
+      <c r="A1" s="272" t="s">
+        <v>66</v>
       </c>
-      <c r="B1" s="274"/>
-      <c r="C1" s="274"/>
-      <c r="D1" s="274"/>
-      <c r="E1" s="274"/>
-      <c r="F1" s="274"/>
-      <c r="G1" s="274"/>
-      <c r="H1" s="274"/>
-      <c r="I1" s="274"/>
-      <c r="J1" s="274"/>
-      <c r="K1" s="274"/>
-      <c r="L1" s="274"/>
-      <c r="M1" s="274"/>
+      <c r="B1" s="272"/>
+      <c r="C1" s="272"/>
+      <c r="D1" s="272"/>
+      <c r="E1" s="272"/>
+      <c r="F1" s="272"/>
+      <c r="G1" s="272"/>
+      <c r="H1" s="272"/>
+      <c r="I1" s="272"/>
+      <c r="J1" s="272"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="272"/>
+      <c r="M1" s="272"/>
     </row>
     <row r="2" spans="1:85" ht="13.75" customHeight="1">
       <c r="A2" s="158"/>
@@ -25486,44 +25484,44 @@
     <row r="3" spans="1:85">
       <c r="A3" s="161"/>
       <c r="B3" s="169" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="CG3" s="162"/>
     </row>
     <row r="4" spans="1:85">
       <c r="A4" s="161"/>
       <c r="D4" s="157" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="CG4" s="162"/>
     </row>
     <row r="5" spans="1:85">
       <c r="A5" s="161"/>
       <c r="C5" s="157" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D5" s="157" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="CG5" s="162"/>
     </row>
     <row r="6" spans="1:85" ht="15" customHeight="1">
       <c r="A6" s="161"/>
       <c r="C6" s="157" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D6" s="157" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="CG6" s="162"/>
     </row>
     <row r="7" spans="1:85" ht="15" customHeight="1">
       <c r="A7" s="161"/>
       <c r="C7" s="157" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D7" s="157" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="CG7" s="162"/>
     </row>
@@ -25534,44 +25532,44 @@
     <row r="9" spans="1:85">
       <c r="A9" s="161"/>
       <c r="B9" s="169" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="CG9" s="162"/>
     </row>
     <row r="10" spans="1:85" ht="15" customHeight="1">
       <c r="A10" s="161"/>
       <c r="D10" s="157" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="CG10" s="162"/>
     </row>
     <row r="11" spans="1:85" ht="15" customHeight="1">
       <c r="A11" s="161"/>
       <c r="C11" s="157" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D11" s="157" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="CG11" s="162"/>
     </row>
     <row r="12" spans="1:85" ht="13.75" customHeight="1">
       <c r="A12" s="161"/>
       <c r="C12" s="157" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D12" s="157" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="CG12" s="162"/>
     </row>
     <row r="13" spans="1:85">
       <c r="A13" s="161"/>
       <c r="C13" s="157" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D13" s="157" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="CG13" s="162"/>
     </row>
